--- a/Documents/ログアウト機能設計書.xlsx
+++ b/Documents/ログアウト機能設計書.xlsx
@@ -1,21 +1,30 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\S-47\Documents\project\taskUN\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EAD0421D-F03D-42C1-A58A-BF9D2DC5E74B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2EC200B-D8C4-4E04-ACF6-6FFCFAAB0D5C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="1" xr2:uid="{72C6CFC4-7293-42D0-8B35-05AE043D8312}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="2" xr2:uid="{72C6CFC4-7293-42D0-8B35-05AE043D8312}"/>
   </bookViews>
   <sheets>
     <sheet name="ユースケース記述" sheetId="3" r:id="rId1"/>
     <sheet name="画面設計書" sheetId="2" r:id="rId2"/>
+    <sheet name="テスト仕様書兼結果報告書" sheetId="4" r:id="rId3"/>
   </sheets>
+  <externalReferences>
+    <externalReference r:id="rId4"/>
+    <externalReference r:id="rId5"/>
+  </externalReferences>
+  <definedNames>
+    <definedName name="あ">#REF!</definedName>
+    <definedName name="範囲１">#REF!</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -26,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="86">
   <si>
     <t>システム名</t>
   </si>
@@ -270,12 +279,191 @@
     </rPh>
     <phoneticPr fontId="3"/>
   </si>
+  <si>
+    <t>ログイン画面へ遷移する</t>
+  </si>
+  <si>
+    <t xml:space="preserve">正常系
+</t>
+  </si>
+  <si>
+    <t>◎</t>
+  </si>
+  <si>
+    <t>結果</t>
+  </si>
+  <si>
+    <t>対応者</t>
+  </si>
+  <si>
+    <t>テスト日</t>
+  </si>
+  <si>
+    <t>予測結果</t>
+  </si>
+  <si>
+    <t>操作手順</t>
+  </si>
+  <si>
+    <t>条件</t>
+  </si>
+  <si>
+    <t>テストテーマ</t>
+  </si>
+  <si>
+    <t>系統</t>
+  </si>
+  <si>
+    <t>重要度</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>×：無くても良い　⇒個別に検討する</t>
+  </si>
+  <si>
+    <t>△：重要ではない　⇒別途テストパス率の指針に従う</t>
+  </si>
+  <si>
+    <t>○：重要　⇒別途テストパス率の指針に従う</t>
+  </si>
+  <si>
+    <t>◎：仕様　⇒100%解決する必要がある</t>
+  </si>
+  <si>
+    <t>重要度は、次のいずれかを持つ</t>
+  </si>
+  <si>
+    <t>テスト対象</t>
+  </si>
+  <si>
+    <t>テストベース</t>
+  </si>
+  <si>
+    <t>システムテスト</t>
+  </si>
+  <si>
+    <t>テストレベル</t>
+  </si>
+  <si>
+    <t>テスト仕様書兼
+結果報告書</t>
+  </si>
+  <si>
+    <t>ログイン状態であること</t>
+    <rPh sb="4" eb="6">
+      <t>ジョウタイ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>ログアウト画面で「はい」ボタンを押下する</t>
+    <rPh sb="5" eb="7">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>オウカ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>「はい」ボタンを押下する</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>◎</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>ログアウト画面で「いいえ」ボタンを押下する</t>
+    <rPh sb="5" eb="7">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>オウカ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>「いいえ」ボタンを押下する</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>メニュー画面へ遷移する</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>異常系</t>
+    <rPh sb="0" eb="3">
+      <t>イジョウケイ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>ログインされていない状態でログアウト画面の表示させる</t>
+    <rPh sb="10" eb="12">
+      <t>ジョウタイ</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="21" eb="23">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>ログアウト状態であること</t>
+    <rPh sb="5" eb="7">
+      <t>ジョウタイ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>ログインされていませんというメッセージが表示され、その下にログイン画面へ誘導するリンクが表示される</t>
+    <rPh sb="20" eb="22">
+      <t>ヒョウジ</t>
+    </rPh>
+    <rPh sb="27" eb="28">
+      <t>シタ</t>
+    </rPh>
+    <rPh sb="33" eb="35">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="36" eb="38">
+      <t>ユウドウ</t>
+    </rPh>
+    <rPh sb="44" eb="46">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>ログアウト画面</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>Junitテスト仕様書</t>
+    <rPh sb="8" eb="11">
+      <t>シヨウショ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>http://localhost:8080/taskUN/logout.jsp</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>〇</t>
+    <phoneticPr fontId="3"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5">
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -311,6 +499,22 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="MS PGothic"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="游ゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -326,7 +530,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="46">
+  <borders count="56">
     <border>
       <left/>
       <right/>
@@ -871,12 +1075,119 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="dotted">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom style="dotted">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="dotted">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="dotted">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="dotted">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="dotted">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="dotted">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="dotted">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="dotted">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="dotted">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="dotted">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top style="dotted">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="91">
+  <cellXfs count="132">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -908,6 +1219,138 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="33" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="56" fontId="2" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1016,140 +1459,132 @@
     <xf numFmtId="56" fontId="2" fillId="0" borderId="12" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="27" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="56" fontId="2" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="56" fontId="2" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="56" fontId="5" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="3">
+    <cellStyle name="ハイパーリンク" xfId="2" builtinId="8"/>
     <cellStyle name="標準" xfId="0" builtinId="0"/>
     <cellStyle name="標準 2" xfId="1" xr:uid="{A8A8EE7C-E6BE-41B2-83FE-4DDDEF0D5153}"/>
   </cellStyles>
@@ -1309,16 +1744,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>47625</xdr:colOff>
-      <xdr:row>8</xdr:row>
-      <xdr:rowOff>95250</xdr:rowOff>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>161925</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>238125</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>819150</xdr:colOff>
-      <xdr:row>9</xdr:row>
-      <xdr:rowOff>114300</xdr:rowOff>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>247650</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>257175</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -1333,7 +1768,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1076325" y="2171700"/>
+          <a:off x="161925" y="2581275"/>
           <a:ext cx="771525" cy="285750"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1382,16 +1817,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>333375</xdr:colOff>
-      <xdr:row>9</xdr:row>
-      <xdr:rowOff>66675</xdr:rowOff>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>285750</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>9525</xdr:colOff>
-      <xdr:row>10</xdr:row>
-      <xdr:rowOff>66675</xdr:rowOff>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -1406,7 +1841,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="333375" y="2409825"/>
+          <a:off x="971550" y="2190750"/>
           <a:ext cx="361950" cy="266700"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1446,16 +1881,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>266700</xdr:colOff>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>285750</xdr:colOff>
       <xdr:row>9</xdr:row>
-      <xdr:rowOff>85725</xdr:rowOff>
+      <xdr:rowOff>247650</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>628650</xdr:colOff>
+      <xdr:colOff>304800</xdr:colOff>
       <xdr:row>10</xdr:row>
-      <xdr:rowOff>85725</xdr:rowOff>
+      <xdr:rowOff>247650</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -1470,7 +1905,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1295400" y="2428875"/>
+          <a:off x="971550" y="2590800"/>
           <a:ext cx="361950" cy="266700"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1509,6 +1944,48 @@
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
+</file>
+
+<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="テスト仕様書兼報告書"/>
+      <sheetName val="サンプル"/>
+      <sheetName val="テストケースに記載する要素"/>
+      <sheetName val="テスト用語"/>
+      <sheetName val="テスト観点一覧"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="1" refreshError="1"/>
+      <sheetData sheetId="2" refreshError="1"/>
+      <sheetData sheetId="3" refreshError="1"/>
+      <sheetData sheetId="4" refreshError="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink2.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="JUnitテスト仕様書兼報告書"/>
+      <sheetName val="別紙"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="1" refreshError="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1811,223 +2288,223 @@
   <dimension ref="A1:J1000"/>
   <sheetFormatPr defaultColWidth="12.625" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="3" width="4.5" style="54" customWidth="1"/>
-    <col min="4" max="10" width="14.625" style="54" customWidth="1"/>
-    <col min="11" max="26" width="7.625" style="54" customWidth="1"/>
-    <col min="27" max="16384" width="12.625" style="54"/>
+    <col min="1" max="3" width="4.5" style="13" customWidth="1"/>
+    <col min="4" max="10" width="14.625" style="13" customWidth="1"/>
+    <col min="11" max="26" width="7.625" style="13" customWidth="1"/>
+    <col min="27" max="16384" width="12.625" style="13"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="47" t="s">
+      <c r="A1" s="19" t="s">
         <v>30</v>
       </c>
-      <c r="B1" s="48"/>
-      <c r="C1" s="49"/>
-      <c r="D1" s="50" t="s">
+      <c r="B1" s="20"/>
+      <c r="C1" s="21"/>
+      <c r="D1" s="28" t="s">
         <v>0</v>
       </c>
-      <c r="E1" s="51"/>
-      <c r="F1" s="50" t="s">
+      <c r="E1" s="29"/>
+      <c r="F1" s="28" t="s">
         <v>1</v>
       </c>
-      <c r="G1" s="51"/>
-      <c r="H1" s="52" t="s">
+      <c r="G1" s="29"/>
+      <c r="H1" s="11" t="s">
         <v>2</v>
       </c>
-      <c r="I1" s="52" t="s">
+      <c r="I1" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="J1" s="53" t="s">
+      <c r="J1" s="12" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="55"/>
-      <c r="B2" s="56"/>
-      <c r="C2" s="57"/>
-      <c r="D2" s="58" t="s">
+      <c r="A2" s="22"/>
+      <c r="B2" s="23"/>
+      <c r="C2" s="24"/>
+      <c r="D2" s="30" t="s">
         <v>6</v>
       </c>
-      <c r="E2" s="59"/>
-      <c r="F2" s="58" t="s">
+      <c r="E2" s="31"/>
+      <c r="F2" s="30" t="s">
         <v>7</v>
       </c>
-      <c r="G2" s="59"/>
-      <c r="H2" s="60">
+      <c r="G2" s="31"/>
+      <c r="H2" s="34">
         <v>45806</v>
       </c>
-      <c r="I2" s="61" t="s">
+      <c r="I2" s="37" t="s">
         <v>28</v>
       </c>
-      <c r="J2" s="62"/>
+      <c r="J2" s="38"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="55"/>
-      <c r="B3" s="56"/>
-      <c r="C3" s="57"/>
-      <c r="D3" s="63"/>
-      <c r="E3" s="57"/>
-      <c r="F3" s="63"/>
-      <c r="G3" s="57"/>
-      <c r="H3" s="64"/>
-      <c r="I3" s="64"/>
-      <c r="J3" s="65"/>
+      <c r="A3" s="22"/>
+      <c r="B3" s="23"/>
+      <c r="C3" s="24"/>
+      <c r="D3" s="32"/>
+      <c r="E3" s="24"/>
+      <c r="F3" s="32"/>
+      <c r="G3" s="24"/>
+      <c r="H3" s="35"/>
+      <c r="I3" s="35"/>
+      <c r="J3" s="39"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="66"/>
-      <c r="B4" s="67"/>
-      <c r="C4" s="68"/>
-      <c r="D4" s="69"/>
-      <c r="E4" s="68"/>
-      <c r="F4" s="69"/>
-      <c r="G4" s="68"/>
-      <c r="H4" s="70"/>
-      <c r="I4" s="70"/>
-      <c r="J4" s="71"/>
+      <c r="A4" s="25"/>
+      <c r="B4" s="26"/>
+      <c r="C4" s="27"/>
+      <c r="D4" s="33"/>
+      <c r="E4" s="27"/>
+      <c r="F4" s="33"/>
+      <c r="G4" s="27"/>
+      <c r="H4" s="36"/>
+      <c r="I4" s="36"/>
+      <c r="J4" s="40"/>
     </row>
     <row r="5" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A5" s="72" t="s">
+      <c r="A5" s="41" t="s">
         <v>31</v>
       </c>
-      <c r="B5" s="73"/>
-      <c r="C5" s="51"/>
-      <c r="D5" s="74" t="s">
+      <c r="B5" s="42"/>
+      <c r="C5" s="29"/>
+      <c r="D5" s="43" t="s">
         <v>41</v>
       </c>
-      <c r="E5" s="73"/>
-      <c r="F5" s="73"/>
-      <c r="G5" s="73"/>
-      <c r="H5" s="73"/>
-      <c r="I5" s="73"/>
-      <c r="J5" s="75"/>
+      <c r="E5" s="42"/>
+      <c r="F5" s="42"/>
+      <c r="G5" s="42"/>
+      <c r="H5" s="42"/>
+      <c r="I5" s="42"/>
+      <c r="J5" s="44"/>
     </row>
     <row r="6" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A6" s="76" t="s">
+      <c r="A6" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="B6" s="77"/>
-      <c r="C6" s="78"/>
-      <c r="D6" s="79" t="s">
+      <c r="B6" s="15"/>
+      <c r="C6" s="16"/>
+      <c r="D6" s="17" t="s">
         <v>42</v>
       </c>
-      <c r="E6" s="77"/>
-      <c r="F6" s="77"/>
-      <c r="G6" s="77"/>
-      <c r="H6" s="77"/>
-      <c r="I6" s="77"/>
-      <c r="J6" s="80"/>
+      <c r="E6" s="15"/>
+      <c r="F6" s="15"/>
+      <c r="G6" s="15"/>
+      <c r="H6" s="15"/>
+      <c r="I6" s="15"/>
+      <c r="J6" s="18"/>
     </row>
     <row r="7" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A7" s="76" t="s">
+      <c r="A7" s="14" t="s">
         <v>33</v>
       </c>
-      <c r="B7" s="77"/>
-      <c r="C7" s="78"/>
-      <c r="D7" s="79" t="s">
+      <c r="B7" s="15"/>
+      <c r="C7" s="16"/>
+      <c r="D7" s="17" t="s">
         <v>34</v>
       </c>
-      <c r="E7" s="77"/>
-      <c r="F7" s="77"/>
-      <c r="G7" s="77"/>
-      <c r="H7" s="77"/>
-      <c r="I7" s="77"/>
-      <c r="J7" s="80"/>
+      <c r="E7" s="15"/>
+      <c r="F7" s="15"/>
+      <c r="G7" s="15"/>
+      <c r="H7" s="15"/>
+      <c r="I7" s="15"/>
+      <c r="J7" s="18"/>
     </row>
     <row r="8" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A8" s="76" t="s">
+      <c r="A8" s="14" t="s">
         <v>35</v>
       </c>
-      <c r="B8" s="77"/>
-      <c r="C8" s="78"/>
-      <c r="D8" s="79" t="s">
+      <c r="B8" s="15"/>
+      <c r="C8" s="16"/>
+      <c r="D8" s="17" t="s">
         <v>43</v>
       </c>
-      <c r="E8" s="77"/>
-      <c r="F8" s="77"/>
-      <c r="G8" s="77"/>
-      <c r="H8" s="77"/>
-      <c r="I8" s="77"/>
-      <c r="J8" s="80"/>
+      <c r="E8" s="15"/>
+      <c r="F8" s="15"/>
+      <c r="G8" s="15"/>
+      <c r="H8" s="15"/>
+      <c r="I8" s="15"/>
+      <c r="J8" s="18"/>
     </row>
     <row r="9" spans="1:10" ht="64.5" customHeight="1">
-      <c r="A9" s="81" t="s">
+      <c r="A9" s="45" t="s">
         <v>36</v>
       </c>
-      <c r="B9" s="82" t="s">
+      <c r="B9" s="48" t="s">
         <v>37</v>
       </c>
-      <c r="C9" s="78"/>
-      <c r="D9" s="83" t="s">
+      <c r="C9" s="16"/>
+      <c r="D9" s="49" t="s">
         <v>44</v>
       </c>
-      <c r="E9" s="77"/>
-      <c r="F9" s="77"/>
-      <c r="G9" s="77"/>
-      <c r="H9" s="77"/>
-      <c r="I9" s="77"/>
-      <c r="J9" s="80"/>
+      <c r="E9" s="15"/>
+      <c r="F9" s="15"/>
+      <c r="G9" s="15"/>
+      <c r="H9" s="15"/>
+      <c r="I9" s="15"/>
+      <c r="J9" s="18"/>
     </row>
     <row r="10" spans="1:10" ht="64.5" customHeight="1">
-      <c r="A10" s="84"/>
-      <c r="B10" s="82" t="s">
+      <c r="A10" s="46"/>
+      <c r="B10" s="48" t="s">
         <v>38</v>
       </c>
-      <c r="C10" s="78"/>
-      <c r="D10" s="83" t="s">
+      <c r="C10" s="16"/>
+      <c r="D10" s="49" t="s">
         <v>45</v>
       </c>
-      <c r="E10" s="77"/>
-      <c r="F10" s="77"/>
-      <c r="G10" s="77"/>
-      <c r="H10" s="77"/>
-      <c r="I10" s="77"/>
-      <c r="J10" s="80"/>
+      <c r="E10" s="15"/>
+      <c r="F10" s="15"/>
+      <c r="G10" s="15"/>
+      <c r="H10" s="15"/>
+      <c r="I10" s="15"/>
+      <c r="J10" s="18"/>
     </row>
     <row r="11" spans="1:10" ht="64.5" customHeight="1">
-      <c r="A11" s="85"/>
-      <c r="B11" s="82" t="s">
+      <c r="A11" s="47"/>
+      <c r="B11" s="48" t="s">
         <v>39</v>
       </c>
-      <c r="C11" s="78"/>
-      <c r="D11" s="83" t="s">
+      <c r="C11" s="16"/>
+      <c r="D11" s="49" t="s">
         <v>46</v>
       </c>
-      <c r="E11" s="77"/>
-      <c r="F11" s="77"/>
-      <c r="G11" s="77"/>
-      <c r="H11" s="77"/>
-      <c r="I11" s="77"/>
-      <c r="J11" s="80"/>
+      <c r="E11" s="15"/>
+      <c r="F11" s="15"/>
+      <c r="G11" s="15"/>
+      <c r="H11" s="15"/>
+      <c r="I11" s="15"/>
+      <c r="J11" s="18"/>
     </row>
     <row r="12" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A12" s="76" t="s">
+      <c r="A12" s="14" t="s">
         <v>40</v>
       </c>
-      <c r="B12" s="77"/>
-      <c r="C12" s="78"/>
-      <c r="D12" s="79" t="s">
+      <c r="B12" s="15"/>
+      <c r="C12" s="16"/>
+      <c r="D12" s="17" t="s">
         <v>47</v>
       </c>
-      <c r="E12" s="77"/>
-      <c r="F12" s="77"/>
-      <c r="G12" s="77"/>
-      <c r="H12" s="77"/>
-      <c r="I12" s="77"/>
-      <c r="J12" s="80"/>
+      <c r="E12" s="15"/>
+      <c r="F12" s="15"/>
+      <c r="G12" s="15"/>
+      <c r="H12" s="15"/>
+      <c r="I12" s="15"/>
+      <c r="J12" s="18"/>
     </row>
     <row r="13" spans="1:10" ht="26.25" customHeight="1" thickBot="1">
-      <c r="A13" s="86" t="s">
+      <c r="A13" s="50" t="s">
         <v>18</v>
       </c>
-      <c r="B13" s="87"/>
-      <c r="C13" s="88"/>
-      <c r="D13" s="89"/>
-      <c r="E13" s="87"/>
-      <c r="F13" s="87"/>
-      <c r="G13" s="87"/>
-      <c r="H13" s="87"/>
-      <c r="I13" s="87"/>
-      <c r="J13" s="90"/>
+      <c r="B13" s="51"/>
+      <c r="C13" s="52"/>
+      <c r="D13" s="53"/>
+      <c r="E13" s="51"/>
+      <c r="F13" s="51"/>
+      <c r="G13" s="51"/>
+      <c r="H13" s="51"/>
+      <c r="I13" s="51"/>
+      <c r="J13" s="54"/>
     </row>
     <row r="14" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="15" spans="1:10" ht="12.75" customHeight="1"/>
@@ -3018,7 +3495,6 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="D11:J11"/>
     <mergeCell ref="A12:C12"/>
     <mergeCell ref="D12:J12"/>
     <mergeCell ref="A13:C13"/>
@@ -3033,11 +3509,7 @@
     <mergeCell ref="B10:C10"/>
     <mergeCell ref="D10:J10"/>
     <mergeCell ref="B11:C11"/>
-    <mergeCell ref="H2:H4"/>
-    <mergeCell ref="I2:I4"/>
-    <mergeCell ref="J2:J4"/>
-    <mergeCell ref="A5:C5"/>
-    <mergeCell ref="D5:J5"/>
+    <mergeCell ref="D11:J11"/>
     <mergeCell ref="A6:C6"/>
     <mergeCell ref="D6:J6"/>
     <mergeCell ref="A1:C4"/>
@@ -3045,6 +3517,11 @@
     <mergeCell ref="F1:G1"/>
     <mergeCell ref="D2:E4"/>
     <mergeCell ref="F2:G4"/>
+    <mergeCell ref="H2:H4"/>
+    <mergeCell ref="I2:I4"/>
+    <mergeCell ref="J2:J4"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="D5:J5"/>
   </mergeCells>
   <phoneticPr fontId="3"/>
   <pageMargins left="0.70833333333333304" right="0.70833333333333304" top="0.74791666666666701" bottom="0.74791666666666701" header="0" footer="0"/>
@@ -3067,19 +3544,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="38" t="s">
+      <c r="A1" s="82" t="s">
         <v>5</v>
       </c>
-      <c r="B1" s="39"/>
-      <c r="C1" s="40"/>
-      <c r="D1" s="42" t="s">
+      <c r="B1" s="83"/>
+      <c r="C1" s="84"/>
+      <c r="D1" s="86" t="s">
         <v>0</v>
       </c>
-      <c r="E1" s="29"/>
-      <c r="F1" s="42" t="s">
+      <c r="E1" s="73"/>
+      <c r="F1" s="86" t="s">
         <v>1</v>
       </c>
-      <c r="G1" s="29"/>
+      <c r="G1" s="73"/>
       <c r="H1" s="1" t="s">
         <v>2</v>
       </c>
@@ -3091,190 +3568,190 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="35"/>
-      <c r="B2" s="36"/>
-      <c r="C2" s="41"/>
-      <c r="D2" s="43" t="s">
+      <c r="A2" s="79"/>
+      <c r="B2" s="80"/>
+      <c r="C2" s="85"/>
+      <c r="D2" s="87" t="s">
         <v>6</v>
       </c>
-      <c r="E2" s="44"/>
-      <c r="F2" s="43" t="s">
+      <c r="E2" s="88"/>
+      <c r="F2" s="87" t="s">
         <v>7</v>
       </c>
-      <c r="G2" s="44"/>
-      <c r="H2" s="46">
+      <c r="G2" s="88"/>
+      <c r="H2" s="90">
         <v>45806</v>
       </c>
-      <c r="I2" s="23" t="s">
+      <c r="I2" s="67" t="s">
         <v>28</v>
       </c>
-      <c r="J2" s="25"/>
+      <c r="J2" s="69"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="35"/>
-      <c r="B3" s="36"/>
-      <c r="C3" s="41"/>
-      <c r="D3" s="45"/>
-      <c r="E3" s="41"/>
-      <c r="F3" s="45"/>
-      <c r="G3" s="41"/>
-      <c r="H3" s="24"/>
-      <c r="I3" s="24"/>
-      <c r="J3" s="26"/>
+      <c r="A3" s="79"/>
+      <c r="B3" s="80"/>
+      <c r="C3" s="85"/>
+      <c r="D3" s="89"/>
+      <c r="E3" s="85"/>
+      <c r="F3" s="89"/>
+      <c r="G3" s="85"/>
+      <c r="H3" s="68"/>
+      <c r="I3" s="68"/>
+      <c r="J3" s="70"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="35"/>
-      <c r="B4" s="36"/>
-      <c r="C4" s="41"/>
-      <c r="D4" s="45"/>
-      <c r="E4" s="41"/>
-      <c r="F4" s="45"/>
-      <c r="G4" s="41"/>
-      <c r="H4" s="24"/>
-      <c r="I4" s="24"/>
-      <c r="J4" s="26"/>
+      <c r="A4" s="79"/>
+      <c r="B4" s="80"/>
+      <c r="C4" s="85"/>
+      <c r="D4" s="89"/>
+      <c r="E4" s="85"/>
+      <c r="F4" s="89"/>
+      <c r="G4" s="85"/>
+      <c r="H4" s="68"/>
+      <c r="I4" s="68"/>
+      <c r="J4" s="70"/>
     </row>
     <row r="5" spans="1:10" ht="28.5" customHeight="1">
-      <c r="A5" s="27" t="s">
+      <c r="A5" s="71" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="28"/>
-      <c r="C5" s="29"/>
-      <c r="D5" s="30" t="s">
+      <c r="B5" s="72"/>
+      <c r="C5" s="73"/>
+      <c r="D5" s="74" t="s">
         <v>19</v>
       </c>
-      <c r="E5" s="28"/>
-      <c r="F5" s="28"/>
-      <c r="G5" s="28"/>
-      <c r="H5" s="28"/>
-      <c r="I5" s="28"/>
-      <c r="J5" s="31"/>
+      <c r="E5" s="72"/>
+      <c r="F5" s="72"/>
+      <c r="G5" s="72"/>
+      <c r="H5" s="72"/>
+      <c r="I5" s="72"/>
+      <c r="J5" s="75"/>
     </row>
     <row r="6" spans="1:10" ht="21" customHeight="1">
-      <c r="A6" s="21" t="s">
+      <c r="A6" s="65" t="s">
         <v>9</v>
       </c>
-      <c r="B6" s="12"/>
-      <c r="C6" s="12"/>
-      <c r="D6" s="12"/>
-      <c r="E6" s="12"/>
-      <c r="F6" s="12"/>
-      <c r="G6" s="12"/>
-      <c r="H6" s="12"/>
-      <c r="I6" s="12"/>
-      <c r="J6" s="15"/>
+      <c r="B6" s="56"/>
+      <c r="C6" s="56"/>
+      <c r="D6" s="56"/>
+      <c r="E6" s="56"/>
+      <c r="F6" s="56"/>
+      <c r="G6" s="56"/>
+      <c r="H6" s="56"/>
+      <c r="I6" s="56"/>
+      <c r="J6" s="59"/>
     </row>
     <row r="7" spans="1:10" ht="21" customHeight="1">
-      <c r="A7" s="32"/>
-      <c r="B7" s="33"/>
-      <c r="C7" s="33"/>
-      <c r="D7" s="33"/>
-      <c r="E7" s="33"/>
-      <c r="F7" s="33"/>
-      <c r="G7" s="33"/>
-      <c r="H7" s="33"/>
-      <c r="I7" s="33"/>
-      <c r="J7" s="34"/>
+      <c r="A7" s="76"/>
+      <c r="B7" s="77"/>
+      <c r="C7" s="77"/>
+      <c r="D7" s="77"/>
+      <c r="E7" s="77"/>
+      <c r="F7" s="77"/>
+      <c r="G7" s="77"/>
+      <c r="H7" s="77"/>
+      <c r="I7" s="77"/>
+      <c r="J7" s="78"/>
     </row>
     <row r="8" spans="1:10" ht="21" customHeight="1">
-      <c r="A8" s="35"/>
-      <c r="B8" s="36"/>
-      <c r="C8" s="36"/>
-      <c r="D8" s="36"/>
-      <c r="E8" s="36"/>
-      <c r="F8" s="36"/>
-      <c r="G8" s="36"/>
-      <c r="H8" s="36"/>
-      <c r="I8" s="36"/>
-      <c r="J8" s="37"/>
+      <c r="A8" s="79"/>
+      <c r="B8" s="80"/>
+      <c r="C8" s="80"/>
+      <c r="D8" s="80"/>
+      <c r="E8" s="80"/>
+      <c r="F8" s="80"/>
+      <c r="G8" s="80"/>
+      <c r="H8" s="80"/>
+      <c r="I8" s="80"/>
+      <c r="J8" s="81"/>
     </row>
     <row r="9" spans="1:10" ht="21" customHeight="1">
-      <c r="A9" s="35"/>
-      <c r="B9" s="36"/>
-      <c r="C9" s="36"/>
-      <c r="D9" s="36"/>
-      <c r="E9" s="36"/>
-      <c r="F9" s="36"/>
-      <c r="G9" s="36"/>
-      <c r="H9" s="36"/>
-      <c r="I9" s="36"/>
-      <c r="J9" s="37"/>
+      <c r="A9" s="79"/>
+      <c r="B9" s="80"/>
+      <c r="C9" s="80"/>
+      <c r="D9" s="80"/>
+      <c r="E9" s="80"/>
+      <c r="F9" s="80"/>
+      <c r="G9" s="80"/>
+      <c r="H9" s="80"/>
+      <c r="I9" s="80"/>
+      <c r="J9" s="81"/>
     </row>
     <row r="10" spans="1:10" ht="21" customHeight="1">
-      <c r="A10" s="35"/>
-      <c r="B10" s="36"/>
-      <c r="C10" s="36"/>
-      <c r="D10" s="36"/>
-      <c r="E10" s="36"/>
-      <c r="F10" s="36"/>
-      <c r="G10" s="36"/>
-      <c r="H10" s="36"/>
-      <c r="I10" s="36"/>
-      <c r="J10" s="37"/>
+      <c r="A10" s="79"/>
+      <c r="B10" s="80"/>
+      <c r="C10" s="80"/>
+      <c r="D10" s="80"/>
+      <c r="E10" s="80"/>
+      <c r="F10" s="80"/>
+      <c r="G10" s="80"/>
+      <c r="H10" s="80"/>
+      <c r="I10" s="80"/>
+      <c r="J10" s="81"/>
     </row>
     <row r="11" spans="1:10" ht="21" customHeight="1">
-      <c r="A11" s="35"/>
-      <c r="B11" s="36"/>
-      <c r="C11" s="36"/>
-      <c r="D11" s="36"/>
-      <c r="E11" s="36"/>
-      <c r="F11" s="36"/>
-      <c r="G11" s="36"/>
-      <c r="H11" s="36"/>
-      <c r="I11" s="36"/>
-      <c r="J11" s="37"/>
+      <c r="A11" s="79"/>
+      <c r="B11" s="80"/>
+      <c r="C11" s="80"/>
+      <c r="D11" s="80"/>
+      <c r="E11" s="80"/>
+      <c r="F11" s="80"/>
+      <c r="G11" s="80"/>
+      <c r="H11" s="80"/>
+      <c r="I11" s="80"/>
+      <c r="J11" s="81"/>
     </row>
     <row r="12" spans="1:10" ht="21" customHeight="1">
-      <c r="A12" s="35"/>
-      <c r="B12" s="36"/>
-      <c r="C12" s="36"/>
-      <c r="D12" s="36"/>
-      <c r="E12" s="36"/>
-      <c r="F12" s="36"/>
-      <c r="G12" s="36"/>
-      <c r="H12" s="36"/>
-      <c r="I12" s="36"/>
-      <c r="J12" s="37"/>
+      <c r="A12" s="79"/>
+      <c r="B12" s="80"/>
+      <c r="C12" s="80"/>
+      <c r="D12" s="80"/>
+      <c r="E12" s="80"/>
+      <c r="F12" s="80"/>
+      <c r="G12" s="80"/>
+      <c r="H12" s="80"/>
+      <c r="I12" s="80"/>
+      <c r="J12" s="81"/>
     </row>
     <row r="13" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A13" s="35"/>
-      <c r="B13" s="36"/>
-      <c r="C13" s="36"/>
-      <c r="D13" s="36"/>
-      <c r="E13" s="36"/>
-      <c r="F13" s="36"/>
-      <c r="G13" s="36"/>
-      <c r="H13" s="36"/>
-      <c r="I13" s="36"/>
-      <c r="J13" s="37"/>
+      <c r="A13" s="79"/>
+      <c r="B13" s="80"/>
+      <c r="C13" s="80"/>
+      <c r="D13" s="80"/>
+      <c r="E13" s="80"/>
+      <c r="F13" s="80"/>
+      <c r="G13" s="80"/>
+      <c r="H13" s="80"/>
+      <c r="I13" s="80"/>
+      <c r="J13" s="81"/>
     </row>
     <row r="14" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A14" s="21" t="s">
+      <c r="A14" s="65" t="s">
         <v>10</v>
       </c>
-      <c r="B14" s="12"/>
-      <c r="C14" s="12"/>
-      <c r="D14" s="12"/>
-      <c r="E14" s="12"/>
-      <c r="F14" s="12"/>
-      <c r="G14" s="12"/>
-      <c r="H14" s="12"/>
-      <c r="I14" s="12"/>
-      <c r="J14" s="15"/>
+      <c r="B14" s="56"/>
+      <c r="C14" s="56"/>
+      <c r="D14" s="56"/>
+      <c r="E14" s="56"/>
+      <c r="F14" s="56"/>
+      <c r="G14" s="56"/>
+      <c r="H14" s="56"/>
+      <c r="I14" s="56"/>
+      <c r="J14" s="59"/>
     </row>
     <row r="15" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A15" s="21" t="s">
+      <c r="A15" s="65" t="s">
         <v>11</v>
       </c>
-      <c r="B15" s="12"/>
-      <c r="C15" s="13"/>
-      <c r="D15" s="14" t="s">
+      <c r="B15" s="56"/>
+      <c r="C15" s="57"/>
+      <c r="D15" s="58" t="s">
         <v>26</v>
       </c>
-      <c r="E15" s="12"/>
-      <c r="F15" s="12"/>
-      <c r="G15" s="12"/>
-      <c r="H15" s="13"/>
+      <c r="E15" s="56"/>
+      <c r="F15" s="56"/>
+      <c r="G15" s="56"/>
+      <c r="H15" s="57"/>
       <c r="I15" s="5" t="s">
         <v>12</v>
       </c>
@@ -3283,11 +3760,11 @@
       </c>
     </row>
     <row r="16" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A16" s="21" t="s">
+      <c r="A16" s="65" t="s">
         <v>13</v>
       </c>
-      <c r="B16" s="12"/>
-      <c r="C16" s="13"/>
+      <c r="B16" s="56"/>
+      <c r="C16" s="57"/>
       <c r="D16" s="5" t="s">
         <v>14</v>
       </c>
@@ -3300,18 +3777,18 @@
       <c r="G16" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="H16" s="22" t="s">
+      <c r="H16" s="66" t="s">
         <v>18</v>
       </c>
-      <c r="I16" s="12"/>
-      <c r="J16" s="15"/>
+      <c r="I16" s="56"/>
+      <c r="J16" s="59"/>
     </row>
     <row r="17" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A17" s="11">
+      <c r="A17" s="55">
         <v>1</v>
       </c>
-      <c r="B17" s="12"/>
-      <c r="C17" s="13"/>
+      <c r="B17" s="56"/>
+      <c r="C17" s="57"/>
       <c r="D17" s="7" t="s">
         <v>21</v>
       </c>
@@ -3324,16 +3801,16 @@
       <c r="G17" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="H17" s="14"/>
-      <c r="I17" s="12"/>
-      <c r="J17" s="15"/>
+      <c r="H17" s="58"/>
+      <c r="I17" s="56"/>
+      <c r="J17" s="59"/>
     </row>
     <row r="18" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A18" s="11">
+      <c r="A18" s="55">
         <v>2</v>
       </c>
-      <c r="B18" s="12"/>
-      <c r="C18" s="13"/>
+      <c r="B18" s="56"/>
+      <c r="C18" s="57"/>
       <c r="D18" s="7" t="s">
         <v>22</v>
       </c>
@@ -3344,71 +3821,71 @@
       <c r="G18" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="H18" s="14" t="s">
+      <c r="H18" s="58" t="s">
         <v>27</v>
       </c>
-      <c r="I18" s="12"/>
-      <c r="J18" s="15"/>
+      <c r="I18" s="56"/>
+      <c r="J18" s="59"/>
     </row>
     <row r="19" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A19" s="11"/>
-      <c r="B19" s="12"/>
-      <c r="C19" s="13"/>
+      <c r="A19" s="55"/>
+      <c r="B19" s="56"/>
+      <c r="C19" s="57"/>
       <c r="D19" s="7"/>
       <c r="E19" s="7"/>
       <c r="F19" s="8"/>
       <c r="G19" s="8"/>
-      <c r="H19" s="14"/>
-      <c r="I19" s="12"/>
-      <c r="J19" s="15"/>
+      <c r="H19" s="58"/>
+      <c r="I19" s="56"/>
+      <c r="J19" s="59"/>
     </row>
     <row r="20" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A20" s="11"/>
-      <c r="B20" s="12"/>
-      <c r="C20" s="13"/>
+      <c r="A20" s="55"/>
+      <c r="B20" s="56"/>
+      <c r="C20" s="57"/>
       <c r="D20" s="7"/>
       <c r="E20" s="7"/>
       <c r="F20" s="8"/>
       <c r="G20" s="8"/>
-      <c r="H20" s="14"/>
-      <c r="I20" s="12"/>
-      <c r="J20" s="15"/>
+      <c r="H20" s="58"/>
+      <c r="I20" s="56"/>
+      <c r="J20" s="59"/>
     </row>
     <row r="21" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A21" s="11"/>
-      <c r="B21" s="12"/>
-      <c r="C21" s="13"/>
+      <c r="A21" s="55"/>
+      <c r="B21" s="56"/>
+      <c r="C21" s="57"/>
       <c r="D21" s="7"/>
       <c r="E21" s="7"/>
       <c r="F21" s="8"/>
       <c r="G21" s="8"/>
-      <c r="H21" s="14"/>
-      <c r="I21" s="12"/>
-      <c r="J21" s="15"/>
+      <c r="H21" s="58"/>
+      <c r="I21" s="56"/>
+      <c r="J21" s="59"/>
     </row>
     <row r="22" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A22" s="11"/>
-      <c r="B22" s="12"/>
-      <c r="C22" s="13"/>
+      <c r="A22" s="55"/>
+      <c r="B22" s="56"/>
+      <c r="C22" s="57"/>
       <c r="D22" s="7"/>
       <c r="E22" s="7"/>
       <c r="F22" s="8"/>
       <c r="G22" s="8"/>
-      <c r="H22" s="14"/>
-      <c r="I22" s="12"/>
-      <c r="J22" s="15"/>
+      <c r="H22" s="58"/>
+      <c r="I22" s="56"/>
+      <c r="J22" s="59"/>
     </row>
     <row r="23" spans="1:10" ht="19.5" customHeight="1" thickBot="1">
-      <c r="A23" s="16"/>
-      <c r="B23" s="17"/>
-      <c r="C23" s="18"/>
+      <c r="A23" s="60"/>
+      <c r="B23" s="61"/>
+      <c r="C23" s="62"/>
       <c r="D23" s="9"/>
       <c r="E23" s="9"/>
       <c r="F23" s="10"/>
       <c r="G23" s="10"/>
-      <c r="H23" s="19"/>
-      <c r="I23" s="17"/>
-      <c r="J23" s="20"/>
+      <c r="H23" s="63"/>
+      <c r="I23" s="61"/>
+      <c r="J23" s="64"/>
     </row>
     <row r="24" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="25" spans="1:10" ht="12.75" customHeight="1"/>
@@ -4389,13 +4866,8 @@
     <row r="1000" s="4" customFormat="1" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="31">
-    <mergeCell ref="A17:C17"/>
-    <mergeCell ref="H17:J17"/>
-    <mergeCell ref="I2:I4"/>
-    <mergeCell ref="J2:J4"/>
-    <mergeCell ref="A5:C5"/>
-    <mergeCell ref="D5:J5"/>
-    <mergeCell ref="A6:J6"/>
+    <mergeCell ref="A14:J14"/>
+    <mergeCell ref="A15:C15"/>
     <mergeCell ref="A7:J13"/>
     <mergeCell ref="A1:C4"/>
     <mergeCell ref="D1:E1"/>
@@ -4403,27 +4875,2111 @@
     <mergeCell ref="D2:E4"/>
     <mergeCell ref="F2:G4"/>
     <mergeCell ref="H2:H4"/>
-    <mergeCell ref="A14:J14"/>
-    <mergeCell ref="A15:C15"/>
+    <mergeCell ref="I2:I4"/>
+    <mergeCell ref="J2:J4"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="D5:J5"/>
+    <mergeCell ref="A6:J6"/>
     <mergeCell ref="D15:H15"/>
     <mergeCell ref="A16:C16"/>
     <mergeCell ref="H16:J16"/>
     <mergeCell ref="A18:C18"/>
     <mergeCell ref="H18:J18"/>
+    <mergeCell ref="A17:C17"/>
+    <mergeCell ref="H17:J17"/>
+    <mergeCell ref="A22:C22"/>
+    <mergeCell ref="H22:J22"/>
+    <mergeCell ref="A23:C23"/>
+    <mergeCell ref="H23:J23"/>
     <mergeCell ref="A19:C19"/>
     <mergeCell ref="H19:J19"/>
     <mergeCell ref="A20:C20"/>
     <mergeCell ref="H20:J20"/>
     <mergeCell ref="A21:C21"/>
     <mergeCell ref="H21:J21"/>
-    <mergeCell ref="A22:C22"/>
-    <mergeCell ref="H22:J22"/>
-    <mergeCell ref="A23:C23"/>
-    <mergeCell ref="H23:J23"/>
   </mergeCells>
   <phoneticPr fontId="3"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup paperSize="9" orientation="landscape"/>
   <drawing r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4B2F631B-71E1-442C-9AE2-53D543A90339}">
+  <dimension ref="A1:Z1000"/>
+  <sheetFormatPr defaultColWidth="12.625" defaultRowHeight="15" customHeight="1"/>
+  <cols>
+    <col min="1" max="6" width="2.5" style="13" customWidth="1"/>
+    <col min="7" max="10" width="7.125" style="13" customWidth="1"/>
+    <col min="11" max="11" width="11.625" style="13" customWidth="1"/>
+    <col min="12" max="12" width="9.75" style="13" customWidth="1"/>
+    <col min="13" max="20" width="7.125" style="13" customWidth="1"/>
+    <col min="21" max="26" width="7.625" style="13" customWidth="1"/>
+    <col min="27" max="16384" width="12.625" style="13"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:26" ht="18" customHeight="1">
+      <c r="A1" s="19" t="s">
+        <v>70</v>
+      </c>
+      <c r="B1" s="20"/>
+      <c r="C1" s="20"/>
+      <c r="D1" s="20"/>
+      <c r="E1" s="20"/>
+      <c r="F1" s="21"/>
+      <c r="G1" s="28" t="s">
+        <v>0</v>
+      </c>
+      <c r="H1" s="42"/>
+      <c r="I1" s="42"/>
+      <c r="J1" s="29"/>
+      <c r="K1" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="L1" s="42"/>
+      <c r="M1" s="42"/>
+      <c r="N1" s="29"/>
+      <c r="O1" s="28" t="s">
+        <v>2</v>
+      </c>
+      <c r="P1" s="29"/>
+      <c r="Q1" s="28" t="s">
+        <v>3</v>
+      </c>
+      <c r="R1" s="29"/>
+      <c r="S1" s="28" t="s">
+        <v>4</v>
+      </c>
+      <c r="T1" s="44"/>
+    </row>
+    <row r="2" spans="1:26" ht="18" customHeight="1">
+      <c r="A2" s="22"/>
+      <c r="B2" s="23"/>
+      <c r="C2" s="23"/>
+      <c r="D2" s="23"/>
+      <c r="E2" s="23"/>
+      <c r="F2" s="24"/>
+      <c r="G2" s="30" t="s">
+        <v>6</v>
+      </c>
+      <c r="H2" s="128"/>
+      <c r="I2" s="128"/>
+      <c r="J2" s="31"/>
+      <c r="K2" s="30" t="s">
+        <v>7</v>
+      </c>
+      <c r="L2" s="128"/>
+      <c r="M2" s="128"/>
+      <c r="N2" s="31"/>
+      <c r="O2" s="130">
+        <v>45810</v>
+      </c>
+      <c r="P2" s="31"/>
+      <c r="Q2" s="30" t="s">
+        <v>28</v>
+      </c>
+      <c r="R2" s="31"/>
+      <c r="S2" s="30"/>
+      <c r="T2" s="127"/>
+    </row>
+    <row r="3" spans="1:26" ht="18" customHeight="1">
+      <c r="A3" s="22"/>
+      <c r="B3" s="23"/>
+      <c r="C3" s="23"/>
+      <c r="D3" s="23"/>
+      <c r="E3" s="23"/>
+      <c r="F3" s="24"/>
+      <c r="G3" s="32"/>
+      <c r="H3" s="23"/>
+      <c r="I3" s="23"/>
+      <c r="J3" s="24"/>
+      <c r="K3" s="32"/>
+      <c r="L3" s="23"/>
+      <c r="M3" s="23"/>
+      <c r="N3" s="24"/>
+      <c r="O3" s="32"/>
+      <c r="P3" s="24"/>
+      <c r="Q3" s="32"/>
+      <c r="R3" s="24"/>
+      <c r="S3" s="32"/>
+      <c r="T3" s="126"/>
+    </row>
+    <row r="4" spans="1:26" ht="18" customHeight="1" thickBot="1">
+      <c r="A4" s="25"/>
+      <c r="B4" s="26"/>
+      <c r="C4" s="26"/>
+      <c r="D4" s="26"/>
+      <c r="E4" s="26"/>
+      <c r="F4" s="27"/>
+      <c r="G4" s="33"/>
+      <c r="H4" s="26"/>
+      <c r="I4" s="26"/>
+      <c r="J4" s="27"/>
+      <c r="K4" s="33"/>
+      <c r="L4" s="26"/>
+      <c r="M4" s="26"/>
+      <c r="N4" s="27"/>
+      <c r="O4" s="33"/>
+      <c r="P4" s="27"/>
+      <c r="Q4" s="33"/>
+      <c r="R4" s="27"/>
+      <c r="S4" s="33"/>
+      <c r="T4" s="125"/>
+    </row>
+    <row r="5" spans="1:26" ht="18" customHeight="1">
+      <c r="A5" s="124" t="s">
+        <v>69</v>
+      </c>
+      <c r="B5" s="42"/>
+      <c r="C5" s="42"/>
+      <c r="D5" s="42"/>
+      <c r="E5" s="42"/>
+      <c r="F5" s="29"/>
+      <c r="G5" s="43" t="s">
+        <v>68</v>
+      </c>
+      <c r="H5" s="42"/>
+      <c r="I5" s="42"/>
+      <c r="J5" s="42"/>
+      <c r="K5" s="42"/>
+      <c r="L5" s="42"/>
+      <c r="M5" s="42"/>
+      <c r="N5" s="42"/>
+      <c r="O5" s="42"/>
+      <c r="P5" s="42"/>
+      <c r="Q5" s="42"/>
+      <c r="R5" s="42"/>
+      <c r="S5" s="42"/>
+      <c r="T5" s="44"/>
+    </row>
+    <row r="6" spans="1:26" ht="18" customHeight="1">
+      <c r="A6" s="109" t="s">
+        <v>67</v>
+      </c>
+      <c r="B6" s="15"/>
+      <c r="C6" s="15"/>
+      <c r="D6" s="15"/>
+      <c r="E6" s="15"/>
+      <c r="F6" s="16"/>
+      <c r="G6" s="17" t="s">
+        <v>83</v>
+      </c>
+      <c r="H6" s="15"/>
+      <c r="I6" s="15"/>
+      <c r="J6" s="15"/>
+      <c r="K6" s="15"/>
+      <c r="L6" s="15"/>
+      <c r="M6" s="15"/>
+      <c r="N6" s="15"/>
+      <c r="O6" s="15"/>
+      <c r="P6" s="15"/>
+      <c r="Q6" s="15"/>
+      <c r="R6" s="15"/>
+      <c r="S6" s="15"/>
+      <c r="T6" s="18"/>
+    </row>
+    <row r="7" spans="1:26" ht="18" customHeight="1">
+      <c r="A7" s="109" t="s">
+        <v>66</v>
+      </c>
+      <c r="B7" s="15"/>
+      <c r="C7" s="15"/>
+      <c r="D7" s="15"/>
+      <c r="E7" s="15"/>
+      <c r="F7" s="16"/>
+      <c r="G7" s="17" t="s">
+        <v>82</v>
+      </c>
+      <c r="H7" s="15"/>
+      <c r="I7" s="15"/>
+      <c r="J7" s="15"/>
+      <c r="K7" s="15"/>
+      <c r="L7" s="15"/>
+      <c r="M7" s="15"/>
+      <c r="N7" s="15"/>
+      <c r="O7" s="15"/>
+      <c r="P7" s="15"/>
+      <c r="Q7" s="15"/>
+      <c r="R7" s="15"/>
+      <c r="S7" s="15"/>
+      <c r="T7" s="18"/>
+    </row>
+    <row r="8" spans="1:26" ht="7.5" customHeight="1">
+      <c r="A8" s="112"/>
+      <c r="B8" s="111"/>
+      <c r="C8" s="111"/>
+      <c r="D8" s="111"/>
+      <c r="E8" s="111"/>
+      <c r="F8" s="111"/>
+      <c r="G8" s="111"/>
+      <c r="H8" s="111"/>
+      <c r="I8" s="111"/>
+      <c r="J8" s="111"/>
+      <c r="K8" s="111"/>
+      <c r="L8" s="111"/>
+      <c r="M8" s="111"/>
+      <c r="N8" s="111"/>
+      <c r="O8" s="111"/>
+      <c r="P8" s="111"/>
+      <c r="Q8" s="111"/>
+      <c r="R8" s="111"/>
+      <c r="S8" s="111"/>
+      <c r="T8" s="110"/>
+    </row>
+    <row r="9" spans="1:26" ht="12.75" customHeight="1">
+      <c r="A9" s="118"/>
+      <c r="B9" s="113"/>
+      <c r="C9" s="123" t="s">
+        <v>59</v>
+      </c>
+      <c r="D9" s="122"/>
+      <c r="E9" s="122" t="s">
+        <v>65</v>
+      </c>
+      <c r="F9" s="122"/>
+      <c r="G9" s="121"/>
+      <c r="H9" s="122"/>
+      <c r="I9" s="122"/>
+      <c r="J9" s="122"/>
+      <c r="K9" s="121"/>
+      <c r="L9" s="113"/>
+      <c r="M9" s="113"/>
+      <c r="N9" s="113"/>
+      <c r="O9" s="113"/>
+      <c r="P9" s="113"/>
+      <c r="Q9" s="113"/>
+      <c r="R9" s="113"/>
+      <c r="S9" s="113"/>
+      <c r="T9" s="114"/>
+      <c r="U9" s="113"/>
+      <c r="V9" s="113"/>
+      <c r="W9" s="113"/>
+      <c r="X9" s="113"/>
+      <c r="Y9" s="113"/>
+      <c r="Z9" s="113"/>
+    </row>
+    <row r="10" spans="1:26" ht="12.75" customHeight="1">
+      <c r="A10" s="118"/>
+      <c r="B10" s="113"/>
+      <c r="C10" s="120"/>
+      <c r="D10" s="113"/>
+      <c r="E10" s="113" t="s">
+        <v>64</v>
+      </c>
+      <c r="F10" s="113"/>
+      <c r="G10" s="119"/>
+      <c r="H10" s="113"/>
+      <c r="I10" s="113"/>
+      <c r="J10" s="113"/>
+      <c r="K10" s="119"/>
+      <c r="L10" s="113"/>
+      <c r="M10" s="113"/>
+      <c r="N10" s="113"/>
+      <c r="O10" s="113"/>
+      <c r="P10" s="113"/>
+      <c r="Q10" s="113"/>
+      <c r="R10" s="113"/>
+      <c r="S10" s="113"/>
+      <c r="T10" s="114"/>
+      <c r="U10" s="113"/>
+      <c r="V10" s="113"/>
+      <c r="W10" s="113"/>
+      <c r="X10" s="113"/>
+      <c r="Y10" s="113"/>
+      <c r="Z10" s="113"/>
+    </row>
+    <row r="11" spans="1:26" ht="12.75" customHeight="1">
+      <c r="A11" s="118"/>
+      <c r="B11" s="113"/>
+      <c r="C11" s="120"/>
+      <c r="D11" s="113"/>
+      <c r="E11" s="113" t="s">
+        <v>63</v>
+      </c>
+      <c r="F11" s="113"/>
+      <c r="G11" s="119"/>
+      <c r="H11" s="113"/>
+      <c r="I11" s="113"/>
+      <c r="J11" s="113"/>
+      <c r="K11" s="119"/>
+      <c r="L11" s="113"/>
+      <c r="M11" s="113"/>
+      <c r="N11" s="113"/>
+      <c r="O11" s="113"/>
+      <c r="P11" s="113"/>
+      <c r="Q11" s="113"/>
+      <c r="R11" s="113"/>
+      <c r="S11" s="113"/>
+      <c r="T11" s="114"/>
+      <c r="U11" s="113"/>
+      <c r="V11" s="113"/>
+      <c r="W11" s="113"/>
+      <c r="X11" s="113"/>
+      <c r="Y11" s="113"/>
+      <c r="Z11" s="113"/>
+    </row>
+    <row r="12" spans="1:26" ht="12.75" customHeight="1">
+      <c r="A12" s="118"/>
+      <c r="B12" s="113"/>
+      <c r="C12" s="120"/>
+      <c r="D12" s="113"/>
+      <c r="E12" s="113" t="s">
+        <v>62</v>
+      </c>
+      <c r="F12" s="113"/>
+      <c r="G12" s="119"/>
+      <c r="H12" s="113"/>
+      <c r="I12" s="113"/>
+      <c r="J12" s="113"/>
+      <c r="K12" s="119"/>
+      <c r="L12" s="113"/>
+      <c r="M12" s="113"/>
+      <c r="N12" s="113"/>
+      <c r="O12" s="113"/>
+      <c r="P12" s="113"/>
+      <c r="Q12" s="113"/>
+      <c r="R12" s="113"/>
+      <c r="S12" s="113"/>
+      <c r="T12" s="114"/>
+      <c r="U12" s="113"/>
+      <c r="V12" s="113"/>
+      <c r="W12" s="113"/>
+      <c r="X12" s="113"/>
+      <c r="Y12" s="113"/>
+      <c r="Z12" s="113"/>
+    </row>
+    <row r="13" spans="1:26" ht="12.75" customHeight="1">
+      <c r="A13" s="118"/>
+      <c r="B13" s="113"/>
+      <c r="C13" s="117"/>
+      <c r="D13" s="116"/>
+      <c r="E13" s="116" t="s">
+        <v>61</v>
+      </c>
+      <c r="F13" s="116"/>
+      <c r="G13" s="115"/>
+      <c r="H13" s="116"/>
+      <c r="I13" s="116"/>
+      <c r="J13" s="116"/>
+      <c r="K13" s="115"/>
+      <c r="L13" s="113"/>
+      <c r="M13" s="113"/>
+      <c r="N13" s="113"/>
+      <c r="O13" s="113"/>
+      <c r="P13" s="113"/>
+      <c r="Q13" s="113"/>
+      <c r="R13" s="113"/>
+      <c r="S13" s="113"/>
+      <c r="T13" s="114"/>
+      <c r="U13" s="113"/>
+      <c r="V13" s="113"/>
+      <c r="W13" s="113"/>
+      <c r="X13" s="113"/>
+      <c r="Y13" s="113"/>
+      <c r="Z13" s="113"/>
+    </row>
+    <row r="14" spans="1:26" ht="8.25" customHeight="1">
+      <c r="A14" s="112"/>
+      <c r="B14" s="111"/>
+      <c r="C14" s="111"/>
+      <c r="D14" s="111"/>
+      <c r="E14" s="111"/>
+      <c r="F14" s="111"/>
+      <c r="G14" s="111"/>
+      <c r="H14" s="111"/>
+      <c r="I14" s="111"/>
+      <c r="J14" s="111"/>
+      <c r="K14" s="111"/>
+      <c r="L14" s="111"/>
+      <c r="M14" s="111"/>
+      <c r="N14" s="111"/>
+      <c r="O14" s="111"/>
+      <c r="P14" s="111"/>
+      <c r="Q14" s="111"/>
+      <c r="R14" s="111"/>
+      <c r="S14" s="111"/>
+      <c r="T14" s="110"/>
+    </row>
+    <row r="15" spans="1:26" ht="18.75" customHeight="1">
+      <c r="A15" s="109" t="s">
+        <v>60</v>
+      </c>
+      <c r="B15" s="16"/>
+      <c r="C15" s="108" t="s">
+        <v>59</v>
+      </c>
+      <c r="D15" s="16"/>
+      <c r="E15" s="107" t="s">
+        <v>58</v>
+      </c>
+      <c r="F15" s="16"/>
+      <c r="G15" s="107" t="s">
+        <v>57</v>
+      </c>
+      <c r="H15" s="15"/>
+      <c r="I15" s="16"/>
+      <c r="J15" s="107" t="s">
+        <v>56</v>
+      </c>
+      <c r="K15" s="16"/>
+      <c r="L15" s="107" t="s">
+        <v>55</v>
+      </c>
+      <c r="M15" s="15"/>
+      <c r="N15" s="16"/>
+      <c r="O15" s="107" t="s">
+        <v>54</v>
+      </c>
+      <c r="P15" s="15"/>
+      <c r="Q15" s="16"/>
+      <c r="R15" s="106" t="s">
+        <v>53</v>
+      </c>
+      <c r="S15" s="106" t="s">
+        <v>52</v>
+      </c>
+      <c r="T15" s="105" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="16" spans="1:26" ht="48" customHeight="1">
+      <c r="A16" s="104">
+        <v>1</v>
+      </c>
+      <c r="B16" s="16"/>
+      <c r="C16" s="103" t="s">
+        <v>50</v>
+      </c>
+      <c r="D16" s="16"/>
+      <c r="E16" s="103" t="s">
+        <v>49</v>
+      </c>
+      <c r="F16" s="16"/>
+      <c r="G16" s="102" t="s">
+        <v>72</v>
+      </c>
+      <c r="H16" s="15"/>
+      <c r="I16" s="16"/>
+      <c r="J16" s="102" t="s">
+        <v>71</v>
+      </c>
+      <c r="K16" s="16"/>
+      <c r="L16" s="101" t="s">
+        <v>73</v>
+      </c>
+      <c r="M16" s="15"/>
+      <c r="N16" s="16"/>
+      <c r="O16" s="101" t="s">
+        <v>48</v>
+      </c>
+      <c r="P16" s="15"/>
+      <c r="Q16" s="16"/>
+      <c r="R16" s="131">
+        <v>45810</v>
+      </c>
+      <c r="S16" s="100" t="s">
+        <v>28</v>
+      </c>
+      <c r="T16" s="99" t="s">
+        <v>85</v>
+      </c>
+      <c r="U16" s="92"/>
+      <c r="V16" s="92"/>
+      <c r="W16" s="92"/>
+      <c r="X16" s="92"/>
+      <c r="Y16" s="92"/>
+      <c r="Z16" s="92"/>
+    </row>
+    <row r="17" spans="1:26" ht="41.25" customHeight="1">
+      <c r="A17" s="104">
+        <v>2</v>
+      </c>
+      <c r="B17" s="16"/>
+      <c r="C17" s="103" t="s">
+        <v>74</v>
+      </c>
+      <c r="D17" s="16"/>
+      <c r="E17" s="103" t="s">
+        <v>49</v>
+      </c>
+      <c r="F17" s="16"/>
+      <c r="G17" s="102" t="s">
+        <v>75</v>
+      </c>
+      <c r="H17" s="15"/>
+      <c r="I17" s="16"/>
+      <c r="J17" s="102" t="s">
+        <v>71</v>
+      </c>
+      <c r="K17" s="16"/>
+      <c r="L17" s="101" t="s">
+        <v>76</v>
+      </c>
+      <c r="M17" s="15"/>
+      <c r="N17" s="16"/>
+      <c r="O17" s="101" t="s">
+        <v>77</v>
+      </c>
+      <c r="P17" s="15"/>
+      <c r="Q17" s="16"/>
+      <c r="R17" s="131">
+        <v>45810</v>
+      </c>
+      <c r="S17" s="100" t="s">
+        <v>28</v>
+      </c>
+      <c r="T17" s="99" t="s">
+        <v>85</v>
+      </c>
+      <c r="U17" s="92"/>
+      <c r="V17" s="92"/>
+      <c r="W17" s="92"/>
+      <c r="X17" s="92"/>
+      <c r="Y17" s="92"/>
+      <c r="Z17" s="92"/>
+    </row>
+    <row r="18" spans="1:26" ht="57.75" customHeight="1">
+      <c r="A18" s="104">
+        <v>3</v>
+      </c>
+      <c r="B18" s="16"/>
+      <c r="C18" s="103" t="s">
+        <v>74</v>
+      </c>
+      <c r="D18" s="16"/>
+      <c r="E18" s="103" t="s">
+        <v>78</v>
+      </c>
+      <c r="F18" s="16"/>
+      <c r="G18" s="102" t="s">
+        <v>79</v>
+      </c>
+      <c r="H18" s="15"/>
+      <c r="I18" s="16"/>
+      <c r="J18" s="102" t="s">
+        <v>80</v>
+      </c>
+      <c r="K18" s="16"/>
+      <c r="L18" s="129" t="s">
+        <v>84</v>
+      </c>
+      <c r="M18" s="15"/>
+      <c r="N18" s="16"/>
+      <c r="O18" s="101" t="s">
+        <v>81</v>
+      </c>
+      <c r="P18" s="15"/>
+      <c r="Q18" s="16"/>
+      <c r="R18" s="131">
+        <v>45810</v>
+      </c>
+      <c r="S18" s="100" t="s">
+        <v>28</v>
+      </c>
+      <c r="T18" s="99" t="s">
+        <v>85</v>
+      </c>
+      <c r="U18" s="92"/>
+      <c r="V18" s="92"/>
+      <c r="W18" s="92"/>
+      <c r="X18" s="92"/>
+      <c r="Y18" s="92"/>
+      <c r="Z18" s="92"/>
+    </row>
+    <row r="19" spans="1:26" ht="12.75" customHeight="1">
+      <c r="A19" s="104"/>
+      <c r="B19" s="16"/>
+      <c r="C19" s="103"/>
+      <c r="D19" s="16"/>
+      <c r="E19" s="103"/>
+      <c r="F19" s="16"/>
+      <c r="G19" s="102"/>
+      <c r="H19" s="15"/>
+      <c r="I19" s="16"/>
+      <c r="J19" s="102"/>
+      <c r="K19" s="16"/>
+      <c r="L19" s="101"/>
+      <c r="M19" s="15"/>
+      <c r="N19" s="16"/>
+      <c r="O19" s="101"/>
+      <c r="P19" s="15"/>
+      <c r="Q19" s="16"/>
+      <c r="R19" s="100"/>
+      <c r="S19" s="100"/>
+      <c r="T19" s="99"/>
+      <c r="U19" s="92"/>
+      <c r="V19" s="92"/>
+      <c r="W19" s="92"/>
+      <c r="X19" s="92"/>
+      <c r="Y19" s="92"/>
+      <c r="Z19" s="92"/>
+    </row>
+    <row r="20" spans="1:26" ht="12.75" customHeight="1">
+      <c r="A20" s="104"/>
+      <c r="B20" s="16"/>
+      <c r="C20" s="103"/>
+      <c r="D20" s="16"/>
+      <c r="E20" s="103"/>
+      <c r="F20" s="16"/>
+      <c r="G20" s="102"/>
+      <c r="H20" s="15"/>
+      <c r="I20" s="16"/>
+      <c r="J20" s="102"/>
+      <c r="K20" s="16"/>
+      <c r="L20" s="101"/>
+      <c r="M20" s="15"/>
+      <c r="N20" s="16"/>
+      <c r="O20" s="101"/>
+      <c r="P20" s="15"/>
+      <c r="Q20" s="16"/>
+      <c r="R20" s="100"/>
+      <c r="S20" s="100"/>
+      <c r="T20" s="99"/>
+      <c r="U20" s="92"/>
+      <c r="V20" s="92"/>
+      <c r="W20" s="92"/>
+      <c r="X20" s="92"/>
+      <c r="Y20" s="92"/>
+      <c r="Z20" s="92"/>
+    </row>
+    <row r="21" spans="1:26" ht="12.75" customHeight="1">
+      <c r="A21" s="104"/>
+      <c r="B21" s="16"/>
+      <c r="C21" s="103"/>
+      <c r="D21" s="16"/>
+      <c r="E21" s="103"/>
+      <c r="F21" s="16"/>
+      <c r="G21" s="102"/>
+      <c r="H21" s="15"/>
+      <c r="I21" s="16"/>
+      <c r="J21" s="102"/>
+      <c r="K21" s="16"/>
+      <c r="L21" s="101"/>
+      <c r="M21" s="15"/>
+      <c r="N21" s="16"/>
+      <c r="O21" s="101"/>
+      <c r="P21" s="15"/>
+      <c r="Q21" s="16"/>
+      <c r="R21" s="100"/>
+      <c r="S21" s="100"/>
+      <c r="T21" s="99"/>
+      <c r="U21" s="92"/>
+      <c r="V21" s="92"/>
+      <c r="W21" s="92"/>
+      <c r="X21" s="92"/>
+      <c r="Y21" s="92"/>
+      <c r="Z21" s="92"/>
+    </row>
+    <row r="22" spans="1:26" ht="12.75" customHeight="1">
+      <c r="A22" s="104"/>
+      <c r="B22" s="16"/>
+      <c r="C22" s="103"/>
+      <c r="D22" s="16"/>
+      <c r="E22" s="103"/>
+      <c r="F22" s="16"/>
+      <c r="G22" s="102"/>
+      <c r="H22" s="15"/>
+      <c r="I22" s="16"/>
+      <c r="J22" s="102"/>
+      <c r="K22" s="16"/>
+      <c r="L22" s="101"/>
+      <c r="M22" s="15"/>
+      <c r="N22" s="16"/>
+      <c r="O22" s="101"/>
+      <c r="P22" s="15"/>
+      <c r="Q22" s="16"/>
+      <c r="R22" s="100"/>
+      <c r="S22" s="100"/>
+      <c r="T22" s="99"/>
+      <c r="U22" s="92"/>
+      <c r="V22" s="92"/>
+      <c r="W22" s="92"/>
+      <c r="X22" s="92"/>
+      <c r="Y22" s="92"/>
+      <c r="Z22" s="92"/>
+    </row>
+    <row r="23" spans="1:26" ht="12.75" customHeight="1">
+      <c r="A23" s="104"/>
+      <c r="B23" s="16"/>
+      <c r="C23" s="103"/>
+      <c r="D23" s="16"/>
+      <c r="E23" s="103"/>
+      <c r="F23" s="16"/>
+      <c r="G23" s="102"/>
+      <c r="H23" s="15"/>
+      <c r="I23" s="16"/>
+      <c r="J23" s="102"/>
+      <c r="K23" s="16"/>
+      <c r="L23" s="101"/>
+      <c r="M23" s="15"/>
+      <c r="N23" s="16"/>
+      <c r="O23" s="101"/>
+      <c r="P23" s="15"/>
+      <c r="Q23" s="16"/>
+      <c r="R23" s="100"/>
+      <c r="S23" s="100"/>
+      <c r="T23" s="99"/>
+      <c r="U23" s="92"/>
+      <c r="V23" s="92"/>
+      <c r="W23" s="92"/>
+      <c r="X23" s="92"/>
+      <c r="Y23" s="92"/>
+      <c r="Z23" s="92"/>
+    </row>
+    <row r="24" spans="1:26" ht="12.75" customHeight="1">
+      <c r="A24" s="104"/>
+      <c r="B24" s="16"/>
+      <c r="C24" s="103"/>
+      <c r="D24" s="16"/>
+      <c r="E24" s="103"/>
+      <c r="F24" s="16"/>
+      <c r="G24" s="102"/>
+      <c r="H24" s="15"/>
+      <c r="I24" s="16"/>
+      <c r="J24" s="102"/>
+      <c r="K24" s="16"/>
+      <c r="L24" s="101"/>
+      <c r="M24" s="15"/>
+      <c r="N24" s="16"/>
+      <c r="O24" s="101"/>
+      <c r="P24" s="15"/>
+      <c r="Q24" s="16"/>
+      <c r="R24" s="100"/>
+      <c r="S24" s="100"/>
+      <c r="T24" s="99"/>
+      <c r="U24" s="92"/>
+      <c r="V24" s="92"/>
+      <c r="W24" s="92"/>
+      <c r="X24" s="92"/>
+      <c r="Y24" s="92"/>
+      <c r="Z24" s="92"/>
+    </row>
+    <row r="25" spans="1:26" ht="12.75" customHeight="1">
+      <c r="A25" s="104"/>
+      <c r="B25" s="16"/>
+      <c r="C25" s="103"/>
+      <c r="D25" s="16"/>
+      <c r="E25" s="103"/>
+      <c r="F25" s="16"/>
+      <c r="G25" s="102"/>
+      <c r="H25" s="15"/>
+      <c r="I25" s="16"/>
+      <c r="J25" s="102"/>
+      <c r="K25" s="16"/>
+      <c r="L25" s="101"/>
+      <c r="M25" s="15"/>
+      <c r="N25" s="16"/>
+      <c r="O25" s="101"/>
+      <c r="P25" s="15"/>
+      <c r="Q25" s="16"/>
+      <c r="R25" s="100"/>
+      <c r="S25" s="100"/>
+      <c r="T25" s="99"/>
+      <c r="U25" s="92"/>
+      <c r="V25" s="92"/>
+      <c r="W25" s="92"/>
+      <c r="X25" s="92"/>
+      <c r="Y25" s="92"/>
+      <c r="Z25" s="92"/>
+    </row>
+    <row r="26" spans="1:26" ht="12.75" customHeight="1">
+      <c r="A26" s="104"/>
+      <c r="B26" s="16"/>
+      <c r="C26" s="103"/>
+      <c r="D26" s="16"/>
+      <c r="E26" s="103"/>
+      <c r="F26" s="16"/>
+      <c r="G26" s="102"/>
+      <c r="H26" s="15"/>
+      <c r="I26" s="16"/>
+      <c r="J26" s="102"/>
+      <c r="K26" s="16"/>
+      <c r="L26" s="101"/>
+      <c r="M26" s="15"/>
+      <c r="N26" s="16"/>
+      <c r="O26" s="101"/>
+      <c r="P26" s="15"/>
+      <c r="Q26" s="16"/>
+      <c r="R26" s="100"/>
+      <c r="S26" s="100"/>
+      <c r="T26" s="99"/>
+      <c r="U26" s="92"/>
+      <c r="V26" s="92"/>
+      <c r="W26" s="92"/>
+      <c r="X26" s="92"/>
+      <c r="Y26" s="92"/>
+      <c r="Z26" s="92"/>
+    </row>
+    <row r="27" spans="1:26" ht="12.75" customHeight="1">
+      <c r="A27" s="104"/>
+      <c r="B27" s="16"/>
+      <c r="C27" s="103"/>
+      <c r="D27" s="16"/>
+      <c r="E27" s="103"/>
+      <c r="F27" s="16"/>
+      <c r="G27" s="102"/>
+      <c r="H27" s="15"/>
+      <c r="I27" s="16"/>
+      <c r="J27" s="102"/>
+      <c r="K27" s="16"/>
+      <c r="L27" s="101"/>
+      <c r="M27" s="15"/>
+      <c r="N27" s="16"/>
+      <c r="O27" s="101"/>
+      <c r="P27" s="15"/>
+      <c r="Q27" s="16"/>
+      <c r="R27" s="100"/>
+      <c r="S27" s="100"/>
+      <c r="T27" s="99"/>
+      <c r="U27" s="92"/>
+      <c r="V27" s="92"/>
+      <c r="W27" s="92"/>
+      <c r="X27" s="92"/>
+      <c r="Y27" s="92"/>
+      <c r="Z27" s="92"/>
+    </row>
+    <row r="28" spans="1:26" ht="12.75" customHeight="1">
+      <c r="A28" s="104"/>
+      <c r="B28" s="16"/>
+      <c r="C28" s="103"/>
+      <c r="D28" s="16"/>
+      <c r="E28" s="103"/>
+      <c r="F28" s="16"/>
+      <c r="G28" s="102"/>
+      <c r="H28" s="15"/>
+      <c r="I28" s="16"/>
+      <c r="J28" s="102"/>
+      <c r="K28" s="16"/>
+      <c r="L28" s="101"/>
+      <c r="M28" s="15"/>
+      <c r="N28" s="16"/>
+      <c r="O28" s="101"/>
+      <c r="P28" s="15"/>
+      <c r="Q28" s="16"/>
+      <c r="R28" s="100"/>
+      <c r="S28" s="100"/>
+      <c r="T28" s="99"/>
+      <c r="U28" s="92"/>
+      <c r="V28" s="92"/>
+      <c r="W28" s="92"/>
+      <c r="X28" s="92"/>
+      <c r="Y28" s="92"/>
+      <c r="Z28" s="92"/>
+    </row>
+    <row r="29" spans="1:26" ht="12.75" customHeight="1">
+      <c r="A29" s="104"/>
+      <c r="B29" s="16"/>
+      <c r="C29" s="103"/>
+      <c r="D29" s="16"/>
+      <c r="E29" s="103"/>
+      <c r="F29" s="16"/>
+      <c r="G29" s="102"/>
+      <c r="H29" s="15"/>
+      <c r="I29" s="16"/>
+      <c r="J29" s="102"/>
+      <c r="K29" s="16"/>
+      <c r="L29" s="101"/>
+      <c r="M29" s="15"/>
+      <c r="N29" s="16"/>
+      <c r="O29" s="101"/>
+      <c r="P29" s="15"/>
+      <c r="Q29" s="16"/>
+      <c r="R29" s="100"/>
+      <c r="S29" s="100"/>
+      <c r="T29" s="99"/>
+      <c r="U29" s="92"/>
+      <c r="V29" s="92"/>
+      <c r="W29" s="92"/>
+      <c r="X29" s="92"/>
+      <c r="Y29" s="92"/>
+      <c r="Z29" s="92"/>
+    </row>
+    <row r="30" spans="1:26" ht="12.75" customHeight="1">
+      <c r="A30" s="104"/>
+      <c r="B30" s="16"/>
+      <c r="C30" s="103"/>
+      <c r="D30" s="16"/>
+      <c r="E30" s="103"/>
+      <c r="F30" s="16"/>
+      <c r="G30" s="102"/>
+      <c r="H30" s="15"/>
+      <c r="I30" s="16"/>
+      <c r="J30" s="102"/>
+      <c r="K30" s="16"/>
+      <c r="L30" s="101"/>
+      <c r="M30" s="15"/>
+      <c r="N30" s="16"/>
+      <c r="O30" s="101"/>
+      <c r="P30" s="15"/>
+      <c r="Q30" s="16"/>
+      <c r="R30" s="100"/>
+      <c r="S30" s="100"/>
+      <c r="T30" s="99"/>
+      <c r="U30" s="92"/>
+      <c r="V30" s="92"/>
+      <c r="W30" s="92"/>
+      <c r="X30" s="92"/>
+      <c r="Y30" s="92"/>
+      <c r="Z30" s="92"/>
+    </row>
+    <row r="31" spans="1:26" ht="12.75" customHeight="1" thickBot="1">
+      <c r="A31" s="98"/>
+      <c r="B31" s="52"/>
+      <c r="C31" s="97"/>
+      <c r="D31" s="52"/>
+      <c r="E31" s="97"/>
+      <c r="F31" s="52"/>
+      <c r="G31" s="96"/>
+      <c r="H31" s="51"/>
+      <c r="I31" s="52"/>
+      <c r="J31" s="96"/>
+      <c r="K31" s="52"/>
+      <c r="L31" s="95"/>
+      <c r="M31" s="51"/>
+      <c r="N31" s="52"/>
+      <c r="O31" s="95"/>
+      <c r="P31" s="51"/>
+      <c r="Q31" s="52"/>
+      <c r="R31" s="94"/>
+      <c r="S31" s="94"/>
+      <c r="T31" s="93"/>
+      <c r="U31" s="92"/>
+      <c r="V31" s="92"/>
+      <c r="W31" s="92"/>
+      <c r="X31" s="92"/>
+      <c r="Y31" s="92"/>
+      <c r="Z31" s="92"/>
+    </row>
+    <row r="32" spans="1:26" ht="12.75" customHeight="1">
+      <c r="D32" s="91"/>
+      <c r="E32" s="91"/>
+      <c r="F32" s="91"/>
+      <c r="G32" s="91"/>
+      <c r="H32" s="91"/>
+      <c r="I32" s="91"/>
+      <c r="J32" s="91"/>
+    </row>
+    <row r="33" spans="4:10" ht="12.75" customHeight="1">
+      <c r="D33" s="91"/>
+      <c r="E33" s="91"/>
+      <c r="F33" s="91"/>
+      <c r="G33" s="91"/>
+      <c r="H33" s="91"/>
+      <c r="I33" s="91"/>
+      <c r="J33" s="91"/>
+    </row>
+    <row r="34" spans="4:10" ht="12.75" customHeight="1"/>
+    <row r="35" spans="4:10" ht="12.75" customHeight="1"/>
+    <row r="36" spans="4:10" ht="12.75" customHeight="1"/>
+    <row r="37" spans="4:10" ht="12.75" customHeight="1"/>
+    <row r="38" spans="4:10" ht="12.75" customHeight="1"/>
+    <row r="39" spans="4:10" ht="12.75" customHeight="1"/>
+    <row r="40" spans="4:10" ht="12.75" customHeight="1"/>
+    <row r="41" spans="4:10" ht="12.75" customHeight="1"/>
+    <row r="42" spans="4:10" ht="12.75" customHeight="1"/>
+    <row r="43" spans="4:10" ht="12.75" customHeight="1"/>
+    <row r="44" spans="4:10" ht="12.75" customHeight="1"/>
+    <row r="45" spans="4:10" ht="12.75" customHeight="1"/>
+    <row r="46" spans="4:10" ht="12.75" customHeight="1"/>
+    <row r="47" spans="4:10" ht="12.75" customHeight="1"/>
+    <row r="48" spans="4:10" ht="12.75" customHeight="1"/>
+    <row r="49" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="50" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="51" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="52" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="53" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="54" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="55" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="56" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="57" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="58" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="59" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="60" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="61" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="62" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="63" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="64" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="65" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="66" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="67" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="68" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="69" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="70" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="71" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="72" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="73" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="74" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="75" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="76" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="77" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="78" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="79" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="80" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="81" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="82" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="83" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="84" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="85" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="86" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="87" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="88" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="89" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="90" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="91" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="92" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="93" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="94" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="95" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="96" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="97" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="98" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="99" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="100" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="101" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="102" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="103" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="104" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="105" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="106" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="107" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="108" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="109" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="110" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="111" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="112" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="113" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="114" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="115" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="116" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="117" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="118" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="119" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="120" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="121" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="122" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="123" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="124" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="125" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="126" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="127" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="128" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="129" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="130" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="131" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="132" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="133" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="134" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="135" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="136" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="137" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="138" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="139" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="140" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="141" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="142" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="143" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="144" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="145" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="146" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="147" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="148" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="149" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="150" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="151" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="152" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="153" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="154" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="155" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="156" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="157" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="158" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="159" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="160" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="161" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="162" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="163" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="164" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="165" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="166" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="167" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="168" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="169" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="170" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="171" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="172" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="173" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="174" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="175" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="176" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="177" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="178" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="179" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="180" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="181" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="182" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="183" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="184" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="185" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="186" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="187" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="188" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="189" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="190" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="191" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="192" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="193" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="194" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="195" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="196" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="197" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="198" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="199" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="200" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="201" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="202" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="203" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="204" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="205" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="206" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="207" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="208" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="209" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="210" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="211" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="212" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="213" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="214" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="215" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="216" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="217" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="218" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="219" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="220" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="221" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="222" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="223" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="224" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="225" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="226" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="227" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="228" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="229" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="230" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="231" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="232" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="233" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="234" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="235" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="236" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="237" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="238" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="239" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="240" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="241" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="242" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="243" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="244" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="245" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="246" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="247" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="248" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="249" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="250" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="251" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="252" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="253" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="254" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="255" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="256" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="257" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="258" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="259" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="260" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="261" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="262" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="263" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="264" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="265" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="266" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="267" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="268" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="269" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="270" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="271" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="272" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="273" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="274" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="275" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="276" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="277" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="278" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="279" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="280" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="281" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="282" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="283" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="284" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="285" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="286" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="287" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="288" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="289" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="290" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="291" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="292" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="293" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="294" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="295" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="296" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="297" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="298" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="299" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="300" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="301" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="302" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="303" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="304" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="305" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="306" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="307" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="308" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="309" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="310" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="311" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="312" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="313" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="314" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="315" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="316" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="317" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="318" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="319" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="320" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="321" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="322" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="323" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="324" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="325" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="326" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="327" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="328" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="329" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="330" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="331" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="332" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="333" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="334" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="335" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="336" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="337" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="338" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="339" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="340" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="341" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="342" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="343" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="344" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="345" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="346" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="347" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="348" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="349" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="350" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="351" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="352" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="353" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="354" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="355" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="356" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="357" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="358" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="359" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="360" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="361" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="362" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="363" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="364" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="365" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="366" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="367" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="368" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="369" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="370" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="371" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="372" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="373" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="374" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="375" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="376" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="377" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="378" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="379" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="380" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="381" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="382" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="383" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="384" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="385" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="386" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="387" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="388" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="389" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="390" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="391" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="392" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="393" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="394" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="395" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="396" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="397" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="398" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="399" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="400" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="401" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="402" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="403" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="404" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="405" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="406" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="407" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="408" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="409" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="410" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="411" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="412" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="413" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="414" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="415" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="416" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="417" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="418" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="419" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="420" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="421" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="422" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="423" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="424" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="425" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="426" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="427" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="428" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="429" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="430" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="431" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="432" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="433" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="434" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="435" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="436" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="437" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="438" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="439" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="440" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="441" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="442" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="443" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="444" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="445" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="446" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="447" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="448" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="449" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="450" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="451" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="452" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="453" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="454" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="455" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="456" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="457" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="458" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="459" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="460" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="461" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="462" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="463" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="464" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="465" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="466" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="467" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="468" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="469" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="470" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="471" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="472" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="473" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="474" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="475" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="476" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="477" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="478" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="479" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="480" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="481" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="482" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="483" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="484" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="485" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="486" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="487" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="488" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="489" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="490" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="491" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="492" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="493" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="494" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="495" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="496" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="497" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="498" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="499" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="500" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="501" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="502" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="503" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="504" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="505" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="506" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="507" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="508" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="509" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="510" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="511" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="512" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="513" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="514" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="515" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="516" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="517" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="518" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="519" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="520" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="521" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="522" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="523" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="524" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="525" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="526" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="527" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="528" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="529" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="530" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="531" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="532" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="533" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="534" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="535" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="536" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="537" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="538" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="539" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="540" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="541" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="542" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="543" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="544" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="545" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="546" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="547" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="548" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="549" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="550" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="551" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="552" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="553" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="554" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="555" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="556" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="557" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="558" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="559" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="560" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="561" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="562" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="563" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="564" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="565" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="566" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="567" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="568" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="569" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="570" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="571" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="572" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="573" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="574" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="575" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="576" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="577" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="578" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="579" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="580" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="581" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="582" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="583" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="584" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="585" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="586" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="587" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="588" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="589" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="590" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="591" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="592" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="593" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="594" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="595" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="596" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="597" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="598" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="599" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="600" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="601" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="602" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="603" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="604" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="605" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="606" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="607" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="608" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="609" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="610" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="611" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="612" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="613" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="614" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="615" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="616" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="617" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="618" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="619" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="620" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="621" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="622" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="623" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="624" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="625" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="626" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="627" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="628" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="629" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="630" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="631" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="632" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="633" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="634" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="635" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="636" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="637" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="638" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="639" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="640" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="641" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="642" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="643" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="644" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="645" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="646" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="647" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="648" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="649" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="650" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="651" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="652" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="653" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="654" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="655" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="656" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="657" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="658" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="659" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="660" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="661" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="662" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="663" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="664" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="665" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="666" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="667" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="668" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="669" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="670" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="671" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="672" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="673" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="674" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="675" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="676" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="677" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="678" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="679" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="680" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="681" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="682" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="683" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="684" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="685" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="686" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="687" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="688" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="689" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="690" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="691" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="692" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="693" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="694" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="695" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="696" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="697" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="698" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="699" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="700" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="701" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="702" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="703" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="704" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="705" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="706" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="707" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="708" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="709" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="710" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="711" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="712" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="713" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="714" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="715" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="716" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="717" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="718" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="719" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="720" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="721" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="722" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="723" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="724" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="725" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="726" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="727" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="728" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="729" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="730" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="731" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="732" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="733" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="734" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="735" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="736" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="737" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="738" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="739" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="740" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="741" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="742" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="743" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="744" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="745" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="746" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="747" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="748" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="749" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="750" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="751" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="752" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="753" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="754" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="755" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="756" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="757" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="758" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="759" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="760" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="761" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="762" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="763" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="764" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="765" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="766" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="767" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="768" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="769" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="770" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="771" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="772" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="773" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="774" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="775" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="776" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="777" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="778" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="779" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="780" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="781" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="782" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="783" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="784" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="785" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="786" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="787" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="788" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="789" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="790" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="791" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="792" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="793" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="794" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="795" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="796" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="797" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="798" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="799" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="800" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="801" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="802" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="803" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="804" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="805" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="806" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="807" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="808" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="809" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="810" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="811" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="812" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="813" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="814" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="815" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="816" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="817" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="818" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="819" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="820" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="821" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="822" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="823" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="824" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="825" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="826" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="827" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="828" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="829" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="830" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="831" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="832" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="833" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="834" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="835" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="836" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="837" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="838" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="839" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="840" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="841" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="842" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="843" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="844" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="845" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="846" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="847" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="848" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="849" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="850" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="851" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="852" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="853" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="854" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="855" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="856" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="857" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="858" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="859" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="860" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="861" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="862" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="863" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="864" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="865" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="866" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="867" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="868" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="869" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="870" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="871" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="872" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="873" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="874" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="875" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="876" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="877" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="878" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="879" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="880" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="881" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="882" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="883" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="884" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="885" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="886" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="887" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="888" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="889" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="890" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="891" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="892" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="893" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="894" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="895" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="896" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="897" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="898" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="899" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="900" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="901" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="902" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="903" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="904" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="905" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="906" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="907" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="908" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="909" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="910" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="911" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="912" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="913" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="914" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="915" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="916" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="917" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="918" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="919" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="920" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="921" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="922" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="923" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="924" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="925" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="926" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="927" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="928" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="929" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="930" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="931" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="932" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="933" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="934" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="935" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="936" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="937" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="938" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="939" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="940" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="941" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="942" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="943" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="944" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="945" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="946" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="947" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="948" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="949" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="950" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="951" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="952" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="953" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="954" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="955" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="956" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="957" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="958" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="959" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="960" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="961" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="962" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="963" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="964" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="965" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="966" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="967" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="968" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="969" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="970" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="971" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="972" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="973" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="974" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="975" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="976" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="977" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="978" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="979" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="980" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="981" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="982" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="983" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="984" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="985" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="986" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="987" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="988" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="989" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="990" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="991" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="992" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="993" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="994" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="995" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="996" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="997" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="998" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="999" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="1000" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+  </sheetData>
+  <mergeCells count="136">
+    <mergeCell ref="C28:D28"/>
+    <mergeCell ref="E28:F28"/>
+    <mergeCell ref="A29:B29"/>
+    <mergeCell ref="A25:B25"/>
+    <mergeCell ref="C25:D25"/>
+    <mergeCell ref="E25:F25"/>
+    <mergeCell ref="A26:B26"/>
+    <mergeCell ref="C29:D29"/>
+    <mergeCell ref="E29:F29"/>
+    <mergeCell ref="A27:B27"/>
+    <mergeCell ref="C27:D27"/>
+    <mergeCell ref="E27:F27"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="A23:B23"/>
+    <mergeCell ref="A30:B30"/>
+    <mergeCell ref="C30:D30"/>
+    <mergeCell ref="E30:F30"/>
+    <mergeCell ref="A31:B31"/>
+    <mergeCell ref="C31:D31"/>
+    <mergeCell ref="E31:F31"/>
+    <mergeCell ref="C26:D26"/>
+    <mergeCell ref="E26:F26"/>
+    <mergeCell ref="A24:B24"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="E21:F21"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="E22:F22"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="E18:F18"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="E19:F19"/>
+    <mergeCell ref="O25:Q25"/>
+    <mergeCell ref="O26:Q26"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="E16:F16"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="E23:F23"/>
+    <mergeCell ref="C24:D24"/>
+    <mergeCell ref="E24:F24"/>
+    <mergeCell ref="O27:Q27"/>
+    <mergeCell ref="O28:Q28"/>
+    <mergeCell ref="O29:Q29"/>
+    <mergeCell ref="O30:Q30"/>
+    <mergeCell ref="O31:Q31"/>
+    <mergeCell ref="O19:Q19"/>
+    <mergeCell ref="O21:Q21"/>
+    <mergeCell ref="O22:Q22"/>
+    <mergeCell ref="O23:Q23"/>
+    <mergeCell ref="O24:Q24"/>
+    <mergeCell ref="O20:Q20"/>
+    <mergeCell ref="L15:N15"/>
+    <mergeCell ref="O15:Q15"/>
+    <mergeCell ref="L16:N16"/>
+    <mergeCell ref="O16:Q16"/>
+    <mergeCell ref="L17:N17"/>
+    <mergeCell ref="O17:Q17"/>
+    <mergeCell ref="O18:Q18"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="A20:B20"/>
+    <mergeCell ref="C20:D20"/>
+    <mergeCell ref="E20:F20"/>
+    <mergeCell ref="G20:I20"/>
+    <mergeCell ref="J20:K20"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="E15:F15"/>
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="G2:J4"/>
+    <mergeCell ref="A5:F5"/>
+    <mergeCell ref="G5:T5"/>
+    <mergeCell ref="A6:F6"/>
+    <mergeCell ref="G6:T6"/>
+    <mergeCell ref="A7:F7"/>
+    <mergeCell ref="G7:T7"/>
+    <mergeCell ref="K2:N4"/>
+    <mergeCell ref="O2:P4"/>
+    <mergeCell ref="Q2:R4"/>
+    <mergeCell ref="S2:T4"/>
+    <mergeCell ref="A1:F4"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="O1:P1"/>
+    <mergeCell ref="Q1:R1"/>
+    <mergeCell ref="S1:T1"/>
+    <mergeCell ref="L30:N30"/>
+    <mergeCell ref="L31:N31"/>
+    <mergeCell ref="L18:N18"/>
+    <mergeCell ref="L19:N19"/>
+    <mergeCell ref="L21:N21"/>
+    <mergeCell ref="L22:N22"/>
+    <mergeCell ref="L23:N23"/>
+    <mergeCell ref="L24:N24"/>
+    <mergeCell ref="L25:N25"/>
+    <mergeCell ref="L20:N20"/>
+    <mergeCell ref="G28:I28"/>
+    <mergeCell ref="J28:K28"/>
+    <mergeCell ref="G29:I29"/>
+    <mergeCell ref="J29:K29"/>
+    <mergeCell ref="L26:N26"/>
+    <mergeCell ref="L27:N27"/>
+    <mergeCell ref="L28:N28"/>
+    <mergeCell ref="L29:N29"/>
+    <mergeCell ref="G25:I25"/>
+    <mergeCell ref="J25:K25"/>
+    <mergeCell ref="J26:K26"/>
+    <mergeCell ref="G30:I30"/>
+    <mergeCell ref="J30:K30"/>
+    <mergeCell ref="G31:I31"/>
+    <mergeCell ref="J31:K31"/>
+    <mergeCell ref="G26:I26"/>
+    <mergeCell ref="G27:I27"/>
+    <mergeCell ref="J27:K27"/>
+    <mergeCell ref="G22:I22"/>
+    <mergeCell ref="J22:K22"/>
+    <mergeCell ref="G23:I23"/>
+    <mergeCell ref="J23:K23"/>
+    <mergeCell ref="G24:I24"/>
+    <mergeCell ref="J24:K24"/>
+    <mergeCell ref="J18:K18"/>
+    <mergeCell ref="G18:I18"/>
+    <mergeCell ref="G19:I19"/>
+    <mergeCell ref="J19:K19"/>
+    <mergeCell ref="G21:I21"/>
+    <mergeCell ref="J21:K21"/>
+    <mergeCell ref="G15:I15"/>
+    <mergeCell ref="J15:K15"/>
+    <mergeCell ref="G16:I16"/>
+    <mergeCell ref="J16:K16"/>
+    <mergeCell ref="G17:I17"/>
+    <mergeCell ref="J17:K17"/>
+  </mergeCells>
+  <phoneticPr fontId="3"/>
+  <hyperlinks>
+    <hyperlink ref="L18" r:id="rId1" xr:uid="{9277DA13-9E2D-44D7-BE3D-3D83610CC568}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
+  <pageSetup paperSize="9" orientation="landscape"/>
+</worksheet>
 </file>
--- a/Documents/ログアウト機能設計書.xlsx
+++ b/Documents/ログアウト機能設計書.xlsx
@@ -8,19 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\S-47\Documents\project\taskUN\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2EC200B-D8C4-4E04-ACF6-6FFCFAAB0D5C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64BD065B-A1F4-405C-8E8E-1A6739912A92}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="2" xr2:uid="{72C6CFC4-7293-42D0-8B35-05AE043D8312}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{72C6CFC4-7293-42D0-8B35-05AE043D8312}"/>
   </bookViews>
   <sheets>
     <sheet name="ユースケース記述" sheetId="3" r:id="rId1"/>
     <sheet name="画面設計書" sheetId="2" r:id="rId2"/>
     <sheet name="テスト仕様書兼結果報告書" sheetId="4" r:id="rId3"/>
   </sheets>
-  <externalReferences>
-    <externalReference r:id="rId4"/>
-    <externalReference r:id="rId5"/>
-  </externalReferences>
   <definedNames>
     <definedName name="あ">#REF!</definedName>
     <definedName name="範囲１">#REF!</definedName>
@@ -202,30 +198,6 @@
     <t>ログアウト画面からログアウトする</t>
     <rPh sb="5" eb="7">
       <t>ガメン</t>
-    </rPh>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t>ログインしていること</t>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t>①ユーザー：ログアウト画面で「はい」ボタンを押下する
-②システム：ログアウト処理をし、ログイン画面に遷移する</t>
-    <rPh sb="11" eb="13">
-      <t>ガメン</t>
-    </rPh>
-    <rPh sb="22" eb="24">
-      <t>オウカ</t>
-    </rPh>
-    <rPh sb="38" eb="40">
-      <t>ショリ</t>
-    </rPh>
-    <rPh sb="47" eb="49">
-      <t>ガメン</t>
-    </rPh>
-    <rPh sb="50" eb="52">
-      <t>センイ</t>
     </rPh>
     <phoneticPr fontId="3"/>
   </si>
@@ -456,6 +428,46 @@
   </si>
   <si>
     <t>〇</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>①ユーザー：ログアウト画面で「はい」ボタンを押下する
+②システム：セッションを破棄しログアウト処理を完了させる
+③システム：ログイン画面へ遷移する</t>
+    <rPh sb="11" eb="13">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="22" eb="24">
+      <t>オウカ</t>
+    </rPh>
+    <rPh sb="39" eb="41">
+      <t>ハキ</t>
+    </rPh>
+    <rPh sb="47" eb="49">
+      <t>ショリ</t>
+    </rPh>
+    <rPh sb="50" eb="52">
+      <t>カンリョウ</t>
+    </rPh>
+    <rPh sb="66" eb="68">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="69" eb="71">
+      <t>センイ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>ログイン状態でログアウト画面を表示していること</t>
+    <rPh sb="4" eb="6">
+      <t>ジョウタイ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>ヒョウジ</t>
+    </rPh>
     <phoneticPr fontId="3"/>
   </si>
 </sst>
@@ -1228,6 +1240,75 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="56" fontId="5" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1321,6 +1402,21 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="255"/>
     </xf>
@@ -1336,21 +1432,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1387,12 +1468,60 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="27" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="24" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="25" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="17" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="56" fontId="2" fillId="0" borderId="12" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1405,182 +1534,65 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="19" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="24" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="25" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="17" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="56" fontId="2" fillId="0" borderId="12" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="27" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="56" fontId="2" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="27" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="56" fontId="2" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="56" fontId="5" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -1946,48 +1958,6 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="テスト仕様書兼報告書"/>
-      <sheetName val="サンプル"/>
-      <sheetName val="テストケースに記載する要素"/>
-      <sheetName val="テスト用語"/>
-      <sheetName val="テスト観点一覧"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1"/>
-      <sheetData sheetId="1" refreshError="1"/>
-      <sheetData sheetId="2" refreshError="1"/>
-      <sheetData sheetId="3" refreshError="1"/>
-      <sheetData sheetId="4" refreshError="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink2.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="JUnitテスト仕様書兼報告書"/>
-      <sheetName val="別紙"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1"/>
-      <sheetData sheetId="1" refreshError="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office テーマ">
   <a:themeElements>
@@ -2295,19 +2265,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="19" t="s">
+      <c r="A1" s="42" t="s">
         <v>30</v>
       </c>
-      <c r="B1" s="20"/>
-      <c r="C1" s="21"/>
-      <c r="D1" s="28" t="s">
+      <c r="B1" s="43"/>
+      <c r="C1" s="44"/>
+      <c r="D1" s="51" t="s">
         <v>0</v>
       </c>
-      <c r="E1" s="29"/>
-      <c r="F1" s="28" t="s">
+      <c r="E1" s="52"/>
+      <c r="F1" s="51" t="s">
         <v>1</v>
       </c>
-      <c r="G1" s="29"/>
+      <c r="G1" s="52"/>
       <c r="H1" s="11" t="s">
         <v>2</v>
       </c>
@@ -2319,192 +2289,192 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="22"/>
-      <c r="B2" s="23"/>
-      <c r="C2" s="24"/>
-      <c r="D2" s="30" t="s">
+      <c r="A2" s="45"/>
+      <c r="B2" s="46"/>
+      <c r="C2" s="47"/>
+      <c r="D2" s="53" t="s">
         <v>6</v>
       </c>
-      <c r="E2" s="31"/>
-      <c r="F2" s="30" t="s">
+      <c r="E2" s="54"/>
+      <c r="F2" s="53" t="s">
         <v>7</v>
       </c>
-      <c r="G2" s="31"/>
-      <c r="H2" s="34">
+      <c r="G2" s="54"/>
+      <c r="H2" s="57">
         <v>45806</v>
       </c>
-      <c r="I2" s="37" t="s">
+      <c r="I2" s="60" t="s">
         <v>28</v>
       </c>
-      <c r="J2" s="38"/>
+      <c r="J2" s="61"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="22"/>
-      <c r="B3" s="23"/>
-      <c r="C3" s="24"/>
-      <c r="D3" s="32"/>
-      <c r="E3" s="24"/>
-      <c r="F3" s="32"/>
-      <c r="G3" s="24"/>
-      <c r="H3" s="35"/>
-      <c r="I3" s="35"/>
-      <c r="J3" s="39"/>
+      <c r="A3" s="45"/>
+      <c r="B3" s="46"/>
+      <c r="C3" s="47"/>
+      <c r="D3" s="55"/>
+      <c r="E3" s="47"/>
+      <c r="F3" s="55"/>
+      <c r="G3" s="47"/>
+      <c r="H3" s="58"/>
+      <c r="I3" s="58"/>
+      <c r="J3" s="62"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="25"/>
-      <c r="B4" s="26"/>
-      <c r="C4" s="27"/>
-      <c r="D4" s="33"/>
-      <c r="E4" s="27"/>
-      <c r="F4" s="33"/>
-      <c r="G4" s="27"/>
-      <c r="H4" s="36"/>
-      <c r="I4" s="36"/>
-      <c r="J4" s="40"/>
+      <c r="A4" s="48"/>
+      <c r="B4" s="49"/>
+      <c r="C4" s="50"/>
+      <c r="D4" s="56"/>
+      <c r="E4" s="50"/>
+      <c r="F4" s="56"/>
+      <c r="G4" s="50"/>
+      <c r="H4" s="59"/>
+      <c r="I4" s="59"/>
+      <c r="J4" s="63"/>
     </row>
     <row r="5" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A5" s="41" t="s">
+      <c r="A5" s="64" t="s">
         <v>31</v>
       </c>
-      <c r="B5" s="42"/>
-      <c r="C5" s="29"/>
-      <c r="D5" s="43" t="s">
+      <c r="B5" s="65"/>
+      <c r="C5" s="52"/>
+      <c r="D5" s="66" t="s">
         <v>41</v>
       </c>
-      <c r="E5" s="42"/>
-      <c r="F5" s="42"/>
-      <c r="G5" s="42"/>
-      <c r="H5" s="42"/>
-      <c r="I5" s="42"/>
-      <c r="J5" s="44"/>
+      <c r="E5" s="65"/>
+      <c r="F5" s="65"/>
+      <c r="G5" s="65"/>
+      <c r="H5" s="65"/>
+      <c r="I5" s="65"/>
+      <c r="J5" s="67"/>
     </row>
     <row r="6" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A6" s="14" t="s">
+      <c r="A6" s="37" t="s">
         <v>32</v>
       </c>
-      <c r="B6" s="15"/>
-      <c r="C6" s="16"/>
-      <c r="D6" s="17" t="s">
+      <c r="B6" s="38"/>
+      <c r="C6" s="39"/>
+      <c r="D6" s="40" t="s">
         <v>42</v>
       </c>
-      <c r="E6" s="15"/>
-      <c r="F6" s="15"/>
-      <c r="G6" s="15"/>
-      <c r="H6" s="15"/>
-      <c r="I6" s="15"/>
-      <c r="J6" s="18"/>
+      <c r="E6" s="38"/>
+      <c r="F6" s="38"/>
+      <c r="G6" s="38"/>
+      <c r="H6" s="38"/>
+      <c r="I6" s="38"/>
+      <c r="J6" s="41"/>
     </row>
     <row r="7" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A7" s="14" t="s">
+      <c r="A7" s="37" t="s">
         <v>33</v>
       </c>
-      <c r="B7" s="15"/>
-      <c r="C7" s="16"/>
-      <c r="D7" s="17" t="s">
+      <c r="B7" s="38"/>
+      <c r="C7" s="39"/>
+      <c r="D7" s="40" t="s">
         <v>34</v>
       </c>
-      <c r="E7" s="15"/>
-      <c r="F7" s="15"/>
-      <c r="G7" s="15"/>
-      <c r="H7" s="15"/>
-      <c r="I7" s="15"/>
-      <c r="J7" s="18"/>
+      <c r="E7" s="38"/>
+      <c r="F7" s="38"/>
+      <c r="G7" s="38"/>
+      <c r="H7" s="38"/>
+      <c r="I7" s="38"/>
+      <c r="J7" s="41"/>
     </row>
     <row r="8" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A8" s="14" t="s">
+      <c r="A8" s="37" t="s">
         <v>35</v>
       </c>
-      <c r="B8" s="15"/>
-      <c r="C8" s="16"/>
-      <c r="D8" s="17" t="s">
-        <v>43</v>
-      </c>
-      <c r="E8" s="15"/>
-      <c r="F8" s="15"/>
-      <c r="G8" s="15"/>
-      <c r="H8" s="15"/>
-      <c r="I8" s="15"/>
-      <c r="J8" s="18"/>
+      <c r="B8" s="38"/>
+      <c r="C8" s="39"/>
+      <c r="D8" s="40" t="s">
+        <v>85</v>
+      </c>
+      <c r="E8" s="38"/>
+      <c r="F8" s="38"/>
+      <c r="G8" s="38"/>
+      <c r="H8" s="38"/>
+      <c r="I8" s="38"/>
+      <c r="J8" s="41"/>
     </row>
     <row r="9" spans="1:10" ht="64.5" customHeight="1">
-      <c r="A9" s="45" t="s">
+      <c r="A9" s="73" t="s">
         <v>36</v>
       </c>
-      <c r="B9" s="48" t="s">
+      <c r="B9" s="76" t="s">
         <v>37</v>
       </c>
-      <c r="C9" s="16"/>
-      <c r="D9" s="49" t="s">
-        <v>44</v>
-      </c>
-      <c r="E9" s="15"/>
-      <c r="F9" s="15"/>
-      <c r="G9" s="15"/>
-      <c r="H9" s="15"/>
-      <c r="I9" s="15"/>
-      <c r="J9" s="18"/>
+      <c r="C9" s="39"/>
+      <c r="D9" s="77" t="s">
+        <v>84</v>
+      </c>
+      <c r="E9" s="38"/>
+      <c r="F9" s="38"/>
+      <c r="G9" s="38"/>
+      <c r="H9" s="38"/>
+      <c r="I9" s="38"/>
+      <c r="J9" s="41"/>
     </row>
     <row r="10" spans="1:10" ht="64.5" customHeight="1">
-      <c r="A10" s="46"/>
-      <c r="B10" s="48" t="s">
+      <c r="A10" s="74"/>
+      <c r="B10" s="76" t="s">
         <v>38</v>
       </c>
-      <c r="C10" s="16"/>
-      <c r="D10" s="49" t="s">
-        <v>45</v>
-      </c>
-      <c r="E10" s="15"/>
-      <c r="F10" s="15"/>
-      <c r="G10" s="15"/>
-      <c r="H10" s="15"/>
-      <c r="I10" s="15"/>
-      <c r="J10" s="18"/>
+      <c r="C10" s="39"/>
+      <c r="D10" s="77" t="s">
+        <v>43</v>
+      </c>
+      <c r="E10" s="38"/>
+      <c r="F10" s="38"/>
+      <c r="G10" s="38"/>
+      <c r="H10" s="38"/>
+      <c r="I10" s="38"/>
+      <c r="J10" s="41"/>
     </row>
     <row r="11" spans="1:10" ht="64.5" customHeight="1">
-      <c r="A11" s="47"/>
-      <c r="B11" s="48" t="s">
+      <c r="A11" s="75"/>
+      <c r="B11" s="76" t="s">
         <v>39</v>
       </c>
-      <c r="C11" s="16"/>
-      <c r="D11" s="49" t="s">
-        <v>46</v>
-      </c>
-      <c r="E11" s="15"/>
-      <c r="F11" s="15"/>
-      <c r="G11" s="15"/>
-      <c r="H11" s="15"/>
-      <c r="I11" s="15"/>
-      <c r="J11" s="18"/>
+      <c r="C11" s="39"/>
+      <c r="D11" s="77" t="s">
+        <v>44</v>
+      </c>
+      <c r="E11" s="38"/>
+      <c r="F11" s="38"/>
+      <c r="G11" s="38"/>
+      <c r="H11" s="38"/>
+      <c r="I11" s="38"/>
+      <c r="J11" s="41"/>
     </row>
     <row r="12" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A12" s="14" t="s">
+      <c r="A12" s="37" t="s">
         <v>40</v>
       </c>
-      <c r="B12" s="15"/>
-      <c r="C12" s="16"/>
-      <c r="D12" s="17" t="s">
-        <v>47</v>
-      </c>
-      <c r="E12" s="15"/>
-      <c r="F12" s="15"/>
-      <c r="G12" s="15"/>
-      <c r="H12" s="15"/>
-      <c r="I12" s="15"/>
-      <c r="J12" s="18"/>
+      <c r="B12" s="38"/>
+      <c r="C12" s="39"/>
+      <c r="D12" s="40" t="s">
+        <v>45</v>
+      </c>
+      <c r="E12" s="38"/>
+      <c r="F12" s="38"/>
+      <c r="G12" s="38"/>
+      <c r="H12" s="38"/>
+      <c r="I12" s="38"/>
+      <c r="J12" s="41"/>
     </row>
     <row r="13" spans="1:10" ht="26.25" customHeight="1" thickBot="1">
-      <c r="A13" s="50" t="s">
+      <c r="A13" s="68" t="s">
         <v>18</v>
       </c>
-      <c r="B13" s="51"/>
-      <c r="C13" s="52"/>
-      <c r="D13" s="53"/>
-      <c r="E13" s="51"/>
-      <c r="F13" s="51"/>
-      <c r="G13" s="51"/>
-      <c r="H13" s="51"/>
-      <c r="I13" s="51"/>
-      <c r="J13" s="54"/>
+      <c r="B13" s="69"/>
+      <c r="C13" s="70"/>
+      <c r="D13" s="71"/>
+      <c r="E13" s="69"/>
+      <c r="F13" s="69"/>
+      <c r="G13" s="69"/>
+      <c r="H13" s="69"/>
+      <c r="I13" s="69"/>
+      <c r="J13" s="72"/>
     </row>
     <row r="14" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="15" spans="1:10" ht="12.75" customHeight="1"/>
@@ -3544,19 +3514,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="82" t="s">
+      <c r="A1" s="96" t="s">
         <v>5</v>
       </c>
-      <c r="B1" s="83"/>
-      <c r="C1" s="84"/>
-      <c r="D1" s="86" t="s">
+      <c r="B1" s="97"/>
+      <c r="C1" s="98"/>
+      <c r="D1" s="100" t="s">
         <v>0</v>
       </c>
-      <c r="E1" s="73"/>
-      <c r="F1" s="86" t="s">
+      <c r="E1" s="101"/>
+      <c r="F1" s="100" t="s">
         <v>1</v>
       </c>
-      <c r="G1" s="73"/>
+      <c r="G1" s="101"/>
       <c r="H1" s="1" t="s">
         <v>2</v>
       </c>
@@ -3568,190 +3538,190 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="79"/>
-      <c r="B2" s="80"/>
-      <c r="C2" s="85"/>
-      <c r="D2" s="87" t="s">
+      <c r="A2" s="93"/>
+      <c r="B2" s="94"/>
+      <c r="C2" s="99"/>
+      <c r="D2" s="102" t="s">
         <v>6</v>
       </c>
-      <c r="E2" s="88"/>
-      <c r="F2" s="87" t="s">
+      <c r="E2" s="103"/>
+      <c r="F2" s="102" t="s">
         <v>7</v>
       </c>
-      <c r="G2" s="88"/>
-      <c r="H2" s="90">
+      <c r="G2" s="103"/>
+      <c r="H2" s="105">
         <v>45806</v>
       </c>
-      <c r="I2" s="67" t="s">
+      <c r="I2" s="107" t="s">
         <v>28</v>
       </c>
-      <c r="J2" s="69"/>
+      <c r="J2" s="108"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="79"/>
-      <c r="B3" s="80"/>
-      <c r="C3" s="85"/>
-      <c r="D3" s="89"/>
-      <c r="E3" s="85"/>
-      <c r="F3" s="89"/>
-      <c r="G3" s="85"/>
-      <c r="H3" s="68"/>
-      <c r="I3" s="68"/>
-      <c r="J3" s="70"/>
+      <c r="A3" s="93"/>
+      <c r="B3" s="94"/>
+      <c r="C3" s="99"/>
+      <c r="D3" s="104"/>
+      <c r="E3" s="99"/>
+      <c r="F3" s="104"/>
+      <c r="G3" s="99"/>
+      <c r="H3" s="106"/>
+      <c r="I3" s="106"/>
+      <c r="J3" s="109"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="79"/>
-      <c r="B4" s="80"/>
-      <c r="C4" s="85"/>
-      <c r="D4" s="89"/>
-      <c r="E4" s="85"/>
-      <c r="F4" s="89"/>
-      <c r="G4" s="85"/>
-      <c r="H4" s="68"/>
-      <c r="I4" s="68"/>
-      <c r="J4" s="70"/>
+      <c r="A4" s="93"/>
+      <c r="B4" s="94"/>
+      <c r="C4" s="99"/>
+      <c r="D4" s="104"/>
+      <c r="E4" s="99"/>
+      <c r="F4" s="104"/>
+      <c r="G4" s="99"/>
+      <c r="H4" s="106"/>
+      <c r="I4" s="106"/>
+      <c r="J4" s="109"/>
     </row>
     <row r="5" spans="1:10" ht="28.5" customHeight="1">
-      <c r="A5" s="71" t="s">
+      <c r="A5" s="110" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="72"/>
-      <c r="C5" s="73"/>
-      <c r="D5" s="74" t="s">
+      <c r="B5" s="111"/>
+      <c r="C5" s="101"/>
+      <c r="D5" s="112" t="s">
         <v>19</v>
       </c>
-      <c r="E5" s="72"/>
-      <c r="F5" s="72"/>
-      <c r="G5" s="72"/>
-      <c r="H5" s="72"/>
-      <c r="I5" s="72"/>
-      <c r="J5" s="75"/>
+      <c r="E5" s="111"/>
+      <c r="F5" s="111"/>
+      <c r="G5" s="111"/>
+      <c r="H5" s="111"/>
+      <c r="I5" s="111"/>
+      <c r="J5" s="113"/>
     </row>
     <row r="6" spans="1:10" ht="21" customHeight="1">
-      <c r="A6" s="65" t="s">
+      <c r="A6" s="88" t="s">
         <v>9</v>
       </c>
-      <c r="B6" s="56"/>
-      <c r="C6" s="56"/>
-      <c r="D6" s="56"/>
-      <c r="E6" s="56"/>
-      <c r="F6" s="56"/>
-      <c r="G6" s="56"/>
-      <c r="H6" s="56"/>
-      <c r="I6" s="56"/>
-      <c r="J6" s="59"/>
+      <c r="B6" s="79"/>
+      <c r="C6" s="79"/>
+      <c r="D6" s="79"/>
+      <c r="E6" s="79"/>
+      <c r="F6" s="79"/>
+      <c r="G6" s="79"/>
+      <c r="H6" s="79"/>
+      <c r="I6" s="79"/>
+      <c r="J6" s="82"/>
     </row>
     <row r="7" spans="1:10" ht="21" customHeight="1">
-      <c r="A7" s="76"/>
-      <c r="B7" s="77"/>
-      <c r="C7" s="77"/>
-      <c r="D7" s="77"/>
-      <c r="E7" s="77"/>
-      <c r="F7" s="77"/>
-      <c r="G7" s="77"/>
-      <c r="H7" s="77"/>
-      <c r="I7" s="77"/>
-      <c r="J7" s="78"/>
+      <c r="A7" s="90"/>
+      <c r="B7" s="91"/>
+      <c r="C7" s="91"/>
+      <c r="D7" s="91"/>
+      <c r="E7" s="91"/>
+      <c r="F7" s="91"/>
+      <c r="G7" s="91"/>
+      <c r="H7" s="91"/>
+      <c r="I7" s="91"/>
+      <c r="J7" s="92"/>
     </row>
     <row r="8" spans="1:10" ht="21" customHeight="1">
-      <c r="A8" s="79"/>
-      <c r="B8" s="80"/>
-      <c r="C8" s="80"/>
-      <c r="D8" s="80"/>
-      <c r="E8" s="80"/>
-      <c r="F8" s="80"/>
-      <c r="G8" s="80"/>
-      <c r="H8" s="80"/>
-      <c r="I8" s="80"/>
-      <c r="J8" s="81"/>
+      <c r="A8" s="93"/>
+      <c r="B8" s="94"/>
+      <c r="C8" s="94"/>
+      <c r="D8" s="94"/>
+      <c r="E8" s="94"/>
+      <c r="F8" s="94"/>
+      <c r="G8" s="94"/>
+      <c r="H8" s="94"/>
+      <c r="I8" s="94"/>
+      <c r="J8" s="95"/>
     </row>
     <row r="9" spans="1:10" ht="21" customHeight="1">
-      <c r="A9" s="79"/>
-      <c r="B9" s="80"/>
-      <c r="C9" s="80"/>
-      <c r="D9" s="80"/>
-      <c r="E9" s="80"/>
-      <c r="F9" s="80"/>
-      <c r="G9" s="80"/>
-      <c r="H9" s="80"/>
-      <c r="I9" s="80"/>
-      <c r="J9" s="81"/>
+      <c r="A9" s="93"/>
+      <c r="B9" s="94"/>
+      <c r="C9" s="94"/>
+      <c r="D9" s="94"/>
+      <c r="E9" s="94"/>
+      <c r="F9" s="94"/>
+      <c r="G9" s="94"/>
+      <c r="H9" s="94"/>
+      <c r="I9" s="94"/>
+      <c r="J9" s="95"/>
     </row>
     <row r="10" spans="1:10" ht="21" customHeight="1">
-      <c r="A10" s="79"/>
-      <c r="B10" s="80"/>
-      <c r="C10" s="80"/>
-      <c r="D10" s="80"/>
-      <c r="E10" s="80"/>
-      <c r="F10" s="80"/>
-      <c r="G10" s="80"/>
-      <c r="H10" s="80"/>
-      <c r="I10" s="80"/>
-      <c r="J10" s="81"/>
+      <c r="A10" s="93"/>
+      <c r="B10" s="94"/>
+      <c r="C10" s="94"/>
+      <c r="D10" s="94"/>
+      <c r="E10" s="94"/>
+      <c r="F10" s="94"/>
+      <c r="G10" s="94"/>
+      <c r="H10" s="94"/>
+      <c r="I10" s="94"/>
+      <c r="J10" s="95"/>
     </row>
     <row r="11" spans="1:10" ht="21" customHeight="1">
-      <c r="A11" s="79"/>
-      <c r="B11" s="80"/>
-      <c r="C11" s="80"/>
-      <c r="D11" s="80"/>
-      <c r="E11" s="80"/>
-      <c r="F11" s="80"/>
-      <c r="G11" s="80"/>
-      <c r="H11" s="80"/>
-      <c r="I11" s="80"/>
-      <c r="J11" s="81"/>
+      <c r="A11" s="93"/>
+      <c r="B11" s="94"/>
+      <c r="C11" s="94"/>
+      <c r="D11" s="94"/>
+      <c r="E11" s="94"/>
+      <c r="F11" s="94"/>
+      <c r="G11" s="94"/>
+      <c r="H11" s="94"/>
+      <c r="I11" s="94"/>
+      <c r="J11" s="95"/>
     </row>
     <row r="12" spans="1:10" ht="21" customHeight="1">
-      <c r="A12" s="79"/>
-      <c r="B12" s="80"/>
-      <c r="C12" s="80"/>
-      <c r="D12" s="80"/>
-      <c r="E12" s="80"/>
-      <c r="F12" s="80"/>
-      <c r="G12" s="80"/>
-      <c r="H12" s="80"/>
-      <c r="I12" s="80"/>
-      <c r="J12" s="81"/>
+      <c r="A12" s="93"/>
+      <c r="B12" s="94"/>
+      <c r="C12" s="94"/>
+      <c r="D12" s="94"/>
+      <c r="E12" s="94"/>
+      <c r="F12" s="94"/>
+      <c r="G12" s="94"/>
+      <c r="H12" s="94"/>
+      <c r="I12" s="94"/>
+      <c r="J12" s="95"/>
     </row>
     <row r="13" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A13" s="79"/>
-      <c r="B13" s="80"/>
-      <c r="C13" s="80"/>
-      <c r="D13" s="80"/>
-      <c r="E13" s="80"/>
-      <c r="F13" s="80"/>
-      <c r="G13" s="80"/>
-      <c r="H13" s="80"/>
-      <c r="I13" s="80"/>
-      <c r="J13" s="81"/>
+      <c r="A13" s="93"/>
+      <c r="B13" s="94"/>
+      <c r="C13" s="94"/>
+      <c r="D13" s="94"/>
+      <c r="E13" s="94"/>
+      <c r="F13" s="94"/>
+      <c r="G13" s="94"/>
+      <c r="H13" s="94"/>
+      <c r="I13" s="94"/>
+      <c r="J13" s="95"/>
     </row>
     <row r="14" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A14" s="65" t="s">
+      <c r="A14" s="88" t="s">
         <v>10</v>
       </c>
-      <c r="B14" s="56"/>
-      <c r="C14" s="56"/>
-      <c r="D14" s="56"/>
-      <c r="E14" s="56"/>
-      <c r="F14" s="56"/>
-      <c r="G14" s="56"/>
-      <c r="H14" s="56"/>
-      <c r="I14" s="56"/>
-      <c r="J14" s="59"/>
+      <c r="B14" s="79"/>
+      <c r="C14" s="79"/>
+      <c r="D14" s="79"/>
+      <c r="E14" s="79"/>
+      <c r="F14" s="79"/>
+      <c r="G14" s="79"/>
+      <c r="H14" s="79"/>
+      <c r="I14" s="79"/>
+      <c r="J14" s="82"/>
     </row>
     <row r="15" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A15" s="65" t="s">
+      <c r="A15" s="88" t="s">
         <v>11</v>
       </c>
-      <c r="B15" s="56"/>
-      <c r="C15" s="57"/>
-      <c r="D15" s="58" t="s">
+      <c r="B15" s="79"/>
+      <c r="C15" s="80"/>
+      <c r="D15" s="81" t="s">
         <v>26</v>
       </c>
-      <c r="E15" s="56"/>
-      <c r="F15" s="56"/>
-      <c r="G15" s="56"/>
-      <c r="H15" s="57"/>
+      <c r="E15" s="79"/>
+      <c r="F15" s="79"/>
+      <c r="G15" s="79"/>
+      <c r="H15" s="80"/>
       <c r="I15" s="5" t="s">
         <v>12</v>
       </c>
@@ -3760,11 +3730,11 @@
       </c>
     </row>
     <row r="16" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A16" s="65" t="s">
+      <c r="A16" s="88" t="s">
         <v>13</v>
       </c>
-      <c r="B16" s="56"/>
-      <c r="C16" s="57"/>
+      <c r="B16" s="79"/>
+      <c r="C16" s="80"/>
       <c r="D16" s="5" t="s">
         <v>14</v>
       </c>
@@ -3777,18 +3747,18 @@
       <c r="G16" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="H16" s="66" t="s">
+      <c r="H16" s="89" t="s">
         <v>18</v>
       </c>
-      <c r="I16" s="56"/>
-      <c r="J16" s="59"/>
+      <c r="I16" s="79"/>
+      <c r="J16" s="82"/>
     </row>
     <row r="17" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A17" s="55">
+      <c r="A17" s="78">
         <v>1</v>
       </c>
-      <c r="B17" s="56"/>
-      <c r="C17" s="57"/>
+      <c r="B17" s="79"/>
+      <c r="C17" s="80"/>
       <c r="D17" s="7" t="s">
         <v>21</v>
       </c>
@@ -3801,16 +3771,16 @@
       <c r="G17" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="H17" s="58"/>
-      <c r="I17" s="56"/>
-      <c r="J17" s="59"/>
+      <c r="H17" s="81"/>
+      <c r="I17" s="79"/>
+      <c r="J17" s="82"/>
     </row>
     <row r="18" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A18" s="55">
+      <c r="A18" s="78">
         <v>2</v>
       </c>
-      <c r="B18" s="56"/>
-      <c r="C18" s="57"/>
+      <c r="B18" s="79"/>
+      <c r="C18" s="80"/>
       <c r="D18" s="7" t="s">
         <v>22</v>
       </c>
@@ -3821,71 +3791,71 @@
       <c r="G18" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="H18" s="58" t="s">
+      <c r="H18" s="81" t="s">
         <v>27</v>
       </c>
-      <c r="I18" s="56"/>
-      <c r="J18" s="59"/>
+      <c r="I18" s="79"/>
+      <c r="J18" s="82"/>
     </row>
     <row r="19" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A19" s="55"/>
-      <c r="B19" s="56"/>
-      <c r="C19" s="57"/>
+      <c r="A19" s="78"/>
+      <c r="B19" s="79"/>
+      <c r="C19" s="80"/>
       <c r="D19" s="7"/>
       <c r="E19" s="7"/>
       <c r="F19" s="8"/>
       <c r="G19" s="8"/>
-      <c r="H19" s="58"/>
-      <c r="I19" s="56"/>
-      <c r="J19" s="59"/>
+      <c r="H19" s="81"/>
+      <c r="I19" s="79"/>
+      <c r="J19" s="82"/>
     </row>
     <row r="20" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A20" s="55"/>
-      <c r="B20" s="56"/>
-      <c r="C20" s="57"/>
+      <c r="A20" s="78"/>
+      <c r="B20" s="79"/>
+      <c r="C20" s="80"/>
       <c r="D20" s="7"/>
       <c r="E20" s="7"/>
       <c r="F20" s="8"/>
       <c r="G20" s="8"/>
-      <c r="H20" s="58"/>
-      <c r="I20" s="56"/>
-      <c r="J20" s="59"/>
+      <c r="H20" s="81"/>
+      <c r="I20" s="79"/>
+      <c r="J20" s="82"/>
     </row>
     <row r="21" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A21" s="55"/>
-      <c r="B21" s="56"/>
-      <c r="C21" s="57"/>
+      <c r="A21" s="78"/>
+      <c r="B21" s="79"/>
+      <c r="C21" s="80"/>
       <c r="D21" s="7"/>
       <c r="E21" s="7"/>
       <c r="F21" s="8"/>
       <c r="G21" s="8"/>
-      <c r="H21" s="58"/>
-      <c r="I21" s="56"/>
-      <c r="J21" s="59"/>
+      <c r="H21" s="81"/>
+      <c r="I21" s="79"/>
+      <c r="J21" s="82"/>
     </row>
     <row r="22" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A22" s="55"/>
-      <c r="B22" s="56"/>
-      <c r="C22" s="57"/>
+      <c r="A22" s="78"/>
+      <c r="B22" s="79"/>
+      <c r="C22" s="80"/>
       <c r="D22" s="7"/>
       <c r="E22" s="7"/>
       <c r="F22" s="8"/>
       <c r="G22" s="8"/>
-      <c r="H22" s="58"/>
-      <c r="I22" s="56"/>
-      <c r="J22" s="59"/>
+      <c r="H22" s="81"/>
+      <c r="I22" s="79"/>
+      <c r="J22" s="82"/>
     </row>
     <row r="23" spans="1:10" ht="19.5" customHeight="1" thickBot="1">
-      <c r="A23" s="60"/>
-      <c r="B23" s="61"/>
-      <c r="C23" s="62"/>
+      <c r="A23" s="83"/>
+      <c r="B23" s="84"/>
+      <c r="C23" s="85"/>
       <c r="D23" s="9"/>
       <c r="E23" s="9"/>
       <c r="F23" s="10"/>
       <c r="G23" s="10"/>
-      <c r="H23" s="63"/>
-      <c r="I23" s="61"/>
-      <c r="J23" s="64"/>
+      <c r="H23" s="86"/>
+      <c r="I23" s="84"/>
+      <c r="J23" s="87"/>
     </row>
     <row r="24" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="25" spans="1:10" ht="12.75" customHeight="1"/>
@@ -4920,954 +4890,954 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="18" customHeight="1">
-      <c r="A1" s="19" t="s">
-        <v>70</v>
-      </c>
-      <c r="B1" s="20"/>
-      <c r="C1" s="20"/>
-      <c r="D1" s="20"/>
-      <c r="E1" s="20"/>
-      <c r="F1" s="21"/>
-      <c r="G1" s="28" t="s">
+      <c r="A1" s="42" t="s">
+        <v>68</v>
+      </c>
+      <c r="B1" s="43"/>
+      <c r="C1" s="43"/>
+      <c r="D1" s="43"/>
+      <c r="E1" s="43"/>
+      <c r="F1" s="44"/>
+      <c r="G1" s="51" t="s">
         <v>0</v>
       </c>
-      <c r="H1" s="42"/>
-      <c r="I1" s="42"/>
-      <c r="J1" s="29"/>
-      <c r="K1" s="28" t="s">
+      <c r="H1" s="65"/>
+      <c r="I1" s="65"/>
+      <c r="J1" s="52"/>
+      <c r="K1" s="51" t="s">
         <v>1</v>
       </c>
-      <c r="L1" s="42"/>
-      <c r="M1" s="42"/>
-      <c r="N1" s="29"/>
-      <c r="O1" s="28" t="s">
+      <c r="L1" s="65"/>
+      <c r="M1" s="65"/>
+      <c r="N1" s="52"/>
+      <c r="O1" s="51" t="s">
         <v>2</v>
       </c>
-      <c r="P1" s="29"/>
-      <c r="Q1" s="28" t="s">
+      <c r="P1" s="52"/>
+      <c r="Q1" s="51" t="s">
         <v>3</v>
       </c>
-      <c r="R1" s="29"/>
-      <c r="S1" s="28" t="s">
+      <c r="R1" s="52"/>
+      <c r="S1" s="51" t="s">
         <v>4</v>
       </c>
-      <c r="T1" s="44"/>
+      <c r="T1" s="67"/>
     </row>
     <row r="2" spans="1:26" ht="18" customHeight="1">
-      <c r="A2" s="22"/>
-      <c r="B2" s="23"/>
-      <c r="C2" s="23"/>
-      <c r="D2" s="23"/>
-      <c r="E2" s="23"/>
-      <c r="F2" s="24"/>
-      <c r="G2" s="30" t="s">
+      <c r="A2" s="45"/>
+      <c r="B2" s="46"/>
+      <c r="C2" s="46"/>
+      <c r="D2" s="46"/>
+      <c r="E2" s="46"/>
+      <c r="F2" s="47"/>
+      <c r="G2" s="53" t="s">
         <v>6</v>
       </c>
-      <c r="H2" s="128"/>
-      <c r="I2" s="128"/>
-      <c r="J2" s="31"/>
-      <c r="K2" s="30" t="s">
+      <c r="H2" s="119"/>
+      <c r="I2" s="119"/>
+      <c r="J2" s="54"/>
+      <c r="K2" s="53" t="s">
         <v>7</v>
       </c>
-      <c r="L2" s="128"/>
-      <c r="M2" s="128"/>
-      <c r="N2" s="31"/>
-      <c r="O2" s="130">
+      <c r="L2" s="119"/>
+      <c r="M2" s="119"/>
+      <c r="N2" s="54"/>
+      <c r="O2" s="122">
         <v>45810</v>
       </c>
-      <c r="P2" s="31"/>
-      <c r="Q2" s="30" t="s">
+      <c r="P2" s="54"/>
+      <c r="Q2" s="53" t="s">
         <v>28</v>
       </c>
-      <c r="R2" s="31"/>
-      <c r="S2" s="30"/>
-      <c r="T2" s="127"/>
+      <c r="R2" s="54"/>
+      <c r="S2" s="53"/>
+      <c r="T2" s="123"/>
     </row>
     <row r="3" spans="1:26" ht="18" customHeight="1">
-      <c r="A3" s="22"/>
-      <c r="B3" s="23"/>
-      <c r="C3" s="23"/>
-      <c r="D3" s="23"/>
-      <c r="E3" s="23"/>
-      <c r="F3" s="24"/>
-      <c r="G3" s="32"/>
-      <c r="H3" s="23"/>
-      <c r="I3" s="23"/>
-      <c r="J3" s="24"/>
-      <c r="K3" s="32"/>
-      <c r="L3" s="23"/>
-      <c r="M3" s="23"/>
-      <c r="N3" s="24"/>
-      <c r="O3" s="32"/>
-      <c r="P3" s="24"/>
-      <c r="Q3" s="32"/>
-      <c r="R3" s="24"/>
-      <c r="S3" s="32"/>
-      <c r="T3" s="126"/>
+      <c r="A3" s="45"/>
+      <c r="B3" s="46"/>
+      <c r="C3" s="46"/>
+      <c r="D3" s="46"/>
+      <c r="E3" s="46"/>
+      <c r="F3" s="47"/>
+      <c r="G3" s="55"/>
+      <c r="H3" s="46"/>
+      <c r="I3" s="46"/>
+      <c r="J3" s="47"/>
+      <c r="K3" s="55"/>
+      <c r="L3" s="46"/>
+      <c r="M3" s="46"/>
+      <c r="N3" s="47"/>
+      <c r="O3" s="55"/>
+      <c r="P3" s="47"/>
+      <c r="Q3" s="55"/>
+      <c r="R3" s="47"/>
+      <c r="S3" s="55"/>
+      <c r="T3" s="124"/>
     </row>
     <row r="4" spans="1:26" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="25"/>
-      <c r="B4" s="26"/>
-      <c r="C4" s="26"/>
-      <c r="D4" s="26"/>
-      <c r="E4" s="26"/>
-      <c r="F4" s="27"/>
-      <c r="G4" s="33"/>
-      <c r="H4" s="26"/>
-      <c r="I4" s="26"/>
-      <c r="J4" s="27"/>
-      <c r="K4" s="33"/>
-      <c r="L4" s="26"/>
-      <c r="M4" s="26"/>
-      <c r="N4" s="27"/>
-      <c r="O4" s="33"/>
-      <c r="P4" s="27"/>
-      <c r="Q4" s="33"/>
-      <c r="R4" s="27"/>
-      <c r="S4" s="33"/>
+      <c r="A4" s="48"/>
+      <c r="B4" s="49"/>
+      <c r="C4" s="49"/>
+      <c r="D4" s="49"/>
+      <c r="E4" s="49"/>
+      <c r="F4" s="50"/>
+      <c r="G4" s="56"/>
+      <c r="H4" s="49"/>
+      <c r="I4" s="49"/>
+      <c r="J4" s="50"/>
+      <c r="K4" s="56"/>
+      <c r="L4" s="49"/>
+      <c r="M4" s="49"/>
+      <c r="N4" s="50"/>
+      <c r="O4" s="56"/>
+      <c r="P4" s="50"/>
+      <c r="Q4" s="56"/>
+      <c r="R4" s="50"/>
+      <c r="S4" s="56"/>
       <c r="T4" s="125"/>
     </row>
     <row r="5" spans="1:26" ht="18" customHeight="1">
-      <c r="A5" s="124" t="s">
-        <v>69</v>
-      </c>
-      <c r="B5" s="42"/>
-      <c r="C5" s="42"/>
-      <c r="D5" s="42"/>
-      <c r="E5" s="42"/>
-      <c r="F5" s="29"/>
-      <c r="G5" s="43" t="s">
-        <v>68</v>
-      </c>
-      <c r="H5" s="42"/>
-      <c r="I5" s="42"/>
-      <c r="J5" s="42"/>
-      <c r="K5" s="42"/>
-      <c r="L5" s="42"/>
-      <c r="M5" s="42"/>
-      <c r="N5" s="42"/>
-      <c r="O5" s="42"/>
-      <c r="P5" s="42"/>
-      <c r="Q5" s="42"/>
-      <c r="R5" s="42"/>
-      <c r="S5" s="42"/>
-      <c r="T5" s="44"/>
+      <c r="A5" s="120" t="s">
+        <v>67</v>
+      </c>
+      <c r="B5" s="65"/>
+      <c r="C5" s="65"/>
+      <c r="D5" s="65"/>
+      <c r="E5" s="65"/>
+      <c r="F5" s="52"/>
+      <c r="G5" s="66" t="s">
+        <v>66</v>
+      </c>
+      <c r="H5" s="65"/>
+      <c r="I5" s="65"/>
+      <c r="J5" s="65"/>
+      <c r="K5" s="65"/>
+      <c r="L5" s="65"/>
+      <c r="M5" s="65"/>
+      <c r="N5" s="65"/>
+      <c r="O5" s="65"/>
+      <c r="P5" s="65"/>
+      <c r="Q5" s="65"/>
+      <c r="R5" s="65"/>
+      <c r="S5" s="65"/>
+      <c r="T5" s="67"/>
     </row>
     <row r="6" spans="1:26" ht="18" customHeight="1">
-      <c r="A6" s="109" t="s">
-        <v>67</v>
-      </c>
-      <c r="B6" s="15"/>
-      <c r="C6" s="15"/>
-      <c r="D6" s="15"/>
-      <c r="E6" s="15"/>
-      <c r="F6" s="16"/>
-      <c r="G6" s="17" t="s">
-        <v>83</v>
-      </c>
-      <c r="H6" s="15"/>
-      <c r="I6" s="15"/>
-      <c r="J6" s="15"/>
-      <c r="K6" s="15"/>
-      <c r="L6" s="15"/>
-      <c r="M6" s="15"/>
-      <c r="N6" s="15"/>
-      <c r="O6" s="15"/>
-      <c r="P6" s="15"/>
-      <c r="Q6" s="15"/>
-      <c r="R6" s="15"/>
-      <c r="S6" s="15"/>
-      <c r="T6" s="18"/>
+      <c r="A6" s="121" t="s">
+        <v>65</v>
+      </c>
+      <c r="B6" s="38"/>
+      <c r="C6" s="38"/>
+      <c r="D6" s="38"/>
+      <c r="E6" s="38"/>
+      <c r="F6" s="39"/>
+      <c r="G6" s="40" t="s">
+        <v>81</v>
+      </c>
+      <c r="H6" s="38"/>
+      <c r="I6" s="38"/>
+      <c r="J6" s="38"/>
+      <c r="K6" s="38"/>
+      <c r="L6" s="38"/>
+      <c r="M6" s="38"/>
+      <c r="N6" s="38"/>
+      <c r="O6" s="38"/>
+      <c r="P6" s="38"/>
+      <c r="Q6" s="38"/>
+      <c r="R6" s="38"/>
+      <c r="S6" s="38"/>
+      <c r="T6" s="41"/>
     </row>
     <row r="7" spans="1:26" ht="18" customHeight="1">
-      <c r="A7" s="109" t="s">
-        <v>66</v>
-      </c>
-      <c r="B7" s="15"/>
-      <c r="C7" s="15"/>
-      <c r="D7" s="15"/>
-      <c r="E7" s="15"/>
-      <c r="F7" s="16"/>
-      <c r="G7" s="17" t="s">
-        <v>82</v>
-      </c>
-      <c r="H7" s="15"/>
-      <c r="I7" s="15"/>
-      <c r="J7" s="15"/>
-      <c r="K7" s="15"/>
-      <c r="L7" s="15"/>
-      <c r="M7" s="15"/>
-      <c r="N7" s="15"/>
-      <c r="O7" s="15"/>
-      <c r="P7" s="15"/>
-      <c r="Q7" s="15"/>
-      <c r="R7" s="15"/>
-      <c r="S7" s="15"/>
-      <c r="T7" s="18"/>
+      <c r="A7" s="121" t="s">
+        <v>64</v>
+      </c>
+      <c r="B7" s="38"/>
+      <c r="C7" s="38"/>
+      <c r="D7" s="38"/>
+      <c r="E7" s="38"/>
+      <c r="F7" s="39"/>
+      <c r="G7" s="40" t="s">
+        <v>80</v>
+      </c>
+      <c r="H7" s="38"/>
+      <c r="I7" s="38"/>
+      <c r="J7" s="38"/>
+      <c r="K7" s="38"/>
+      <c r="L7" s="38"/>
+      <c r="M7" s="38"/>
+      <c r="N7" s="38"/>
+      <c r="O7" s="38"/>
+      <c r="P7" s="38"/>
+      <c r="Q7" s="38"/>
+      <c r="R7" s="38"/>
+      <c r="S7" s="38"/>
+      <c r="T7" s="41"/>
     </row>
     <row r="8" spans="1:26" ht="7.5" customHeight="1">
-      <c r="A8" s="112"/>
-      <c r="B8" s="111"/>
-      <c r="C8" s="111"/>
-      <c r="D8" s="111"/>
-      <c r="E8" s="111"/>
-      <c r="F8" s="111"/>
-      <c r="G8" s="111"/>
-      <c r="H8" s="111"/>
-      <c r="I8" s="111"/>
-      <c r="J8" s="111"/>
-      <c r="K8" s="111"/>
-      <c r="L8" s="111"/>
-      <c r="M8" s="111"/>
-      <c r="N8" s="111"/>
-      <c r="O8" s="111"/>
-      <c r="P8" s="111"/>
-      <c r="Q8" s="111"/>
-      <c r="R8" s="111"/>
-      <c r="S8" s="111"/>
-      <c r="T8" s="110"/>
+      <c r="A8" s="24"/>
+      <c r="B8" s="23"/>
+      <c r="C8" s="23"/>
+      <c r="D8" s="23"/>
+      <c r="E8" s="23"/>
+      <c r="F8" s="23"/>
+      <c r="G8" s="23"/>
+      <c r="H8" s="23"/>
+      <c r="I8" s="23"/>
+      <c r="J8" s="23"/>
+      <c r="K8" s="23"/>
+      <c r="L8" s="23"/>
+      <c r="M8" s="23"/>
+      <c r="N8" s="23"/>
+      <c r="O8" s="23"/>
+      <c r="P8" s="23"/>
+      <c r="Q8" s="23"/>
+      <c r="R8" s="23"/>
+      <c r="S8" s="23"/>
+      <c r="T8" s="22"/>
     </row>
     <row r="9" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A9" s="118"/>
-      <c r="B9" s="113"/>
-      <c r="C9" s="123" t="s">
-        <v>59</v>
-      </c>
-      <c r="D9" s="122"/>
-      <c r="E9" s="122" t="s">
-        <v>65</v>
-      </c>
-      <c r="F9" s="122"/>
-      <c r="G9" s="121"/>
-      <c r="H9" s="122"/>
-      <c r="I9" s="122"/>
-      <c r="J9" s="122"/>
-      <c r="K9" s="121"/>
-      <c r="L9" s="113"/>
-      <c r="M9" s="113"/>
-      <c r="N9" s="113"/>
-      <c r="O9" s="113"/>
-      <c r="P9" s="113"/>
-      <c r="Q9" s="113"/>
-      <c r="R9" s="113"/>
-      <c r="S9" s="113"/>
-      <c r="T9" s="114"/>
-      <c r="U9" s="113"/>
-      <c r="V9" s="113"/>
-      <c r="W9" s="113"/>
-      <c r="X9" s="113"/>
-      <c r="Y9" s="113"/>
-      <c r="Z9" s="113"/>
+      <c r="A9" s="30"/>
+      <c r="B9" s="25"/>
+      <c r="C9" s="35" t="s">
+        <v>57</v>
+      </c>
+      <c r="D9" s="34"/>
+      <c r="E9" s="34" t="s">
+        <v>63</v>
+      </c>
+      <c r="F9" s="34"/>
+      <c r="G9" s="33"/>
+      <c r="H9" s="34"/>
+      <c r="I9" s="34"/>
+      <c r="J9" s="34"/>
+      <c r="K9" s="33"/>
+      <c r="L9" s="25"/>
+      <c r="M9" s="25"/>
+      <c r="N9" s="25"/>
+      <c r="O9" s="25"/>
+      <c r="P9" s="25"/>
+      <c r="Q9" s="25"/>
+      <c r="R9" s="25"/>
+      <c r="S9" s="25"/>
+      <c r="T9" s="26"/>
+      <c r="U9" s="25"/>
+      <c r="V9" s="25"/>
+      <c r="W9" s="25"/>
+      <c r="X9" s="25"/>
+      <c r="Y9" s="25"/>
+      <c r="Z9" s="25"/>
     </row>
     <row r="10" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A10" s="118"/>
-      <c r="B10" s="113"/>
-      <c r="C10" s="120"/>
-      <c r="D10" s="113"/>
-      <c r="E10" s="113" t="s">
-        <v>64</v>
-      </c>
-      <c r="F10" s="113"/>
-      <c r="G10" s="119"/>
-      <c r="H10" s="113"/>
-      <c r="I10" s="113"/>
-      <c r="J10" s="113"/>
-      <c r="K10" s="119"/>
-      <c r="L10" s="113"/>
-      <c r="M10" s="113"/>
-      <c r="N10" s="113"/>
-      <c r="O10" s="113"/>
-      <c r="P10" s="113"/>
-      <c r="Q10" s="113"/>
-      <c r="R10" s="113"/>
-      <c r="S10" s="113"/>
-      <c r="T10" s="114"/>
-      <c r="U10" s="113"/>
-      <c r="V10" s="113"/>
-      <c r="W10" s="113"/>
-      <c r="X10" s="113"/>
-      <c r="Y10" s="113"/>
-      <c r="Z10" s="113"/>
+      <c r="A10" s="30"/>
+      <c r="B10" s="25"/>
+      <c r="C10" s="32"/>
+      <c r="D10" s="25"/>
+      <c r="E10" s="25" t="s">
+        <v>62</v>
+      </c>
+      <c r="F10" s="25"/>
+      <c r="G10" s="31"/>
+      <c r="H10" s="25"/>
+      <c r="I10" s="25"/>
+      <c r="J10" s="25"/>
+      <c r="K10" s="31"/>
+      <c r="L10" s="25"/>
+      <c r="M10" s="25"/>
+      <c r="N10" s="25"/>
+      <c r="O10" s="25"/>
+      <c r="P10" s="25"/>
+      <c r="Q10" s="25"/>
+      <c r="R10" s="25"/>
+      <c r="S10" s="25"/>
+      <c r="T10" s="26"/>
+      <c r="U10" s="25"/>
+      <c r="V10" s="25"/>
+      <c r="W10" s="25"/>
+      <c r="X10" s="25"/>
+      <c r="Y10" s="25"/>
+      <c r="Z10" s="25"/>
     </row>
     <row r="11" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A11" s="118"/>
-      <c r="B11" s="113"/>
-      <c r="C11" s="120"/>
-      <c r="D11" s="113"/>
-      <c r="E11" s="113" t="s">
-        <v>63</v>
-      </c>
-      <c r="F11" s="113"/>
-      <c r="G11" s="119"/>
-      <c r="H11" s="113"/>
-      <c r="I11" s="113"/>
-      <c r="J11" s="113"/>
-      <c r="K11" s="119"/>
-      <c r="L11" s="113"/>
-      <c r="M11" s="113"/>
-      <c r="N11" s="113"/>
-      <c r="O11" s="113"/>
-      <c r="P11" s="113"/>
-      <c r="Q11" s="113"/>
-      <c r="R11" s="113"/>
-      <c r="S11" s="113"/>
-      <c r="T11" s="114"/>
-      <c r="U11" s="113"/>
-      <c r="V11" s="113"/>
-      <c r="W11" s="113"/>
-      <c r="X11" s="113"/>
-      <c r="Y11" s="113"/>
-      <c r="Z11" s="113"/>
+      <c r="A11" s="30"/>
+      <c r="B11" s="25"/>
+      <c r="C11" s="32"/>
+      <c r="D11" s="25"/>
+      <c r="E11" s="25" t="s">
+        <v>61</v>
+      </c>
+      <c r="F11" s="25"/>
+      <c r="G11" s="31"/>
+      <c r="H11" s="25"/>
+      <c r="I11" s="25"/>
+      <c r="J11" s="25"/>
+      <c r="K11" s="31"/>
+      <c r="L11" s="25"/>
+      <c r="M11" s="25"/>
+      <c r="N11" s="25"/>
+      <c r="O11" s="25"/>
+      <c r="P11" s="25"/>
+      <c r="Q11" s="25"/>
+      <c r="R11" s="25"/>
+      <c r="S11" s="25"/>
+      <c r="T11" s="26"/>
+      <c r="U11" s="25"/>
+      <c r="V11" s="25"/>
+      <c r="W11" s="25"/>
+      <c r="X11" s="25"/>
+      <c r="Y11" s="25"/>
+      <c r="Z11" s="25"/>
     </row>
     <row r="12" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A12" s="118"/>
-      <c r="B12" s="113"/>
-      <c r="C12" s="120"/>
-      <c r="D12" s="113"/>
-      <c r="E12" s="113" t="s">
-        <v>62</v>
-      </c>
-      <c r="F12" s="113"/>
-      <c r="G12" s="119"/>
-      <c r="H12" s="113"/>
-      <c r="I12" s="113"/>
-      <c r="J12" s="113"/>
-      <c r="K12" s="119"/>
-      <c r="L12" s="113"/>
-      <c r="M12" s="113"/>
-      <c r="N12" s="113"/>
-      <c r="O12" s="113"/>
-      <c r="P12" s="113"/>
-      <c r="Q12" s="113"/>
-      <c r="R12" s="113"/>
-      <c r="S12" s="113"/>
-      <c r="T12" s="114"/>
-      <c r="U12" s="113"/>
-      <c r="V12" s="113"/>
-      <c r="W12" s="113"/>
-      <c r="X12" s="113"/>
-      <c r="Y12" s="113"/>
-      <c r="Z12" s="113"/>
+      <c r="A12" s="30"/>
+      <c r="B12" s="25"/>
+      <c r="C12" s="32"/>
+      <c r="D12" s="25"/>
+      <c r="E12" s="25" t="s">
+        <v>60</v>
+      </c>
+      <c r="F12" s="25"/>
+      <c r="G12" s="31"/>
+      <c r="H12" s="25"/>
+      <c r="I12" s="25"/>
+      <c r="J12" s="25"/>
+      <c r="K12" s="31"/>
+      <c r="L12" s="25"/>
+      <c r="M12" s="25"/>
+      <c r="N12" s="25"/>
+      <c r="O12" s="25"/>
+      <c r="P12" s="25"/>
+      <c r="Q12" s="25"/>
+      <c r="R12" s="25"/>
+      <c r="S12" s="25"/>
+      <c r="T12" s="26"/>
+      <c r="U12" s="25"/>
+      <c r="V12" s="25"/>
+      <c r="W12" s="25"/>
+      <c r="X12" s="25"/>
+      <c r="Y12" s="25"/>
+      <c r="Z12" s="25"/>
     </row>
     <row r="13" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A13" s="118"/>
-      <c r="B13" s="113"/>
-      <c r="C13" s="117"/>
-      <c r="D13" s="116"/>
-      <c r="E13" s="116" t="s">
-        <v>61</v>
-      </c>
-      <c r="F13" s="116"/>
-      <c r="G13" s="115"/>
-      <c r="H13" s="116"/>
-      <c r="I13" s="116"/>
-      <c r="J13" s="116"/>
-      <c r="K13" s="115"/>
-      <c r="L13" s="113"/>
-      <c r="M13" s="113"/>
-      <c r="N13" s="113"/>
-      <c r="O13" s="113"/>
-      <c r="P13" s="113"/>
-      <c r="Q13" s="113"/>
-      <c r="R13" s="113"/>
-      <c r="S13" s="113"/>
-      <c r="T13" s="114"/>
-      <c r="U13" s="113"/>
-      <c r="V13" s="113"/>
-      <c r="W13" s="113"/>
-      <c r="X13" s="113"/>
-      <c r="Y13" s="113"/>
-      <c r="Z13" s="113"/>
+      <c r="A13" s="30"/>
+      <c r="B13" s="25"/>
+      <c r="C13" s="29"/>
+      <c r="D13" s="28"/>
+      <c r="E13" s="28" t="s">
+        <v>59</v>
+      </c>
+      <c r="F13" s="28"/>
+      <c r="G13" s="27"/>
+      <c r="H13" s="28"/>
+      <c r="I13" s="28"/>
+      <c r="J13" s="28"/>
+      <c r="K13" s="27"/>
+      <c r="L13" s="25"/>
+      <c r="M13" s="25"/>
+      <c r="N13" s="25"/>
+      <c r="O13" s="25"/>
+      <c r="P13" s="25"/>
+      <c r="Q13" s="25"/>
+      <c r="R13" s="25"/>
+      <c r="S13" s="25"/>
+      <c r="T13" s="26"/>
+      <c r="U13" s="25"/>
+      <c r="V13" s="25"/>
+      <c r="W13" s="25"/>
+      <c r="X13" s="25"/>
+      <c r="Y13" s="25"/>
+      <c r="Z13" s="25"/>
     </row>
     <row r="14" spans="1:26" ht="8.25" customHeight="1">
-      <c r="A14" s="112"/>
-      <c r="B14" s="111"/>
-      <c r="C14" s="111"/>
-      <c r="D14" s="111"/>
-      <c r="E14" s="111"/>
-      <c r="F14" s="111"/>
-      <c r="G14" s="111"/>
-      <c r="H14" s="111"/>
-      <c r="I14" s="111"/>
-      <c r="J14" s="111"/>
-      <c r="K14" s="111"/>
-      <c r="L14" s="111"/>
-      <c r="M14" s="111"/>
-      <c r="N14" s="111"/>
-      <c r="O14" s="111"/>
-      <c r="P14" s="111"/>
-      <c r="Q14" s="111"/>
-      <c r="R14" s="111"/>
-      <c r="S14" s="111"/>
-      <c r="T14" s="110"/>
+      <c r="A14" s="24"/>
+      <c r="B14" s="23"/>
+      <c r="C14" s="23"/>
+      <c r="D14" s="23"/>
+      <c r="E14" s="23"/>
+      <c r="F14" s="23"/>
+      <c r="G14" s="23"/>
+      <c r="H14" s="23"/>
+      <c r="I14" s="23"/>
+      <c r="J14" s="23"/>
+      <c r="K14" s="23"/>
+      <c r="L14" s="23"/>
+      <c r="M14" s="23"/>
+      <c r="N14" s="23"/>
+      <c r="O14" s="23"/>
+      <c r="P14" s="23"/>
+      <c r="Q14" s="23"/>
+      <c r="R14" s="23"/>
+      <c r="S14" s="23"/>
+      <c r="T14" s="22"/>
     </row>
     <row r="15" spans="1:26" ht="18.75" customHeight="1">
-      <c r="A15" s="109" t="s">
-        <v>60</v>
-      </c>
-      <c r="B15" s="16"/>
-      <c r="C15" s="108" t="s">
-        <v>59</v>
-      </c>
-      <c r="D15" s="16"/>
-      <c r="E15" s="107" t="s">
+      <c r="A15" s="121" t="s">
         <v>58</v>
       </c>
-      <c r="F15" s="16"/>
-      <c r="G15" s="107" t="s">
+      <c r="B15" s="39"/>
+      <c r="C15" s="129" t="s">
         <v>57</v>
       </c>
-      <c r="H15" s="15"/>
-      <c r="I15" s="16"/>
-      <c r="J15" s="107" t="s">
+      <c r="D15" s="39"/>
+      <c r="E15" s="126" t="s">
         <v>56</v>
       </c>
-      <c r="K15" s="16"/>
-      <c r="L15" s="107" t="s">
+      <c r="F15" s="39"/>
+      <c r="G15" s="126" t="s">
         <v>55</v>
       </c>
-      <c r="M15" s="15"/>
-      <c r="N15" s="16"/>
-      <c r="O15" s="107" t="s">
+      <c r="H15" s="38"/>
+      <c r="I15" s="39"/>
+      <c r="J15" s="126" t="s">
         <v>54</v>
       </c>
-      <c r="P15" s="15"/>
-      <c r="Q15" s="16"/>
-      <c r="R15" s="106" t="s">
+      <c r="K15" s="39"/>
+      <c r="L15" s="126" t="s">
         <v>53</v>
       </c>
-      <c r="S15" s="106" t="s">
+      <c r="M15" s="38"/>
+      <c r="N15" s="39"/>
+      <c r="O15" s="126" t="s">
         <v>52</v>
       </c>
-      <c r="T15" s="105" t="s">
+      <c r="P15" s="38"/>
+      <c r="Q15" s="39"/>
+      <c r="R15" s="21" t="s">
         <v>51</v>
+      </c>
+      <c r="S15" s="21" t="s">
+        <v>50</v>
+      </c>
+      <c r="T15" s="20" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="16" spans="1:26" ht="48" customHeight="1">
-      <c r="A16" s="104">
+      <c r="A16" s="127">
         <v>1</v>
       </c>
-      <c r="B16" s="16"/>
-      <c r="C16" s="103" t="s">
-        <v>50</v>
-      </c>
-      <c r="D16" s="16"/>
-      <c r="E16" s="103" t="s">
-        <v>49</v>
-      </c>
-      <c r="F16" s="16"/>
-      <c r="G16" s="102" t="s">
-        <v>72</v>
-      </c>
-      <c r="H16" s="15"/>
-      <c r="I16" s="16"/>
-      <c r="J16" s="102" t="s">
+      <c r="B16" s="39"/>
+      <c r="C16" s="128" t="s">
+        <v>48</v>
+      </c>
+      <c r="D16" s="39"/>
+      <c r="E16" s="128" t="s">
+        <v>47</v>
+      </c>
+      <c r="F16" s="39"/>
+      <c r="G16" s="114" t="s">
+        <v>70</v>
+      </c>
+      <c r="H16" s="38"/>
+      <c r="I16" s="39"/>
+      <c r="J16" s="114" t="s">
+        <v>69</v>
+      </c>
+      <c r="K16" s="39"/>
+      <c r="L16" s="116" t="s">
         <v>71</v>
       </c>
-      <c r="K16" s="16"/>
-      <c r="L16" s="101" t="s">
-        <v>73</v>
-      </c>
-      <c r="M16" s="15"/>
-      <c r="N16" s="16"/>
-      <c r="O16" s="101" t="s">
-        <v>48</v>
-      </c>
-      <c r="P16" s="15"/>
-      <c r="Q16" s="16"/>
-      <c r="R16" s="131">
+      <c r="M16" s="38"/>
+      <c r="N16" s="39"/>
+      <c r="O16" s="116" t="s">
+        <v>46</v>
+      </c>
+      <c r="P16" s="38"/>
+      <c r="Q16" s="39"/>
+      <c r="R16" s="36">
         <v>45810</v>
       </c>
-      <c r="S16" s="100" t="s">
+      <c r="S16" s="19" t="s">
         <v>28</v>
       </c>
-      <c r="T16" s="99" t="s">
-        <v>85</v>
-      </c>
-      <c r="U16" s="92"/>
-      <c r="V16" s="92"/>
-      <c r="W16" s="92"/>
-      <c r="X16" s="92"/>
-      <c r="Y16" s="92"/>
-      <c r="Z16" s="92"/>
+      <c r="T16" s="18" t="s">
+        <v>83</v>
+      </c>
+      <c r="U16" s="15"/>
+      <c r="V16" s="15"/>
+      <c r="W16" s="15"/>
+      <c r="X16" s="15"/>
+      <c r="Y16" s="15"/>
+      <c r="Z16" s="15"/>
     </row>
     <row r="17" spans="1:26" ht="41.25" customHeight="1">
-      <c r="A17" s="104">
+      <c r="A17" s="127">
         <v>2</v>
       </c>
-      <c r="B17" s="16"/>
-      <c r="C17" s="103" t="s">
+      <c r="B17" s="39"/>
+      <c r="C17" s="128" t="s">
+        <v>72</v>
+      </c>
+      <c r="D17" s="39"/>
+      <c r="E17" s="128" t="s">
+        <v>47</v>
+      </c>
+      <c r="F17" s="39"/>
+      <c r="G17" s="114" t="s">
+        <v>73</v>
+      </c>
+      <c r="H17" s="38"/>
+      <c r="I17" s="39"/>
+      <c r="J17" s="114" t="s">
+        <v>69</v>
+      </c>
+      <c r="K17" s="39"/>
+      <c r="L17" s="116" t="s">
         <v>74</v>
       </c>
-      <c r="D17" s="16"/>
-      <c r="E17" s="103" t="s">
-        <v>49</v>
-      </c>
-      <c r="F17" s="16"/>
-      <c r="G17" s="102" t="s">
+      <c r="M17" s="38"/>
+      <c r="N17" s="39"/>
+      <c r="O17" s="116" t="s">
         <v>75</v>
       </c>
-      <c r="H17" s="15"/>
-      <c r="I17" s="16"/>
-      <c r="J17" s="102" t="s">
-        <v>71</v>
-      </c>
-      <c r="K17" s="16"/>
-      <c r="L17" s="101" t="s">
-        <v>76</v>
-      </c>
-      <c r="M17" s="15"/>
-      <c r="N17" s="16"/>
-      <c r="O17" s="101" t="s">
-        <v>77</v>
-      </c>
-      <c r="P17" s="15"/>
-      <c r="Q17" s="16"/>
-      <c r="R17" s="131">
+      <c r="P17" s="38"/>
+      <c r="Q17" s="39"/>
+      <c r="R17" s="36">
         <v>45810</v>
       </c>
-      <c r="S17" s="100" t="s">
+      <c r="S17" s="19" t="s">
         <v>28</v>
       </c>
-      <c r="T17" s="99" t="s">
-        <v>85</v>
-      </c>
-      <c r="U17" s="92"/>
-      <c r="V17" s="92"/>
-      <c r="W17" s="92"/>
-      <c r="X17" s="92"/>
-      <c r="Y17" s="92"/>
-      <c r="Z17" s="92"/>
+      <c r="T17" s="18" t="s">
+        <v>83</v>
+      </c>
+      <c r="U17" s="15"/>
+      <c r="V17" s="15"/>
+      <c r="W17" s="15"/>
+      <c r="X17" s="15"/>
+      <c r="Y17" s="15"/>
+      <c r="Z17" s="15"/>
     </row>
     <row r="18" spans="1:26" ht="57.75" customHeight="1">
-      <c r="A18" s="104">
+      <c r="A18" s="127">
         <v>3</v>
       </c>
-      <c r="B18" s="16"/>
-      <c r="C18" s="103" t="s">
-        <v>74</v>
-      </c>
-      <c r="D18" s="16"/>
-      <c r="E18" s="103" t="s">
+      <c r="B18" s="39"/>
+      <c r="C18" s="128" t="s">
+        <v>72</v>
+      </c>
+      <c r="D18" s="39"/>
+      <c r="E18" s="128" t="s">
+        <v>76</v>
+      </c>
+      <c r="F18" s="39"/>
+      <c r="G18" s="114" t="s">
+        <v>77</v>
+      </c>
+      <c r="H18" s="38"/>
+      <c r="I18" s="39"/>
+      <c r="J18" s="114" t="s">
         <v>78</v>
       </c>
-      <c r="F18" s="16"/>
-      <c r="G18" s="102" t="s">
+      <c r="K18" s="39"/>
+      <c r="L18" s="118" t="s">
+        <v>82</v>
+      </c>
+      <c r="M18" s="38"/>
+      <c r="N18" s="39"/>
+      <c r="O18" s="116" t="s">
         <v>79</v>
       </c>
-      <c r="H18" s="15"/>
-      <c r="I18" s="16"/>
-      <c r="J18" s="102" t="s">
-        <v>80</v>
-      </c>
-      <c r="K18" s="16"/>
-      <c r="L18" s="129" t="s">
-        <v>84</v>
-      </c>
-      <c r="M18" s="15"/>
-      <c r="N18" s="16"/>
-      <c r="O18" s="101" t="s">
-        <v>81</v>
-      </c>
-      <c r="P18" s="15"/>
-      <c r="Q18" s="16"/>
-      <c r="R18" s="131">
+      <c r="P18" s="38"/>
+      <c r="Q18" s="39"/>
+      <c r="R18" s="36">
         <v>45810</v>
       </c>
-      <c r="S18" s="100" t="s">
+      <c r="S18" s="19" t="s">
         <v>28</v>
       </c>
-      <c r="T18" s="99" t="s">
-        <v>85</v>
-      </c>
-      <c r="U18" s="92"/>
-      <c r="V18" s="92"/>
-      <c r="W18" s="92"/>
-      <c r="X18" s="92"/>
-      <c r="Y18" s="92"/>
-      <c r="Z18" s="92"/>
+      <c r="T18" s="18" t="s">
+        <v>83</v>
+      </c>
+      <c r="U18" s="15"/>
+      <c r="V18" s="15"/>
+      <c r="W18" s="15"/>
+      <c r="X18" s="15"/>
+      <c r="Y18" s="15"/>
+      <c r="Z18" s="15"/>
     </row>
     <row r="19" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A19" s="104"/>
-      <c r="B19" s="16"/>
-      <c r="C19" s="103"/>
-      <c r="D19" s="16"/>
-      <c r="E19" s="103"/>
-      <c r="F19" s="16"/>
-      <c r="G19" s="102"/>
-      <c r="H19" s="15"/>
-      <c r="I19" s="16"/>
-      <c r="J19" s="102"/>
-      <c r="K19" s="16"/>
-      <c r="L19" s="101"/>
-      <c r="M19" s="15"/>
-      <c r="N19" s="16"/>
-      <c r="O19" s="101"/>
-      <c r="P19" s="15"/>
-      <c r="Q19" s="16"/>
-      <c r="R19" s="100"/>
-      <c r="S19" s="100"/>
-      <c r="T19" s="99"/>
-      <c r="U19" s="92"/>
-      <c r="V19" s="92"/>
-      <c r="W19" s="92"/>
-      <c r="X19" s="92"/>
-      <c r="Y19" s="92"/>
-      <c r="Z19" s="92"/>
+      <c r="A19" s="127"/>
+      <c r="B19" s="39"/>
+      <c r="C19" s="128"/>
+      <c r="D19" s="39"/>
+      <c r="E19" s="128"/>
+      <c r="F19" s="39"/>
+      <c r="G19" s="114"/>
+      <c r="H19" s="38"/>
+      <c r="I19" s="39"/>
+      <c r="J19" s="114"/>
+      <c r="K19" s="39"/>
+      <c r="L19" s="116"/>
+      <c r="M19" s="38"/>
+      <c r="N19" s="39"/>
+      <c r="O19" s="116"/>
+      <c r="P19" s="38"/>
+      <c r="Q19" s="39"/>
+      <c r="R19" s="19"/>
+      <c r="S19" s="19"/>
+      <c r="T19" s="18"/>
+      <c r="U19" s="15"/>
+      <c r="V19" s="15"/>
+      <c r="W19" s="15"/>
+      <c r="X19" s="15"/>
+      <c r="Y19" s="15"/>
+      <c r="Z19" s="15"/>
     </row>
     <row r="20" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A20" s="104"/>
-      <c r="B20" s="16"/>
-      <c r="C20" s="103"/>
-      <c r="D20" s="16"/>
-      <c r="E20" s="103"/>
-      <c r="F20" s="16"/>
-      <c r="G20" s="102"/>
-      <c r="H20" s="15"/>
-      <c r="I20" s="16"/>
-      <c r="J20" s="102"/>
-      <c r="K20" s="16"/>
-      <c r="L20" s="101"/>
-      <c r="M20" s="15"/>
-      <c r="N20" s="16"/>
-      <c r="O20" s="101"/>
-      <c r="P20" s="15"/>
-      <c r="Q20" s="16"/>
-      <c r="R20" s="100"/>
-      <c r="S20" s="100"/>
-      <c r="T20" s="99"/>
-      <c r="U20" s="92"/>
-      <c r="V20" s="92"/>
-      <c r="W20" s="92"/>
-      <c r="X20" s="92"/>
-      <c r="Y20" s="92"/>
-      <c r="Z20" s="92"/>
+      <c r="A20" s="127"/>
+      <c r="B20" s="39"/>
+      <c r="C20" s="128"/>
+      <c r="D20" s="39"/>
+      <c r="E20" s="128"/>
+      <c r="F20" s="39"/>
+      <c r="G20" s="114"/>
+      <c r="H20" s="38"/>
+      <c r="I20" s="39"/>
+      <c r="J20" s="114"/>
+      <c r="K20" s="39"/>
+      <c r="L20" s="116"/>
+      <c r="M20" s="38"/>
+      <c r="N20" s="39"/>
+      <c r="O20" s="116"/>
+      <c r="P20" s="38"/>
+      <c r="Q20" s="39"/>
+      <c r="R20" s="19"/>
+      <c r="S20" s="19"/>
+      <c r="T20" s="18"/>
+      <c r="U20" s="15"/>
+      <c r="V20" s="15"/>
+      <c r="W20" s="15"/>
+      <c r="X20" s="15"/>
+      <c r="Y20" s="15"/>
+      <c r="Z20" s="15"/>
     </row>
     <row r="21" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A21" s="104"/>
-      <c r="B21" s="16"/>
-      <c r="C21" s="103"/>
-      <c r="D21" s="16"/>
-      <c r="E21" s="103"/>
-      <c r="F21" s="16"/>
-      <c r="G21" s="102"/>
-      <c r="H21" s="15"/>
-      <c r="I21" s="16"/>
-      <c r="J21" s="102"/>
-      <c r="K21" s="16"/>
-      <c r="L21" s="101"/>
-      <c r="M21" s="15"/>
-      <c r="N21" s="16"/>
-      <c r="O21" s="101"/>
-      <c r="P21" s="15"/>
-      <c r="Q21" s="16"/>
-      <c r="R21" s="100"/>
-      <c r="S21" s="100"/>
-      <c r="T21" s="99"/>
-      <c r="U21" s="92"/>
-      <c r="V21" s="92"/>
-      <c r="W21" s="92"/>
-      <c r="X21" s="92"/>
-      <c r="Y21" s="92"/>
-      <c r="Z21" s="92"/>
+      <c r="A21" s="127"/>
+      <c r="B21" s="39"/>
+      <c r="C21" s="128"/>
+      <c r="D21" s="39"/>
+      <c r="E21" s="128"/>
+      <c r="F21" s="39"/>
+      <c r="G21" s="114"/>
+      <c r="H21" s="38"/>
+      <c r="I21" s="39"/>
+      <c r="J21" s="114"/>
+      <c r="K21" s="39"/>
+      <c r="L21" s="116"/>
+      <c r="M21" s="38"/>
+      <c r="N21" s="39"/>
+      <c r="O21" s="116"/>
+      <c r="P21" s="38"/>
+      <c r="Q21" s="39"/>
+      <c r="R21" s="19"/>
+      <c r="S21" s="19"/>
+      <c r="T21" s="18"/>
+      <c r="U21" s="15"/>
+      <c r="V21" s="15"/>
+      <c r="W21" s="15"/>
+      <c r="X21" s="15"/>
+      <c r="Y21" s="15"/>
+      <c r="Z21" s="15"/>
     </row>
     <row r="22" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A22" s="104"/>
-      <c r="B22" s="16"/>
-      <c r="C22" s="103"/>
-      <c r="D22" s="16"/>
-      <c r="E22" s="103"/>
-      <c r="F22" s="16"/>
-      <c r="G22" s="102"/>
-      <c r="H22" s="15"/>
-      <c r="I22" s="16"/>
-      <c r="J22" s="102"/>
-      <c r="K22" s="16"/>
-      <c r="L22" s="101"/>
-      <c r="M22" s="15"/>
-      <c r="N22" s="16"/>
-      <c r="O22" s="101"/>
-      <c r="P22" s="15"/>
-      <c r="Q22" s="16"/>
-      <c r="R22" s="100"/>
-      <c r="S22" s="100"/>
-      <c r="T22" s="99"/>
-      <c r="U22" s="92"/>
-      <c r="V22" s="92"/>
-      <c r="W22" s="92"/>
-      <c r="X22" s="92"/>
-      <c r="Y22" s="92"/>
-      <c r="Z22" s="92"/>
+      <c r="A22" s="127"/>
+      <c r="B22" s="39"/>
+      <c r="C22" s="128"/>
+      <c r="D22" s="39"/>
+      <c r="E22" s="128"/>
+      <c r="F22" s="39"/>
+      <c r="G22" s="114"/>
+      <c r="H22" s="38"/>
+      <c r="I22" s="39"/>
+      <c r="J22" s="114"/>
+      <c r="K22" s="39"/>
+      <c r="L22" s="116"/>
+      <c r="M22" s="38"/>
+      <c r="N22" s="39"/>
+      <c r="O22" s="116"/>
+      <c r="P22" s="38"/>
+      <c r="Q22" s="39"/>
+      <c r="R22" s="19"/>
+      <c r="S22" s="19"/>
+      <c r="T22" s="18"/>
+      <c r="U22" s="15"/>
+      <c r="V22" s="15"/>
+      <c r="W22" s="15"/>
+      <c r="X22" s="15"/>
+      <c r="Y22" s="15"/>
+      <c r="Z22" s="15"/>
     </row>
     <row r="23" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A23" s="104"/>
-      <c r="B23" s="16"/>
-      <c r="C23" s="103"/>
-      <c r="D23" s="16"/>
-      <c r="E23" s="103"/>
-      <c r="F23" s="16"/>
-      <c r="G23" s="102"/>
-      <c r="H23" s="15"/>
-      <c r="I23" s="16"/>
-      <c r="J23" s="102"/>
-      <c r="K23" s="16"/>
-      <c r="L23" s="101"/>
-      <c r="M23" s="15"/>
-      <c r="N23" s="16"/>
-      <c r="O23" s="101"/>
-      <c r="P23" s="15"/>
-      <c r="Q23" s="16"/>
-      <c r="R23" s="100"/>
-      <c r="S23" s="100"/>
-      <c r="T23" s="99"/>
-      <c r="U23" s="92"/>
-      <c r="V23" s="92"/>
-      <c r="W23" s="92"/>
-      <c r="X23" s="92"/>
-      <c r="Y23" s="92"/>
-      <c r="Z23" s="92"/>
+      <c r="A23" s="127"/>
+      <c r="B23" s="39"/>
+      <c r="C23" s="128"/>
+      <c r="D23" s="39"/>
+      <c r="E23" s="128"/>
+      <c r="F23" s="39"/>
+      <c r="G23" s="114"/>
+      <c r="H23" s="38"/>
+      <c r="I23" s="39"/>
+      <c r="J23" s="114"/>
+      <c r="K23" s="39"/>
+      <c r="L23" s="116"/>
+      <c r="M23" s="38"/>
+      <c r="N23" s="39"/>
+      <c r="O23" s="116"/>
+      <c r="P23" s="38"/>
+      <c r="Q23" s="39"/>
+      <c r="R23" s="19"/>
+      <c r="S23" s="19"/>
+      <c r="T23" s="18"/>
+      <c r="U23" s="15"/>
+      <c r="V23" s="15"/>
+      <c r="W23" s="15"/>
+      <c r="X23" s="15"/>
+      <c r="Y23" s="15"/>
+      <c r="Z23" s="15"/>
     </row>
     <row r="24" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A24" s="104"/>
-      <c r="B24" s="16"/>
-      <c r="C24" s="103"/>
-      <c r="D24" s="16"/>
-      <c r="E24" s="103"/>
-      <c r="F24" s="16"/>
-      <c r="G24" s="102"/>
-      <c r="H24" s="15"/>
-      <c r="I24" s="16"/>
-      <c r="J24" s="102"/>
-      <c r="K24" s="16"/>
-      <c r="L24" s="101"/>
-      <c r="M24" s="15"/>
-      <c r="N24" s="16"/>
-      <c r="O24" s="101"/>
-      <c r="P24" s="15"/>
-      <c r="Q24" s="16"/>
-      <c r="R24" s="100"/>
-      <c r="S24" s="100"/>
-      <c r="T24" s="99"/>
-      <c r="U24" s="92"/>
-      <c r="V24" s="92"/>
-      <c r="W24" s="92"/>
-      <c r="X24" s="92"/>
-      <c r="Y24" s="92"/>
-      <c r="Z24" s="92"/>
+      <c r="A24" s="127"/>
+      <c r="B24" s="39"/>
+      <c r="C24" s="128"/>
+      <c r="D24" s="39"/>
+      <c r="E24" s="128"/>
+      <c r="F24" s="39"/>
+      <c r="G24" s="114"/>
+      <c r="H24" s="38"/>
+      <c r="I24" s="39"/>
+      <c r="J24" s="114"/>
+      <c r="K24" s="39"/>
+      <c r="L24" s="116"/>
+      <c r="M24" s="38"/>
+      <c r="N24" s="39"/>
+      <c r="O24" s="116"/>
+      <c r="P24" s="38"/>
+      <c r="Q24" s="39"/>
+      <c r="R24" s="19"/>
+      <c r="S24" s="19"/>
+      <c r="T24" s="18"/>
+      <c r="U24" s="15"/>
+      <c r="V24" s="15"/>
+      <c r="W24" s="15"/>
+      <c r="X24" s="15"/>
+      <c r="Y24" s="15"/>
+      <c r="Z24" s="15"/>
     </row>
     <row r="25" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A25" s="104"/>
-      <c r="B25" s="16"/>
-      <c r="C25" s="103"/>
-      <c r="D25" s="16"/>
-      <c r="E25" s="103"/>
-      <c r="F25" s="16"/>
-      <c r="G25" s="102"/>
-      <c r="H25" s="15"/>
-      <c r="I25" s="16"/>
-      <c r="J25" s="102"/>
-      <c r="K25" s="16"/>
-      <c r="L25" s="101"/>
-      <c r="M25" s="15"/>
-      <c r="N25" s="16"/>
-      <c r="O25" s="101"/>
-      <c r="P25" s="15"/>
-      <c r="Q25" s="16"/>
-      <c r="R25" s="100"/>
-      <c r="S25" s="100"/>
-      <c r="T25" s="99"/>
-      <c r="U25" s="92"/>
-      <c r="V25" s="92"/>
-      <c r="W25" s="92"/>
-      <c r="X25" s="92"/>
-      <c r="Y25" s="92"/>
-      <c r="Z25" s="92"/>
+      <c r="A25" s="127"/>
+      <c r="B25" s="39"/>
+      <c r="C25" s="128"/>
+      <c r="D25" s="39"/>
+      <c r="E25" s="128"/>
+      <c r="F25" s="39"/>
+      <c r="G25" s="114"/>
+      <c r="H25" s="38"/>
+      <c r="I25" s="39"/>
+      <c r="J25" s="114"/>
+      <c r="K25" s="39"/>
+      <c r="L25" s="116"/>
+      <c r="M25" s="38"/>
+      <c r="N25" s="39"/>
+      <c r="O25" s="116"/>
+      <c r="P25" s="38"/>
+      <c r="Q25" s="39"/>
+      <c r="R25" s="19"/>
+      <c r="S25" s="19"/>
+      <c r="T25" s="18"/>
+      <c r="U25" s="15"/>
+      <c r="V25" s="15"/>
+      <c r="W25" s="15"/>
+      <c r="X25" s="15"/>
+      <c r="Y25" s="15"/>
+      <c r="Z25" s="15"/>
     </row>
     <row r="26" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A26" s="104"/>
-      <c r="B26" s="16"/>
-      <c r="C26" s="103"/>
-      <c r="D26" s="16"/>
-      <c r="E26" s="103"/>
-      <c r="F26" s="16"/>
-      <c r="G26" s="102"/>
-      <c r="H26" s="15"/>
-      <c r="I26" s="16"/>
-      <c r="J26" s="102"/>
-      <c r="K26" s="16"/>
-      <c r="L26" s="101"/>
-      <c r="M26" s="15"/>
-      <c r="N26" s="16"/>
-      <c r="O26" s="101"/>
-      <c r="P26" s="15"/>
-      <c r="Q26" s="16"/>
-      <c r="R26" s="100"/>
-      <c r="S26" s="100"/>
-      <c r="T26" s="99"/>
-      <c r="U26" s="92"/>
-      <c r="V26" s="92"/>
-      <c r="W26" s="92"/>
-      <c r="X26" s="92"/>
-      <c r="Y26" s="92"/>
-      <c r="Z26" s="92"/>
+      <c r="A26" s="127"/>
+      <c r="B26" s="39"/>
+      <c r="C26" s="128"/>
+      <c r="D26" s="39"/>
+      <c r="E26" s="128"/>
+      <c r="F26" s="39"/>
+      <c r="G26" s="114"/>
+      <c r="H26" s="38"/>
+      <c r="I26" s="39"/>
+      <c r="J26" s="114"/>
+      <c r="K26" s="39"/>
+      <c r="L26" s="116"/>
+      <c r="M26" s="38"/>
+      <c r="N26" s="39"/>
+      <c r="O26" s="116"/>
+      <c r="P26" s="38"/>
+      <c r="Q26" s="39"/>
+      <c r="R26" s="19"/>
+      <c r="S26" s="19"/>
+      <c r="T26" s="18"/>
+      <c r="U26" s="15"/>
+      <c r="V26" s="15"/>
+      <c r="W26" s="15"/>
+      <c r="X26" s="15"/>
+      <c r="Y26" s="15"/>
+      <c r="Z26" s="15"/>
     </row>
     <row r="27" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A27" s="104"/>
-      <c r="B27" s="16"/>
-      <c r="C27" s="103"/>
-      <c r="D27" s="16"/>
-      <c r="E27" s="103"/>
-      <c r="F27" s="16"/>
-      <c r="G27" s="102"/>
-      <c r="H27" s="15"/>
-      <c r="I27" s="16"/>
-      <c r="J27" s="102"/>
-      <c r="K27" s="16"/>
-      <c r="L27" s="101"/>
-      <c r="M27" s="15"/>
-      <c r="N27" s="16"/>
-      <c r="O27" s="101"/>
-      <c r="P27" s="15"/>
-      <c r="Q27" s="16"/>
-      <c r="R27" s="100"/>
-      <c r="S27" s="100"/>
-      <c r="T27" s="99"/>
-      <c r="U27" s="92"/>
-      <c r="V27" s="92"/>
-      <c r="W27" s="92"/>
-      <c r="X27" s="92"/>
-      <c r="Y27" s="92"/>
-      <c r="Z27" s="92"/>
+      <c r="A27" s="127"/>
+      <c r="B27" s="39"/>
+      <c r="C27" s="128"/>
+      <c r="D27" s="39"/>
+      <c r="E27" s="128"/>
+      <c r="F27" s="39"/>
+      <c r="G27" s="114"/>
+      <c r="H27" s="38"/>
+      <c r="I27" s="39"/>
+      <c r="J27" s="114"/>
+      <c r="K27" s="39"/>
+      <c r="L27" s="116"/>
+      <c r="M27" s="38"/>
+      <c r="N27" s="39"/>
+      <c r="O27" s="116"/>
+      <c r="P27" s="38"/>
+      <c r="Q27" s="39"/>
+      <c r="R27" s="19"/>
+      <c r="S27" s="19"/>
+      <c r="T27" s="18"/>
+      <c r="U27" s="15"/>
+      <c r="V27" s="15"/>
+      <c r="W27" s="15"/>
+      <c r="X27" s="15"/>
+      <c r="Y27" s="15"/>
+      <c r="Z27" s="15"/>
     </row>
     <row r="28" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A28" s="104"/>
-      <c r="B28" s="16"/>
-      <c r="C28" s="103"/>
-      <c r="D28" s="16"/>
-      <c r="E28" s="103"/>
-      <c r="F28" s="16"/>
-      <c r="G28" s="102"/>
-      <c r="H28" s="15"/>
-      <c r="I28" s="16"/>
-      <c r="J28" s="102"/>
-      <c r="K28" s="16"/>
-      <c r="L28" s="101"/>
-      <c r="M28" s="15"/>
-      <c r="N28" s="16"/>
-      <c r="O28" s="101"/>
-      <c r="P28" s="15"/>
-      <c r="Q28" s="16"/>
-      <c r="R28" s="100"/>
-      <c r="S28" s="100"/>
-      <c r="T28" s="99"/>
-      <c r="U28" s="92"/>
-      <c r="V28" s="92"/>
-      <c r="W28" s="92"/>
-      <c r="X28" s="92"/>
-      <c r="Y28" s="92"/>
-      <c r="Z28" s="92"/>
+      <c r="A28" s="127"/>
+      <c r="B28" s="39"/>
+      <c r="C28" s="128"/>
+      <c r="D28" s="39"/>
+      <c r="E28" s="128"/>
+      <c r="F28" s="39"/>
+      <c r="G28" s="114"/>
+      <c r="H28" s="38"/>
+      <c r="I28" s="39"/>
+      <c r="J28" s="114"/>
+      <c r="K28" s="39"/>
+      <c r="L28" s="116"/>
+      <c r="M28" s="38"/>
+      <c r="N28" s="39"/>
+      <c r="O28" s="116"/>
+      <c r="P28" s="38"/>
+      <c r="Q28" s="39"/>
+      <c r="R28" s="19"/>
+      <c r="S28" s="19"/>
+      <c r="T28" s="18"/>
+      <c r="U28" s="15"/>
+      <c r="V28" s="15"/>
+      <c r="W28" s="15"/>
+      <c r="X28" s="15"/>
+      <c r="Y28" s="15"/>
+      <c r="Z28" s="15"/>
     </row>
     <row r="29" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A29" s="104"/>
-      <c r="B29" s="16"/>
-      <c r="C29" s="103"/>
-      <c r="D29" s="16"/>
-      <c r="E29" s="103"/>
-      <c r="F29" s="16"/>
-      <c r="G29" s="102"/>
-      <c r="H29" s="15"/>
-      <c r="I29" s="16"/>
-      <c r="J29" s="102"/>
-      <c r="K29" s="16"/>
-      <c r="L29" s="101"/>
-      <c r="M29" s="15"/>
-      <c r="N29" s="16"/>
-      <c r="O29" s="101"/>
-      <c r="P29" s="15"/>
-      <c r="Q29" s="16"/>
-      <c r="R29" s="100"/>
-      <c r="S29" s="100"/>
-      <c r="T29" s="99"/>
-      <c r="U29" s="92"/>
-      <c r="V29" s="92"/>
-      <c r="W29" s="92"/>
-      <c r="X29" s="92"/>
-      <c r="Y29" s="92"/>
-      <c r="Z29" s="92"/>
+      <c r="A29" s="127"/>
+      <c r="B29" s="39"/>
+      <c r="C29" s="128"/>
+      <c r="D29" s="39"/>
+      <c r="E29" s="128"/>
+      <c r="F29" s="39"/>
+      <c r="G29" s="114"/>
+      <c r="H29" s="38"/>
+      <c r="I29" s="39"/>
+      <c r="J29" s="114"/>
+      <c r="K29" s="39"/>
+      <c r="L29" s="116"/>
+      <c r="M29" s="38"/>
+      <c r="N29" s="39"/>
+      <c r="O29" s="116"/>
+      <c r="P29" s="38"/>
+      <c r="Q29" s="39"/>
+      <c r="R29" s="19"/>
+      <c r="S29" s="19"/>
+      <c r="T29" s="18"/>
+      <c r="U29" s="15"/>
+      <c r="V29" s="15"/>
+      <c r="W29" s="15"/>
+      <c r="X29" s="15"/>
+      <c r="Y29" s="15"/>
+      <c r="Z29" s="15"/>
     </row>
     <row r="30" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A30" s="104"/>
-      <c r="B30" s="16"/>
-      <c r="C30" s="103"/>
-      <c r="D30" s="16"/>
-      <c r="E30" s="103"/>
-      <c r="F30" s="16"/>
-      <c r="G30" s="102"/>
-      <c r="H30" s="15"/>
-      <c r="I30" s="16"/>
-      <c r="J30" s="102"/>
-      <c r="K30" s="16"/>
-      <c r="L30" s="101"/>
-      <c r="M30" s="15"/>
-      <c r="N30" s="16"/>
-      <c r="O30" s="101"/>
-      <c r="P30" s="15"/>
-      <c r="Q30" s="16"/>
-      <c r="R30" s="100"/>
-      <c r="S30" s="100"/>
-      <c r="T30" s="99"/>
-      <c r="U30" s="92"/>
-      <c r="V30" s="92"/>
-      <c r="W30" s="92"/>
-      <c r="X30" s="92"/>
-      <c r="Y30" s="92"/>
-      <c r="Z30" s="92"/>
+      <c r="A30" s="127"/>
+      <c r="B30" s="39"/>
+      <c r="C30" s="128"/>
+      <c r="D30" s="39"/>
+      <c r="E30" s="128"/>
+      <c r="F30" s="39"/>
+      <c r="G30" s="114"/>
+      <c r="H30" s="38"/>
+      <c r="I30" s="39"/>
+      <c r="J30" s="114"/>
+      <c r="K30" s="39"/>
+      <c r="L30" s="116"/>
+      <c r="M30" s="38"/>
+      <c r="N30" s="39"/>
+      <c r="O30" s="116"/>
+      <c r="P30" s="38"/>
+      <c r="Q30" s="39"/>
+      <c r="R30" s="19"/>
+      <c r="S30" s="19"/>
+      <c r="T30" s="18"/>
+      <c r="U30" s="15"/>
+      <c r="V30" s="15"/>
+      <c r="W30" s="15"/>
+      <c r="X30" s="15"/>
+      <c r="Y30" s="15"/>
+      <c r="Z30" s="15"/>
     </row>
     <row r="31" spans="1:26" ht="12.75" customHeight="1" thickBot="1">
-      <c r="A31" s="98"/>
-      <c r="B31" s="52"/>
-      <c r="C31" s="97"/>
-      <c r="D31" s="52"/>
-      <c r="E31" s="97"/>
-      <c r="F31" s="52"/>
-      <c r="G31" s="96"/>
-      <c r="H31" s="51"/>
-      <c r="I31" s="52"/>
-      <c r="J31" s="96"/>
-      <c r="K31" s="52"/>
-      <c r="L31" s="95"/>
-      <c r="M31" s="51"/>
-      <c r="N31" s="52"/>
-      <c r="O31" s="95"/>
-      <c r="P31" s="51"/>
-      <c r="Q31" s="52"/>
-      <c r="R31" s="94"/>
-      <c r="S31" s="94"/>
-      <c r="T31" s="93"/>
-      <c r="U31" s="92"/>
-      <c r="V31" s="92"/>
-      <c r="W31" s="92"/>
-      <c r="X31" s="92"/>
-      <c r="Y31" s="92"/>
-      <c r="Z31" s="92"/>
+      <c r="A31" s="130"/>
+      <c r="B31" s="70"/>
+      <c r="C31" s="131"/>
+      <c r="D31" s="70"/>
+      <c r="E31" s="131"/>
+      <c r="F31" s="70"/>
+      <c r="G31" s="115"/>
+      <c r="H31" s="69"/>
+      <c r="I31" s="70"/>
+      <c r="J31" s="115"/>
+      <c r="K31" s="70"/>
+      <c r="L31" s="117"/>
+      <c r="M31" s="69"/>
+      <c r="N31" s="70"/>
+      <c r="O31" s="117"/>
+      <c r="P31" s="69"/>
+      <c r="Q31" s="70"/>
+      <c r="R31" s="17"/>
+      <c r="S31" s="17"/>
+      <c r="T31" s="16"/>
+      <c r="U31" s="15"/>
+      <c r="V31" s="15"/>
+      <c r="W31" s="15"/>
+      <c r="X31" s="15"/>
+      <c r="Y31" s="15"/>
+      <c r="Z31" s="15"/>
     </row>
     <row r="32" spans="1:26" ht="12.75" customHeight="1">
-      <c r="D32" s="91"/>
-      <c r="E32" s="91"/>
-      <c r="F32" s="91"/>
-      <c r="G32" s="91"/>
-      <c r="H32" s="91"/>
-      <c r="I32" s="91"/>
-      <c r="J32" s="91"/>
+      <c r="D32" s="14"/>
+      <c r="E32" s="14"/>
+      <c r="F32" s="14"/>
+      <c r="G32" s="14"/>
+      <c r="H32" s="14"/>
+      <c r="I32" s="14"/>
+      <c r="J32" s="14"/>
     </row>
     <row r="33" spans="4:10" ht="12.75" customHeight="1">
-      <c r="D33" s="91"/>
-      <c r="E33" s="91"/>
-      <c r="F33" s="91"/>
-      <c r="G33" s="91"/>
-      <c r="H33" s="91"/>
-      <c r="I33" s="91"/>
-      <c r="J33" s="91"/>
+      <c r="D33" s="14"/>
+      <c r="E33" s="14"/>
+      <c r="F33" s="14"/>
+      <c r="G33" s="14"/>
+      <c r="H33" s="14"/>
+      <c r="I33" s="14"/>
+      <c r="J33" s="14"/>
     </row>
     <row r="34" spans="4:10" ht="12.75" customHeight="1"/>
     <row r="35" spans="4:10" ht="12.75" customHeight="1"/>
@@ -6838,6 +6808,16 @@
     <row r="1000" s="13" customFormat="1" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="136">
+    <mergeCell ref="A23:B23"/>
+    <mergeCell ref="A30:B30"/>
+    <mergeCell ref="C30:D30"/>
+    <mergeCell ref="E30:F30"/>
+    <mergeCell ref="A31:B31"/>
+    <mergeCell ref="C31:D31"/>
+    <mergeCell ref="E31:F31"/>
+    <mergeCell ref="C26:D26"/>
+    <mergeCell ref="E26:F26"/>
+    <mergeCell ref="A24:B24"/>
     <mergeCell ref="C28:D28"/>
     <mergeCell ref="E28:F28"/>
     <mergeCell ref="A29:B29"/>
@@ -6851,16 +6831,6 @@
     <mergeCell ref="C27:D27"/>
     <mergeCell ref="E27:F27"/>
     <mergeCell ref="A28:B28"/>
-    <mergeCell ref="A23:B23"/>
-    <mergeCell ref="A30:B30"/>
-    <mergeCell ref="C30:D30"/>
-    <mergeCell ref="E30:F30"/>
-    <mergeCell ref="A31:B31"/>
-    <mergeCell ref="C31:D31"/>
-    <mergeCell ref="E31:F31"/>
-    <mergeCell ref="C26:D26"/>
-    <mergeCell ref="E26:F26"/>
-    <mergeCell ref="A24:B24"/>
     <mergeCell ref="A21:B21"/>
     <mergeCell ref="C21:D21"/>
     <mergeCell ref="E21:F21"/>
@@ -6873,9 +6843,6 @@
     <mergeCell ref="A19:B19"/>
     <mergeCell ref="C19:D19"/>
     <mergeCell ref="E19:F19"/>
-    <mergeCell ref="O25:Q25"/>
-    <mergeCell ref="O26:Q26"/>
-    <mergeCell ref="C16:D16"/>
     <mergeCell ref="E16:F16"/>
     <mergeCell ref="C17:D17"/>
     <mergeCell ref="E17:F17"/>
@@ -6883,6 +6850,11 @@
     <mergeCell ref="E23:F23"/>
     <mergeCell ref="C24:D24"/>
     <mergeCell ref="E24:F24"/>
+    <mergeCell ref="G21:I21"/>
+    <mergeCell ref="J21:K21"/>
+    <mergeCell ref="J16:K16"/>
+    <mergeCell ref="G17:I17"/>
+    <mergeCell ref="J17:K17"/>
     <mergeCell ref="O27:Q27"/>
     <mergeCell ref="O28:Q28"/>
     <mergeCell ref="O29:Q29"/>
@@ -6894,7 +6866,8 @@
     <mergeCell ref="O23:Q23"/>
     <mergeCell ref="O24:Q24"/>
     <mergeCell ref="O20:Q20"/>
-    <mergeCell ref="L15:N15"/>
+    <mergeCell ref="O25:Q25"/>
+    <mergeCell ref="O26:Q26"/>
     <mergeCell ref="O15:Q15"/>
     <mergeCell ref="L16:N16"/>
     <mergeCell ref="O16:Q16"/>
@@ -6911,7 +6884,14 @@
     <mergeCell ref="E15:F15"/>
     <mergeCell ref="A16:B16"/>
     <mergeCell ref="A17:B17"/>
-    <mergeCell ref="G2:J4"/>
+    <mergeCell ref="J18:K18"/>
+    <mergeCell ref="G18:I18"/>
+    <mergeCell ref="G19:I19"/>
+    <mergeCell ref="J19:K19"/>
+    <mergeCell ref="G15:I15"/>
+    <mergeCell ref="J15:K15"/>
+    <mergeCell ref="G16:I16"/>
+    <mergeCell ref="C16:D16"/>
     <mergeCell ref="A5:F5"/>
     <mergeCell ref="G5:T5"/>
     <mergeCell ref="A6:F6"/>
@@ -6928,8 +6908,6 @@
     <mergeCell ref="O1:P1"/>
     <mergeCell ref="Q1:R1"/>
     <mergeCell ref="S1:T1"/>
-    <mergeCell ref="L30:N30"/>
-    <mergeCell ref="L31:N31"/>
     <mergeCell ref="L18:N18"/>
     <mergeCell ref="L19:N19"/>
     <mergeCell ref="L21:N21"/>
@@ -6938,10 +6916,8 @@
     <mergeCell ref="L24:N24"/>
     <mergeCell ref="L25:N25"/>
     <mergeCell ref="L20:N20"/>
-    <mergeCell ref="G28:I28"/>
-    <mergeCell ref="J28:K28"/>
-    <mergeCell ref="G29:I29"/>
-    <mergeCell ref="J29:K29"/>
+    <mergeCell ref="G2:J4"/>
+    <mergeCell ref="L15:N15"/>
     <mergeCell ref="L26:N26"/>
     <mergeCell ref="L27:N27"/>
     <mergeCell ref="L28:N28"/>
@@ -6949,6 +6925,8 @@
     <mergeCell ref="G25:I25"/>
     <mergeCell ref="J25:K25"/>
     <mergeCell ref="J26:K26"/>
+    <mergeCell ref="L30:N30"/>
+    <mergeCell ref="L31:N31"/>
     <mergeCell ref="G30:I30"/>
     <mergeCell ref="J30:K30"/>
     <mergeCell ref="G31:I31"/>
@@ -6962,18 +6940,10 @@
     <mergeCell ref="J23:K23"/>
     <mergeCell ref="G24:I24"/>
     <mergeCell ref="J24:K24"/>
-    <mergeCell ref="J18:K18"/>
-    <mergeCell ref="G18:I18"/>
-    <mergeCell ref="G19:I19"/>
-    <mergeCell ref="J19:K19"/>
-    <mergeCell ref="G21:I21"/>
-    <mergeCell ref="J21:K21"/>
-    <mergeCell ref="G15:I15"/>
-    <mergeCell ref="J15:K15"/>
-    <mergeCell ref="G16:I16"/>
-    <mergeCell ref="J16:K16"/>
-    <mergeCell ref="G17:I17"/>
-    <mergeCell ref="J17:K17"/>
+    <mergeCell ref="G28:I28"/>
+    <mergeCell ref="J28:K28"/>
+    <mergeCell ref="G29:I29"/>
+    <mergeCell ref="J29:K29"/>
   </mergeCells>
   <phoneticPr fontId="3"/>
   <hyperlinks>

--- a/Documents/ログアウト機能設計書.xlsx
+++ b/Documents/ログアウト機能設計書.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\S-47\Documents\project\taskUN\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64BD065B-A1F4-405C-8E8E-1A6739912A92}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3EE410CA-D455-4589-9D36-E9FE5BF5E7A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{72C6CFC4-7293-42D0-8B35-05AE043D8312}"/>
   </bookViews>
@@ -238,16 +238,6 @@
     </rPh>
     <rPh sb="68" eb="70">
       <t>ヒョウジ</t>
-    </rPh>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t>画面が遷移する</t>
-    <rPh sb="0" eb="2">
-      <t>ガメン</t>
-    </rPh>
-    <rPh sb="3" eb="5">
-      <t>センイ</t>
     </rPh>
     <phoneticPr fontId="3"/>
   </si>
@@ -467,6 +457,19 @@
     </rPh>
     <rPh sb="15" eb="17">
       <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>セッションが破棄されたのちに、画面が遷移する</t>
+    <rPh sb="6" eb="8">
+      <t>ハキ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>センイ</t>
     </rPh>
     <phoneticPr fontId="3"/>
   </si>
@@ -1541,23 +1544,26 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="27" xfId="2" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1575,9 +1581,6 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
@@ -2387,7 +2390,7 @@
       <c r="B8" s="38"/>
       <c r="C8" s="39"/>
       <c r="D8" s="40" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E8" s="38"/>
       <c r="F8" s="38"/>
@@ -2405,7 +2408,7 @@
       </c>
       <c r="C9" s="39"/>
       <c r="D9" s="77" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E9" s="38"/>
       <c r="F9" s="38"/>
@@ -2453,7 +2456,7 @@
       <c r="B12" s="38"/>
       <c r="C12" s="39"/>
       <c r="D12" s="40" t="s">
-        <v>45</v>
+        <v>85</v>
       </c>
       <c r="E12" s="38"/>
       <c r="F12" s="38"/>
@@ -4891,7 +4894,7 @@
   <sheetData>
     <row r="1" spans="1:26" ht="18" customHeight="1">
       <c r="A1" s="42" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B1" s="43"/>
       <c r="C1" s="43"/>
@@ -4942,7 +4945,7 @@
       <c r="L2" s="119"/>
       <c r="M2" s="119"/>
       <c r="N2" s="54"/>
-      <c r="O2" s="122">
+      <c r="O2" s="123">
         <v>45810</v>
       </c>
       <c r="P2" s="54"/>
@@ -4951,7 +4954,7 @@
       </c>
       <c r="R2" s="54"/>
       <c r="S2" s="53"/>
-      <c r="T2" s="123"/>
+      <c r="T2" s="124"/>
     </row>
     <row r="3" spans="1:26" ht="18" customHeight="1">
       <c r="A3" s="45"/>
@@ -4973,7 +4976,7 @@
       <c r="Q3" s="55"/>
       <c r="R3" s="47"/>
       <c r="S3" s="55"/>
-      <c r="T3" s="124"/>
+      <c r="T3" s="125"/>
     </row>
     <row r="4" spans="1:26" ht="18" customHeight="1" thickBot="1">
       <c r="A4" s="48"/>
@@ -4995,11 +4998,11 @@
       <c r="Q4" s="56"/>
       <c r="R4" s="50"/>
       <c r="S4" s="56"/>
-      <c r="T4" s="125"/>
+      <c r="T4" s="126"/>
     </row>
     <row r="5" spans="1:26" ht="18" customHeight="1">
-      <c r="A5" s="120" t="s">
-        <v>67</v>
+      <c r="A5" s="121" t="s">
+        <v>66</v>
       </c>
       <c r="B5" s="65"/>
       <c r="C5" s="65"/>
@@ -5007,7 +5010,7 @@
       <c r="E5" s="65"/>
       <c r="F5" s="52"/>
       <c r="G5" s="66" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="H5" s="65"/>
       <c r="I5" s="65"/>
@@ -5024,8 +5027,8 @@
       <c r="T5" s="67"/>
     </row>
     <row r="6" spans="1:26" ht="18" customHeight="1">
-      <c r="A6" s="121" t="s">
-        <v>65</v>
+      <c r="A6" s="122" t="s">
+        <v>64</v>
       </c>
       <c r="B6" s="38"/>
       <c r="C6" s="38"/>
@@ -5033,7 +5036,7 @@
       <c r="E6" s="38"/>
       <c r="F6" s="39"/>
       <c r="G6" s="40" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H6" s="38"/>
       <c r="I6" s="38"/>
@@ -5050,8 +5053,8 @@
       <c r="T6" s="41"/>
     </row>
     <row r="7" spans="1:26" ht="18" customHeight="1">
-      <c r="A7" s="121" t="s">
-        <v>64</v>
+      <c r="A7" s="122" t="s">
+        <v>63</v>
       </c>
       <c r="B7" s="38"/>
       <c r="C7" s="38"/>
@@ -5059,7 +5062,7 @@
       <c r="E7" s="38"/>
       <c r="F7" s="39"/>
       <c r="G7" s="40" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="H7" s="38"/>
       <c r="I7" s="38"/>
@@ -5101,11 +5104,11 @@
       <c r="A9" s="30"/>
       <c r="B9" s="25"/>
       <c r="C9" s="35" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D9" s="34"/>
       <c r="E9" s="34" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F9" s="34"/>
       <c r="G9" s="33"/>
@@ -5135,7 +5138,7 @@
       <c r="C10" s="32"/>
       <c r="D10" s="25"/>
       <c r="E10" s="25" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="F10" s="25"/>
       <c r="G10" s="31"/>
@@ -5165,7 +5168,7 @@
       <c r="C11" s="32"/>
       <c r="D11" s="25"/>
       <c r="E11" s="25" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F11" s="25"/>
       <c r="G11" s="31"/>
@@ -5195,7 +5198,7 @@
       <c r="C12" s="32"/>
       <c r="D12" s="25"/>
       <c r="E12" s="25" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F12" s="25"/>
       <c r="G12" s="31"/>
@@ -5225,7 +5228,7 @@
       <c r="C13" s="29"/>
       <c r="D13" s="28"/>
       <c r="E13" s="28" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="F13" s="28"/>
       <c r="G13" s="27"/>
@@ -5272,45 +5275,45 @@
       <c r="T14" s="22"/>
     </row>
     <row r="15" spans="1:26" ht="18.75" customHeight="1">
-      <c r="A15" s="121" t="s">
-        <v>58</v>
+      <c r="A15" s="122" t="s">
+        <v>57</v>
       </c>
       <c r="B15" s="39"/>
       <c r="C15" s="129" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D15" s="39"/>
-      <c r="E15" s="126" t="s">
-        <v>56</v>
+      <c r="E15" s="120" t="s">
+        <v>55</v>
       </c>
       <c r="F15" s="39"/>
-      <c r="G15" s="126" t="s">
-        <v>55</v>
+      <c r="G15" s="120" t="s">
+        <v>54</v>
       </c>
       <c r="H15" s="38"/>
       <c r="I15" s="39"/>
-      <c r="J15" s="126" t="s">
-        <v>54</v>
+      <c r="J15" s="120" t="s">
+        <v>53</v>
       </c>
       <c r="K15" s="39"/>
-      <c r="L15" s="126" t="s">
-        <v>53</v>
+      <c r="L15" s="120" t="s">
+        <v>52</v>
       </c>
       <c r="M15" s="38"/>
       <c r="N15" s="39"/>
-      <c r="O15" s="126" t="s">
-        <v>52</v>
+      <c r="O15" s="120" t="s">
+        <v>51</v>
       </c>
       <c r="P15" s="38"/>
       <c r="Q15" s="39"/>
       <c r="R15" s="21" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="S15" s="21" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="T15" s="20" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="16" spans="1:26" ht="48" customHeight="1">
@@ -5319,29 +5322,29 @@
       </c>
       <c r="B16" s="39"/>
       <c r="C16" s="128" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D16" s="39"/>
       <c r="E16" s="128" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F16" s="39"/>
-      <c r="G16" s="114" t="s">
-        <v>70</v>
+      <c r="G16" s="115" t="s">
+        <v>69</v>
       </c>
       <c r="H16" s="38"/>
       <c r="I16" s="39"/>
-      <c r="J16" s="114" t="s">
-        <v>69</v>
+      <c r="J16" s="115" t="s">
+        <v>68</v>
       </c>
       <c r="K16" s="39"/>
-      <c r="L16" s="116" t="s">
-        <v>71</v>
+      <c r="L16" s="114" t="s">
+        <v>70</v>
       </c>
       <c r="M16" s="38"/>
       <c r="N16" s="39"/>
-      <c r="O16" s="116" t="s">
-        <v>46</v>
+      <c r="O16" s="114" t="s">
+        <v>45</v>
       </c>
       <c r="P16" s="38"/>
       <c r="Q16" s="39"/>
@@ -5352,7 +5355,7 @@
         <v>28</v>
       </c>
       <c r="T16" s="18" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="U16" s="15"/>
       <c r="V16" s="15"/>
@@ -5367,29 +5370,29 @@
       </c>
       <c r="B17" s="39"/>
       <c r="C17" s="128" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D17" s="39"/>
       <c r="E17" s="128" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F17" s="39"/>
-      <c r="G17" s="114" t="s">
-        <v>73</v>
+      <c r="G17" s="115" t="s">
+        <v>72</v>
       </c>
       <c r="H17" s="38"/>
       <c r="I17" s="39"/>
-      <c r="J17" s="114" t="s">
-        <v>69</v>
+      <c r="J17" s="115" t="s">
+        <v>68</v>
       </c>
       <c r="K17" s="39"/>
-      <c r="L17" s="116" t="s">
-        <v>74</v>
+      <c r="L17" s="114" t="s">
+        <v>73</v>
       </c>
       <c r="M17" s="38"/>
       <c r="N17" s="39"/>
-      <c r="O17" s="116" t="s">
-        <v>75</v>
+      <c r="O17" s="114" t="s">
+        <v>74</v>
       </c>
       <c r="P17" s="38"/>
       <c r="Q17" s="39"/>
@@ -5400,7 +5403,7 @@
         <v>28</v>
       </c>
       <c r="T17" s="18" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="U17" s="15"/>
       <c r="V17" s="15"/>
@@ -5415,29 +5418,29 @@
       </c>
       <c r="B18" s="39"/>
       <c r="C18" s="128" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D18" s="39"/>
       <c r="E18" s="128" t="s">
+        <v>75</v>
+      </c>
+      <c r="F18" s="39"/>
+      <c r="G18" s="115" t="s">
         <v>76</v>
-      </c>
-      <c r="F18" s="39"/>
-      <c r="G18" s="114" t="s">
-        <v>77</v>
       </c>
       <c r="H18" s="38"/>
       <c r="I18" s="39"/>
-      <c r="J18" s="114" t="s">
-        <v>78</v>
+      <c r="J18" s="115" t="s">
+        <v>77</v>
       </c>
       <c r="K18" s="39"/>
       <c r="L18" s="118" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="M18" s="38"/>
       <c r="N18" s="39"/>
-      <c r="O18" s="116" t="s">
-        <v>79</v>
+      <c r="O18" s="114" t="s">
+        <v>78</v>
       </c>
       <c r="P18" s="38"/>
       <c r="Q18" s="39"/>
@@ -5448,7 +5451,7 @@
         <v>28</v>
       </c>
       <c r="T18" s="18" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="U18" s="15"/>
       <c r="V18" s="15"/>
@@ -5464,15 +5467,15 @@
       <c r="D19" s="39"/>
       <c r="E19" s="128"/>
       <c r="F19" s="39"/>
-      <c r="G19" s="114"/>
+      <c r="G19" s="115"/>
       <c r="H19" s="38"/>
       <c r="I19" s="39"/>
-      <c r="J19" s="114"/>
+      <c r="J19" s="115"/>
       <c r="K19" s="39"/>
-      <c r="L19" s="116"/>
+      <c r="L19" s="114"/>
       <c r="M19" s="38"/>
       <c r="N19" s="39"/>
-      <c r="O19" s="116"/>
+      <c r="O19" s="114"/>
       <c r="P19" s="38"/>
       <c r="Q19" s="39"/>
       <c r="R19" s="19"/>
@@ -5492,15 +5495,15 @@
       <c r="D20" s="39"/>
       <c r="E20" s="128"/>
       <c r="F20" s="39"/>
-      <c r="G20" s="114"/>
+      <c r="G20" s="115"/>
       <c r="H20" s="38"/>
       <c r="I20" s="39"/>
-      <c r="J20" s="114"/>
+      <c r="J20" s="115"/>
       <c r="K20" s="39"/>
-      <c r="L20" s="116"/>
+      <c r="L20" s="114"/>
       <c r="M20" s="38"/>
       <c r="N20" s="39"/>
-      <c r="O20" s="116"/>
+      <c r="O20" s="114"/>
       <c r="P20" s="38"/>
       <c r="Q20" s="39"/>
       <c r="R20" s="19"/>
@@ -5520,15 +5523,15 @@
       <c r="D21" s="39"/>
       <c r="E21" s="128"/>
       <c r="F21" s="39"/>
-      <c r="G21" s="114"/>
+      <c r="G21" s="115"/>
       <c r="H21" s="38"/>
       <c r="I21" s="39"/>
-      <c r="J21" s="114"/>
+      <c r="J21" s="115"/>
       <c r="K21" s="39"/>
-      <c r="L21" s="116"/>
+      <c r="L21" s="114"/>
       <c r="M21" s="38"/>
       <c r="N21" s="39"/>
-      <c r="O21" s="116"/>
+      <c r="O21" s="114"/>
       <c r="P21" s="38"/>
       <c r="Q21" s="39"/>
       <c r="R21" s="19"/>
@@ -5548,15 +5551,15 @@
       <c r="D22" s="39"/>
       <c r="E22" s="128"/>
       <c r="F22" s="39"/>
-      <c r="G22" s="114"/>
+      <c r="G22" s="115"/>
       <c r="H22" s="38"/>
       <c r="I22" s="39"/>
-      <c r="J22" s="114"/>
+      <c r="J22" s="115"/>
       <c r="K22" s="39"/>
-      <c r="L22" s="116"/>
+      <c r="L22" s="114"/>
       <c r="M22" s="38"/>
       <c r="N22" s="39"/>
-      <c r="O22" s="116"/>
+      <c r="O22" s="114"/>
       <c r="P22" s="38"/>
       <c r="Q22" s="39"/>
       <c r="R22" s="19"/>
@@ -5576,15 +5579,15 @@
       <c r="D23" s="39"/>
       <c r="E23" s="128"/>
       <c r="F23" s="39"/>
-      <c r="G23" s="114"/>
+      <c r="G23" s="115"/>
       <c r="H23" s="38"/>
       <c r="I23" s="39"/>
-      <c r="J23" s="114"/>
+      <c r="J23" s="115"/>
       <c r="K23" s="39"/>
-      <c r="L23" s="116"/>
+      <c r="L23" s="114"/>
       <c r="M23" s="38"/>
       <c r="N23" s="39"/>
-      <c r="O23" s="116"/>
+      <c r="O23" s="114"/>
       <c r="P23" s="38"/>
       <c r="Q23" s="39"/>
       <c r="R23" s="19"/>
@@ -5604,15 +5607,15 @@
       <c r="D24" s="39"/>
       <c r="E24" s="128"/>
       <c r="F24" s="39"/>
-      <c r="G24" s="114"/>
+      <c r="G24" s="115"/>
       <c r="H24" s="38"/>
       <c r="I24" s="39"/>
-      <c r="J24" s="114"/>
+      <c r="J24" s="115"/>
       <c r="K24" s="39"/>
-      <c r="L24" s="116"/>
+      <c r="L24" s="114"/>
       <c r="M24" s="38"/>
       <c r="N24" s="39"/>
-      <c r="O24" s="116"/>
+      <c r="O24" s="114"/>
       <c r="P24" s="38"/>
       <c r="Q24" s="39"/>
       <c r="R24" s="19"/>
@@ -5632,15 +5635,15 @@
       <c r="D25" s="39"/>
       <c r="E25" s="128"/>
       <c r="F25" s="39"/>
-      <c r="G25" s="114"/>
+      <c r="G25" s="115"/>
       <c r="H25" s="38"/>
       <c r="I25" s="39"/>
-      <c r="J25" s="114"/>
+      <c r="J25" s="115"/>
       <c r="K25" s="39"/>
-      <c r="L25" s="116"/>
+      <c r="L25" s="114"/>
       <c r="M25" s="38"/>
       <c r="N25" s="39"/>
-      <c r="O25" s="116"/>
+      <c r="O25" s="114"/>
       <c r="P25" s="38"/>
       <c r="Q25" s="39"/>
       <c r="R25" s="19"/>
@@ -5660,15 +5663,15 @@
       <c r="D26" s="39"/>
       <c r="E26" s="128"/>
       <c r="F26" s="39"/>
-      <c r="G26" s="114"/>
+      <c r="G26" s="115"/>
       <c r="H26" s="38"/>
       <c r="I26" s="39"/>
-      <c r="J26" s="114"/>
+      <c r="J26" s="115"/>
       <c r="K26" s="39"/>
-      <c r="L26" s="116"/>
+      <c r="L26" s="114"/>
       <c r="M26" s="38"/>
       <c r="N26" s="39"/>
-      <c r="O26" s="116"/>
+      <c r="O26" s="114"/>
       <c r="P26" s="38"/>
       <c r="Q26" s="39"/>
       <c r="R26" s="19"/>
@@ -5688,15 +5691,15 @@
       <c r="D27" s="39"/>
       <c r="E27" s="128"/>
       <c r="F27" s="39"/>
-      <c r="G27" s="114"/>
+      <c r="G27" s="115"/>
       <c r="H27" s="38"/>
       <c r="I27" s="39"/>
-      <c r="J27" s="114"/>
+      <c r="J27" s="115"/>
       <c r="K27" s="39"/>
-      <c r="L27" s="116"/>
+      <c r="L27" s="114"/>
       <c r="M27" s="38"/>
       <c r="N27" s="39"/>
-      <c r="O27" s="116"/>
+      <c r="O27" s="114"/>
       <c r="P27" s="38"/>
       <c r="Q27" s="39"/>
       <c r="R27" s="19"/>
@@ -5716,15 +5719,15 @@
       <c r="D28" s="39"/>
       <c r="E28" s="128"/>
       <c r="F28" s="39"/>
-      <c r="G28" s="114"/>
+      <c r="G28" s="115"/>
       <c r="H28" s="38"/>
       <c r="I28" s="39"/>
-      <c r="J28" s="114"/>
+      <c r="J28" s="115"/>
       <c r="K28" s="39"/>
-      <c r="L28" s="116"/>
+      <c r="L28" s="114"/>
       <c r="M28" s="38"/>
       <c r="N28" s="39"/>
-      <c r="O28" s="116"/>
+      <c r="O28" s="114"/>
       <c r="P28" s="38"/>
       <c r="Q28" s="39"/>
       <c r="R28" s="19"/>
@@ -5744,15 +5747,15 @@
       <c r="D29" s="39"/>
       <c r="E29" s="128"/>
       <c r="F29" s="39"/>
-      <c r="G29" s="114"/>
+      <c r="G29" s="115"/>
       <c r="H29" s="38"/>
       <c r="I29" s="39"/>
-      <c r="J29" s="114"/>
+      <c r="J29" s="115"/>
       <c r="K29" s="39"/>
-      <c r="L29" s="116"/>
+      <c r="L29" s="114"/>
       <c r="M29" s="38"/>
       <c r="N29" s="39"/>
-      <c r="O29" s="116"/>
+      <c r="O29" s="114"/>
       <c r="P29" s="38"/>
       <c r="Q29" s="39"/>
       <c r="R29" s="19"/>
@@ -5772,15 +5775,15 @@
       <c r="D30" s="39"/>
       <c r="E30" s="128"/>
       <c r="F30" s="39"/>
-      <c r="G30" s="114"/>
+      <c r="G30" s="115"/>
       <c r="H30" s="38"/>
       <c r="I30" s="39"/>
-      <c r="J30" s="114"/>
+      <c r="J30" s="115"/>
       <c r="K30" s="39"/>
-      <c r="L30" s="116"/>
+      <c r="L30" s="114"/>
       <c r="M30" s="38"/>
       <c r="N30" s="39"/>
-      <c r="O30" s="116"/>
+      <c r="O30" s="114"/>
       <c r="P30" s="38"/>
       <c r="Q30" s="39"/>
       <c r="R30" s="19"/>
@@ -5800,15 +5803,15 @@
       <c r="D31" s="70"/>
       <c r="E31" s="131"/>
       <c r="F31" s="70"/>
-      <c r="G31" s="115"/>
+      <c r="G31" s="117"/>
       <c r="H31" s="69"/>
       <c r="I31" s="70"/>
-      <c r="J31" s="115"/>
+      <c r="J31" s="117"/>
       <c r="K31" s="70"/>
-      <c r="L31" s="117"/>
+      <c r="L31" s="116"/>
       <c r="M31" s="69"/>
       <c r="N31" s="70"/>
-      <c r="O31" s="117"/>
+      <c r="O31" s="116"/>
       <c r="P31" s="69"/>
       <c r="Q31" s="70"/>
       <c r="R31" s="17"/>
@@ -6918,6 +6921,12 @@
     <mergeCell ref="L20:N20"/>
     <mergeCell ref="G2:J4"/>
     <mergeCell ref="L15:N15"/>
+    <mergeCell ref="G22:I22"/>
+    <mergeCell ref="J22:K22"/>
+    <mergeCell ref="G23:I23"/>
+    <mergeCell ref="J23:K23"/>
+    <mergeCell ref="G24:I24"/>
+    <mergeCell ref="J24:K24"/>
     <mergeCell ref="L26:N26"/>
     <mergeCell ref="L27:N27"/>
     <mergeCell ref="L28:N28"/>
@@ -6934,12 +6943,6 @@
     <mergeCell ref="G26:I26"/>
     <mergeCell ref="G27:I27"/>
     <mergeCell ref="J27:K27"/>
-    <mergeCell ref="G22:I22"/>
-    <mergeCell ref="J22:K22"/>
-    <mergeCell ref="G23:I23"/>
-    <mergeCell ref="J23:K23"/>
-    <mergeCell ref="G24:I24"/>
-    <mergeCell ref="J24:K24"/>
     <mergeCell ref="G28:I28"/>
     <mergeCell ref="J28:K28"/>
     <mergeCell ref="G29:I29"/>

--- a/Documents/ログアウト機能設計書.xlsx
+++ b/Documents/ログアウト機能設計書.xlsx
@@ -8,14 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\S-47\Documents\project\taskUN\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3EE410CA-D455-4589-9D36-E9FE5BF5E7A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB63E4EF-80C4-4541-9EA6-A1C9641E39C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{72C6CFC4-7293-42D0-8B35-05AE043D8312}"/>
   </bookViews>
   <sheets>
     <sheet name="ユースケース記述" sheetId="3" r:id="rId1"/>
     <sheet name="画面設計書" sheetId="2" r:id="rId2"/>
-    <sheet name="テスト仕様書兼結果報告書" sheetId="4" r:id="rId3"/>
+    <sheet name="画面遷移図" sheetId="5" r:id="rId3"/>
+    <sheet name="テスト仕様書兼結果報告書" sheetId="4" r:id="rId4"/>
   </sheets>
   <definedNames>
     <definedName name="あ">#REF!</definedName>
@@ -31,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="87">
   <si>
     <t>システム名</t>
   </si>
@@ -472,6 +473,9 @@
       <t>センイ</t>
     </rPh>
     <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>画面遷移図</t>
   </si>
 </sst>
 </file>
@@ -1202,7 +1206,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="132">
+  <cellXfs count="138">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1312,6 +1316,21 @@
     <xf numFmtId="56" fontId="5" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1596,6 +1615,9 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -1961,6 +1983,61 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>104775</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>85725</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>504825</xdr:colOff>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>9525</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="図 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C27FEAF6-90D7-6ED2-6E54-438823FFC101}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="447675" y="1000125"/>
+          <a:ext cx="7772400" cy="4295775"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office テーマ">
   <a:themeElements>
@@ -2268,19 +2345,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="42" t="s">
+      <c r="A1" s="47" t="s">
         <v>30</v>
       </c>
-      <c r="B1" s="43"/>
-      <c r="C1" s="44"/>
-      <c r="D1" s="51" t="s">
+      <c r="B1" s="48"/>
+      <c r="C1" s="49"/>
+      <c r="D1" s="56" t="s">
         <v>0</v>
       </c>
-      <c r="E1" s="52"/>
-      <c r="F1" s="51" t="s">
+      <c r="E1" s="57"/>
+      <c r="F1" s="56" t="s">
         <v>1</v>
       </c>
-      <c r="G1" s="52"/>
+      <c r="G1" s="57"/>
       <c r="H1" s="11" t="s">
         <v>2</v>
       </c>
@@ -2292,192 +2369,192 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="45"/>
-      <c r="B2" s="46"/>
-      <c r="C2" s="47"/>
-      <c r="D2" s="53" t="s">
+      <c r="A2" s="50"/>
+      <c r="B2" s="51"/>
+      <c r="C2" s="52"/>
+      <c r="D2" s="58" t="s">
         <v>6</v>
       </c>
-      <c r="E2" s="54"/>
-      <c r="F2" s="53" t="s">
+      <c r="E2" s="59"/>
+      <c r="F2" s="58" t="s">
         <v>7</v>
       </c>
-      <c r="G2" s="54"/>
-      <c r="H2" s="57">
+      <c r="G2" s="59"/>
+      <c r="H2" s="62">
         <v>45806</v>
       </c>
-      <c r="I2" s="60" t="s">
+      <c r="I2" s="65" t="s">
         <v>28</v>
       </c>
-      <c r="J2" s="61"/>
+      <c r="J2" s="66"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="45"/>
-      <c r="B3" s="46"/>
-      <c r="C3" s="47"/>
-      <c r="D3" s="55"/>
-      <c r="E3" s="47"/>
-      <c r="F3" s="55"/>
-      <c r="G3" s="47"/>
-      <c r="H3" s="58"/>
-      <c r="I3" s="58"/>
-      <c r="J3" s="62"/>
+      <c r="A3" s="50"/>
+      <c r="B3" s="51"/>
+      <c r="C3" s="52"/>
+      <c r="D3" s="60"/>
+      <c r="E3" s="52"/>
+      <c r="F3" s="60"/>
+      <c r="G3" s="52"/>
+      <c r="H3" s="63"/>
+      <c r="I3" s="63"/>
+      <c r="J3" s="67"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="48"/>
-      <c r="B4" s="49"/>
-      <c r="C4" s="50"/>
-      <c r="D4" s="56"/>
-      <c r="E4" s="50"/>
-      <c r="F4" s="56"/>
-      <c r="G4" s="50"/>
-      <c r="H4" s="59"/>
-      <c r="I4" s="59"/>
-      <c r="J4" s="63"/>
+      <c r="A4" s="53"/>
+      <c r="B4" s="54"/>
+      <c r="C4" s="55"/>
+      <c r="D4" s="61"/>
+      <c r="E4" s="55"/>
+      <c r="F4" s="61"/>
+      <c r="G4" s="55"/>
+      <c r="H4" s="64"/>
+      <c r="I4" s="64"/>
+      <c r="J4" s="68"/>
     </row>
     <row r="5" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A5" s="64" t="s">
+      <c r="A5" s="69" t="s">
         <v>31</v>
       </c>
-      <c r="B5" s="65"/>
-      <c r="C5" s="52"/>
-      <c r="D5" s="66" t="s">
+      <c r="B5" s="70"/>
+      <c r="C5" s="57"/>
+      <c r="D5" s="71" t="s">
         <v>41</v>
       </c>
-      <c r="E5" s="65"/>
-      <c r="F5" s="65"/>
-      <c r="G5" s="65"/>
-      <c r="H5" s="65"/>
-      <c r="I5" s="65"/>
-      <c r="J5" s="67"/>
+      <c r="E5" s="70"/>
+      <c r="F5" s="70"/>
+      <c r="G5" s="70"/>
+      <c r="H5" s="70"/>
+      <c r="I5" s="70"/>
+      <c r="J5" s="72"/>
     </row>
     <row r="6" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A6" s="37" t="s">
+      <c r="A6" s="42" t="s">
         <v>32</v>
       </c>
-      <c r="B6" s="38"/>
-      <c r="C6" s="39"/>
-      <c r="D6" s="40" t="s">
+      <c r="B6" s="43"/>
+      <c r="C6" s="44"/>
+      <c r="D6" s="45" t="s">
         <v>42</v>
       </c>
-      <c r="E6" s="38"/>
-      <c r="F6" s="38"/>
-      <c r="G6" s="38"/>
-      <c r="H6" s="38"/>
-      <c r="I6" s="38"/>
-      <c r="J6" s="41"/>
+      <c r="E6" s="43"/>
+      <c r="F6" s="43"/>
+      <c r="G6" s="43"/>
+      <c r="H6" s="43"/>
+      <c r="I6" s="43"/>
+      <c r="J6" s="46"/>
     </row>
     <row r="7" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A7" s="37" t="s">
+      <c r="A7" s="42" t="s">
         <v>33</v>
       </c>
-      <c r="B7" s="38"/>
-      <c r="C7" s="39"/>
-      <c r="D7" s="40" t="s">
+      <c r="B7" s="43"/>
+      <c r="C7" s="44"/>
+      <c r="D7" s="45" t="s">
         <v>34</v>
       </c>
-      <c r="E7" s="38"/>
-      <c r="F7" s="38"/>
-      <c r="G7" s="38"/>
-      <c r="H7" s="38"/>
-      <c r="I7" s="38"/>
-      <c r="J7" s="41"/>
+      <c r="E7" s="43"/>
+      <c r="F7" s="43"/>
+      <c r="G7" s="43"/>
+      <c r="H7" s="43"/>
+      <c r="I7" s="43"/>
+      <c r="J7" s="46"/>
     </row>
     <row r="8" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A8" s="37" t="s">
+      <c r="A8" s="42" t="s">
         <v>35</v>
       </c>
-      <c r="B8" s="38"/>
-      <c r="C8" s="39"/>
-      <c r="D8" s="40" t="s">
+      <c r="B8" s="43"/>
+      <c r="C8" s="44"/>
+      <c r="D8" s="45" t="s">
         <v>84</v>
       </c>
-      <c r="E8" s="38"/>
-      <c r="F8" s="38"/>
-      <c r="G8" s="38"/>
-      <c r="H8" s="38"/>
-      <c r="I8" s="38"/>
-      <c r="J8" s="41"/>
+      <c r="E8" s="43"/>
+      <c r="F8" s="43"/>
+      <c r="G8" s="43"/>
+      <c r="H8" s="43"/>
+      <c r="I8" s="43"/>
+      <c r="J8" s="46"/>
     </row>
     <row r="9" spans="1:10" ht="64.5" customHeight="1">
-      <c r="A9" s="73" t="s">
+      <c r="A9" s="78" t="s">
         <v>36</v>
       </c>
-      <c r="B9" s="76" t="s">
+      <c r="B9" s="81" t="s">
         <v>37</v>
       </c>
-      <c r="C9" s="39"/>
-      <c r="D9" s="77" t="s">
+      <c r="C9" s="44"/>
+      <c r="D9" s="82" t="s">
         <v>83</v>
       </c>
-      <c r="E9" s="38"/>
-      <c r="F9" s="38"/>
-      <c r="G9" s="38"/>
-      <c r="H9" s="38"/>
-      <c r="I9" s="38"/>
-      <c r="J9" s="41"/>
+      <c r="E9" s="43"/>
+      <c r="F9" s="43"/>
+      <c r="G9" s="43"/>
+      <c r="H9" s="43"/>
+      <c r="I9" s="43"/>
+      <c r="J9" s="46"/>
     </row>
     <row r="10" spans="1:10" ht="64.5" customHeight="1">
-      <c r="A10" s="74"/>
-      <c r="B10" s="76" t="s">
+      <c r="A10" s="79"/>
+      <c r="B10" s="81" t="s">
         <v>38</v>
       </c>
-      <c r="C10" s="39"/>
-      <c r="D10" s="77" t="s">
+      <c r="C10" s="44"/>
+      <c r="D10" s="82" t="s">
         <v>43</v>
       </c>
-      <c r="E10" s="38"/>
-      <c r="F10" s="38"/>
-      <c r="G10" s="38"/>
-      <c r="H10" s="38"/>
-      <c r="I10" s="38"/>
-      <c r="J10" s="41"/>
+      <c r="E10" s="43"/>
+      <c r="F10" s="43"/>
+      <c r="G10" s="43"/>
+      <c r="H10" s="43"/>
+      <c r="I10" s="43"/>
+      <c r="J10" s="46"/>
     </row>
     <row r="11" spans="1:10" ht="64.5" customHeight="1">
-      <c r="A11" s="75"/>
-      <c r="B11" s="76" t="s">
+      <c r="A11" s="80"/>
+      <c r="B11" s="81" t="s">
         <v>39</v>
       </c>
-      <c r="C11" s="39"/>
-      <c r="D11" s="77" t="s">
+      <c r="C11" s="44"/>
+      <c r="D11" s="82" t="s">
         <v>44</v>
       </c>
-      <c r="E11" s="38"/>
-      <c r="F11" s="38"/>
-      <c r="G11" s="38"/>
-      <c r="H11" s="38"/>
-      <c r="I11" s="38"/>
-      <c r="J11" s="41"/>
+      <c r="E11" s="43"/>
+      <c r="F11" s="43"/>
+      <c r="G11" s="43"/>
+      <c r="H11" s="43"/>
+      <c r="I11" s="43"/>
+      <c r="J11" s="46"/>
     </row>
     <row r="12" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A12" s="37" t="s">
+      <c r="A12" s="42" t="s">
         <v>40</v>
       </c>
-      <c r="B12" s="38"/>
-      <c r="C12" s="39"/>
-      <c r="D12" s="40" t="s">
+      <c r="B12" s="43"/>
+      <c r="C12" s="44"/>
+      <c r="D12" s="45" t="s">
         <v>85</v>
       </c>
-      <c r="E12" s="38"/>
-      <c r="F12" s="38"/>
-      <c r="G12" s="38"/>
-      <c r="H12" s="38"/>
-      <c r="I12" s="38"/>
-      <c r="J12" s="41"/>
+      <c r="E12" s="43"/>
+      <c r="F12" s="43"/>
+      <c r="G12" s="43"/>
+      <c r="H12" s="43"/>
+      <c r="I12" s="43"/>
+      <c r="J12" s="46"/>
     </row>
     <row r="13" spans="1:10" ht="26.25" customHeight="1" thickBot="1">
-      <c r="A13" s="68" t="s">
+      <c r="A13" s="73" t="s">
         <v>18</v>
       </c>
-      <c r="B13" s="69"/>
-      <c r="C13" s="70"/>
-      <c r="D13" s="71"/>
-      <c r="E13" s="69"/>
-      <c r="F13" s="69"/>
-      <c r="G13" s="69"/>
-      <c r="H13" s="69"/>
-      <c r="I13" s="69"/>
-      <c r="J13" s="72"/>
+      <c r="B13" s="74"/>
+      <c r="C13" s="75"/>
+      <c r="D13" s="76"/>
+      <c r="E13" s="74"/>
+      <c r="F13" s="74"/>
+      <c r="G13" s="74"/>
+      <c r="H13" s="74"/>
+      <c r="I13" s="74"/>
+      <c r="J13" s="77"/>
     </row>
     <row r="14" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="15" spans="1:10" ht="12.75" customHeight="1"/>
@@ -3517,19 +3594,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="96" t="s">
+      <c r="A1" s="101" t="s">
         <v>5</v>
       </c>
-      <c r="B1" s="97"/>
-      <c r="C1" s="98"/>
-      <c r="D1" s="100" t="s">
+      <c r="B1" s="102"/>
+      <c r="C1" s="103"/>
+      <c r="D1" s="105" t="s">
         <v>0</v>
       </c>
-      <c r="E1" s="101"/>
-      <c r="F1" s="100" t="s">
+      <c r="E1" s="106"/>
+      <c r="F1" s="105" t="s">
         <v>1</v>
       </c>
-      <c r="G1" s="101"/>
+      <c r="G1" s="106"/>
       <c r="H1" s="1" t="s">
         <v>2</v>
       </c>
@@ -3541,190 +3618,190 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="93"/>
-      <c r="B2" s="94"/>
-      <c r="C2" s="99"/>
-      <c r="D2" s="102" t="s">
+      <c r="A2" s="98"/>
+      <c r="B2" s="99"/>
+      <c r="C2" s="104"/>
+      <c r="D2" s="107" t="s">
         <v>6</v>
       </c>
-      <c r="E2" s="103"/>
-      <c r="F2" s="102" t="s">
+      <c r="E2" s="108"/>
+      <c r="F2" s="107" t="s">
         <v>7</v>
       </c>
-      <c r="G2" s="103"/>
-      <c r="H2" s="105">
+      <c r="G2" s="108"/>
+      <c r="H2" s="110">
         <v>45806</v>
       </c>
-      <c r="I2" s="107" t="s">
+      <c r="I2" s="112" t="s">
         <v>28</v>
       </c>
-      <c r="J2" s="108"/>
+      <c r="J2" s="113"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="93"/>
-      <c r="B3" s="94"/>
-      <c r="C3" s="99"/>
-      <c r="D3" s="104"/>
-      <c r="E3" s="99"/>
-      <c r="F3" s="104"/>
-      <c r="G3" s="99"/>
-      <c r="H3" s="106"/>
-      <c r="I3" s="106"/>
-      <c r="J3" s="109"/>
+      <c r="A3" s="98"/>
+      <c r="B3" s="99"/>
+      <c r="C3" s="104"/>
+      <c r="D3" s="109"/>
+      <c r="E3" s="104"/>
+      <c r="F3" s="109"/>
+      <c r="G3" s="104"/>
+      <c r="H3" s="111"/>
+      <c r="I3" s="111"/>
+      <c r="J3" s="114"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="93"/>
-      <c r="B4" s="94"/>
-      <c r="C4" s="99"/>
-      <c r="D4" s="104"/>
-      <c r="E4" s="99"/>
-      <c r="F4" s="104"/>
-      <c r="G4" s="99"/>
-      <c r="H4" s="106"/>
-      <c r="I4" s="106"/>
-      <c r="J4" s="109"/>
+      <c r="A4" s="98"/>
+      <c r="B4" s="99"/>
+      <c r="C4" s="104"/>
+      <c r="D4" s="109"/>
+      <c r="E4" s="104"/>
+      <c r="F4" s="109"/>
+      <c r="G4" s="104"/>
+      <c r="H4" s="111"/>
+      <c r="I4" s="111"/>
+      <c r="J4" s="114"/>
     </row>
     <row r="5" spans="1:10" ht="28.5" customHeight="1">
-      <c r="A5" s="110" t="s">
+      <c r="A5" s="115" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="111"/>
-      <c r="C5" s="101"/>
-      <c r="D5" s="112" t="s">
+      <c r="B5" s="116"/>
+      <c r="C5" s="106"/>
+      <c r="D5" s="117" t="s">
         <v>19</v>
       </c>
-      <c r="E5" s="111"/>
-      <c r="F5" s="111"/>
-      <c r="G5" s="111"/>
-      <c r="H5" s="111"/>
-      <c r="I5" s="111"/>
-      <c r="J5" s="113"/>
+      <c r="E5" s="116"/>
+      <c r="F5" s="116"/>
+      <c r="G5" s="116"/>
+      <c r="H5" s="116"/>
+      <c r="I5" s="116"/>
+      <c r="J5" s="118"/>
     </row>
     <row r="6" spans="1:10" ht="21" customHeight="1">
-      <c r="A6" s="88" t="s">
+      <c r="A6" s="93" t="s">
         <v>9</v>
       </c>
-      <c r="B6" s="79"/>
-      <c r="C6" s="79"/>
-      <c r="D6" s="79"/>
-      <c r="E6" s="79"/>
-      <c r="F6" s="79"/>
-      <c r="G6" s="79"/>
-      <c r="H6" s="79"/>
-      <c r="I6" s="79"/>
-      <c r="J6" s="82"/>
+      <c r="B6" s="84"/>
+      <c r="C6" s="84"/>
+      <c r="D6" s="84"/>
+      <c r="E6" s="84"/>
+      <c r="F6" s="84"/>
+      <c r="G6" s="84"/>
+      <c r="H6" s="84"/>
+      <c r="I6" s="84"/>
+      <c r="J6" s="87"/>
     </row>
     <row r="7" spans="1:10" ht="21" customHeight="1">
-      <c r="A7" s="90"/>
-      <c r="B7" s="91"/>
-      <c r="C7" s="91"/>
-      <c r="D7" s="91"/>
-      <c r="E7" s="91"/>
-      <c r="F7" s="91"/>
-      <c r="G7" s="91"/>
-      <c r="H7" s="91"/>
-      <c r="I7" s="91"/>
-      <c r="J7" s="92"/>
+      <c r="A7" s="95"/>
+      <c r="B7" s="96"/>
+      <c r="C7" s="96"/>
+      <c r="D7" s="96"/>
+      <c r="E7" s="96"/>
+      <c r="F7" s="96"/>
+      <c r="G7" s="96"/>
+      <c r="H7" s="96"/>
+      <c r="I7" s="96"/>
+      <c r="J7" s="97"/>
     </row>
     <row r="8" spans="1:10" ht="21" customHeight="1">
-      <c r="A8" s="93"/>
-      <c r="B8" s="94"/>
-      <c r="C8" s="94"/>
-      <c r="D8" s="94"/>
-      <c r="E8" s="94"/>
-      <c r="F8" s="94"/>
-      <c r="G8" s="94"/>
-      <c r="H8" s="94"/>
-      <c r="I8" s="94"/>
-      <c r="J8" s="95"/>
+      <c r="A8" s="98"/>
+      <c r="B8" s="99"/>
+      <c r="C8" s="99"/>
+      <c r="D8" s="99"/>
+      <c r="E8" s="99"/>
+      <c r="F8" s="99"/>
+      <c r="G8" s="99"/>
+      <c r="H8" s="99"/>
+      <c r="I8" s="99"/>
+      <c r="J8" s="100"/>
     </row>
     <row r="9" spans="1:10" ht="21" customHeight="1">
-      <c r="A9" s="93"/>
-      <c r="B9" s="94"/>
-      <c r="C9" s="94"/>
-      <c r="D9" s="94"/>
-      <c r="E9" s="94"/>
-      <c r="F9" s="94"/>
-      <c r="G9" s="94"/>
-      <c r="H9" s="94"/>
-      <c r="I9" s="94"/>
-      <c r="J9" s="95"/>
+      <c r="A9" s="98"/>
+      <c r="B9" s="99"/>
+      <c r="C9" s="99"/>
+      <c r="D9" s="99"/>
+      <c r="E9" s="99"/>
+      <c r="F9" s="99"/>
+      <c r="G9" s="99"/>
+      <c r="H9" s="99"/>
+      <c r="I9" s="99"/>
+      <c r="J9" s="100"/>
     </row>
     <row r="10" spans="1:10" ht="21" customHeight="1">
-      <c r="A10" s="93"/>
-      <c r="B10" s="94"/>
-      <c r="C10" s="94"/>
-      <c r="D10" s="94"/>
-      <c r="E10" s="94"/>
-      <c r="F10" s="94"/>
-      <c r="G10" s="94"/>
-      <c r="H10" s="94"/>
-      <c r="I10" s="94"/>
-      <c r="J10" s="95"/>
+      <c r="A10" s="98"/>
+      <c r="B10" s="99"/>
+      <c r="C10" s="99"/>
+      <c r="D10" s="99"/>
+      <c r="E10" s="99"/>
+      <c r="F10" s="99"/>
+      <c r="G10" s="99"/>
+      <c r="H10" s="99"/>
+      <c r="I10" s="99"/>
+      <c r="J10" s="100"/>
     </row>
     <row r="11" spans="1:10" ht="21" customHeight="1">
-      <c r="A11" s="93"/>
-      <c r="B11" s="94"/>
-      <c r="C11" s="94"/>
-      <c r="D11" s="94"/>
-      <c r="E11" s="94"/>
-      <c r="F11" s="94"/>
-      <c r="G11" s="94"/>
-      <c r="H11" s="94"/>
-      <c r="I11" s="94"/>
-      <c r="J11" s="95"/>
+      <c r="A11" s="98"/>
+      <c r="B11" s="99"/>
+      <c r="C11" s="99"/>
+      <c r="D11" s="99"/>
+      <c r="E11" s="99"/>
+      <c r="F11" s="99"/>
+      <c r="G11" s="99"/>
+      <c r="H11" s="99"/>
+      <c r="I11" s="99"/>
+      <c r="J11" s="100"/>
     </row>
     <row r="12" spans="1:10" ht="21" customHeight="1">
-      <c r="A12" s="93"/>
-      <c r="B12" s="94"/>
-      <c r="C12" s="94"/>
-      <c r="D12" s="94"/>
-      <c r="E12" s="94"/>
-      <c r="F12" s="94"/>
-      <c r="G12" s="94"/>
-      <c r="H12" s="94"/>
-      <c r="I12" s="94"/>
-      <c r="J12" s="95"/>
+      <c r="A12" s="98"/>
+      <c r="B12" s="99"/>
+      <c r="C12" s="99"/>
+      <c r="D12" s="99"/>
+      <c r="E12" s="99"/>
+      <c r="F12" s="99"/>
+      <c r="G12" s="99"/>
+      <c r="H12" s="99"/>
+      <c r="I12" s="99"/>
+      <c r="J12" s="100"/>
     </row>
     <row r="13" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A13" s="93"/>
-      <c r="B13" s="94"/>
-      <c r="C13" s="94"/>
-      <c r="D13" s="94"/>
-      <c r="E13" s="94"/>
-      <c r="F13" s="94"/>
-      <c r="G13" s="94"/>
-      <c r="H13" s="94"/>
-      <c r="I13" s="94"/>
-      <c r="J13" s="95"/>
+      <c r="A13" s="98"/>
+      <c r="B13" s="99"/>
+      <c r="C13" s="99"/>
+      <c r="D13" s="99"/>
+      <c r="E13" s="99"/>
+      <c r="F13" s="99"/>
+      <c r="G13" s="99"/>
+      <c r="H13" s="99"/>
+      <c r="I13" s="99"/>
+      <c r="J13" s="100"/>
     </row>
     <row r="14" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A14" s="88" t="s">
+      <c r="A14" s="93" t="s">
         <v>10</v>
       </c>
-      <c r="B14" s="79"/>
-      <c r="C14" s="79"/>
-      <c r="D14" s="79"/>
-      <c r="E14" s="79"/>
-      <c r="F14" s="79"/>
-      <c r="G14" s="79"/>
-      <c r="H14" s="79"/>
-      <c r="I14" s="79"/>
-      <c r="J14" s="82"/>
+      <c r="B14" s="84"/>
+      <c r="C14" s="84"/>
+      <c r="D14" s="84"/>
+      <c r="E14" s="84"/>
+      <c r="F14" s="84"/>
+      <c r="G14" s="84"/>
+      <c r="H14" s="84"/>
+      <c r="I14" s="84"/>
+      <c r="J14" s="87"/>
     </row>
     <row r="15" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A15" s="88" t="s">
+      <c r="A15" s="93" t="s">
         <v>11</v>
       </c>
-      <c r="B15" s="79"/>
-      <c r="C15" s="80"/>
-      <c r="D15" s="81" t="s">
+      <c r="B15" s="84"/>
+      <c r="C15" s="85"/>
+      <c r="D15" s="86" t="s">
         <v>26</v>
       </c>
-      <c r="E15" s="79"/>
-      <c r="F15" s="79"/>
-      <c r="G15" s="79"/>
-      <c r="H15" s="80"/>
+      <c r="E15" s="84"/>
+      <c r="F15" s="84"/>
+      <c r="G15" s="84"/>
+      <c r="H15" s="85"/>
       <c r="I15" s="5" t="s">
         <v>12</v>
       </c>
@@ -3733,11 +3810,11 @@
       </c>
     </row>
     <row r="16" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A16" s="88" t="s">
+      <c r="A16" s="93" t="s">
         <v>13</v>
       </c>
-      <c r="B16" s="79"/>
-      <c r="C16" s="80"/>
+      <c r="B16" s="84"/>
+      <c r="C16" s="85"/>
       <c r="D16" s="5" t="s">
         <v>14</v>
       </c>
@@ -3750,18 +3827,18 @@
       <c r="G16" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="H16" s="89" t="s">
+      <c r="H16" s="94" t="s">
         <v>18</v>
       </c>
-      <c r="I16" s="79"/>
-      <c r="J16" s="82"/>
+      <c r="I16" s="84"/>
+      <c r="J16" s="87"/>
     </row>
     <row r="17" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A17" s="78">
+      <c r="A17" s="83">
         <v>1</v>
       </c>
-      <c r="B17" s="79"/>
-      <c r="C17" s="80"/>
+      <c r="B17" s="84"/>
+      <c r="C17" s="85"/>
       <c r="D17" s="7" t="s">
         <v>21</v>
       </c>
@@ -3774,16 +3851,16 @@
       <c r="G17" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="H17" s="81"/>
-      <c r="I17" s="79"/>
-      <c r="J17" s="82"/>
+      <c r="H17" s="86"/>
+      <c r="I17" s="84"/>
+      <c r="J17" s="87"/>
     </row>
     <row r="18" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A18" s="78">
+      <c r="A18" s="83">
         <v>2</v>
       </c>
-      <c r="B18" s="79"/>
-      <c r="C18" s="80"/>
+      <c r="B18" s="84"/>
+      <c r="C18" s="85"/>
       <c r="D18" s="7" t="s">
         <v>22</v>
       </c>
@@ -3794,71 +3871,71 @@
       <c r="G18" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="H18" s="81" t="s">
+      <c r="H18" s="86" t="s">
         <v>27</v>
       </c>
-      <c r="I18" s="79"/>
-      <c r="J18" s="82"/>
+      <c r="I18" s="84"/>
+      <c r="J18" s="87"/>
     </row>
     <row r="19" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A19" s="78"/>
-      <c r="B19" s="79"/>
-      <c r="C19" s="80"/>
+      <c r="A19" s="83"/>
+      <c r="B19" s="84"/>
+      <c r="C19" s="85"/>
       <c r="D19" s="7"/>
       <c r="E19" s="7"/>
       <c r="F19" s="8"/>
       <c r="G19" s="8"/>
-      <c r="H19" s="81"/>
-      <c r="I19" s="79"/>
-      <c r="J19" s="82"/>
+      <c r="H19" s="86"/>
+      <c r="I19" s="84"/>
+      <c r="J19" s="87"/>
     </row>
     <row r="20" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A20" s="78"/>
-      <c r="B20" s="79"/>
-      <c r="C20" s="80"/>
+      <c r="A20" s="83"/>
+      <c r="B20" s="84"/>
+      <c r="C20" s="85"/>
       <c r="D20" s="7"/>
       <c r="E20" s="7"/>
       <c r="F20" s="8"/>
       <c r="G20" s="8"/>
-      <c r="H20" s="81"/>
-      <c r="I20" s="79"/>
-      <c r="J20" s="82"/>
+      <c r="H20" s="86"/>
+      <c r="I20" s="84"/>
+      <c r="J20" s="87"/>
     </row>
     <row r="21" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A21" s="78"/>
-      <c r="B21" s="79"/>
-      <c r="C21" s="80"/>
+      <c r="A21" s="83"/>
+      <c r="B21" s="84"/>
+      <c r="C21" s="85"/>
       <c r="D21" s="7"/>
       <c r="E21" s="7"/>
       <c r="F21" s="8"/>
       <c r="G21" s="8"/>
-      <c r="H21" s="81"/>
-      <c r="I21" s="79"/>
-      <c r="J21" s="82"/>
+      <c r="H21" s="86"/>
+      <c r="I21" s="84"/>
+      <c r="J21" s="87"/>
     </row>
     <row r="22" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A22" s="78"/>
-      <c r="B22" s="79"/>
-      <c r="C22" s="80"/>
+      <c r="A22" s="83"/>
+      <c r="B22" s="84"/>
+      <c r="C22" s="85"/>
       <c r="D22" s="7"/>
       <c r="E22" s="7"/>
       <c r="F22" s="8"/>
       <c r="G22" s="8"/>
-      <c r="H22" s="81"/>
-      <c r="I22" s="79"/>
-      <c r="J22" s="82"/>
+      <c r="H22" s="86"/>
+      <c r="I22" s="84"/>
+      <c r="J22" s="87"/>
     </row>
     <row r="23" spans="1:10" ht="19.5" customHeight="1" thickBot="1">
-      <c r="A23" s="83"/>
-      <c r="B23" s="84"/>
-      <c r="C23" s="85"/>
+      <c r="A23" s="88"/>
+      <c r="B23" s="89"/>
+      <c r="C23" s="90"/>
       <c r="D23" s="9"/>
       <c r="E23" s="9"/>
       <c r="F23" s="10"/>
       <c r="G23" s="10"/>
-      <c r="H23" s="86"/>
-      <c r="I23" s="84"/>
-      <c r="J23" s="87"/>
+      <c r="H23" s="91"/>
+      <c r="I23" s="89"/>
+      <c r="J23" s="92"/>
     </row>
     <row r="24" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="25" spans="1:10" ht="12.75" customHeight="1"/>
@@ -4879,6 +4956,1429 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F3EE704D-4986-4CB2-806F-AC50916B16CA}">
+  <dimension ref="A1:J1000"/>
+  <sheetFormatPr defaultColWidth="12.625" defaultRowHeight="15" customHeight="1"/>
+  <cols>
+    <col min="1" max="3" width="4.5" style="13" customWidth="1"/>
+    <col min="4" max="10" width="14.625" style="13" customWidth="1"/>
+    <col min="11" max="26" width="7.625" style="13" customWidth="1"/>
+    <col min="27" max="16384" width="12.625" style="13"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" ht="18" customHeight="1">
+      <c r="A1" s="137" t="s">
+        <v>86</v>
+      </c>
+      <c r="B1" s="48"/>
+      <c r="C1" s="49"/>
+      <c r="D1" s="56" t="s">
+        <v>0</v>
+      </c>
+      <c r="E1" s="57"/>
+      <c r="F1" s="56" t="s">
+        <v>1</v>
+      </c>
+      <c r="G1" s="57"/>
+      <c r="H1" s="37" t="s">
+        <v>2</v>
+      </c>
+      <c r="I1" s="11" t="s">
+        <v>3</v>
+      </c>
+      <c r="J1" s="41" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" ht="18" customHeight="1">
+      <c r="A2" s="50"/>
+      <c r="B2" s="51"/>
+      <c r="C2" s="52"/>
+      <c r="D2" s="58" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2" s="59"/>
+      <c r="F2" s="58" t="s">
+        <v>7</v>
+      </c>
+      <c r="G2" s="59"/>
+      <c r="H2" s="62">
+        <v>45818</v>
+      </c>
+      <c r="I2" s="65" t="s">
+        <v>28</v>
+      </c>
+      <c r="J2" s="66"/>
+    </row>
+    <row r="3" spans="1:10" ht="18" customHeight="1">
+      <c r="A3" s="50"/>
+      <c r="B3" s="51"/>
+      <c r="C3" s="52"/>
+      <c r="D3" s="60"/>
+      <c r="E3" s="52"/>
+      <c r="F3" s="60"/>
+      <c r="G3" s="52"/>
+      <c r="H3" s="63"/>
+      <c r="I3" s="63"/>
+      <c r="J3" s="67"/>
+    </row>
+    <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
+      <c r="A4" s="53"/>
+      <c r="B4" s="54"/>
+      <c r="C4" s="55"/>
+      <c r="D4" s="61"/>
+      <c r="E4" s="55"/>
+      <c r="F4" s="61"/>
+      <c r="G4" s="55"/>
+      <c r="H4" s="64"/>
+      <c r="I4" s="64"/>
+      <c r="J4" s="68"/>
+    </row>
+    <row r="5" spans="1:10" ht="12.75" customHeight="1">
+      <c r="A5" s="24"/>
+      <c r="B5" s="23"/>
+      <c r="C5" s="23"/>
+      <c r="D5" s="23"/>
+      <c r="E5" s="23"/>
+      <c r="F5" s="23"/>
+      <c r="G5" s="23"/>
+      <c r="H5" s="23"/>
+      <c r="I5" s="23"/>
+      <c r="J5" s="22"/>
+    </row>
+    <row r="6" spans="1:10" ht="12.75" customHeight="1">
+      <c r="A6" s="24"/>
+      <c r="B6" s="23"/>
+      <c r="C6" s="23"/>
+      <c r="D6" s="23"/>
+      <c r="E6" s="23"/>
+      <c r="F6" s="23"/>
+      <c r="G6" s="23"/>
+      <c r="H6" s="23"/>
+      <c r="I6" s="23"/>
+      <c r="J6" s="22"/>
+    </row>
+    <row r="7" spans="1:10" ht="12.75" customHeight="1">
+      <c r="A7" s="24"/>
+      <c r="B7" s="23"/>
+      <c r="C7" s="23"/>
+      <c r="D7" s="23"/>
+      <c r="E7" s="23"/>
+      <c r="F7" s="23"/>
+      <c r="G7" s="23"/>
+      <c r="H7" s="23"/>
+      <c r="I7" s="23"/>
+      <c r="J7" s="22"/>
+    </row>
+    <row r="8" spans="1:10" ht="12.75" customHeight="1">
+      <c r="A8" s="24"/>
+      <c r="B8" s="23"/>
+      <c r="C8" s="23"/>
+      <c r="D8" s="23"/>
+      <c r="E8" s="23"/>
+      <c r="F8" s="23"/>
+      <c r="G8" s="23"/>
+      <c r="H8" s="23"/>
+      <c r="I8" s="23"/>
+      <c r="J8" s="22"/>
+    </row>
+    <row r="9" spans="1:10" ht="12.75" customHeight="1">
+      <c r="A9" s="24"/>
+      <c r="B9" s="23"/>
+      <c r="C9" s="23"/>
+      <c r="D9" s="23"/>
+      <c r="E9" s="23"/>
+      <c r="F9" s="23"/>
+      <c r="G9" s="23"/>
+      <c r="H9" s="23"/>
+      <c r="I9" s="23"/>
+      <c r="J9" s="22"/>
+    </row>
+    <row r="10" spans="1:10" ht="12.75" customHeight="1">
+      <c r="A10" s="24"/>
+      <c r="B10" s="23"/>
+      <c r="C10" s="23"/>
+      <c r="D10" s="23"/>
+      <c r="E10" s="23"/>
+      <c r="F10" s="23"/>
+      <c r="G10" s="23"/>
+      <c r="H10" s="23"/>
+      <c r="I10" s="23"/>
+      <c r="J10" s="22"/>
+    </row>
+    <row r="11" spans="1:10" ht="12.75" customHeight="1">
+      <c r="A11" s="24"/>
+      <c r="B11" s="23"/>
+      <c r="C11" s="23"/>
+      <c r="D11" s="23"/>
+      <c r="E11" s="23"/>
+      <c r="F11" s="23"/>
+      <c r="G11" s="23"/>
+      <c r="H11" s="23"/>
+      <c r="I11" s="23"/>
+      <c r="J11" s="22"/>
+    </row>
+    <row r="12" spans="1:10" ht="12.75" customHeight="1">
+      <c r="A12" s="24"/>
+      <c r="B12" s="23"/>
+      <c r="C12" s="23"/>
+      <c r="D12" s="23"/>
+      <c r="E12" s="23"/>
+      <c r="F12" s="23"/>
+      <c r="G12" s="23"/>
+      <c r="H12" s="23"/>
+      <c r="I12" s="23"/>
+      <c r="J12" s="22"/>
+    </row>
+    <row r="13" spans="1:10" ht="12.75" customHeight="1">
+      <c r="A13" s="24"/>
+      <c r="B13" s="23"/>
+      <c r="C13" s="23"/>
+      <c r="D13" s="23"/>
+      <c r="E13" s="23"/>
+      <c r="F13" s="23"/>
+      <c r="G13" s="23"/>
+      <c r="H13" s="23"/>
+      <c r="I13" s="23"/>
+      <c r="J13" s="22"/>
+    </row>
+    <row r="14" spans="1:10" ht="12.75" customHeight="1">
+      <c r="A14" s="24"/>
+      <c r="B14" s="23"/>
+      <c r="C14" s="23"/>
+      <c r="D14" s="23"/>
+      <c r="E14" s="23"/>
+      <c r="F14" s="23"/>
+      <c r="G14" s="23"/>
+      <c r="H14" s="23"/>
+      <c r="I14" s="23"/>
+      <c r="J14" s="22"/>
+    </row>
+    <row r="15" spans="1:10" ht="12.75" customHeight="1">
+      <c r="A15" s="24"/>
+      <c r="B15" s="23"/>
+      <c r="C15" s="23"/>
+      <c r="D15" s="23"/>
+      <c r="E15" s="23"/>
+      <c r="F15" s="23"/>
+      <c r="G15" s="23"/>
+      <c r="H15" s="23"/>
+      <c r="I15" s="23"/>
+      <c r="J15" s="22"/>
+    </row>
+    <row r="16" spans="1:10" ht="12.75" customHeight="1">
+      <c r="A16" s="24"/>
+      <c r="B16" s="23"/>
+      <c r="C16" s="23"/>
+      <c r="D16" s="23"/>
+      <c r="E16" s="23"/>
+      <c r="F16" s="23"/>
+      <c r="G16" s="23"/>
+      <c r="H16" s="23"/>
+      <c r="I16" s="23"/>
+      <c r="J16" s="22"/>
+    </row>
+    <row r="17" spans="1:10" ht="12.75" customHeight="1">
+      <c r="A17" s="24"/>
+      <c r="B17" s="23"/>
+      <c r="C17" s="23"/>
+      <c r="D17" s="23"/>
+      <c r="E17" s="23"/>
+      <c r="F17" s="23"/>
+      <c r="G17" s="23"/>
+      <c r="H17" s="23"/>
+      <c r="I17" s="23"/>
+      <c r="J17" s="22"/>
+    </row>
+    <row r="18" spans="1:10" ht="12.75" customHeight="1">
+      <c r="A18" s="24"/>
+      <c r="B18" s="23"/>
+      <c r="C18" s="23"/>
+      <c r="D18" s="23"/>
+      <c r="E18" s="23"/>
+      <c r="F18" s="23"/>
+      <c r="G18" s="23"/>
+      <c r="H18" s="23"/>
+      <c r="I18" s="23"/>
+      <c r="J18" s="22"/>
+    </row>
+    <row r="19" spans="1:10" ht="12.75" customHeight="1">
+      <c r="A19" s="24"/>
+      <c r="B19" s="23"/>
+      <c r="C19" s="23"/>
+      <c r="D19" s="23"/>
+      <c r="E19" s="23"/>
+      <c r="F19" s="23"/>
+      <c r="G19" s="23"/>
+      <c r="H19" s="23"/>
+      <c r="I19" s="23"/>
+      <c r="J19" s="22"/>
+    </row>
+    <row r="20" spans="1:10" ht="12.75" customHeight="1">
+      <c r="A20" s="24"/>
+      <c r="B20" s="23"/>
+      <c r="C20" s="23"/>
+      <c r="D20" s="23"/>
+      <c r="E20" s="23"/>
+      <c r="F20" s="23"/>
+      <c r="G20" s="23"/>
+      <c r="H20" s="23"/>
+      <c r="I20" s="23"/>
+      <c r="J20" s="22"/>
+    </row>
+    <row r="21" spans="1:10" ht="12.75" customHeight="1">
+      <c r="A21" s="24"/>
+      <c r="B21" s="23"/>
+      <c r="C21" s="23"/>
+      <c r="D21" s="23"/>
+      <c r="E21" s="23"/>
+      <c r="F21" s="23"/>
+      <c r="G21" s="23"/>
+      <c r="H21" s="23"/>
+      <c r="I21" s="23"/>
+      <c r="J21" s="22"/>
+    </row>
+    <row r="22" spans="1:10" ht="12.75" customHeight="1">
+      <c r="A22" s="24"/>
+      <c r="B22" s="23"/>
+      <c r="C22" s="23"/>
+      <c r="D22" s="23"/>
+      <c r="E22" s="23"/>
+      <c r="F22" s="23"/>
+      <c r="G22" s="23"/>
+      <c r="H22" s="23"/>
+      <c r="I22" s="23"/>
+      <c r="J22" s="22"/>
+    </row>
+    <row r="23" spans="1:10" ht="12.75" customHeight="1">
+      <c r="A23" s="24"/>
+      <c r="B23" s="23"/>
+      <c r="C23" s="23"/>
+      <c r="D23" s="23"/>
+      <c r="E23" s="23"/>
+      <c r="F23" s="23"/>
+      <c r="G23" s="23"/>
+      <c r="H23" s="23"/>
+      <c r="I23" s="23"/>
+      <c r="J23" s="22"/>
+    </row>
+    <row r="24" spans="1:10" ht="12.75" customHeight="1">
+      <c r="A24" s="24"/>
+      <c r="B24" s="23"/>
+      <c r="C24" s="23"/>
+      <c r="D24" s="23"/>
+      <c r="E24" s="23"/>
+      <c r="F24" s="23"/>
+      <c r="G24" s="23"/>
+      <c r="H24" s="23"/>
+      <c r="I24" s="23"/>
+      <c r="J24" s="22"/>
+    </row>
+    <row r="25" spans="1:10" ht="12.75" customHeight="1">
+      <c r="A25" s="24"/>
+      <c r="B25" s="23"/>
+      <c r="C25" s="23"/>
+      <c r="D25" s="23"/>
+      <c r="E25" s="23"/>
+      <c r="F25" s="23"/>
+      <c r="G25" s="23"/>
+      <c r="H25" s="23"/>
+      <c r="I25" s="23"/>
+      <c r="J25" s="22"/>
+    </row>
+    <row r="26" spans="1:10" ht="12.75" customHeight="1">
+      <c r="A26" s="24"/>
+      <c r="B26" s="23"/>
+      <c r="C26" s="23"/>
+      <c r="D26" s="23"/>
+      <c r="E26" s="23"/>
+      <c r="F26" s="23"/>
+      <c r="G26" s="23"/>
+      <c r="H26" s="23"/>
+      <c r="I26" s="23"/>
+      <c r="J26" s="22"/>
+    </row>
+    <row r="27" spans="1:10" ht="12.75" customHeight="1">
+      <c r="A27" s="24"/>
+      <c r="B27" s="23"/>
+      <c r="C27" s="23"/>
+      <c r="D27" s="23"/>
+      <c r="E27" s="23"/>
+      <c r="F27" s="23"/>
+      <c r="G27" s="23"/>
+      <c r="H27" s="23"/>
+      <c r="I27" s="23"/>
+      <c r="J27" s="22"/>
+    </row>
+    <row r="28" spans="1:10" ht="12.75" customHeight="1">
+      <c r="A28" s="24"/>
+      <c r="B28" s="23"/>
+      <c r="C28" s="23"/>
+      <c r="D28" s="23"/>
+      <c r="E28" s="23"/>
+      <c r="F28" s="23"/>
+      <c r="G28" s="23"/>
+      <c r="H28" s="23"/>
+      <c r="I28" s="23"/>
+      <c r="J28" s="22"/>
+    </row>
+    <row r="29" spans="1:10" ht="12.75" customHeight="1">
+      <c r="A29" s="24"/>
+      <c r="B29" s="23"/>
+      <c r="C29" s="23"/>
+      <c r="D29" s="23"/>
+      <c r="E29" s="23"/>
+      <c r="F29" s="23"/>
+      <c r="G29" s="23"/>
+      <c r="H29" s="23"/>
+      <c r="I29" s="23"/>
+      <c r="J29" s="22"/>
+    </row>
+    <row r="30" spans="1:10" ht="12.75" customHeight="1">
+      <c r="A30" s="24"/>
+      <c r="B30" s="23"/>
+      <c r="C30" s="23"/>
+      <c r="D30" s="23"/>
+      <c r="E30" s="23"/>
+      <c r="F30" s="23"/>
+      <c r="G30" s="23"/>
+      <c r="H30" s="23"/>
+      <c r="I30" s="23"/>
+      <c r="J30" s="22"/>
+    </row>
+    <row r="31" spans="1:10" ht="12.75" customHeight="1">
+      <c r="A31" s="24"/>
+      <c r="B31" s="23"/>
+      <c r="C31" s="23"/>
+      <c r="D31" s="23"/>
+      <c r="E31" s="23"/>
+      <c r="F31" s="23"/>
+      <c r="G31" s="23"/>
+      <c r="H31" s="23"/>
+      <c r="I31" s="23"/>
+      <c r="J31" s="22"/>
+    </row>
+    <row r="32" spans="1:10" ht="12.75" customHeight="1">
+      <c r="A32" s="24"/>
+      <c r="B32" s="23"/>
+      <c r="C32" s="23"/>
+      <c r="D32" s="23"/>
+      <c r="E32" s="23"/>
+      <c r="F32" s="23"/>
+      <c r="G32" s="23"/>
+      <c r="H32" s="23"/>
+      <c r="I32" s="23"/>
+      <c r="J32" s="22"/>
+    </row>
+    <row r="33" spans="1:10" ht="12.75" customHeight="1">
+      <c r="A33" s="24"/>
+      <c r="B33" s="23"/>
+      <c r="C33" s="23"/>
+      <c r="D33" s="23"/>
+      <c r="E33" s="23"/>
+      <c r="F33" s="23"/>
+      <c r="G33" s="23"/>
+      <c r="H33" s="23"/>
+      <c r="I33" s="23"/>
+      <c r="J33" s="22"/>
+    </row>
+    <row r="34" spans="1:10" ht="12.75" customHeight="1" thickBot="1">
+      <c r="A34" s="40"/>
+      <c r="B34" s="39"/>
+      <c r="C34" s="39"/>
+      <c r="D34" s="39"/>
+      <c r="E34" s="39"/>
+      <c r="F34" s="39"/>
+      <c r="G34" s="39"/>
+      <c r="H34" s="39"/>
+      <c r="I34" s="39"/>
+      <c r="J34" s="38"/>
+    </row>
+    <row r="35" spans="1:10" ht="12.75" customHeight="1"/>
+    <row r="36" spans="1:10" ht="12.75" customHeight="1"/>
+    <row r="37" spans="1:10" ht="12.75" customHeight="1"/>
+    <row r="38" spans="1:10" ht="12.75" customHeight="1"/>
+    <row r="39" spans="1:10" ht="12.75" customHeight="1"/>
+    <row r="40" spans="1:10" ht="12.75" customHeight="1"/>
+    <row r="41" spans="1:10" ht="12.75" customHeight="1"/>
+    <row r="42" spans="1:10" ht="12.75" customHeight="1"/>
+    <row r="43" spans="1:10" ht="12.75" customHeight="1"/>
+    <row r="44" spans="1:10" ht="12.75" customHeight="1"/>
+    <row r="45" spans="1:10" ht="12.75" customHeight="1"/>
+    <row r="46" spans="1:10" ht="12.75" customHeight="1"/>
+    <row r="47" spans="1:10" ht="12.75" customHeight="1"/>
+    <row r="48" spans="1:10" ht="12.75" customHeight="1"/>
+    <row r="49" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="50" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="51" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="52" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="53" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="54" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="55" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="56" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="57" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="58" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="59" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="60" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="61" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="62" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="63" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="64" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="65" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="66" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="67" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="68" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="69" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="70" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="71" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="72" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="73" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="74" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="75" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="76" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="77" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="78" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="79" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="80" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="81" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="82" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="83" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="84" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="85" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="86" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="87" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="88" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="89" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="90" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="91" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="92" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="93" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="94" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="95" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="96" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="97" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="98" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="99" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="100" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="101" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="102" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="103" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="104" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="105" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="106" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="107" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="108" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="109" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="110" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="111" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="112" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="113" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="114" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="115" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="116" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="117" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="118" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="119" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="120" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="121" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="122" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="123" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="124" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="125" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="126" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="127" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="128" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="129" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="130" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="131" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="132" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="133" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="134" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="135" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="136" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="137" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="138" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="139" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="140" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="141" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="142" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="143" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="144" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="145" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="146" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="147" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="148" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="149" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="150" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="151" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="152" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="153" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="154" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="155" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="156" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="157" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="158" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="159" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="160" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="161" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="162" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="163" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="164" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="165" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="166" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="167" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="168" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="169" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="170" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="171" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="172" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="173" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="174" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="175" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="176" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="177" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="178" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="179" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="180" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="181" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="182" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="183" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="184" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="185" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="186" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="187" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="188" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="189" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="190" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="191" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="192" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="193" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="194" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="195" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="196" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="197" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="198" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="199" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="200" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="201" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="202" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="203" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="204" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="205" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="206" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="207" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="208" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="209" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="210" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="211" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="212" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="213" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="214" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="215" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="216" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="217" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="218" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="219" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="220" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="221" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="222" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="223" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="224" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="225" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="226" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="227" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="228" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="229" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="230" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="231" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="232" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="233" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="234" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="235" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="236" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="237" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="238" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="239" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="240" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="241" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="242" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="243" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="244" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="245" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="246" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="247" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="248" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="249" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="250" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="251" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="252" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="253" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="254" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="255" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="256" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="257" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="258" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="259" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="260" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="261" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="262" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="263" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="264" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="265" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="266" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="267" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="268" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="269" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="270" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="271" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="272" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="273" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="274" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="275" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="276" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="277" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="278" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="279" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="280" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="281" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="282" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="283" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="284" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="285" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="286" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="287" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="288" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="289" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="290" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="291" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="292" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="293" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="294" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="295" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="296" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="297" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="298" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="299" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="300" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="301" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="302" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="303" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="304" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="305" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="306" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="307" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="308" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="309" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="310" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="311" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="312" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="313" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="314" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="315" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="316" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="317" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="318" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="319" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="320" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="321" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="322" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="323" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="324" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="325" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="326" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="327" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="328" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="329" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="330" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="331" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="332" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="333" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="334" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="335" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="336" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="337" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="338" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="339" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="340" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="341" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="342" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="343" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="344" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="345" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="346" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="347" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="348" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="349" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="350" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="351" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="352" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="353" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="354" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="355" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="356" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="357" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="358" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="359" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="360" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="361" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="362" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="363" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="364" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="365" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="366" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="367" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="368" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="369" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="370" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="371" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="372" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="373" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="374" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="375" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="376" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="377" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="378" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="379" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="380" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="381" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="382" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="383" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="384" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="385" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="386" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="387" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="388" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="389" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="390" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="391" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="392" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="393" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="394" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="395" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="396" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="397" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="398" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="399" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="400" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="401" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="402" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="403" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="404" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="405" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="406" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="407" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="408" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="409" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="410" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="411" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="412" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="413" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="414" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="415" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="416" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="417" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="418" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="419" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="420" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="421" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="422" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="423" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="424" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="425" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="426" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="427" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="428" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="429" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="430" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="431" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="432" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="433" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="434" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="435" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="436" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="437" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="438" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="439" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="440" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="441" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="442" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="443" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="444" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="445" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="446" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="447" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="448" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="449" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="450" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="451" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="452" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="453" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="454" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="455" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="456" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="457" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="458" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="459" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="460" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="461" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="462" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="463" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="464" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="465" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="466" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="467" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="468" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="469" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="470" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="471" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="472" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="473" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="474" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="475" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="476" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="477" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="478" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="479" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="480" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="481" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="482" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="483" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="484" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="485" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="486" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="487" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="488" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="489" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="490" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="491" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="492" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="493" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="494" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="495" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="496" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="497" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="498" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="499" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="500" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="501" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="502" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="503" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="504" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="505" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="506" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="507" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="508" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="509" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="510" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="511" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="512" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="513" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="514" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="515" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="516" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="517" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="518" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="519" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="520" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="521" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="522" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="523" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="524" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="525" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="526" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="527" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="528" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="529" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="530" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="531" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="532" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="533" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="534" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="535" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="536" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="537" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="538" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="539" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="540" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="541" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="542" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="543" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="544" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="545" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="546" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="547" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="548" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="549" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="550" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="551" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="552" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="553" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="554" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="555" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="556" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="557" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="558" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="559" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="560" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="561" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="562" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="563" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="564" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="565" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="566" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="567" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="568" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="569" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="570" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="571" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="572" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="573" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="574" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="575" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="576" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="577" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="578" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="579" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="580" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="581" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="582" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="583" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="584" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="585" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="586" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="587" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="588" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="589" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="590" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="591" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="592" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="593" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="594" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="595" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="596" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="597" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="598" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="599" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="600" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="601" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="602" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="603" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="604" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="605" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="606" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="607" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="608" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="609" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="610" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="611" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="612" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="613" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="614" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="615" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="616" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="617" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="618" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="619" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="620" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="621" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="622" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="623" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="624" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="625" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="626" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="627" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="628" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="629" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="630" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="631" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="632" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="633" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="634" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="635" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="636" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="637" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="638" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="639" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="640" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="641" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="642" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="643" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="644" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="645" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="646" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="647" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="648" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="649" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="650" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="651" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="652" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="653" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="654" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="655" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="656" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="657" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="658" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="659" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="660" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="661" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="662" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="663" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="664" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="665" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="666" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="667" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="668" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="669" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="670" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="671" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="672" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="673" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="674" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="675" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="676" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="677" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="678" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="679" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="680" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="681" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="682" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="683" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="684" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="685" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="686" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="687" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="688" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="689" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="690" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="691" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="692" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="693" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="694" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="695" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="696" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="697" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="698" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="699" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="700" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="701" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="702" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="703" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="704" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="705" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="706" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="707" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="708" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="709" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="710" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="711" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="712" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="713" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="714" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="715" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="716" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="717" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="718" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="719" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="720" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="721" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="722" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="723" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="724" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="725" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="726" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="727" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="728" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="729" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="730" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="731" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="732" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="733" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="734" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="735" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="736" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="737" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="738" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="739" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="740" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="741" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="742" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="743" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="744" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="745" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="746" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="747" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="748" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="749" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="750" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="751" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="752" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="753" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="754" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="755" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="756" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="757" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="758" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="759" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="760" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="761" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="762" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="763" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="764" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="765" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="766" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="767" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="768" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="769" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="770" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="771" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="772" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="773" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="774" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="775" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="776" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="777" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="778" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="779" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="780" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="781" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="782" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="783" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="784" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="785" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="786" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="787" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="788" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="789" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="790" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="791" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="792" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="793" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="794" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="795" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="796" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="797" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="798" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="799" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="800" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="801" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="802" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="803" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="804" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="805" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="806" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="807" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="808" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="809" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="810" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="811" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="812" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="813" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="814" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="815" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="816" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="817" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="818" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="819" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="820" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="821" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="822" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="823" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="824" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="825" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="826" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="827" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="828" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="829" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="830" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="831" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="832" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="833" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="834" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="835" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="836" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="837" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="838" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="839" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="840" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="841" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="842" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="843" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="844" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="845" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="846" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="847" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="848" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="849" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="850" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="851" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="852" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="853" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="854" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="855" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="856" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="857" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="858" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="859" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="860" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="861" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="862" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="863" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="864" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="865" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="866" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="867" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="868" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="869" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="870" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="871" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="872" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="873" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="874" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="875" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="876" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="877" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="878" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="879" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="880" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="881" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="882" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="883" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="884" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="885" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="886" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="887" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="888" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="889" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="890" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="891" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="892" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="893" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="894" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="895" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="896" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="897" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="898" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="899" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="900" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="901" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="902" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="903" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="904" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="905" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="906" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="907" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="908" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="909" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="910" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="911" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="912" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="913" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="914" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="915" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="916" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="917" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="918" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="919" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="920" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="921" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="922" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="923" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="924" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="925" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="926" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="927" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="928" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="929" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="930" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="931" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="932" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="933" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="934" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="935" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="936" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="937" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="938" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="939" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="940" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="941" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="942" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="943" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="944" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="945" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="946" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="947" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="948" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="949" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="950" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="951" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="952" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="953" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="954" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="955" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="956" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="957" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="958" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="959" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="960" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="961" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="962" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="963" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="964" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="965" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="966" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="967" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="968" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="969" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="970" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="971" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="972" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="973" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="974" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="975" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="976" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="977" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="978" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="979" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="980" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="981" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="982" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="983" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="984" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="985" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="986" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="987" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="988" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="989" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="990" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="991" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="992" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="993" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="994" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="995" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="996" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="997" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="998" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="999" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="1000" s="13" customFormat="1" ht="12.75" customHeight="1"/>
+  </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="H2:H4"/>
+    <mergeCell ref="I2:I4"/>
+    <mergeCell ref="J2:J4"/>
+    <mergeCell ref="A1:C4"/>
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="F1:G1"/>
+    <mergeCell ref="D2:E4"/>
+    <mergeCell ref="F2:G4"/>
+  </mergeCells>
+  <phoneticPr fontId="3"/>
+  <pageMargins left="0.70833333333333304" right="0.70833333333333304" top="0.74791666666666701" bottom="0.74791666666666701" header="0" footer="0"/>
+  <pageSetup paperSize="9" orientation="landscape"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4B2F631B-71E1-442C-9AE2-53D543A90339}">
   <dimension ref="A1:Z1000"/>
   <sheetFormatPr defaultColWidth="12.625" defaultRowHeight="15" customHeight="1"/>
@@ -4893,190 +6393,190 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="18" customHeight="1">
-      <c r="A1" s="42" t="s">
+      <c r="A1" s="47" t="s">
         <v>67</v>
       </c>
-      <c r="B1" s="43"/>
-      <c r="C1" s="43"/>
-      <c r="D1" s="43"/>
-      <c r="E1" s="43"/>
-      <c r="F1" s="44"/>
-      <c r="G1" s="51" t="s">
+      <c r="B1" s="48"/>
+      <c r="C1" s="48"/>
+      <c r="D1" s="48"/>
+      <c r="E1" s="48"/>
+      <c r="F1" s="49"/>
+      <c r="G1" s="56" t="s">
         <v>0</v>
       </c>
-      <c r="H1" s="65"/>
-      <c r="I1" s="65"/>
-      <c r="J1" s="52"/>
-      <c r="K1" s="51" t="s">
+      <c r="H1" s="70"/>
+      <c r="I1" s="70"/>
+      <c r="J1" s="57"/>
+      <c r="K1" s="56" t="s">
         <v>1</v>
       </c>
-      <c r="L1" s="65"/>
-      <c r="M1" s="65"/>
-      <c r="N1" s="52"/>
-      <c r="O1" s="51" t="s">
+      <c r="L1" s="70"/>
+      <c r="M1" s="70"/>
+      <c r="N1" s="57"/>
+      <c r="O1" s="56" t="s">
         <v>2</v>
       </c>
-      <c r="P1" s="52"/>
-      <c r="Q1" s="51" t="s">
+      <c r="P1" s="57"/>
+      <c r="Q1" s="56" t="s">
         <v>3</v>
       </c>
-      <c r="R1" s="52"/>
-      <c r="S1" s="51" t="s">
+      <c r="R1" s="57"/>
+      <c r="S1" s="56" t="s">
         <v>4</v>
       </c>
-      <c r="T1" s="67"/>
+      <c r="T1" s="72"/>
     </row>
     <row r="2" spans="1:26" ht="18" customHeight="1">
-      <c r="A2" s="45"/>
-      <c r="B2" s="46"/>
-      <c r="C2" s="46"/>
-      <c r="D2" s="46"/>
-      <c r="E2" s="46"/>
-      <c r="F2" s="47"/>
-      <c r="G2" s="53" t="s">
+      <c r="A2" s="50"/>
+      <c r="B2" s="51"/>
+      <c r="C2" s="51"/>
+      <c r="D2" s="51"/>
+      <c r="E2" s="51"/>
+      <c r="F2" s="52"/>
+      <c r="G2" s="58" t="s">
         <v>6</v>
       </c>
-      <c r="H2" s="119"/>
-      <c r="I2" s="119"/>
-      <c r="J2" s="54"/>
-      <c r="K2" s="53" t="s">
+      <c r="H2" s="124"/>
+      <c r="I2" s="124"/>
+      <c r="J2" s="59"/>
+      <c r="K2" s="58" t="s">
         <v>7</v>
       </c>
-      <c r="L2" s="119"/>
-      <c r="M2" s="119"/>
-      <c r="N2" s="54"/>
-      <c r="O2" s="123">
+      <c r="L2" s="124"/>
+      <c r="M2" s="124"/>
+      <c r="N2" s="59"/>
+      <c r="O2" s="128">
         <v>45810</v>
       </c>
-      <c r="P2" s="54"/>
-      <c r="Q2" s="53" t="s">
+      <c r="P2" s="59"/>
+      <c r="Q2" s="58" t="s">
         <v>28</v>
       </c>
-      <c r="R2" s="54"/>
-      <c r="S2" s="53"/>
-      <c r="T2" s="124"/>
+      <c r="R2" s="59"/>
+      <c r="S2" s="58"/>
+      <c r="T2" s="129"/>
     </row>
     <row r="3" spans="1:26" ht="18" customHeight="1">
-      <c r="A3" s="45"/>
-      <c r="B3" s="46"/>
-      <c r="C3" s="46"/>
-      <c r="D3" s="46"/>
-      <c r="E3" s="46"/>
-      <c r="F3" s="47"/>
-      <c r="G3" s="55"/>
-      <c r="H3" s="46"/>
-      <c r="I3" s="46"/>
-      <c r="J3" s="47"/>
-      <c r="K3" s="55"/>
-      <c r="L3" s="46"/>
-      <c r="M3" s="46"/>
-      <c r="N3" s="47"/>
-      <c r="O3" s="55"/>
-      <c r="P3" s="47"/>
-      <c r="Q3" s="55"/>
-      <c r="R3" s="47"/>
-      <c r="S3" s="55"/>
-      <c r="T3" s="125"/>
+      <c r="A3" s="50"/>
+      <c r="B3" s="51"/>
+      <c r="C3" s="51"/>
+      <c r="D3" s="51"/>
+      <c r="E3" s="51"/>
+      <c r="F3" s="52"/>
+      <c r="G3" s="60"/>
+      <c r="H3" s="51"/>
+      <c r="I3" s="51"/>
+      <c r="J3" s="52"/>
+      <c r="K3" s="60"/>
+      <c r="L3" s="51"/>
+      <c r="M3" s="51"/>
+      <c r="N3" s="52"/>
+      <c r="O3" s="60"/>
+      <c r="P3" s="52"/>
+      <c r="Q3" s="60"/>
+      <c r="R3" s="52"/>
+      <c r="S3" s="60"/>
+      <c r="T3" s="130"/>
     </row>
     <row r="4" spans="1:26" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="48"/>
-      <c r="B4" s="49"/>
-      <c r="C4" s="49"/>
-      <c r="D4" s="49"/>
-      <c r="E4" s="49"/>
-      <c r="F4" s="50"/>
-      <c r="G4" s="56"/>
-      <c r="H4" s="49"/>
-      <c r="I4" s="49"/>
-      <c r="J4" s="50"/>
-      <c r="K4" s="56"/>
-      <c r="L4" s="49"/>
-      <c r="M4" s="49"/>
-      <c r="N4" s="50"/>
-      <c r="O4" s="56"/>
-      <c r="P4" s="50"/>
-      <c r="Q4" s="56"/>
-      <c r="R4" s="50"/>
-      <c r="S4" s="56"/>
-      <c r="T4" s="126"/>
+      <c r="A4" s="53"/>
+      <c r="B4" s="54"/>
+      <c r="C4" s="54"/>
+      <c r="D4" s="54"/>
+      <c r="E4" s="54"/>
+      <c r="F4" s="55"/>
+      <c r="G4" s="61"/>
+      <c r="H4" s="54"/>
+      <c r="I4" s="54"/>
+      <c r="J4" s="55"/>
+      <c r="K4" s="61"/>
+      <c r="L4" s="54"/>
+      <c r="M4" s="54"/>
+      <c r="N4" s="55"/>
+      <c r="O4" s="61"/>
+      <c r="P4" s="55"/>
+      <c r="Q4" s="61"/>
+      <c r="R4" s="55"/>
+      <c r="S4" s="61"/>
+      <c r="T4" s="131"/>
     </row>
     <row r="5" spans="1:26" ht="18" customHeight="1">
-      <c r="A5" s="121" t="s">
+      <c r="A5" s="126" t="s">
         <v>66</v>
       </c>
-      <c r="B5" s="65"/>
-      <c r="C5" s="65"/>
-      <c r="D5" s="65"/>
-      <c r="E5" s="65"/>
-      <c r="F5" s="52"/>
-      <c r="G5" s="66" t="s">
+      <c r="B5" s="70"/>
+      <c r="C5" s="70"/>
+      <c r="D5" s="70"/>
+      <c r="E5" s="70"/>
+      <c r="F5" s="57"/>
+      <c r="G5" s="71" t="s">
         <v>65</v>
       </c>
-      <c r="H5" s="65"/>
-      <c r="I5" s="65"/>
-      <c r="J5" s="65"/>
-      <c r="K5" s="65"/>
-      <c r="L5" s="65"/>
-      <c r="M5" s="65"/>
-      <c r="N5" s="65"/>
-      <c r="O5" s="65"/>
-      <c r="P5" s="65"/>
-      <c r="Q5" s="65"/>
-      <c r="R5" s="65"/>
-      <c r="S5" s="65"/>
-      <c r="T5" s="67"/>
+      <c r="H5" s="70"/>
+      <c r="I5" s="70"/>
+      <c r="J5" s="70"/>
+      <c r="K5" s="70"/>
+      <c r="L5" s="70"/>
+      <c r="M5" s="70"/>
+      <c r="N5" s="70"/>
+      <c r="O5" s="70"/>
+      <c r="P5" s="70"/>
+      <c r="Q5" s="70"/>
+      <c r="R5" s="70"/>
+      <c r="S5" s="70"/>
+      <c r="T5" s="72"/>
     </row>
     <row r="6" spans="1:26" ht="18" customHeight="1">
-      <c r="A6" s="122" t="s">
+      <c r="A6" s="127" t="s">
         <v>64</v>
       </c>
-      <c r="B6" s="38"/>
-      <c r="C6" s="38"/>
-      <c r="D6" s="38"/>
-      <c r="E6" s="38"/>
-      <c r="F6" s="39"/>
-      <c r="G6" s="40" t="s">
+      <c r="B6" s="43"/>
+      <c r="C6" s="43"/>
+      <c r="D6" s="43"/>
+      <c r="E6" s="43"/>
+      <c r="F6" s="44"/>
+      <c r="G6" s="45" t="s">
         <v>80</v>
       </c>
-      <c r="H6" s="38"/>
-      <c r="I6" s="38"/>
-      <c r="J6" s="38"/>
-      <c r="K6" s="38"/>
-      <c r="L6" s="38"/>
-      <c r="M6" s="38"/>
-      <c r="N6" s="38"/>
-      <c r="O6" s="38"/>
-      <c r="P6" s="38"/>
-      <c r="Q6" s="38"/>
-      <c r="R6" s="38"/>
-      <c r="S6" s="38"/>
-      <c r="T6" s="41"/>
+      <c r="H6" s="43"/>
+      <c r="I6" s="43"/>
+      <c r="J6" s="43"/>
+      <c r="K6" s="43"/>
+      <c r="L6" s="43"/>
+      <c r="M6" s="43"/>
+      <c r="N6" s="43"/>
+      <c r="O6" s="43"/>
+      <c r="P6" s="43"/>
+      <c r="Q6" s="43"/>
+      <c r="R6" s="43"/>
+      <c r="S6" s="43"/>
+      <c r="T6" s="46"/>
     </row>
     <row r="7" spans="1:26" ht="18" customHeight="1">
-      <c r="A7" s="122" t="s">
+      <c r="A7" s="127" t="s">
         <v>63</v>
       </c>
-      <c r="B7" s="38"/>
-      <c r="C7" s="38"/>
-      <c r="D7" s="38"/>
-      <c r="E7" s="38"/>
-      <c r="F7" s="39"/>
-      <c r="G7" s="40" t="s">
+      <c r="B7" s="43"/>
+      <c r="C7" s="43"/>
+      <c r="D7" s="43"/>
+      <c r="E7" s="43"/>
+      <c r="F7" s="44"/>
+      <c r="G7" s="45" t="s">
         <v>79</v>
       </c>
-      <c r="H7" s="38"/>
-      <c r="I7" s="38"/>
-      <c r="J7" s="38"/>
-      <c r="K7" s="38"/>
-      <c r="L7" s="38"/>
-      <c r="M7" s="38"/>
-      <c r="N7" s="38"/>
-      <c r="O7" s="38"/>
-      <c r="P7" s="38"/>
-      <c r="Q7" s="38"/>
-      <c r="R7" s="38"/>
-      <c r="S7" s="38"/>
-      <c r="T7" s="41"/>
+      <c r="H7" s="43"/>
+      <c r="I7" s="43"/>
+      <c r="J7" s="43"/>
+      <c r="K7" s="43"/>
+      <c r="L7" s="43"/>
+      <c r="M7" s="43"/>
+      <c r="N7" s="43"/>
+      <c r="O7" s="43"/>
+      <c r="P7" s="43"/>
+      <c r="Q7" s="43"/>
+      <c r="R7" s="43"/>
+      <c r="S7" s="43"/>
+      <c r="T7" s="46"/>
     </row>
     <row r="8" spans="1:26" ht="7.5" customHeight="1">
       <c r="A8" s="24"/>
@@ -5275,37 +6775,37 @@
       <c r="T14" s="22"/>
     </row>
     <row r="15" spans="1:26" ht="18.75" customHeight="1">
-      <c r="A15" s="122" t="s">
+      <c r="A15" s="127" t="s">
         <v>57</v>
       </c>
-      <c r="B15" s="39"/>
-      <c r="C15" s="129" t="s">
+      <c r="B15" s="44"/>
+      <c r="C15" s="134" t="s">
         <v>56</v>
       </c>
-      <c r="D15" s="39"/>
-      <c r="E15" s="120" t="s">
+      <c r="D15" s="44"/>
+      <c r="E15" s="125" t="s">
         <v>55</v>
       </c>
-      <c r="F15" s="39"/>
-      <c r="G15" s="120" t="s">
+      <c r="F15" s="44"/>
+      <c r="G15" s="125" t="s">
         <v>54</v>
       </c>
-      <c r="H15" s="38"/>
-      <c r="I15" s="39"/>
-      <c r="J15" s="120" t="s">
+      <c r="H15" s="43"/>
+      <c r="I15" s="44"/>
+      <c r="J15" s="125" t="s">
         <v>53</v>
       </c>
-      <c r="K15" s="39"/>
-      <c r="L15" s="120" t="s">
+      <c r="K15" s="44"/>
+      <c r="L15" s="125" t="s">
         <v>52</v>
       </c>
-      <c r="M15" s="38"/>
-      <c r="N15" s="39"/>
-      <c r="O15" s="120" t="s">
+      <c r="M15" s="43"/>
+      <c r="N15" s="44"/>
+      <c r="O15" s="125" t="s">
         <v>51</v>
       </c>
-      <c r="P15" s="38"/>
-      <c r="Q15" s="39"/>
+      <c r="P15" s="43"/>
+      <c r="Q15" s="44"/>
       <c r="R15" s="21" t="s">
         <v>50</v>
       </c>
@@ -5317,37 +6817,37 @@
       </c>
     </row>
     <row r="16" spans="1:26" ht="48" customHeight="1">
-      <c r="A16" s="127">
+      <c r="A16" s="132">
         <v>1</v>
       </c>
-      <c r="B16" s="39"/>
-      <c r="C16" s="128" t="s">
+      <c r="B16" s="44"/>
+      <c r="C16" s="133" t="s">
         <v>47</v>
       </c>
-      <c r="D16" s="39"/>
-      <c r="E16" s="128" t="s">
+      <c r="D16" s="44"/>
+      <c r="E16" s="133" t="s">
         <v>46</v>
       </c>
-      <c r="F16" s="39"/>
-      <c r="G16" s="115" t="s">
+      <c r="F16" s="44"/>
+      <c r="G16" s="120" t="s">
         <v>69</v>
       </c>
-      <c r="H16" s="38"/>
-      <c r="I16" s="39"/>
-      <c r="J16" s="115" t="s">
+      <c r="H16" s="43"/>
+      <c r="I16" s="44"/>
+      <c r="J16" s="120" t="s">
         <v>68</v>
       </c>
-      <c r="K16" s="39"/>
-      <c r="L16" s="114" t="s">
+      <c r="K16" s="44"/>
+      <c r="L16" s="119" t="s">
         <v>70</v>
       </c>
-      <c r="M16" s="38"/>
-      <c r="N16" s="39"/>
-      <c r="O16" s="114" t="s">
+      <c r="M16" s="43"/>
+      <c r="N16" s="44"/>
+      <c r="O16" s="119" t="s">
         <v>45</v>
       </c>
-      <c r="P16" s="38"/>
-      <c r="Q16" s="39"/>
+      <c r="P16" s="43"/>
+      <c r="Q16" s="44"/>
       <c r="R16" s="36">
         <v>45810</v>
       </c>
@@ -5365,37 +6865,37 @@
       <c r="Z16" s="15"/>
     </row>
     <row r="17" spans="1:26" ht="41.25" customHeight="1">
-      <c r="A17" s="127">
+      <c r="A17" s="132">
         <v>2</v>
       </c>
-      <c r="B17" s="39"/>
-      <c r="C17" s="128" t="s">
+      <c r="B17" s="44"/>
+      <c r="C17" s="133" t="s">
         <v>71</v>
       </c>
-      <c r="D17" s="39"/>
-      <c r="E17" s="128" t="s">
+      <c r="D17" s="44"/>
+      <c r="E17" s="133" t="s">
         <v>46</v>
       </c>
-      <c r="F17" s="39"/>
-      <c r="G17" s="115" t="s">
+      <c r="F17" s="44"/>
+      <c r="G17" s="120" t="s">
         <v>72</v>
       </c>
-      <c r="H17" s="38"/>
-      <c r="I17" s="39"/>
-      <c r="J17" s="115" t="s">
+      <c r="H17" s="43"/>
+      <c r="I17" s="44"/>
+      <c r="J17" s="120" t="s">
         <v>68</v>
       </c>
-      <c r="K17" s="39"/>
-      <c r="L17" s="114" t="s">
+      <c r="K17" s="44"/>
+      <c r="L17" s="119" t="s">
         <v>73</v>
       </c>
-      <c r="M17" s="38"/>
-      <c r="N17" s="39"/>
-      <c r="O17" s="114" t="s">
+      <c r="M17" s="43"/>
+      <c r="N17" s="44"/>
+      <c r="O17" s="119" t="s">
         <v>74</v>
       </c>
-      <c r="P17" s="38"/>
-      <c r="Q17" s="39"/>
+      <c r="P17" s="43"/>
+      <c r="Q17" s="44"/>
       <c r="R17" s="36">
         <v>45810</v>
       </c>
@@ -5413,37 +6913,37 @@
       <c r="Z17" s="15"/>
     </row>
     <row r="18" spans="1:26" ht="57.75" customHeight="1">
-      <c r="A18" s="127">
+      <c r="A18" s="132">
         <v>3</v>
       </c>
-      <c r="B18" s="39"/>
-      <c r="C18" s="128" t="s">
+      <c r="B18" s="44"/>
+      <c r="C18" s="133" t="s">
         <v>71</v>
       </c>
-      <c r="D18" s="39"/>
-      <c r="E18" s="128" t="s">
+      <c r="D18" s="44"/>
+      <c r="E18" s="133" t="s">
         <v>75</v>
       </c>
-      <c r="F18" s="39"/>
-      <c r="G18" s="115" t="s">
+      <c r="F18" s="44"/>
+      <c r="G18" s="120" t="s">
         <v>76</v>
       </c>
-      <c r="H18" s="38"/>
-      <c r="I18" s="39"/>
-      <c r="J18" s="115" t="s">
+      <c r="H18" s="43"/>
+      <c r="I18" s="44"/>
+      <c r="J18" s="120" t="s">
         <v>77</v>
       </c>
-      <c r="K18" s="39"/>
-      <c r="L18" s="118" t="s">
+      <c r="K18" s="44"/>
+      <c r="L18" s="123" t="s">
         <v>81</v>
       </c>
-      <c r="M18" s="38"/>
-      <c r="N18" s="39"/>
-      <c r="O18" s="114" t="s">
+      <c r="M18" s="43"/>
+      <c r="N18" s="44"/>
+      <c r="O18" s="119" t="s">
         <v>78</v>
       </c>
-      <c r="P18" s="38"/>
-      <c r="Q18" s="39"/>
+      <c r="P18" s="43"/>
+      <c r="Q18" s="44"/>
       <c r="R18" s="36">
         <v>45810</v>
       </c>
@@ -5461,23 +6961,23 @@
       <c r="Z18" s="15"/>
     </row>
     <row r="19" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A19" s="127"/>
-      <c r="B19" s="39"/>
-      <c r="C19" s="128"/>
-      <c r="D19" s="39"/>
-      <c r="E19" s="128"/>
-      <c r="F19" s="39"/>
-      <c r="G19" s="115"/>
-      <c r="H19" s="38"/>
-      <c r="I19" s="39"/>
-      <c r="J19" s="115"/>
-      <c r="K19" s="39"/>
-      <c r="L19" s="114"/>
-      <c r="M19" s="38"/>
-      <c r="N19" s="39"/>
-      <c r="O19" s="114"/>
-      <c r="P19" s="38"/>
-      <c r="Q19" s="39"/>
+      <c r="A19" s="132"/>
+      <c r="B19" s="44"/>
+      <c r="C19" s="133"/>
+      <c r="D19" s="44"/>
+      <c r="E19" s="133"/>
+      <c r="F19" s="44"/>
+      <c r="G19" s="120"/>
+      <c r="H19" s="43"/>
+      <c r="I19" s="44"/>
+      <c r="J19" s="120"/>
+      <c r="K19" s="44"/>
+      <c r="L19" s="119"/>
+      <c r="M19" s="43"/>
+      <c r="N19" s="44"/>
+      <c r="O19" s="119"/>
+      <c r="P19" s="43"/>
+      <c r="Q19" s="44"/>
       <c r="R19" s="19"/>
       <c r="S19" s="19"/>
       <c r="T19" s="18"/>
@@ -5489,23 +6989,23 @@
       <c r="Z19" s="15"/>
     </row>
     <row r="20" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A20" s="127"/>
-      <c r="B20" s="39"/>
-      <c r="C20" s="128"/>
-      <c r="D20" s="39"/>
-      <c r="E20" s="128"/>
-      <c r="F20" s="39"/>
-      <c r="G20" s="115"/>
-      <c r="H20" s="38"/>
-      <c r="I20" s="39"/>
-      <c r="J20" s="115"/>
-      <c r="K20" s="39"/>
-      <c r="L20" s="114"/>
-      <c r="M20" s="38"/>
-      <c r="N20" s="39"/>
-      <c r="O20" s="114"/>
-      <c r="P20" s="38"/>
-      <c r="Q20" s="39"/>
+      <c r="A20" s="132"/>
+      <c r="B20" s="44"/>
+      <c r="C20" s="133"/>
+      <c r="D20" s="44"/>
+      <c r="E20" s="133"/>
+      <c r="F20" s="44"/>
+      <c r="G20" s="120"/>
+      <c r="H20" s="43"/>
+      <c r="I20" s="44"/>
+      <c r="J20" s="120"/>
+      <c r="K20" s="44"/>
+      <c r="L20" s="119"/>
+      <c r="M20" s="43"/>
+      <c r="N20" s="44"/>
+      <c r="O20" s="119"/>
+      <c r="P20" s="43"/>
+      <c r="Q20" s="44"/>
       <c r="R20" s="19"/>
       <c r="S20" s="19"/>
       <c r="T20" s="18"/>
@@ -5517,23 +7017,23 @@
       <c r="Z20" s="15"/>
     </row>
     <row r="21" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A21" s="127"/>
-      <c r="B21" s="39"/>
-      <c r="C21" s="128"/>
-      <c r="D21" s="39"/>
-      <c r="E21" s="128"/>
-      <c r="F21" s="39"/>
-      <c r="G21" s="115"/>
-      <c r="H21" s="38"/>
-      <c r="I21" s="39"/>
-      <c r="J21" s="115"/>
-      <c r="K21" s="39"/>
-      <c r="L21" s="114"/>
-      <c r="M21" s="38"/>
-      <c r="N21" s="39"/>
-      <c r="O21" s="114"/>
-      <c r="P21" s="38"/>
-      <c r="Q21" s="39"/>
+      <c r="A21" s="132"/>
+      <c r="B21" s="44"/>
+      <c r="C21" s="133"/>
+      <c r="D21" s="44"/>
+      <c r="E21" s="133"/>
+      <c r="F21" s="44"/>
+      <c r="G21" s="120"/>
+      <c r="H21" s="43"/>
+      <c r="I21" s="44"/>
+      <c r="J21" s="120"/>
+      <c r="K21" s="44"/>
+      <c r="L21" s="119"/>
+      <c r="M21" s="43"/>
+      <c r="N21" s="44"/>
+      <c r="O21" s="119"/>
+      <c r="P21" s="43"/>
+      <c r="Q21" s="44"/>
       <c r="R21" s="19"/>
       <c r="S21" s="19"/>
       <c r="T21" s="18"/>
@@ -5545,23 +7045,23 @@
       <c r="Z21" s="15"/>
     </row>
     <row r="22" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A22" s="127"/>
-      <c r="B22" s="39"/>
-      <c r="C22" s="128"/>
-      <c r="D22" s="39"/>
-      <c r="E22" s="128"/>
-      <c r="F22" s="39"/>
-      <c r="G22" s="115"/>
-      <c r="H22" s="38"/>
-      <c r="I22" s="39"/>
-      <c r="J22" s="115"/>
-      <c r="K22" s="39"/>
-      <c r="L22" s="114"/>
-      <c r="M22" s="38"/>
-      <c r="N22" s="39"/>
-      <c r="O22" s="114"/>
-      <c r="P22" s="38"/>
-      <c r="Q22" s="39"/>
+      <c r="A22" s="132"/>
+      <c r="B22" s="44"/>
+      <c r="C22" s="133"/>
+      <c r="D22" s="44"/>
+      <c r="E22" s="133"/>
+      <c r="F22" s="44"/>
+      <c r="G22" s="120"/>
+      <c r="H22" s="43"/>
+      <c r="I22" s="44"/>
+      <c r="J22" s="120"/>
+      <c r="K22" s="44"/>
+      <c r="L22" s="119"/>
+      <c r="M22" s="43"/>
+      <c r="N22" s="44"/>
+      <c r="O22" s="119"/>
+      <c r="P22" s="43"/>
+      <c r="Q22" s="44"/>
       <c r="R22" s="19"/>
       <c r="S22" s="19"/>
       <c r="T22" s="18"/>
@@ -5573,23 +7073,23 @@
       <c r="Z22" s="15"/>
     </row>
     <row r="23" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A23" s="127"/>
-      <c r="B23" s="39"/>
-      <c r="C23" s="128"/>
-      <c r="D23" s="39"/>
-      <c r="E23" s="128"/>
-      <c r="F23" s="39"/>
-      <c r="G23" s="115"/>
-      <c r="H23" s="38"/>
-      <c r="I23" s="39"/>
-      <c r="J23" s="115"/>
-      <c r="K23" s="39"/>
-      <c r="L23" s="114"/>
-      <c r="M23" s="38"/>
-      <c r="N23" s="39"/>
-      <c r="O23" s="114"/>
-      <c r="P23" s="38"/>
-      <c r="Q23" s="39"/>
+      <c r="A23" s="132"/>
+      <c r="B23" s="44"/>
+      <c r="C23" s="133"/>
+      <c r="D23" s="44"/>
+      <c r="E23" s="133"/>
+      <c r="F23" s="44"/>
+      <c r="G23" s="120"/>
+      <c r="H23" s="43"/>
+      <c r="I23" s="44"/>
+      <c r="J23" s="120"/>
+      <c r="K23" s="44"/>
+      <c r="L23" s="119"/>
+      <c r="M23" s="43"/>
+      <c r="N23" s="44"/>
+      <c r="O23" s="119"/>
+      <c r="P23" s="43"/>
+      <c r="Q23" s="44"/>
       <c r="R23" s="19"/>
       <c r="S23" s="19"/>
       <c r="T23" s="18"/>
@@ -5601,23 +7101,23 @@
       <c r="Z23" s="15"/>
     </row>
     <row r="24" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A24" s="127"/>
-      <c r="B24" s="39"/>
-      <c r="C24" s="128"/>
-      <c r="D24" s="39"/>
-      <c r="E24" s="128"/>
-      <c r="F24" s="39"/>
-      <c r="G24" s="115"/>
-      <c r="H24" s="38"/>
-      <c r="I24" s="39"/>
-      <c r="J24" s="115"/>
-      <c r="K24" s="39"/>
-      <c r="L24" s="114"/>
-      <c r="M24" s="38"/>
-      <c r="N24" s="39"/>
-      <c r="O24" s="114"/>
-      <c r="P24" s="38"/>
-      <c r="Q24" s="39"/>
+      <c r="A24" s="132"/>
+      <c r="B24" s="44"/>
+      <c r="C24" s="133"/>
+      <c r="D24" s="44"/>
+      <c r="E24" s="133"/>
+      <c r="F24" s="44"/>
+      <c r="G24" s="120"/>
+      <c r="H24" s="43"/>
+      <c r="I24" s="44"/>
+      <c r="J24" s="120"/>
+      <c r="K24" s="44"/>
+      <c r="L24" s="119"/>
+      <c r="M24" s="43"/>
+      <c r="N24" s="44"/>
+      <c r="O24" s="119"/>
+      <c r="P24" s="43"/>
+      <c r="Q24" s="44"/>
       <c r="R24" s="19"/>
       <c r="S24" s="19"/>
       <c r="T24" s="18"/>
@@ -5629,23 +7129,23 @@
       <c r="Z24" s="15"/>
     </row>
     <row r="25" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A25" s="127"/>
-      <c r="B25" s="39"/>
-      <c r="C25" s="128"/>
-      <c r="D25" s="39"/>
-      <c r="E25" s="128"/>
-      <c r="F25" s="39"/>
-      <c r="G25" s="115"/>
-      <c r="H25" s="38"/>
-      <c r="I25" s="39"/>
-      <c r="J25" s="115"/>
-      <c r="K25" s="39"/>
-      <c r="L25" s="114"/>
-      <c r="M25" s="38"/>
-      <c r="N25" s="39"/>
-      <c r="O25" s="114"/>
-      <c r="P25" s="38"/>
-      <c r="Q25" s="39"/>
+      <c r="A25" s="132"/>
+      <c r="B25" s="44"/>
+      <c r="C25" s="133"/>
+      <c r="D25" s="44"/>
+      <c r="E25" s="133"/>
+      <c r="F25" s="44"/>
+      <c r="G25" s="120"/>
+      <c r="H25" s="43"/>
+      <c r="I25" s="44"/>
+      <c r="J25" s="120"/>
+      <c r="K25" s="44"/>
+      <c r="L25" s="119"/>
+      <c r="M25" s="43"/>
+      <c r="N25" s="44"/>
+      <c r="O25" s="119"/>
+      <c r="P25" s="43"/>
+      <c r="Q25" s="44"/>
       <c r="R25" s="19"/>
       <c r="S25" s="19"/>
       <c r="T25" s="18"/>
@@ -5657,23 +7157,23 @@
       <c r="Z25" s="15"/>
     </row>
     <row r="26" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A26" s="127"/>
-      <c r="B26" s="39"/>
-      <c r="C26" s="128"/>
-      <c r="D26" s="39"/>
-      <c r="E26" s="128"/>
-      <c r="F26" s="39"/>
-      <c r="G26" s="115"/>
-      <c r="H26" s="38"/>
-      <c r="I26" s="39"/>
-      <c r="J26" s="115"/>
-      <c r="K26" s="39"/>
-      <c r="L26" s="114"/>
-      <c r="M26" s="38"/>
-      <c r="N26" s="39"/>
-      <c r="O26" s="114"/>
-      <c r="P26" s="38"/>
-      <c r="Q26" s="39"/>
+      <c r="A26" s="132"/>
+      <c r="B26" s="44"/>
+      <c r="C26" s="133"/>
+      <c r="D26" s="44"/>
+      <c r="E26" s="133"/>
+      <c r="F26" s="44"/>
+      <c r="G26" s="120"/>
+      <c r="H26" s="43"/>
+      <c r="I26" s="44"/>
+      <c r="J26" s="120"/>
+      <c r="K26" s="44"/>
+      <c r="L26" s="119"/>
+      <c r="M26" s="43"/>
+      <c r="N26" s="44"/>
+      <c r="O26" s="119"/>
+      <c r="P26" s="43"/>
+      <c r="Q26" s="44"/>
       <c r="R26" s="19"/>
       <c r="S26" s="19"/>
       <c r="T26" s="18"/>
@@ -5685,23 +7185,23 @@
       <c r="Z26" s="15"/>
     </row>
     <row r="27" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A27" s="127"/>
-      <c r="B27" s="39"/>
-      <c r="C27" s="128"/>
-      <c r="D27" s="39"/>
-      <c r="E27" s="128"/>
-      <c r="F27" s="39"/>
-      <c r="G27" s="115"/>
-      <c r="H27" s="38"/>
-      <c r="I27" s="39"/>
-      <c r="J27" s="115"/>
-      <c r="K27" s="39"/>
-      <c r="L27" s="114"/>
-      <c r="M27" s="38"/>
-      <c r="N27" s="39"/>
-      <c r="O27" s="114"/>
-      <c r="P27" s="38"/>
-      <c r="Q27" s="39"/>
+      <c r="A27" s="132"/>
+      <c r="B27" s="44"/>
+      <c r="C27" s="133"/>
+      <c r="D27" s="44"/>
+      <c r="E27" s="133"/>
+      <c r="F27" s="44"/>
+      <c r="G27" s="120"/>
+      <c r="H27" s="43"/>
+      <c r="I27" s="44"/>
+      <c r="J27" s="120"/>
+      <c r="K27" s="44"/>
+      <c r="L27" s="119"/>
+      <c r="M27" s="43"/>
+      <c r="N27" s="44"/>
+      <c r="O27" s="119"/>
+      <c r="P27" s="43"/>
+      <c r="Q27" s="44"/>
       <c r="R27" s="19"/>
       <c r="S27" s="19"/>
       <c r="T27" s="18"/>
@@ -5713,23 +7213,23 @@
       <c r="Z27" s="15"/>
     </row>
     <row r="28" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A28" s="127"/>
-      <c r="B28" s="39"/>
-      <c r="C28" s="128"/>
-      <c r="D28" s="39"/>
-      <c r="E28" s="128"/>
-      <c r="F28" s="39"/>
-      <c r="G28" s="115"/>
-      <c r="H28" s="38"/>
-      <c r="I28" s="39"/>
-      <c r="J28" s="115"/>
-      <c r="K28" s="39"/>
-      <c r="L28" s="114"/>
-      <c r="M28" s="38"/>
-      <c r="N28" s="39"/>
-      <c r="O28" s="114"/>
-      <c r="P28" s="38"/>
-      <c r="Q28" s="39"/>
+      <c r="A28" s="132"/>
+      <c r="B28" s="44"/>
+      <c r="C28" s="133"/>
+      <c r="D28" s="44"/>
+      <c r="E28" s="133"/>
+      <c r="F28" s="44"/>
+      <c r="G28" s="120"/>
+      <c r="H28" s="43"/>
+      <c r="I28" s="44"/>
+      <c r="J28" s="120"/>
+      <c r="K28" s="44"/>
+      <c r="L28" s="119"/>
+      <c r="M28" s="43"/>
+      <c r="N28" s="44"/>
+      <c r="O28" s="119"/>
+      <c r="P28" s="43"/>
+      <c r="Q28" s="44"/>
       <c r="R28" s="19"/>
       <c r="S28" s="19"/>
       <c r="T28" s="18"/>
@@ -5741,23 +7241,23 @@
       <c r="Z28" s="15"/>
     </row>
     <row r="29" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A29" s="127"/>
-      <c r="B29" s="39"/>
-      <c r="C29" s="128"/>
-      <c r="D29" s="39"/>
-      <c r="E29" s="128"/>
-      <c r="F29" s="39"/>
-      <c r="G29" s="115"/>
-      <c r="H29" s="38"/>
-      <c r="I29" s="39"/>
-      <c r="J29" s="115"/>
-      <c r="K29" s="39"/>
-      <c r="L29" s="114"/>
-      <c r="M29" s="38"/>
-      <c r="N29" s="39"/>
-      <c r="O29" s="114"/>
-      <c r="P29" s="38"/>
-      <c r="Q29" s="39"/>
+      <c r="A29" s="132"/>
+      <c r="B29" s="44"/>
+      <c r="C29" s="133"/>
+      <c r="D29" s="44"/>
+      <c r="E29" s="133"/>
+      <c r="F29" s="44"/>
+      <c r="G29" s="120"/>
+      <c r="H29" s="43"/>
+      <c r="I29" s="44"/>
+      <c r="J29" s="120"/>
+      <c r="K29" s="44"/>
+      <c r="L29" s="119"/>
+      <c r="M29" s="43"/>
+      <c r="N29" s="44"/>
+      <c r="O29" s="119"/>
+      <c r="P29" s="43"/>
+      <c r="Q29" s="44"/>
       <c r="R29" s="19"/>
       <c r="S29" s="19"/>
       <c r="T29" s="18"/>
@@ -5769,23 +7269,23 @@
       <c r="Z29" s="15"/>
     </row>
     <row r="30" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A30" s="127"/>
-      <c r="B30" s="39"/>
-      <c r="C30" s="128"/>
-      <c r="D30" s="39"/>
-      <c r="E30" s="128"/>
-      <c r="F30" s="39"/>
-      <c r="G30" s="115"/>
-      <c r="H30" s="38"/>
-      <c r="I30" s="39"/>
-      <c r="J30" s="115"/>
-      <c r="K30" s="39"/>
-      <c r="L30" s="114"/>
-      <c r="M30" s="38"/>
-      <c r="N30" s="39"/>
-      <c r="O30" s="114"/>
-      <c r="P30" s="38"/>
-      <c r="Q30" s="39"/>
+      <c r="A30" s="132"/>
+      <c r="B30" s="44"/>
+      <c r="C30" s="133"/>
+      <c r="D30" s="44"/>
+      <c r="E30" s="133"/>
+      <c r="F30" s="44"/>
+      <c r="G30" s="120"/>
+      <c r="H30" s="43"/>
+      <c r="I30" s="44"/>
+      <c r="J30" s="120"/>
+      <c r="K30" s="44"/>
+      <c r="L30" s="119"/>
+      <c r="M30" s="43"/>
+      <c r="N30" s="44"/>
+      <c r="O30" s="119"/>
+      <c r="P30" s="43"/>
+      <c r="Q30" s="44"/>
       <c r="R30" s="19"/>
       <c r="S30" s="19"/>
       <c r="T30" s="18"/>
@@ -5797,23 +7297,23 @@
       <c r="Z30" s="15"/>
     </row>
     <row r="31" spans="1:26" ht="12.75" customHeight="1" thickBot="1">
-      <c r="A31" s="130"/>
-      <c r="B31" s="70"/>
-      <c r="C31" s="131"/>
-      <c r="D31" s="70"/>
-      <c r="E31" s="131"/>
-      <c r="F31" s="70"/>
-      <c r="G31" s="117"/>
-      <c r="H31" s="69"/>
-      <c r="I31" s="70"/>
-      <c r="J31" s="117"/>
-      <c r="K31" s="70"/>
-      <c r="L31" s="116"/>
-      <c r="M31" s="69"/>
-      <c r="N31" s="70"/>
-      <c r="O31" s="116"/>
-      <c r="P31" s="69"/>
-      <c r="Q31" s="70"/>
+      <c r="A31" s="135"/>
+      <c r="B31" s="75"/>
+      <c r="C31" s="136"/>
+      <c r="D31" s="75"/>
+      <c r="E31" s="136"/>
+      <c r="F31" s="75"/>
+      <c r="G31" s="122"/>
+      <c r="H31" s="74"/>
+      <c r="I31" s="75"/>
+      <c r="J31" s="122"/>
+      <c r="K31" s="75"/>
+      <c r="L31" s="121"/>
+      <c r="M31" s="74"/>
+      <c r="N31" s="75"/>
+      <c r="O31" s="121"/>
+      <c r="P31" s="74"/>
+      <c r="Q31" s="75"/>
       <c r="R31" s="17"/>
       <c r="S31" s="17"/>
       <c r="T31" s="16"/>

--- a/Documents/ログアウト機能設計書.xlsx
+++ b/Documents/ログアウト機能設計書.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\S-47\Documents\project\taskUN\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB63E4EF-80C4-4541-9EA6-A1C9641E39C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F803266E-78D7-45B7-AE0E-540C28136D45}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{72C6CFC4-7293-42D0-8B35-05AE043D8312}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="3" xr2:uid="{72C6CFC4-7293-42D0-8B35-05AE043D8312}"/>
   </bookViews>
   <sheets>
     <sheet name="ユースケース記述" sheetId="3" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="89">
   <si>
     <t>システム名</t>
   </si>
@@ -476,6 +476,41 @@
   </si>
   <si>
     <t>画面遷移図</t>
+  </si>
+  <si>
+    <t>ログアウト画面でログアウトボタンを押下し、遷移先のログイン画面でブラウザバックした際、エラーとなることを確認する</t>
+    <rPh sb="5" eb="7">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>オウカ</t>
+    </rPh>
+    <rPh sb="21" eb="23">
+      <t>センイ</t>
+    </rPh>
+    <rPh sb="23" eb="24">
+      <t>サキ</t>
+    </rPh>
+    <rPh sb="29" eb="31">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="41" eb="42">
+      <t>サイ</t>
+    </rPh>
+    <rPh sb="52" eb="54">
+      <t>カクニン</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>ログアウト後、ログイン画面でブラウザバックする</t>
+    <rPh sb="5" eb="6">
+      <t>ゴ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>ガメン</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
   </si>
 </sst>
 </file>
@@ -1346,6 +1381,36 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1424,51 +1489,99 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="20" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="21" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="22" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="26" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="24" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="25" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="17" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="56" fontId="2" fillId="0" borderId="12" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="18" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="19" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="27" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="27" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="21" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="26" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="27" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="22" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="30" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1484,140 +1597,62 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="35" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="20" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="27" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="24" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="25" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="17" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="56" fontId="2" fillId="0" borderId="12" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="18" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="19" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="56" fontId="2" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="27" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="27" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="56" fontId="2" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -2345,19 +2380,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="47" t="s">
+      <c r="A1" s="57" t="s">
         <v>30</v>
       </c>
-      <c r="B1" s="48"/>
-      <c r="C1" s="49"/>
-      <c r="D1" s="56" t="s">
+      <c r="B1" s="58"/>
+      <c r="C1" s="59"/>
+      <c r="D1" s="66" t="s">
         <v>0</v>
       </c>
-      <c r="E1" s="57"/>
-      <c r="F1" s="56" t="s">
+      <c r="E1" s="67"/>
+      <c r="F1" s="66" t="s">
         <v>1</v>
       </c>
-      <c r="G1" s="57"/>
+      <c r="G1" s="67"/>
       <c r="H1" s="11" t="s">
         <v>2</v>
       </c>
@@ -2369,64 +2404,64 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="50"/>
-      <c r="B2" s="51"/>
-      <c r="C2" s="52"/>
-      <c r="D2" s="58" t="s">
+      <c r="A2" s="60"/>
+      <c r="B2" s="61"/>
+      <c r="C2" s="62"/>
+      <c r="D2" s="68" t="s">
         <v>6</v>
       </c>
-      <c r="E2" s="59"/>
-      <c r="F2" s="58" t="s">
+      <c r="E2" s="69"/>
+      <c r="F2" s="68" t="s">
         <v>7</v>
       </c>
-      <c r="G2" s="59"/>
-      <c r="H2" s="62">
+      <c r="G2" s="69"/>
+      <c r="H2" s="72">
         <v>45806</v>
       </c>
-      <c r="I2" s="65" t="s">
+      <c r="I2" s="75" t="s">
         <v>28</v>
       </c>
-      <c r="J2" s="66"/>
+      <c r="J2" s="76"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="50"/>
-      <c r="B3" s="51"/>
-      <c r="C3" s="52"/>
-      <c r="D3" s="60"/>
-      <c r="E3" s="52"/>
-      <c r="F3" s="60"/>
-      <c r="G3" s="52"/>
-      <c r="H3" s="63"/>
-      <c r="I3" s="63"/>
-      <c r="J3" s="67"/>
+      <c r="A3" s="60"/>
+      <c r="B3" s="61"/>
+      <c r="C3" s="62"/>
+      <c r="D3" s="70"/>
+      <c r="E3" s="62"/>
+      <c r="F3" s="70"/>
+      <c r="G3" s="62"/>
+      <c r="H3" s="73"/>
+      <c r="I3" s="73"/>
+      <c r="J3" s="77"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="53"/>
-      <c r="B4" s="54"/>
-      <c r="C4" s="55"/>
-      <c r="D4" s="61"/>
-      <c r="E4" s="55"/>
-      <c r="F4" s="61"/>
-      <c r="G4" s="55"/>
-      <c r="H4" s="64"/>
-      <c r="I4" s="64"/>
-      <c r="J4" s="68"/>
+      <c r="A4" s="63"/>
+      <c r="B4" s="64"/>
+      <c r="C4" s="65"/>
+      <c r="D4" s="71"/>
+      <c r="E4" s="65"/>
+      <c r="F4" s="71"/>
+      <c r="G4" s="65"/>
+      <c r="H4" s="74"/>
+      <c r="I4" s="74"/>
+      <c r="J4" s="78"/>
     </row>
     <row r="5" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A5" s="69" t="s">
+      <c r="A5" s="79" t="s">
         <v>31</v>
       </c>
-      <c r="B5" s="70"/>
-      <c r="C5" s="57"/>
-      <c r="D5" s="71" t="s">
+      <c r="B5" s="80"/>
+      <c r="C5" s="67"/>
+      <c r="D5" s="81" t="s">
         <v>41</v>
       </c>
-      <c r="E5" s="70"/>
-      <c r="F5" s="70"/>
-      <c r="G5" s="70"/>
-      <c r="H5" s="70"/>
-      <c r="I5" s="70"/>
-      <c r="J5" s="72"/>
+      <c r="E5" s="80"/>
+      <c r="F5" s="80"/>
+      <c r="G5" s="80"/>
+      <c r="H5" s="80"/>
+      <c r="I5" s="80"/>
+      <c r="J5" s="82"/>
     </row>
     <row r="6" spans="1:10" ht="26.25" customHeight="1">
       <c r="A6" s="42" t="s">
@@ -2477,14 +2512,14 @@
       <c r="J8" s="46"/>
     </row>
     <row r="9" spans="1:10" ht="64.5" customHeight="1">
-      <c r="A9" s="78" t="s">
+      <c r="A9" s="52" t="s">
         <v>36</v>
       </c>
-      <c r="B9" s="81" t="s">
+      <c r="B9" s="55" t="s">
         <v>37</v>
       </c>
       <c r="C9" s="44"/>
-      <c r="D9" s="82" t="s">
+      <c r="D9" s="56" t="s">
         <v>83</v>
       </c>
       <c r="E9" s="43"/>
@@ -2495,12 +2530,12 @@
       <c r="J9" s="46"/>
     </row>
     <row r="10" spans="1:10" ht="64.5" customHeight="1">
-      <c r="A10" s="79"/>
-      <c r="B10" s="81" t="s">
+      <c r="A10" s="53"/>
+      <c r="B10" s="55" t="s">
         <v>38</v>
       </c>
       <c r="C10" s="44"/>
-      <c r="D10" s="82" t="s">
+      <c r="D10" s="56" t="s">
         <v>43</v>
       </c>
       <c r="E10" s="43"/>
@@ -2511,12 +2546,12 @@
       <c r="J10" s="46"/>
     </row>
     <row r="11" spans="1:10" ht="64.5" customHeight="1">
-      <c r="A11" s="80"/>
-      <c r="B11" s="81" t="s">
+      <c r="A11" s="54"/>
+      <c r="B11" s="55" t="s">
         <v>39</v>
       </c>
       <c r="C11" s="44"/>
-      <c r="D11" s="82" t="s">
+      <c r="D11" s="56" t="s">
         <v>44</v>
       </c>
       <c r="E11" s="43"/>
@@ -2543,18 +2578,18 @@
       <c r="J12" s="46"/>
     </row>
     <row r="13" spans="1:10" ht="26.25" customHeight="1" thickBot="1">
-      <c r="A13" s="73" t="s">
+      <c r="A13" s="47" t="s">
         <v>18</v>
       </c>
-      <c r="B13" s="74"/>
-      <c r="C13" s="75"/>
-      <c r="D13" s="76"/>
-      <c r="E13" s="74"/>
-      <c r="F13" s="74"/>
-      <c r="G13" s="74"/>
-      <c r="H13" s="74"/>
-      <c r="I13" s="74"/>
-      <c r="J13" s="77"/>
+      <c r="B13" s="48"/>
+      <c r="C13" s="49"/>
+      <c r="D13" s="50"/>
+      <c r="E13" s="48"/>
+      <c r="F13" s="48"/>
+      <c r="G13" s="48"/>
+      <c r="H13" s="48"/>
+      <c r="I13" s="48"/>
+      <c r="J13" s="51"/>
     </row>
     <row r="14" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="15" spans="1:10" ht="12.75" customHeight="1"/>
@@ -3545,6 +3580,18 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="A6:C6"/>
+    <mergeCell ref="D6:J6"/>
+    <mergeCell ref="A1:C4"/>
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="F1:G1"/>
+    <mergeCell ref="D2:E4"/>
+    <mergeCell ref="F2:G4"/>
+    <mergeCell ref="H2:H4"/>
+    <mergeCell ref="I2:I4"/>
+    <mergeCell ref="J2:J4"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="D5:J5"/>
     <mergeCell ref="A12:C12"/>
     <mergeCell ref="D12:J12"/>
     <mergeCell ref="A13:C13"/>
@@ -3560,18 +3607,6 @@
     <mergeCell ref="D10:J10"/>
     <mergeCell ref="B11:C11"/>
     <mergeCell ref="D11:J11"/>
-    <mergeCell ref="A6:C6"/>
-    <mergeCell ref="D6:J6"/>
-    <mergeCell ref="A1:C4"/>
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="F1:G1"/>
-    <mergeCell ref="D2:E4"/>
-    <mergeCell ref="F2:G4"/>
-    <mergeCell ref="H2:H4"/>
-    <mergeCell ref="I2:I4"/>
-    <mergeCell ref="J2:J4"/>
-    <mergeCell ref="A5:C5"/>
-    <mergeCell ref="D5:J5"/>
   </mergeCells>
   <phoneticPr fontId="3"/>
   <pageMargins left="0.70833333333333304" right="0.70833333333333304" top="0.74791666666666701" bottom="0.74791666666666701" header="0" footer="0"/>
@@ -3594,19 +3629,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="101" t="s">
+      <c r="A1" s="93" t="s">
         <v>5</v>
       </c>
-      <c r="B1" s="102"/>
-      <c r="C1" s="103"/>
-      <c r="D1" s="105" t="s">
+      <c r="B1" s="94"/>
+      <c r="C1" s="95"/>
+      <c r="D1" s="97" t="s">
         <v>0</v>
       </c>
-      <c r="E1" s="106"/>
-      <c r="F1" s="105" t="s">
+      <c r="E1" s="98"/>
+      <c r="F1" s="97" t="s">
         <v>1</v>
       </c>
-      <c r="G1" s="106"/>
+      <c r="G1" s="98"/>
       <c r="H1" s="1" t="s">
         <v>2</v>
       </c>
@@ -3618,67 +3653,67 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="98"/>
-      <c r="B2" s="99"/>
-      <c r="C2" s="104"/>
-      <c r="D2" s="107" t="s">
+      <c r="A2" s="90"/>
+      <c r="B2" s="91"/>
+      <c r="C2" s="96"/>
+      <c r="D2" s="99" t="s">
         <v>6</v>
       </c>
-      <c r="E2" s="108"/>
-      <c r="F2" s="107" t="s">
+      <c r="E2" s="100"/>
+      <c r="F2" s="99" t="s">
         <v>7</v>
       </c>
-      <c r="G2" s="108"/>
-      <c r="H2" s="110">
+      <c r="G2" s="100"/>
+      <c r="H2" s="102">
         <v>45806</v>
       </c>
-      <c r="I2" s="112" t="s">
+      <c r="I2" s="104" t="s">
         <v>28</v>
       </c>
-      <c r="J2" s="113"/>
+      <c r="J2" s="105"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="98"/>
-      <c r="B3" s="99"/>
-      <c r="C3" s="104"/>
-      <c r="D3" s="109"/>
-      <c r="E3" s="104"/>
-      <c r="F3" s="109"/>
-      <c r="G3" s="104"/>
-      <c r="H3" s="111"/>
-      <c r="I3" s="111"/>
-      <c r="J3" s="114"/>
+      <c r="A3" s="90"/>
+      <c r="B3" s="91"/>
+      <c r="C3" s="96"/>
+      <c r="D3" s="101"/>
+      <c r="E3" s="96"/>
+      <c r="F3" s="101"/>
+      <c r="G3" s="96"/>
+      <c r="H3" s="103"/>
+      <c r="I3" s="103"/>
+      <c r="J3" s="106"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="98"/>
-      <c r="B4" s="99"/>
-      <c r="C4" s="104"/>
-      <c r="D4" s="109"/>
-      <c r="E4" s="104"/>
-      <c r="F4" s="109"/>
-      <c r="G4" s="104"/>
-      <c r="H4" s="111"/>
-      <c r="I4" s="111"/>
-      <c r="J4" s="114"/>
+      <c r="A4" s="90"/>
+      <c r="B4" s="91"/>
+      <c r="C4" s="96"/>
+      <c r="D4" s="101"/>
+      <c r="E4" s="96"/>
+      <c r="F4" s="101"/>
+      <c r="G4" s="96"/>
+      <c r="H4" s="103"/>
+      <c r="I4" s="103"/>
+      <c r="J4" s="106"/>
     </row>
     <row r="5" spans="1:10" ht="28.5" customHeight="1">
-      <c r="A5" s="115" t="s">
+      <c r="A5" s="107" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="116"/>
-      <c r="C5" s="106"/>
-      <c r="D5" s="117" t="s">
+      <c r="B5" s="108"/>
+      <c r="C5" s="98"/>
+      <c r="D5" s="109" t="s">
         <v>19</v>
       </c>
-      <c r="E5" s="116"/>
-      <c r="F5" s="116"/>
-      <c r="G5" s="116"/>
-      <c r="H5" s="116"/>
-      <c r="I5" s="116"/>
-      <c r="J5" s="118"/>
+      <c r="E5" s="108"/>
+      <c r="F5" s="108"/>
+      <c r="G5" s="108"/>
+      <c r="H5" s="108"/>
+      <c r="I5" s="108"/>
+      <c r="J5" s="110"/>
     </row>
     <row r="6" spans="1:10" ht="21" customHeight="1">
-      <c r="A6" s="93" t="s">
+      <c r="A6" s="83" t="s">
         <v>9</v>
       </c>
       <c r="B6" s="84"/>
@@ -3689,94 +3724,94 @@
       <c r="G6" s="84"/>
       <c r="H6" s="84"/>
       <c r="I6" s="84"/>
-      <c r="J6" s="87"/>
+      <c r="J6" s="85"/>
     </row>
     <row r="7" spans="1:10" ht="21" customHeight="1">
-      <c r="A7" s="95"/>
-      <c r="B7" s="96"/>
-      <c r="C7" s="96"/>
-      <c r="D7" s="96"/>
-      <c r="E7" s="96"/>
-      <c r="F7" s="96"/>
-      <c r="G7" s="96"/>
-      <c r="H7" s="96"/>
-      <c r="I7" s="96"/>
-      <c r="J7" s="97"/>
+      <c r="A7" s="87"/>
+      <c r="B7" s="88"/>
+      <c r="C7" s="88"/>
+      <c r="D7" s="88"/>
+      <c r="E7" s="88"/>
+      <c r="F7" s="88"/>
+      <c r="G7" s="88"/>
+      <c r="H7" s="88"/>
+      <c r="I7" s="88"/>
+      <c r="J7" s="89"/>
     </row>
     <row r="8" spans="1:10" ht="21" customHeight="1">
-      <c r="A8" s="98"/>
-      <c r="B8" s="99"/>
-      <c r="C8" s="99"/>
-      <c r="D8" s="99"/>
-      <c r="E8" s="99"/>
-      <c r="F8" s="99"/>
-      <c r="G8" s="99"/>
-      <c r="H8" s="99"/>
-      <c r="I8" s="99"/>
-      <c r="J8" s="100"/>
+      <c r="A8" s="90"/>
+      <c r="B8" s="91"/>
+      <c r="C8" s="91"/>
+      <c r="D8" s="91"/>
+      <c r="E8" s="91"/>
+      <c r="F8" s="91"/>
+      <c r="G8" s="91"/>
+      <c r="H8" s="91"/>
+      <c r="I8" s="91"/>
+      <c r="J8" s="92"/>
     </row>
     <row r="9" spans="1:10" ht="21" customHeight="1">
-      <c r="A9" s="98"/>
-      <c r="B9" s="99"/>
-      <c r="C9" s="99"/>
-      <c r="D9" s="99"/>
-      <c r="E9" s="99"/>
-      <c r="F9" s="99"/>
-      <c r="G9" s="99"/>
-      <c r="H9" s="99"/>
-      <c r="I9" s="99"/>
-      <c r="J9" s="100"/>
+      <c r="A9" s="90"/>
+      <c r="B9" s="91"/>
+      <c r="C9" s="91"/>
+      <c r="D9" s="91"/>
+      <c r="E9" s="91"/>
+      <c r="F9" s="91"/>
+      <c r="G9" s="91"/>
+      <c r="H9" s="91"/>
+      <c r="I9" s="91"/>
+      <c r="J9" s="92"/>
     </row>
     <row r="10" spans="1:10" ht="21" customHeight="1">
-      <c r="A10" s="98"/>
-      <c r="B10" s="99"/>
-      <c r="C10" s="99"/>
-      <c r="D10" s="99"/>
-      <c r="E10" s="99"/>
-      <c r="F10" s="99"/>
-      <c r="G10" s="99"/>
-      <c r="H10" s="99"/>
-      <c r="I10" s="99"/>
-      <c r="J10" s="100"/>
+      <c r="A10" s="90"/>
+      <c r="B10" s="91"/>
+      <c r="C10" s="91"/>
+      <c r="D10" s="91"/>
+      <c r="E10" s="91"/>
+      <c r="F10" s="91"/>
+      <c r="G10" s="91"/>
+      <c r="H10" s="91"/>
+      <c r="I10" s="91"/>
+      <c r="J10" s="92"/>
     </row>
     <row r="11" spans="1:10" ht="21" customHeight="1">
-      <c r="A11" s="98"/>
-      <c r="B11" s="99"/>
-      <c r="C11" s="99"/>
-      <c r="D11" s="99"/>
-      <c r="E11" s="99"/>
-      <c r="F11" s="99"/>
-      <c r="G11" s="99"/>
-      <c r="H11" s="99"/>
-      <c r="I11" s="99"/>
-      <c r="J11" s="100"/>
+      <c r="A11" s="90"/>
+      <c r="B11" s="91"/>
+      <c r="C11" s="91"/>
+      <c r="D11" s="91"/>
+      <c r="E11" s="91"/>
+      <c r="F11" s="91"/>
+      <c r="G11" s="91"/>
+      <c r="H11" s="91"/>
+      <c r="I11" s="91"/>
+      <c r="J11" s="92"/>
     </row>
     <row r="12" spans="1:10" ht="21" customHeight="1">
-      <c r="A12" s="98"/>
-      <c r="B12" s="99"/>
-      <c r="C12" s="99"/>
-      <c r="D12" s="99"/>
-      <c r="E12" s="99"/>
-      <c r="F12" s="99"/>
-      <c r="G12" s="99"/>
-      <c r="H12" s="99"/>
-      <c r="I12" s="99"/>
-      <c r="J12" s="100"/>
+      <c r="A12" s="90"/>
+      <c r="B12" s="91"/>
+      <c r="C12" s="91"/>
+      <c r="D12" s="91"/>
+      <c r="E12" s="91"/>
+      <c r="F12" s="91"/>
+      <c r="G12" s="91"/>
+      <c r="H12" s="91"/>
+      <c r="I12" s="91"/>
+      <c r="J12" s="92"/>
     </row>
     <row r="13" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A13" s="98"/>
-      <c r="B13" s="99"/>
-      <c r="C13" s="99"/>
-      <c r="D13" s="99"/>
-      <c r="E13" s="99"/>
-      <c r="F13" s="99"/>
-      <c r="G13" s="99"/>
-      <c r="H13" s="99"/>
-      <c r="I13" s="99"/>
-      <c r="J13" s="100"/>
+      <c r="A13" s="90"/>
+      <c r="B13" s="91"/>
+      <c r="C13" s="91"/>
+      <c r="D13" s="91"/>
+      <c r="E13" s="91"/>
+      <c r="F13" s="91"/>
+      <c r="G13" s="91"/>
+      <c r="H13" s="91"/>
+      <c r="I13" s="91"/>
+      <c r="J13" s="92"/>
     </row>
     <row r="14" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A14" s="93" t="s">
+      <c r="A14" s="83" t="s">
         <v>10</v>
       </c>
       <c r="B14" s="84"/>
@@ -3787,21 +3822,21 @@
       <c r="G14" s="84"/>
       <c r="H14" s="84"/>
       <c r="I14" s="84"/>
-      <c r="J14" s="87"/>
+      <c r="J14" s="85"/>
     </row>
     <row r="15" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A15" s="93" t="s">
+      <c r="A15" s="83" t="s">
         <v>11</v>
       </c>
       <c r="B15" s="84"/>
-      <c r="C15" s="85"/>
-      <c r="D15" s="86" t="s">
+      <c r="C15" s="86"/>
+      <c r="D15" s="111" t="s">
         <v>26</v>
       </c>
       <c r="E15" s="84"/>
       <c r="F15" s="84"/>
       <c r="G15" s="84"/>
-      <c r="H15" s="85"/>
+      <c r="H15" s="86"/>
       <c r="I15" s="5" t="s">
         <v>12</v>
       </c>
@@ -3810,11 +3845,11 @@
       </c>
     </row>
     <row r="16" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A16" s="93" t="s">
+      <c r="A16" s="83" t="s">
         <v>13</v>
       </c>
       <c r="B16" s="84"/>
-      <c r="C16" s="85"/>
+      <c r="C16" s="86"/>
       <c r="D16" s="5" t="s">
         <v>14</v>
       </c>
@@ -3827,18 +3862,18 @@
       <c r="G16" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="H16" s="94" t="s">
+      <c r="H16" s="112" t="s">
         <v>18</v>
       </c>
       <c r="I16" s="84"/>
-      <c r="J16" s="87"/>
+      <c r="J16" s="85"/>
     </row>
     <row r="17" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A17" s="83">
+      <c r="A17" s="113">
         <v>1</v>
       </c>
       <c r="B17" s="84"/>
-      <c r="C17" s="85"/>
+      <c r="C17" s="86"/>
       <c r="D17" s="7" t="s">
         <v>21</v>
       </c>
@@ -3851,16 +3886,16 @@
       <c r="G17" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="H17" s="86"/>
+      <c r="H17" s="111"/>
       <c r="I17" s="84"/>
-      <c r="J17" s="87"/>
+      <c r="J17" s="85"/>
     </row>
     <row r="18" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A18" s="83">
+      <c r="A18" s="113">
         <v>2</v>
       </c>
       <c r="B18" s="84"/>
-      <c r="C18" s="85"/>
+      <c r="C18" s="86"/>
       <c r="D18" s="7" t="s">
         <v>22</v>
       </c>
@@ -3871,71 +3906,71 @@
       <c r="G18" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="H18" s="86" t="s">
+      <c r="H18" s="111" t="s">
         <v>27</v>
       </c>
       <c r="I18" s="84"/>
-      <c r="J18" s="87"/>
+      <c r="J18" s="85"/>
     </row>
     <row r="19" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A19" s="83"/>
+      <c r="A19" s="113"/>
       <c r="B19" s="84"/>
-      <c r="C19" s="85"/>
+      <c r="C19" s="86"/>
       <c r="D19" s="7"/>
       <c r="E19" s="7"/>
       <c r="F19" s="8"/>
       <c r="G19" s="8"/>
-      <c r="H19" s="86"/>
+      <c r="H19" s="111"/>
       <c r="I19" s="84"/>
-      <c r="J19" s="87"/>
+      <c r="J19" s="85"/>
     </row>
     <row r="20" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A20" s="83"/>
+      <c r="A20" s="113"/>
       <c r="B20" s="84"/>
-      <c r="C20" s="85"/>
+      <c r="C20" s="86"/>
       <c r="D20" s="7"/>
       <c r="E20" s="7"/>
       <c r="F20" s="8"/>
       <c r="G20" s="8"/>
-      <c r="H20" s="86"/>
+      <c r="H20" s="111"/>
       <c r="I20" s="84"/>
-      <c r="J20" s="87"/>
+      <c r="J20" s="85"/>
     </row>
     <row r="21" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A21" s="83"/>
+      <c r="A21" s="113"/>
       <c r="B21" s="84"/>
-      <c r="C21" s="85"/>
+      <c r="C21" s="86"/>
       <c r="D21" s="7"/>
       <c r="E21" s="7"/>
       <c r="F21" s="8"/>
       <c r="G21" s="8"/>
-      <c r="H21" s="86"/>
+      <c r="H21" s="111"/>
       <c r="I21" s="84"/>
-      <c r="J21" s="87"/>
+      <c r="J21" s="85"/>
     </row>
     <row r="22" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A22" s="83"/>
+      <c r="A22" s="113"/>
       <c r="B22" s="84"/>
-      <c r="C22" s="85"/>
+      <c r="C22" s="86"/>
       <c r="D22" s="7"/>
       <c r="E22" s="7"/>
       <c r="F22" s="8"/>
       <c r="G22" s="8"/>
-      <c r="H22" s="86"/>
+      <c r="H22" s="111"/>
       <c r="I22" s="84"/>
-      <c r="J22" s="87"/>
+      <c r="J22" s="85"/>
     </row>
     <row r="23" spans="1:10" ht="19.5" customHeight="1" thickBot="1">
-      <c r="A23" s="88"/>
-      <c r="B23" s="89"/>
-      <c r="C23" s="90"/>
+      <c r="A23" s="114"/>
+      <c r="B23" s="115"/>
+      <c r="C23" s="116"/>
       <c r="D23" s="9"/>
       <c r="E23" s="9"/>
       <c r="F23" s="10"/>
       <c r="G23" s="10"/>
-      <c r="H23" s="91"/>
-      <c r="I23" s="89"/>
-      <c r="J23" s="92"/>
+      <c r="H23" s="117"/>
+      <c r="I23" s="115"/>
+      <c r="J23" s="118"/>
     </row>
     <row r="24" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="25" spans="1:10" ht="12.75" customHeight="1"/>
@@ -4916,6 +4951,22 @@
     <row r="1000" s="4" customFormat="1" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="31">
+    <mergeCell ref="A22:C22"/>
+    <mergeCell ref="H22:J22"/>
+    <mergeCell ref="A23:C23"/>
+    <mergeCell ref="H23:J23"/>
+    <mergeCell ref="A19:C19"/>
+    <mergeCell ref="H19:J19"/>
+    <mergeCell ref="A20:C20"/>
+    <mergeCell ref="H20:J20"/>
+    <mergeCell ref="A21:C21"/>
+    <mergeCell ref="H21:J21"/>
+    <mergeCell ref="A16:C16"/>
+    <mergeCell ref="H16:J16"/>
+    <mergeCell ref="A18:C18"/>
+    <mergeCell ref="H18:J18"/>
+    <mergeCell ref="A17:C17"/>
+    <mergeCell ref="H17:J17"/>
     <mergeCell ref="A14:J14"/>
     <mergeCell ref="A15:C15"/>
     <mergeCell ref="A7:J13"/>
@@ -4931,22 +4982,6 @@
     <mergeCell ref="D5:J5"/>
     <mergeCell ref="A6:J6"/>
     <mergeCell ref="D15:H15"/>
-    <mergeCell ref="A16:C16"/>
-    <mergeCell ref="H16:J16"/>
-    <mergeCell ref="A18:C18"/>
-    <mergeCell ref="H18:J18"/>
-    <mergeCell ref="A17:C17"/>
-    <mergeCell ref="H17:J17"/>
-    <mergeCell ref="A22:C22"/>
-    <mergeCell ref="H22:J22"/>
-    <mergeCell ref="A23:C23"/>
-    <mergeCell ref="H23:J23"/>
-    <mergeCell ref="A19:C19"/>
-    <mergeCell ref="H19:J19"/>
-    <mergeCell ref="A20:C20"/>
-    <mergeCell ref="H20:J20"/>
-    <mergeCell ref="A21:C21"/>
-    <mergeCell ref="H21:J21"/>
   </mergeCells>
   <phoneticPr fontId="3"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
@@ -4967,19 +5002,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="137" t="s">
+      <c r="A1" s="119" t="s">
         <v>86</v>
       </c>
-      <c r="B1" s="48"/>
-      <c r="C1" s="49"/>
-      <c r="D1" s="56" t="s">
+      <c r="B1" s="58"/>
+      <c r="C1" s="59"/>
+      <c r="D1" s="66" t="s">
         <v>0</v>
       </c>
-      <c r="E1" s="57"/>
-      <c r="F1" s="56" t="s">
+      <c r="E1" s="67"/>
+      <c r="F1" s="66" t="s">
         <v>1</v>
       </c>
-      <c r="G1" s="57"/>
+      <c r="G1" s="67"/>
       <c r="H1" s="37" t="s">
         <v>2</v>
       </c>
@@ -4991,48 +5026,48 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="50"/>
-      <c r="B2" s="51"/>
-      <c r="C2" s="52"/>
-      <c r="D2" s="58" t="s">
+      <c r="A2" s="60"/>
+      <c r="B2" s="61"/>
+      <c r="C2" s="62"/>
+      <c r="D2" s="68" t="s">
         <v>6</v>
       </c>
-      <c r="E2" s="59"/>
-      <c r="F2" s="58" t="s">
+      <c r="E2" s="69"/>
+      <c r="F2" s="68" t="s">
         <v>7</v>
       </c>
-      <c r="G2" s="59"/>
-      <c r="H2" s="62">
+      <c r="G2" s="69"/>
+      <c r="H2" s="72">
         <v>45818</v>
       </c>
-      <c r="I2" s="65" t="s">
+      <c r="I2" s="75" t="s">
         <v>28</v>
       </c>
-      <c r="J2" s="66"/>
+      <c r="J2" s="76"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="50"/>
-      <c r="B3" s="51"/>
-      <c r="C3" s="52"/>
-      <c r="D3" s="60"/>
-      <c r="E3" s="52"/>
-      <c r="F3" s="60"/>
-      <c r="G3" s="52"/>
-      <c r="H3" s="63"/>
-      <c r="I3" s="63"/>
-      <c r="J3" s="67"/>
+      <c r="A3" s="60"/>
+      <c r="B3" s="61"/>
+      <c r="C3" s="62"/>
+      <c r="D3" s="70"/>
+      <c r="E3" s="62"/>
+      <c r="F3" s="70"/>
+      <c r="G3" s="62"/>
+      <c r="H3" s="73"/>
+      <c r="I3" s="73"/>
+      <c r="J3" s="77"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="53"/>
-      <c r="B4" s="54"/>
-      <c r="C4" s="55"/>
-      <c r="D4" s="61"/>
-      <c r="E4" s="55"/>
-      <c r="F4" s="61"/>
-      <c r="G4" s="55"/>
-      <c r="H4" s="64"/>
-      <c r="I4" s="64"/>
-      <c r="J4" s="68"/>
+      <c r="A4" s="63"/>
+      <c r="B4" s="64"/>
+      <c r="C4" s="65"/>
+      <c r="D4" s="71"/>
+      <c r="E4" s="65"/>
+      <c r="F4" s="71"/>
+      <c r="G4" s="65"/>
+      <c r="H4" s="74"/>
+      <c r="I4" s="74"/>
+      <c r="J4" s="78"/>
     </row>
     <row r="5" spans="1:10" ht="12.75" customHeight="1">
       <c r="A5" s="24"/>
@@ -6393,141 +6428,141 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="18" customHeight="1">
-      <c r="A1" s="47" t="s">
+      <c r="A1" s="57" t="s">
         <v>67</v>
       </c>
-      <c r="B1" s="48"/>
-      <c r="C1" s="48"/>
-      <c r="D1" s="48"/>
-      <c r="E1" s="48"/>
-      <c r="F1" s="49"/>
-      <c r="G1" s="56" t="s">
+      <c r="B1" s="58"/>
+      <c r="C1" s="58"/>
+      <c r="D1" s="58"/>
+      <c r="E1" s="58"/>
+      <c r="F1" s="59"/>
+      <c r="G1" s="66" t="s">
         <v>0</v>
       </c>
-      <c r="H1" s="70"/>
-      <c r="I1" s="70"/>
-      <c r="J1" s="57"/>
-      <c r="K1" s="56" t="s">
+      <c r="H1" s="80"/>
+      <c r="I1" s="80"/>
+      <c r="J1" s="67"/>
+      <c r="K1" s="66" t="s">
         <v>1</v>
       </c>
-      <c r="L1" s="70"/>
-      <c r="M1" s="70"/>
-      <c r="N1" s="57"/>
-      <c r="O1" s="56" t="s">
+      <c r="L1" s="80"/>
+      <c r="M1" s="80"/>
+      <c r="N1" s="67"/>
+      <c r="O1" s="66" t="s">
         <v>2</v>
       </c>
-      <c r="P1" s="57"/>
-      <c r="Q1" s="56" t="s">
+      <c r="P1" s="67"/>
+      <c r="Q1" s="66" t="s">
         <v>3</v>
       </c>
-      <c r="R1" s="57"/>
-      <c r="S1" s="56" t="s">
+      <c r="R1" s="67"/>
+      <c r="S1" s="66" t="s">
         <v>4</v>
       </c>
-      <c r="T1" s="72"/>
+      <c r="T1" s="82"/>
     </row>
     <row r="2" spans="1:26" ht="18" customHeight="1">
-      <c r="A2" s="50"/>
-      <c r="B2" s="51"/>
-      <c r="C2" s="51"/>
-      <c r="D2" s="51"/>
-      <c r="E2" s="51"/>
-      <c r="F2" s="52"/>
-      <c r="G2" s="58" t="s">
+      <c r="A2" s="60"/>
+      <c r="B2" s="61"/>
+      <c r="C2" s="61"/>
+      <c r="D2" s="61"/>
+      <c r="E2" s="61"/>
+      <c r="F2" s="62"/>
+      <c r="G2" s="68" t="s">
         <v>6</v>
       </c>
-      <c r="H2" s="124"/>
-      <c r="I2" s="124"/>
-      <c r="J2" s="59"/>
-      <c r="K2" s="58" t="s">
+      <c r="H2" s="131"/>
+      <c r="I2" s="131"/>
+      <c r="J2" s="69"/>
+      <c r="K2" s="68" t="s">
         <v>7</v>
       </c>
-      <c r="L2" s="124"/>
-      <c r="M2" s="124"/>
-      <c r="N2" s="59"/>
-      <c r="O2" s="128">
+      <c r="L2" s="131"/>
+      <c r="M2" s="131"/>
+      <c r="N2" s="69"/>
+      <c r="O2" s="132">
         <v>45810</v>
       </c>
-      <c r="P2" s="59"/>
-      <c r="Q2" s="58" t="s">
+      <c r="P2" s="69"/>
+      <c r="Q2" s="68" t="s">
         <v>28</v>
       </c>
-      <c r="R2" s="59"/>
-      <c r="S2" s="58"/>
-      <c r="T2" s="129"/>
+      <c r="R2" s="69"/>
+      <c r="S2" s="68"/>
+      <c r="T2" s="133"/>
     </row>
     <row r="3" spans="1:26" ht="18" customHeight="1">
-      <c r="A3" s="50"/>
-      <c r="B3" s="51"/>
-      <c r="C3" s="51"/>
-      <c r="D3" s="51"/>
-      <c r="E3" s="51"/>
-      <c r="F3" s="52"/>
-      <c r="G3" s="60"/>
-      <c r="H3" s="51"/>
-      <c r="I3" s="51"/>
-      <c r="J3" s="52"/>
-      <c r="K3" s="60"/>
-      <c r="L3" s="51"/>
-      <c r="M3" s="51"/>
-      <c r="N3" s="52"/>
-      <c r="O3" s="60"/>
-      <c r="P3" s="52"/>
-      <c r="Q3" s="60"/>
-      <c r="R3" s="52"/>
-      <c r="S3" s="60"/>
-      <c r="T3" s="130"/>
+      <c r="A3" s="60"/>
+      <c r="B3" s="61"/>
+      <c r="C3" s="61"/>
+      <c r="D3" s="61"/>
+      <c r="E3" s="61"/>
+      <c r="F3" s="62"/>
+      <c r="G3" s="70"/>
+      <c r="H3" s="61"/>
+      <c r="I3" s="61"/>
+      <c r="J3" s="62"/>
+      <c r="K3" s="70"/>
+      <c r="L3" s="61"/>
+      <c r="M3" s="61"/>
+      <c r="N3" s="62"/>
+      <c r="O3" s="70"/>
+      <c r="P3" s="62"/>
+      <c r="Q3" s="70"/>
+      <c r="R3" s="62"/>
+      <c r="S3" s="70"/>
+      <c r="T3" s="134"/>
     </row>
     <row r="4" spans="1:26" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="53"/>
-      <c r="B4" s="54"/>
-      <c r="C4" s="54"/>
-      <c r="D4" s="54"/>
-      <c r="E4" s="54"/>
-      <c r="F4" s="55"/>
-      <c r="G4" s="61"/>
-      <c r="H4" s="54"/>
-      <c r="I4" s="54"/>
-      <c r="J4" s="55"/>
-      <c r="K4" s="61"/>
-      <c r="L4" s="54"/>
-      <c r="M4" s="54"/>
-      <c r="N4" s="55"/>
-      <c r="O4" s="61"/>
-      <c r="P4" s="55"/>
-      <c r="Q4" s="61"/>
-      <c r="R4" s="55"/>
-      <c r="S4" s="61"/>
-      <c r="T4" s="131"/>
+      <c r="A4" s="63"/>
+      <c r="B4" s="64"/>
+      <c r="C4" s="64"/>
+      <c r="D4" s="64"/>
+      <c r="E4" s="64"/>
+      <c r="F4" s="65"/>
+      <c r="G4" s="71"/>
+      <c r="H4" s="64"/>
+      <c r="I4" s="64"/>
+      <c r="J4" s="65"/>
+      <c r="K4" s="71"/>
+      <c r="L4" s="64"/>
+      <c r="M4" s="64"/>
+      <c r="N4" s="65"/>
+      <c r="O4" s="71"/>
+      <c r="P4" s="65"/>
+      <c r="Q4" s="71"/>
+      <c r="R4" s="65"/>
+      <c r="S4" s="71"/>
+      <c r="T4" s="135"/>
     </row>
     <row r="5" spans="1:26" ht="18" customHeight="1">
-      <c r="A5" s="126" t="s">
+      <c r="A5" s="130" t="s">
         <v>66</v>
       </c>
-      <c r="B5" s="70"/>
-      <c r="C5" s="70"/>
-      <c r="D5" s="70"/>
-      <c r="E5" s="70"/>
-      <c r="F5" s="57"/>
-      <c r="G5" s="71" t="s">
+      <c r="B5" s="80"/>
+      <c r="C5" s="80"/>
+      <c r="D5" s="80"/>
+      <c r="E5" s="80"/>
+      <c r="F5" s="67"/>
+      <c r="G5" s="81" t="s">
         <v>65</v>
       </c>
-      <c r="H5" s="70"/>
-      <c r="I5" s="70"/>
-      <c r="J5" s="70"/>
-      <c r="K5" s="70"/>
-      <c r="L5" s="70"/>
-      <c r="M5" s="70"/>
-      <c r="N5" s="70"/>
-      <c r="O5" s="70"/>
-      <c r="P5" s="70"/>
-      <c r="Q5" s="70"/>
-      <c r="R5" s="70"/>
-      <c r="S5" s="70"/>
-      <c r="T5" s="72"/>
+      <c r="H5" s="80"/>
+      <c r="I5" s="80"/>
+      <c r="J5" s="80"/>
+      <c r="K5" s="80"/>
+      <c r="L5" s="80"/>
+      <c r="M5" s="80"/>
+      <c r="N5" s="80"/>
+      <c r="O5" s="80"/>
+      <c r="P5" s="80"/>
+      <c r="Q5" s="80"/>
+      <c r="R5" s="80"/>
+      <c r="S5" s="80"/>
+      <c r="T5" s="82"/>
     </row>
     <row r="6" spans="1:26" ht="18" customHeight="1">
-      <c r="A6" s="127" t="s">
+      <c r="A6" s="128" t="s">
         <v>64</v>
       </c>
       <c r="B6" s="43"/>
@@ -6553,7 +6588,7 @@
       <c r="T6" s="46"/>
     </row>
     <row r="7" spans="1:26" ht="18" customHeight="1">
-      <c r="A7" s="127" t="s">
+      <c r="A7" s="128" t="s">
         <v>63</v>
       </c>
       <c r="B7" s="43"/>
@@ -6775,33 +6810,33 @@
       <c r="T14" s="22"/>
     </row>
     <row r="15" spans="1:26" ht="18.75" customHeight="1">
-      <c r="A15" s="127" t="s">
+      <c r="A15" s="128" t="s">
         <v>57</v>
       </c>
       <c r="B15" s="44"/>
-      <c r="C15" s="134" t="s">
+      <c r="C15" s="129" t="s">
         <v>56</v>
       </c>
       <c r="D15" s="44"/>
-      <c r="E15" s="125" t="s">
+      <c r="E15" s="127" t="s">
         <v>55</v>
       </c>
       <c r="F15" s="44"/>
-      <c r="G15" s="125" t="s">
+      <c r="G15" s="127" t="s">
         <v>54</v>
       </c>
       <c r="H15" s="43"/>
       <c r="I15" s="44"/>
-      <c r="J15" s="125" t="s">
+      <c r="J15" s="127" t="s">
         <v>53</v>
       </c>
       <c r="K15" s="44"/>
-      <c r="L15" s="125" t="s">
+      <c r="L15" s="127" t="s">
         <v>52</v>
       </c>
       <c r="M15" s="43"/>
       <c r="N15" s="44"/>
-      <c r="O15" s="125" t="s">
+      <c r="O15" s="127" t="s">
         <v>51</v>
       </c>
       <c r="P15" s="43"/>
@@ -6817,33 +6852,33 @@
       </c>
     </row>
     <row r="16" spans="1:26" ht="48" customHeight="1">
-      <c r="A16" s="132">
+      <c r="A16" s="120">
         <v>1</v>
       </c>
       <c r="B16" s="44"/>
-      <c r="C16" s="133" t="s">
+      <c r="C16" s="121" t="s">
         <v>47</v>
       </c>
       <c r="D16" s="44"/>
-      <c r="E16" s="133" t="s">
+      <c r="E16" s="121" t="s">
         <v>46</v>
       </c>
       <c r="F16" s="44"/>
-      <c r="G16" s="120" t="s">
+      <c r="G16" s="124" t="s">
         <v>69</v>
       </c>
       <c r="H16" s="43"/>
       <c r="I16" s="44"/>
-      <c r="J16" s="120" t="s">
+      <c r="J16" s="124" t="s">
         <v>68</v>
       </c>
       <c r="K16" s="44"/>
-      <c r="L16" s="119" t="s">
+      <c r="L16" s="125" t="s">
         <v>70</v>
       </c>
       <c r="M16" s="43"/>
       <c r="N16" s="44"/>
-      <c r="O16" s="119" t="s">
+      <c r="O16" s="125" t="s">
         <v>45</v>
       </c>
       <c r="P16" s="43"/>
@@ -6864,34 +6899,34 @@
       <c r="Y16" s="15"/>
       <c r="Z16" s="15"/>
     </row>
-    <row r="17" spans="1:26" ht="41.25" customHeight="1">
-      <c r="A17" s="132">
+    <row r="17" spans="1:26" ht="51" customHeight="1">
+      <c r="A17" s="120">
         <v>2</v>
       </c>
       <c r="B17" s="44"/>
-      <c r="C17" s="133" t="s">
+      <c r="C17" s="121" t="s">
         <v>71</v>
       </c>
       <c r="D17" s="44"/>
-      <c r="E17" s="133" t="s">
+      <c r="E17" s="121" t="s">
         <v>46</v>
       </c>
       <c r="F17" s="44"/>
-      <c r="G17" s="120" t="s">
+      <c r="G17" s="124" t="s">
         <v>72</v>
       </c>
       <c r="H17" s="43"/>
       <c r="I17" s="44"/>
-      <c r="J17" s="120" t="s">
+      <c r="J17" s="124" t="s">
         <v>68</v>
       </c>
       <c r="K17" s="44"/>
-      <c r="L17" s="119" t="s">
+      <c r="L17" s="125" t="s">
         <v>73</v>
       </c>
       <c r="M17" s="43"/>
       <c r="N17" s="44"/>
-      <c r="O17" s="119" t="s">
+      <c r="O17" s="125" t="s">
         <v>74</v>
       </c>
       <c r="P17" s="43"/>
@@ -6913,33 +6948,33 @@
       <c r="Z17" s="15"/>
     </row>
     <row r="18" spans="1:26" ht="57.75" customHeight="1">
-      <c r="A18" s="132">
+      <c r="A18" s="120">
         <v>3</v>
       </c>
       <c r="B18" s="44"/>
-      <c r="C18" s="133" t="s">
+      <c r="C18" s="121" t="s">
         <v>71</v>
       </c>
       <c r="D18" s="44"/>
-      <c r="E18" s="133" t="s">
+      <c r="E18" s="121" t="s">
         <v>75</v>
       </c>
       <c r="F18" s="44"/>
-      <c r="G18" s="120" t="s">
+      <c r="G18" s="124" t="s">
         <v>76</v>
       </c>
       <c r="H18" s="43"/>
       <c r="I18" s="44"/>
-      <c r="J18" s="120" t="s">
+      <c r="J18" s="124" t="s">
         <v>77</v>
       </c>
       <c r="K18" s="44"/>
-      <c r="L18" s="123" t="s">
+      <c r="L18" s="136" t="s">
         <v>81</v>
       </c>
       <c r="M18" s="43"/>
       <c r="N18" s="44"/>
-      <c r="O18" s="119" t="s">
+      <c r="O18" s="125" t="s">
         <v>78</v>
       </c>
       <c r="P18" s="43"/>
@@ -6960,27 +6995,47 @@
       <c r="Y18" s="15"/>
       <c r="Z18" s="15"/>
     </row>
-    <row r="19" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A19" s="132"/>
+    <row r="19" spans="1:26" ht="63.75" customHeight="1">
+      <c r="A19" s="120">
+        <v>4</v>
+      </c>
       <c r="B19" s="44"/>
-      <c r="C19" s="133"/>
+      <c r="C19" s="121" t="s">
+        <v>71</v>
+      </c>
       <c r="D19" s="44"/>
-      <c r="E19" s="133"/>
+      <c r="E19" s="121" t="s">
+        <v>46</v>
+      </c>
       <c r="F19" s="44"/>
-      <c r="G19" s="120"/>
+      <c r="G19" s="124" t="s">
+        <v>87</v>
+      </c>
       <c r="H19" s="43"/>
       <c r="I19" s="44"/>
-      <c r="J19" s="120"/>
+      <c r="J19" s="124" t="s">
+        <v>77</v>
+      </c>
       <c r="K19" s="44"/>
-      <c r="L19" s="119"/>
+      <c r="L19" s="125" t="s">
+        <v>88</v>
+      </c>
       <c r="M19" s="43"/>
       <c r="N19" s="44"/>
-      <c r="O19" s="119"/>
+      <c r="O19" s="125" t="s">
+        <v>78</v>
+      </c>
       <c r="P19" s="43"/>
       <c r="Q19" s="44"/>
-      <c r="R19" s="19"/>
-      <c r="S19" s="19"/>
-      <c r="T19" s="18"/>
+      <c r="R19" s="36">
+        <v>45826</v>
+      </c>
+      <c r="S19" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="T19" s="18" t="s">
+        <v>82</v>
+      </c>
       <c r="U19" s="15"/>
       <c r="V19" s="15"/>
       <c r="W19" s="15"/>
@@ -6989,21 +7044,21 @@
       <c r="Z19" s="15"/>
     </row>
     <row r="20" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A20" s="132"/>
+      <c r="A20" s="120"/>
       <c r="B20" s="44"/>
-      <c r="C20" s="133"/>
+      <c r="C20" s="121"/>
       <c r="D20" s="44"/>
-      <c r="E20" s="133"/>
+      <c r="E20" s="121"/>
       <c r="F20" s="44"/>
-      <c r="G20" s="120"/>
+      <c r="G20" s="124"/>
       <c r="H20" s="43"/>
       <c r="I20" s="44"/>
-      <c r="J20" s="120"/>
+      <c r="J20" s="124"/>
       <c r="K20" s="44"/>
-      <c r="L20" s="119"/>
+      <c r="L20" s="125"/>
       <c r="M20" s="43"/>
       <c r="N20" s="44"/>
-      <c r="O20" s="119"/>
+      <c r="O20" s="125"/>
       <c r="P20" s="43"/>
       <c r="Q20" s="44"/>
       <c r="R20" s="19"/>
@@ -7017,21 +7072,21 @@
       <c r="Z20" s="15"/>
     </row>
     <row r="21" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A21" s="132"/>
+      <c r="A21" s="120"/>
       <c r="B21" s="44"/>
-      <c r="C21" s="133"/>
+      <c r="C21" s="121"/>
       <c r="D21" s="44"/>
-      <c r="E21" s="133"/>
+      <c r="E21" s="121"/>
       <c r="F21" s="44"/>
-      <c r="G21" s="120"/>
+      <c r="G21" s="124"/>
       <c r="H21" s="43"/>
       <c r="I21" s="44"/>
-      <c r="J21" s="120"/>
+      <c r="J21" s="124"/>
       <c r="K21" s="44"/>
-      <c r="L21" s="119"/>
+      <c r="L21" s="125"/>
       <c r="M21" s="43"/>
       <c r="N21" s="44"/>
-      <c r="O21" s="119"/>
+      <c r="O21" s="125"/>
       <c r="P21" s="43"/>
       <c r="Q21" s="44"/>
       <c r="R21" s="19"/>
@@ -7045,21 +7100,21 @@
       <c r="Z21" s="15"/>
     </row>
     <row r="22" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A22" s="132"/>
+      <c r="A22" s="120"/>
       <c r="B22" s="44"/>
-      <c r="C22" s="133"/>
+      <c r="C22" s="121"/>
       <c r="D22" s="44"/>
-      <c r="E22" s="133"/>
+      <c r="E22" s="121"/>
       <c r="F22" s="44"/>
-      <c r="G22" s="120"/>
+      <c r="G22" s="124"/>
       <c r="H22" s="43"/>
       <c r="I22" s="44"/>
-      <c r="J22" s="120"/>
+      <c r="J22" s="124"/>
       <c r="K22" s="44"/>
-      <c r="L22" s="119"/>
+      <c r="L22" s="125"/>
       <c r="M22" s="43"/>
       <c r="N22" s="44"/>
-      <c r="O22" s="119"/>
+      <c r="O22" s="125"/>
       <c r="P22" s="43"/>
       <c r="Q22" s="44"/>
       <c r="R22" s="19"/>
@@ -7073,21 +7128,21 @@
       <c r="Z22" s="15"/>
     </row>
     <row r="23" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A23" s="132"/>
+      <c r="A23" s="120"/>
       <c r="B23" s="44"/>
-      <c r="C23" s="133"/>
+      <c r="C23" s="121"/>
       <c r="D23" s="44"/>
-      <c r="E23" s="133"/>
+      <c r="E23" s="121"/>
       <c r="F23" s="44"/>
-      <c r="G23" s="120"/>
+      <c r="G23" s="124"/>
       <c r="H23" s="43"/>
       <c r="I23" s="44"/>
-      <c r="J23" s="120"/>
+      <c r="J23" s="124"/>
       <c r="K23" s="44"/>
-      <c r="L23" s="119"/>
+      <c r="L23" s="125"/>
       <c r="M23" s="43"/>
       <c r="N23" s="44"/>
-      <c r="O23" s="119"/>
+      <c r="O23" s="125"/>
       <c r="P23" s="43"/>
       <c r="Q23" s="44"/>
       <c r="R23" s="19"/>
@@ -7101,21 +7156,21 @@
       <c r="Z23" s="15"/>
     </row>
     <row r="24" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A24" s="132"/>
+      <c r="A24" s="120"/>
       <c r="B24" s="44"/>
-      <c r="C24" s="133"/>
+      <c r="C24" s="121"/>
       <c r="D24" s="44"/>
-      <c r="E24" s="133"/>
+      <c r="E24" s="121"/>
       <c r="F24" s="44"/>
-      <c r="G24" s="120"/>
+      <c r="G24" s="124"/>
       <c r="H24" s="43"/>
       <c r="I24" s="44"/>
-      <c r="J24" s="120"/>
+      <c r="J24" s="124"/>
       <c r="K24" s="44"/>
-      <c r="L24" s="119"/>
+      <c r="L24" s="125"/>
       <c r="M24" s="43"/>
       <c r="N24" s="44"/>
-      <c r="O24" s="119"/>
+      <c r="O24" s="125"/>
       <c r="P24" s="43"/>
       <c r="Q24" s="44"/>
       <c r="R24" s="19"/>
@@ -7129,21 +7184,21 @@
       <c r="Z24" s="15"/>
     </row>
     <row r="25" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A25" s="132"/>
+      <c r="A25" s="120"/>
       <c r="B25" s="44"/>
-      <c r="C25" s="133"/>
+      <c r="C25" s="121"/>
       <c r="D25" s="44"/>
-      <c r="E25" s="133"/>
+      <c r="E25" s="121"/>
       <c r="F25" s="44"/>
-      <c r="G25" s="120"/>
+      <c r="G25" s="124"/>
       <c r="H25" s="43"/>
       <c r="I25" s="44"/>
-      <c r="J25" s="120"/>
+      <c r="J25" s="124"/>
       <c r="K25" s="44"/>
-      <c r="L25" s="119"/>
+      <c r="L25" s="125"/>
       <c r="M25" s="43"/>
       <c r="N25" s="44"/>
-      <c r="O25" s="119"/>
+      <c r="O25" s="125"/>
       <c r="P25" s="43"/>
       <c r="Q25" s="44"/>
       <c r="R25" s="19"/>
@@ -7157,21 +7212,21 @@
       <c r="Z25" s="15"/>
     </row>
     <row r="26" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A26" s="132"/>
+      <c r="A26" s="120"/>
       <c r="B26" s="44"/>
-      <c r="C26" s="133"/>
+      <c r="C26" s="121"/>
       <c r="D26" s="44"/>
-      <c r="E26" s="133"/>
+      <c r="E26" s="121"/>
       <c r="F26" s="44"/>
-      <c r="G26" s="120"/>
+      <c r="G26" s="124"/>
       <c r="H26" s="43"/>
       <c r="I26" s="44"/>
-      <c r="J26" s="120"/>
+      <c r="J26" s="124"/>
       <c r="K26" s="44"/>
-      <c r="L26" s="119"/>
+      <c r="L26" s="125"/>
       <c r="M26" s="43"/>
       <c r="N26" s="44"/>
-      <c r="O26" s="119"/>
+      <c r="O26" s="125"/>
       <c r="P26" s="43"/>
       <c r="Q26" s="44"/>
       <c r="R26" s="19"/>
@@ -7185,21 +7240,21 @@
       <c r="Z26" s="15"/>
     </row>
     <row r="27" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A27" s="132"/>
+      <c r="A27" s="120"/>
       <c r="B27" s="44"/>
-      <c r="C27" s="133"/>
+      <c r="C27" s="121"/>
       <c r="D27" s="44"/>
-      <c r="E27" s="133"/>
+      <c r="E27" s="121"/>
       <c r="F27" s="44"/>
-      <c r="G27" s="120"/>
+      <c r="G27" s="124"/>
       <c r="H27" s="43"/>
       <c r="I27" s="44"/>
-      <c r="J27" s="120"/>
+      <c r="J27" s="124"/>
       <c r="K27" s="44"/>
-      <c r="L27" s="119"/>
+      <c r="L27" s="125"/>
       <c r="M27" s="43"/>
       <c r="N27" s="44"/>
-      <c r="O27" s="119"/>
+      <c r="O27" s="125"/>
       <c r="P27" s="43"/>
       <c r="Q27" s="44"/>
       <c r="R27" s="19"/>
@@ -7213,21 +7268,21 @@
       <c r="Z27" s="15"/>
     </row>
     <row r="28" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A28" s="132"/>
+      <c r="A28" s="120"/>
       <c r="B28" s="44"/>
-      <c r="C28" s="133"/>
+      <c r="C28" s="121"/>
       <c r="D28" s="44"/>
-      <c r="E28" s="133"/>
+      <c r="E28" s="121"/>
       <c r="F28" s="44"/>
-      <c r="G28" s="120"/>
+      <c r="G28" s="124"/>
       <c r="H28" s="43"/>
       <c r="I28" s="44"/>
-      <c r="J28" s="120"/>
+      <c r="J28" s="124"/>
       <c r="K28" s="44"/>
-      <c r="L28" s="119"/>
+      <c r="L28" s="125"/>
       <c r="M28" s="43"/>
       <c r="N28" s="44"/>
-      <c r="O28" s="119"/>
+      <c r="O28" s="125"/>
       <c r="P28" s="43"/>
       <c r="Q28" s="44"/>
       <c r="R28" s="19"/>
@@ -7241,21 +7296,21 @@
       <c r="Z28" s="15"/>
     </row>
     <row r="29" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A29" s="132"/>
+      <c r="A29" s="120"/>
       <c r="B29" s="44"/>
-      <c r="C29" s="133"/>
+      <c r="C29" s="121"/>
       <c r="D29" s="44"/>
-      <c r="E29" s="133"/>
+      <c r="E29" s="121"/>
       <c r="F29" s="44"/>
-      <c r="G29" s="120"/>
+      <c r="G29" s="124"/>
       <c r="H29" s="43"/>
       <c r="I29" s="44"/>
-      <c r="J29" s="120"/>
+      <c r="J29" s="124"/>
       <c r="K29" s="44"/>
-      <c r="L29" s="119"/>
+      <c r="L29" s="125"/>
       <c r="M29" s="43"/>
       <c r="N29" s="44"/>
-      <c r="O29" s="119"/>
+      <c r="O29" s="125"/>
       <c r="P29" s="43"/>
       <c r="Q29" s="44"/>
       <c r="R29" s="19"/>
@@ -7269,21 +7324,21 @@
       <c r="Z29" s="15"/>
     </row>
     <row r="30" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A30" s="132"/>
+      <c r="A30" s="120"/>
       <c r="B30" s="44"/>
-      <c r="C30" s="133"/>
+      <c r="C30" s="121"/>
       <c r="D30" s="44"/>
-      <c r="E30" s="133"/>
+      <c r="E30" s="121"/>
       <c r="F30" s="44"/>
-      <c r="G30" s="120"/>
+      <c r="G30" s="124"/>
       <c r="H30" s="43"/>
       <c r="I30" s="44"/>
-      <c r="J30" s="120"/>
+      <c r="J30" s="124"/>
       <c r="K30" s="44"/>
-      <c r="L30" s="119"/>
+      <c r="L30" s="125"/>
       <c r="M30" s="43"/>
       <c r="N30" s="44"/>
-      <c r="O30" s="119"/>
+      <c r="O30" s="125"/>
       <c r="P30" s="43"/>
       <c r="Q30" s="44"/>
       <c r="R30" s="19"/>
@@ -7297,23 +7352,23 @@
       <c r="Z30" s="15"/>
     </row>
     <row r="31" spans="1:26" ht="12.75" customHeight="1" thickBot="1">
-      <c r="A31" s="135"/>
-      <c r="B31" s="75"/>
-      <c r="C31" s="136"/>
-      <c r="D31" s="75"/>
-      <c r="E31" s="136"/>
-      <c r="F31" s="75"/>
-      <c r="G31" s="122"/>
-      <c r="H31" s="74"/>
-      <c r="I31" s="75"/>
-      <c r="J31" s="122"/>
-      <c r="K31" s="75"/>
-      <c r="L31" s="121"/>
-      <c r="M31" s="74"/>
-      <c r="N31" s="75"/>
-      <c r="O31" s="121"/>
-      <c r="P31" s="74"/>
-      <c r="Q31" s="75"/>
+      <c r="A31" s="122"/>
+      <c r="B31" s="49"/>
+      <c r="C31" s="123"/>
+      <c r="D31" s="49"/>
+      <c r="E31" s="123"/>
+      <c r="F31" s="49"/>
+      <c r="G31" s="137"/>
+      <c r="H31" s="48"/>
+      <c r="I31" s="49"/>
+      <c r="J31" s="137"/>
+      <c r="K31" s="49"/>
+      <c r="L31" s="126"/>
+      <c r="M31" s="48"/>
+      <c r="N31" s="49"/>
+      <c r="O31" s="126"/>
+      <c r="P31" s="48"/>
+      <c r="Q31" s="49"/>
       <c r="R31" s="17"/>
       <c r="S31" s="17"/>
       <c r="T31" s="16"/>
@@ -8311,66 +8366,58 @@
     <row r="1000" s="13" customFormat="1" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="136">
-    <mergeCell ref="A23:B23"/>
-    <mergeCell ref="A30:B30"/>
-    <mergeCell ref="C30:D30"/>
-    <mergeCell ref="E30:F30"/>
-    <mergeCell ref="A31:B31"/>
-    <mergeCell ref="C31:D31"/>
-    <mergeCell ref="E31:F31"/>
-    <mergeCell ref="C26:D26"/>
-    <mergeCell ref="E26:F26"/>
-    <mergeCell ref="A24:B24"/>
-    <mergeCell ref="C28:D28"/>
-    <mergeCell ref="E28:F28"/>
-    <mergeCell ref="A29:B29"/>
-    <mergeCell ref="A25:B25"/>
-    <mergeCell ref="C25:D25"/>
-    <mergeCell ref="E25:F25"/>
-    <mergeCell ref="A26:B26"/>
-    <mergeCell ref="C29:D29"/>
-    <mergeCell ref="E29:F29"/>
-    <mergeCell ref="A27:B27"/>
-    <mergeCell ref="C27:D27"/>
-    <mergeCell ref="E27:F27"/>
-    <mergeCell ref="A28:B28"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="E21:F21"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="E22:F22"/>
-    <mergeCell ref="A18:B18"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="E18:F18"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="E19:F19"/>
-    <mergeCell ref="E16:F16"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="E17:F17"/>
-    <mergeCell ref="C23:D23"/>
-    <mergeCell ref="E23:F23"/>
-    <mergeCell ref="C24:D24"/>
-    <mergeCell ref="E24:F24"/>
-    <mergeCell ref="G21:I21"/>
-    <mergeCell ref="J21:K21"/>
-    <mergeCell ref="J16:K16"/>
-    <mergeCell ref="G17:I17"/>
-    <mergeCell ref="J17:K17"/>
-    <mergeCell ref="O27:Q27"/>
-    <mergeCell ref="O28:Q28"/>
-    <mergeCell ref="O29:Q29"/>
-    <mergeCell ref="O30:Q30"/>
-    <mergeCell ref="O31:Q31"/>
-    <mergeCell ref="O19:Q19"/>
-    <mergeCell ref="O21:Q21"/>
-    <mergeCell ref="O22:Q22"/>
-    <mergeCell ref="O23:Q23"/>
-    <mergeCell ref="O24:Q24"/>
-    <mergeCell ref="O20:Q20"/>
-    <mergeCell ref="O25:Q25"/>
-    <mergeCell ref="O26:Q26"/>
+    <mergeCell ref="L26:N26"/>
+    <mergeCell ref="L27:N27"/>
+    <mergeCell ref="L28:N28"/>
+    <mergeCell ref="L29:N29"/>
+    <mergeCell ref="G25:I25"/>
+    <mergeCell ref="J25:K25"/>
+    <mergeCell ref="J26:K26"/>
+    <mergeCell ref="L30:N30"/>
+    <mergeCell ref="L31:N31"/>
+    <mergeCell ref="G30:I30"/>
+    <mergeCell ref="J30:K30"/>
+    <mergeCell ref="G31:I31"/>
+    <mergeCell ref="J31:K31"/>
+    <mergeCell ref="G26:I26"/>
+    <mergeCell ref="G27:I27"/>
+    <mergeCell ref="J27:K27"/>
+    <mergeCell ref="G28:I28"/>
+    <mergeCell ref="J28:K28"/>
+    <mergeCell ref="G29:I29"/>
+    <mergeCell ref="J29:K29"/>
+    <mergeCell ref="L18:N18"/>
+    <mergeCell ref="L19:N19"/>
+    <mergeCell ref="L21:N21"/>
+    <mergeCell ref="L22:N22"/>
+    <mergeCell ref="L23:N23"/>
+    <mergeCell ref="L24:N24"/>
+    <mergeCell ref="L25:N25"/>
+    <mergeCell ref="L20:N20"/>
+    <mergeCell ref="G2:J4"/>
+    <mergeCell ref="L15:N15"/>
+    <mergeCell ref="G22:I22"/>
+    <mergeCell ref="J22:K22"/>
+    <mergeCell ref="G23:I23"/>
+    <mergeCell ref="J23:K23"/>
+    <mergeCell ref="G24:I24"/>
+    <mergeCell ref="J24:K24"/>
+    <mergeCell ref="A5:F5"/>
+    <mergeCell ref="G5:T5"/>
+    <mergeCell ref="A6:F6"/>
+    <mergeCell ref="G6:T6"/>
+    <mergeCell ref="A7:F7"/>
+    <mergeCell ref="G7:T7"/>
+    <mergeCell ref="K2:N4"/>
+    <mergeCell ref="O2:P4"/>
+    <mergeCell ref="Q2:R4"/>
+    <mergeCell ref="S2:T4"/>
+    <mergeCell ref="A1:F4"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="O1:P1"/>
+    <mergeCell ref="Q1:R1"/>
+    <mergeCell ref="S1:T1"/>
     <mergeCell ref="O15:Q15"/>
     <mergeCell ref="L16:N16"/>
     <mergeCell ref="O16:Q16"/>
@@ -8395,58 +8442,66 @@
     <mergeCell ref="J15:K15"/>
     <mergeCell ref="G16:I16"/>
     <mergeCell ref="C16:D16"/>
-    <mergeCell ref="A5:F5"/>
-    <mergeCell ref="G5:T5"/>
-    <mergeCell ref="A6:F6"/>
-    <mergeCell ref="G6:T6"/>
-    <mergeCell ref="A7:F7"/>
-    <mergeCell ref="G7:T7"/>
-    <mergeCell ref="K2:N4"/>
-    <mergeCell ref="O2:P4"/>
-    <mergeCell ref="Q2:R4"/>
-    <mergeCell ref="S2:T4"/>
-    <mergeCell ref="A1:F4"/>
-    <mergeCell ref="G1:J1"/>
-    <mergeCell ref="K1:N1"/>
-    <mergeCell ref="O1:P1"/>
-    <mergeCell ref="Q1:R1"/>
-    <mergeCell ref="S1:T1"/>
-    <mergeCell ref="L18:N18"/>
-    <mergeCell ref="L19:N19"/>
-    <mergeCell ref="L21:N21"/>
-    <mergeCell ref="L22:N22"/>
-    <mergeCell ref="L23:N23"/>
-    <mergeCell ref="L24:N24"/>
-    <mergeCell ref="L25:N25"/>
-    <mergeCell ref="L20:N20"/>
-    <mergeCell ref="G2:J4"/>
-    <mergeCell ref="L15:N15"/>
-    <mergeCell ref="G22:I22"/>
-    <mergeCell ref="J22:K22"/>
-    <mergeCell ref="G23:I23"/>
-    <mergeCell ref="J23:K23"/>
-    <mergeCell ref="G24:I24"/>
-    <mergeCell ref="J24:K24"/>
-    <mergeCell ref="L26:N26"/>
-    <mergeCell ref="L27:N27"/>
-    <mergeCell ref="L28:N28"/>
-    <mergeCell ref="L29:N29"/>
-    <mergeCell ref="G25:I25"/>
-    <mergeCell ref="J25:K25"/>
-    <mergeCell ref="J26:K26"/>
-    <mergeCell ref="L30:N30"/>
-    <mergeCell ref="L31:N31"/>
-    <mergeCell ref="G30:I30"/>
-    <mergeCell ref="J30:K30"/>
-    <mergeCell ref="G31:I31"/>
-    <mergeCell ref="J31:K31"/>
-    <mergeCell ref="G26:I26"/>
-    <mergeCell ref="G27:I27"/>
-    <mergeCell ref="J27:K27"/>
-    <mergeCell ref="G28:I28"/>
-    <mergeCell ref="J28:K28"/>
-    <mergeCell ref="G29:I29"/>
-    <mergeCell ref="J29:K29"/>
+    <mergeCell ref="O27:Q27"/>
+    <mergeCell ref="O28:Q28"/>
+    <mergeCell ref="O29:Q29"/>
+    <mergeCell ref="O30:Q30"/>
+    <mergeCell ref="O31:Q31"/>
+    <mergeCell ref="O19:Q19"/>
+    <mergeCell ref="O21:Q21"/>
+    <mergeCell ref="O22:Q22"/>
+    <mergeCell ref="O23:Q23"/>
+    <mergeCell ref="O24:Q24"/>
+    <mergeCell ref="O20:Q20"/>
+    <mergeCell ref="O25:Q25"/>
+    <mergeCell ref="O26:Q26"/>
+    <mergeCell ref="E16:F16"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="E23:F23"/>
+    <mergeCell ref="C24:D24"/>
+    <mergeCell ref="E24:F24"/>
+    <mergeCell ref="G21:I21"/>
+    <mergeCell ref="J21:K21"/>
+    <mergeCell ref="J16:K16"/>
+    <mergeCell ref="G17:I17"/>
+    <mergeCell ref="J17:K17"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="E21:F21"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="E22:F22"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="E18:F18"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="E19:F19"/>
+    <mergeCell ref="A23:B23"/>
+    <mergeCell ref="A30:B30"/>
+    <mergeCell ref="C30:D30"/>
+    <mergeCell ref="E30:F30"/>
+    <mergeCell ref="A31:B31"/>
+    <mergeCell ref="C31:D31"/>
+    <mergeCell ref="E31:F31"/>
+    <mergeCell ref="C26:D26"/>
+    <mergeCell ref="E26:F26"/>
+    <mergeCell ref="A24:B24"/>
+    <mergeCell ref="C28:D28"/>
+    <mergeCell ref="E28:F28"/>
+    <mergeCell ref="A29:B29"/>
+    <mergeCell ref="A25:B25"/>
+    <mergeCell ref="C25:D25"/>
+    <mergeCell ref="E25:F25"/>
+    <mergeCell ref="A26:B26"/>
+    <mergeCell ref="C29:D29"/>
+    <mergeCell ref="E29:F29"/>
+    <mergeCell ref="A27:B27"/>
+    <mergeCell ref="C27:D27"/>
+    <mergeCell ref="E27:F27"/>
+    <mergeCell ref="A28:B28"/>
   </mergeCells>
   <phoneticPr fontId="3"/>
   <hyperlinks>

--- a/Documents/ログアウト機能設計書.xlsx
+++ b/Documents/ログアウト機能設計書.xlsx
@@ -8,18 +8,23 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\S-47\Documents\project\taskUN\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB63E4EF-80C4-4541-9EA6-A1C9641E39C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73255702-AD06-4BCD-94FC-DBC4417A7FFD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{72C6CFC4-7293-42D0-8B35-05AE043D8312}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="4" xr2:uid="{72C6CFC4-7293-42D0-8B35-05AE043D8312}"/>
   </bookViews>
   <sheets>
     <sheet name="ユースケース記述" sheetId="3" r:id="rId1"/>
     <sheet name="画面設計書" sheetId="2" r:id="rId2"/>
     <sheet name="画面遷移図" sheetId="5" r:id="rId3"/>
     <sheet name="テスト仕様書兼結果報告書" sheetId="4" r:id="rId4"/>
+    <sheet name="エビデンス" sheetId="6" r:id="rId5"/>
   </sheets>
+  <externalReferences>
+    <externalReference r:id="rId6"/>
+  </externalReferences>
   <definedNames>
     <definedName name="あ">#REF!</definedName>
+    <definedName name="ああ">#REF!</definedName>
     <definedName name="範囲１">#REF!</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -32,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="96">
   <si>
     <t>システム名</t>
   </si>
@@ -53,14 +58,14 @@
   </si>
   <si>
     <t>taskUN</t>
-    <phoneticPr fontId="3"/>
+    <phoneticPr fontId="4"/>
   </si>
   <si>
     <t>56期</t>
     <rPh sb="2" eb="3">
       <t>キ</t>
     </rPh>
-    <phoneticPr fontId="3"/>
+    <phoneticPr fontId="4"/>
   </si>
   <si>
     <t>画面名称</t>
@@ -100,35 +105,35 @@
     <rPh sb="5" eb="7">
       <t>ガメン</t>
     </rPh>
-    <phoneticPr fontId="3"/>
+    <phoneticPr fontId="4"/>
   </si>
   <si>
     <t>POST</t>
-    <phoneticPr fontId="3"/>
+    <phoneticPr fontId="4"/>
   </si>
   <si>
     <t>はいボタン</t>
-    <phoneticPr fontId="3"/>
+    <phoneticPr fontId="4"/>
   </si>
   <si>
     <t>いいえボタン</t>
-    <phoneticPr fontId="3"/>
+    <phoneticPr fontId="4"/>
   </si>
   <si>
     <t>submit</t>
-    <phoneticPr fontId="3"/>
+    <phoneticPr fontId="4"/>
   </si>
   <si>
     <t>はい</t>
-    <phoneticPr fontId="3"/>
+    <phoneticPr fontId="4"/>
   </si>
   <si>
     <t>いいえ</t>
-    <phoneticPr fontId="3"/>
+    <phoneticPr fontId="4"/>
   </si>
   <si>
     <t>logout-servlet</t>
-    <phoneticPr fontId="3"/>
+    <phoneticPr fontId="4"/>
   </si>
   <si>
     <t>いいえボタンが押下された場合メニュー画面に遷移</t>
@@ -144,18 +149,18 @@
     <rPh sb="21" eb="23">
       <t>センイ</t>
     </rPh>
-    <phoneticPr fontId="3"/>
+    <phoneticPr fontId="4"/>
   </si>
   <si>
     <t>山形</t>
     <rPh sb="0" eb="2">
       <t>ヤマガタ</t>
     </rPh>
-    <phoneticPr fontId="3"/>
+    <phoneticPr fontId="4"/>
   </si>
   <si>
     <t>なし</t>
-    <phoneticPr fontId="3"/>
+    <phoneticPr fontId="4"/>
   </si>
   <si>
     <t>ユースケース記述</t>
@@ -171,7 +176,7 @@
   </si>
   <si>
     <t>ユーザー</t>
-    <phoneticPr fontId="3"/>
+    <phoneticPr fontId="4"/>
   </si>
   <si>
     <t>事前条件</t>
@@ -193,14 +198,14 @@
   </si>
   <si>
     <t>ログアウト</t>
-    <phoneticPr fontId="3"/>
+    <phoneticPr fontId="4"/>
   </si>
   <si>
     <t>ログアウト画面からログアウトする</t>
     <rPh sb="5" eb="7">
       <t>ガメン</t>
     </rPh>
-    <phoneticPr fontId="3"/>
+    <phoneticPr fontId="4"/>
   </si>
   <si>
     <t>①ユーザー：ログアウト画面で「いいえ」ボタンを押下する
@@ -217,7 +222,7 @@
     <rPh sb="41" eb="43">
       <t>センイ</t>
     </rPh>
-    <phoneticPr fontId="3"/>
+    <phoneticPr fontId="4"/>
   </si>
   <si>
     <t>①ユーザー：ログインしていない状態で画面を開く
@@ -240,7 +245,7 @@
     <rPh sb="68" eb="70">
       <t>ヒョウジ</t>
     </rPh>
-    <phoneticPr fontId="3"/>
+    <phoneticPr fontId="4"/>
   </si>
   <si>
     <t>ログイン画面へ遷移する</t>
@@ -318,7 +323,7 @@
     <rPh sb="4" eb="6">
       <t>ジョウタイ</t>
     </rPh>
-    <phoneticPr fontId="3"/>
+    <phoneticPr fontId="4"/>
   </si>
   <si>
     <t>ログアウト画面で「はい」ボタンを押下する</t>
@@ -328,15 +333,15 @@
     <rPh sb="16" eb="18">
       <t>オウカ</t>
     </rPh>
-    <phoneticPr fontId="3"/>
+    <phoneticPr fontId="4"/>
   </si>
   <si>
     <t>「はい」ボタンを押下する</t>
-    <phoneticPr fontId="3"/>
+    <phoneticPr fontId="4"/>
   </si>
   <si>
     <t>◎</t>
-    <phoneticPr fontId="3"/>
+    <phoneticPr fontId="4"/>
   </si>
   <si>
     <t>ログアウト画面で「いいえ」ボタンを押下する</t>
@@ -346,22 +351,22 @@
     <rPh sb="17" eb="19">
       <t>オウカ</t>
     </rPh>
-    <phoneticPr fontId="3"/>
+    <phoneticPr fontId="4"/>
   </si>
   <si>
     <t>「いいえ」ボタンを押下する</t>
-    <phoneticPr fontId="3"/>
+    <phoneticPr fontId="4"/>
   </si>
   <si>
     <t>メニュー画面へ遷移する</t>
-    <phoneticPr fontId="3"/>
+    <phoneticPr fontId="4"/>
   </si>
   <si>
     <t>異常系</t>
     <rPh sb="0" eb="3">
       <t>イジョウケイ</t>
     </rPh>
-    <phoneticPr fontId="3"/>
+    <phoneticPr fontId="4"/>
   </si>
   <si>
     <t>ログインされていない状態でログアウト画面の表示させる</t>
@@ -374,14 +379,14 @@
     <rPh sb="21" eb="23">
       <t>ヒョウジ</t>
     </rPh>
-    <phoneticPr fontId="3"/>
+    <phoneticPr fontId="4"/>
   </si>
   <si>
     <t>ログアウト状態であること</t>
     <rPh sb="5" eb="7">
       <t>ジョウタイ</t>
     </rPh>
-    <phoneticPr fontId="3"/>
+    <phoneticPr fontId="4"/>
   </si>
   <si>
     <t>ログインされていませんというメッセージが表示され、その下にログイン画面へ誘導するリンクが表示される</t>
@@ -400,26 +405,26 @@
     <rPh sb="44" eb="46">
       <t>ヒョウジ</t>
     </rPh>
-    <phoneticPr fontId="3"/>
+    <phoneticPr fontId="4"/>
   </si>
   <si>
     <t>ログアウト画面</t>
-    <phoneticPr fontId="3"/>
+    <phoneticPr fontId="4"/>
   </si>
   <si>
     <t>Junitテスト仕様書</t>
     <rPh sb="8" eb="11">
       <t>シヨウショ</t>
     </rPh>
-    <phoneticPr fontId="3"/>
+    <phoneticPr fontId="4"/>
   </si>
   <si>
     <t>http://localhost:8080/taskUN/logout.jsp</t>
-    <phoneticPr fontId="3"/>
+    <phoneticPr fontId="4"/>
   </si>
   <si>
     <t>〇</t>
-    <phoneticPr fontId="3"/>
+    <phoneticPr fontId="4"/>
   </si>
   <si>
     <t>①ユーザー：ログアウト画面で「はい」ボタンを押下する
@@ -446,7 +451,7 @@
     <rPh sb="69" eb="71">
       <t>センイ</t>
     </rPh>
-    <phoneticPr fontId="3"/>
+    <phoneticPr fontId="4"/>
   </si>
   <si>
     <t>ログイン状態でログアウト画面を表示していること</t>
@@ -459,7 +464,7 @@
     <rPh sb="15" eb="17">
       <t>ヒョウジ</t>
     </rPh>
-    <phoneticPr fontId="3"/>
+    <phoneticPr fontId="4"/>
   </si>
   <si>
     <t>セッションが破棄されたのちに、画面が遷移する</t>
@@ -472,22 +477,90 @@
     <rPh sb="18" eb="20">
       <t>センイ</t>
     </rPh>
-    <phoneticPr fontId="3"/>
+    <phoneticPr fontId="4"/>
   </si>
   <si>
     <t>画面遷移図</t>
+  </si>
+  <si>
+    <t>テストエビデンス</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>システム名</t>
+    <rPh sb="4" eb="5">
+      <t>メイ</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>グループ名</t>
+    <rPh sb="4" eb="5">
+      <t>メイ</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>作成日</t>
+    <rPh sb="0" eb="3">
+      <t>サクセイビ</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>担当</t>
+    <rPh sb="0" eb="2">
+      <t>タントウ</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>承認印</t>
+    <rPh sb="0" eb="3">
+      <t>ショウニンイン</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>機能名称</t>
+    <rPh sb="0" eb="2">
+      <t>キノウ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>メイショウ</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>項番</t>
+    <rPh sb="0" eb="2">
+      <t>コウバン</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>エビデンス</t>
+    <phoneticPr fontId="8"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7">
+  <fonts count="9">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="游ゴシック"/>
       <family val="3"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="游ゴシック"/>
+      <family val="2"/>
       <charset val="128"/>
       <scheme val="minor"/>
     </font>
@@ -534,6 +607,13 @@
       <charset val="128"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="6"/>
+      <name val="游ゴシック"/>
+      <family val="2"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -549,7 +629,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="56">
+  <borders count="67">
     <border>
       <left/>
       <right/>
@@ -1200,430 +1280,641 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="3">
+  <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="138">
+  <cellXfs count="168">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="28" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="28" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="29" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="28" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="28" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="33" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="33" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="33" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="33" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="56" fontId="6" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="56" fontId="3" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="20" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="21" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="22" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="26" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="24" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="25" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="56" fontId="3" fillId="0" borderId="12" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="18" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="19" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="19" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="27" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="27" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="20" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="30" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="31" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="32" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="34" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="35" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="56" fontId="3" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="27" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="56" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="57" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="58" xfId="3" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="59" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="60" xfId="3" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="59" xfId="3" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="58" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="60" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="59" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="56" xfId="3" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="3">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="61" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="62" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="63" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="61" xfId="3" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="64" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="65" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="66" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="56" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="63" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="57" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="64" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="66" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="65" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="63" xfId="3" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="62" xfId="3" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="56" fontId="5" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="66" xfId="3" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="65" xfId="3" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="57" xfId="3" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="56" fontId="1" fillId="0" borderId="56" xfId="3" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="56" fontId="2" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="21" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="26" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="27" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="22" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="30" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="31" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="32" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="34" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="35" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="20" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="27" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="24" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="25" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="17" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="56" fontId="2" fillId="0" borderId="12" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="18" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="19" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="27" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="56" fontId="2" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
   </cellXfs>
-  <cellStyles count="3">
+  <cellStyles count="4">
     <cellStyle name="ハイパーリンク" xfId="2" builtinId="8"/>
     <cellStyle name="標準" xfId="0" builtinId="0"/>
     <cellStyle name="標準 2" xfId="1" xr:uid="{A8A8EE7C-E6BE-41B2-83FE-4DDDEF0D5153}"/>
+    <cellStyle name="標準 3" xfId="3" xr:uid="{E06FF395-FDC6-45AE-93E9-080B605A3B0E}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -2038,6 +2329,191 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>504826</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>59702</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>447676</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>436016</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="図 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B68B0D19-DD04-C0FC-49FF-BD730F251394}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3248026" y="1526552"/>
+          <a:ext cx="4057650" cy="2281314"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>466725</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>66188</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>523875</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>744889</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="5" name="図 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EE290B45-3498-2D80-D859-B966938FB30A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3209925" y="4209563"/>
+          <a:ext cx="4171950" cy="2345576"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>219075</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>200026</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>229890</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>1000126</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="7" name="図 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0B4F823D-9820-B621-FB57-ED4A0B5300B5}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2962275" y="7105651"/>
+          <a:ext cx="4811415" cy="2705100"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="ユースケース記述"/>
+      <sheetName val="画面設計書"/>
+      <sheetName val="画面遷移図"/>
+      <sheetName val="詳細クラス図"/>
+      <sheetName val="テスト仕様書兼結果報告書"/>
+      <sheetName val="JUnitテスト仕様書兼報告書"/>
+      <sheetName val="カバレッジレポート"/>
+      <sheetName val="エビデンス"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="1" refreshError="1"/>
+      <sheetData sheetId="2" refreshError="1"/>
+      <sheetData sheetId="3" refreshError="1"/>
+      <sheetData sheetId="4" refreshError="1"/>
+      <sheetData sheetId="5" refreshError="1"/>
+      <sheetData sheetId="6" refreshError="1"/>
+      <sheetData sheetId="7" refreshError="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office テーマ">
   <a:themeElements>
@@ -2345,19 +2821,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="47" t="s">
+      <c r="A1" s="57" t="s">
         <v>30</v>
       </c>
-      <c r="B1" s="48"/>
-      <c r="C1" s="49"/>
-      <c r="D1" s="56" t="s">
+      <c r="B1" s="58"/>
+      <c r="C1" s="59"/>
+      <c r="D1" s="66" t="s">
         <v>0</v>
       </c>
-      <c r="E1" s="57"/>
-      <c r="F1" s="56" t="s">
+      <c r="E1" s="67"/>
+      <c r="F1" s="66" t="s">
         <v>1</v>
       </c>
-      <c r="G1" s="57"/>
+      <c r="G1" s="67"/>
       <c r="H1" s="11" t="s">
         <v>2</v>
       </c>
@@ -2369,64 +2845,64 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="50"/>
-      <c r="B2" s="51"/>
-      <c r="C2" s="52"/>
-      <c r="D2" s="58" t="s">
+      <c r="A2" s="60"/>
+      <c r="B2" s="61"/>
+      <c r="C2" s="62"/>
+      <c r="D2" s="68" t="s">
         <v>6</v>
       </c>
-      <c r="E2" s="59"/>
-      <c r="F2" s="58" t="s">
+      <c r="E2" s="69"/>
+      <c r="F2" s="68" t="s">
         <v>7</v>
       </c>
-      <c r="G2" s="59"/>
-      <c r="H2" s="62">
+      <c r="G2" s="69"/>
+      <c r="H2" s="72">
         <v>45806</v>
       </c>
-      <c r="I2" s="65" t="s">
+      <c r="I2" s="75" t="s">
         <v>28</v>
       </c>
-      <c r="J2" s="66"/>
+      <c r="J2" s="76"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="50"/>
-      <c r="B3" s="51"/>
-      <c r="C3" s="52"/>
-      <c r="D3" s="60"/>
-      <c r="E3" s="52"/>
-      <c r="F3" s="60"/>
-      <c r="G3" s="52"/>
-      <c r="H3" s="63"/>
-      <c r="I3" s="63"/>
-      <c r="J3" s="67"/>
+      <c r="A3" s="60"/>
+      <c r="B3" s="61"/>
+      <c r="C3" s="62"/>
+      <c r="D3" s="70"/>
+      <c r="E3" s="62"/>
+      <c r="F3" s="70"/>
+      <c r="G3" s="62"/>
+      <c r="H3" s="73"/>
+      <c r="I3" s="73"/>
+      <c r="J3" s="77"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="53"/>
-      <c r="B4" s="54"/>
-      <c r="C4" s="55"/>
-      <c r="D4" s="61"/>
-      <c r="E4" s="55"/>
-      <c r="F4" s="61"/>
-      <c r="G4" s="55"/>
-      <c r="H4" s="64"/>
-      <c r="I4" s="64"/>
-      <c r="J4" s="68"/>
+      <c r="A4" s="63"/>
+      <c r="B4" s="64"/>
+      <c r="C4" s="65"/>
+      <c r="D4" s="71"/>
+      <c r="E4" s="65"/>
+      <c r="F4" s="71"/>
+      <c r="G4" s="65"/>
+      <c r="H4" s="74"/>
+      <c r="I4" s="74"/>
+      <c r="J4" s="78"/>
     </row>
     <row r="5" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A5" s="69" t="s">
+      <c r="A5" s="79" t="s">
         <v>31</v>
       </c>
-      <c r="B5" s="70"/>
-      <c r="C5" s="57"/>
-      <c r="D5" s="71" t="s">
+      <c r="B5" s="80"/>
+      <c r="C5" s="67"/>
+      <c r="D5" s="81" t="s">
         <v>41</v>
       </c>
-      <c r="E5" s="70"/>
-      <c r="F5" s="70"/>
-      <c r="G5" s="70"/>
-      <c r="H5" s="70"/>
-      <c r="I5" s="70"/>
-      <c r="J5" s="72"/>
+      <c r="E5" s="80"/>
+      <c r="F5" s="80"/>
+      <c r="G5" s="80"/>
+      <c r="H5" s="80"/>
+      <c r="I5" s="80"/>
+      <c r="J5" s="82"/>
     </row>
     <row r="6" spans="1:10" ht="26.25" customHeight="1">
       <c r="A6" s="42" t="s">
@@ -2477,14 +2953,14 @@
       <c r="J8" s="46"/>
     </row>
     <row r="9" spans="1:10" ht="64.5" customHeight="1">
-      <c r="A9" s="78" t="s">
+      <c r="A9" s="52" t="s">
         <v>36</v>
       </c>
-      <c r="B9" s="81" t="s">
+      <c r="B9" s="55" t="s">
         <v>37</v>
       </c>
       <c r="C9" s="44"/>
-      <c r="D9" s="82" t="s">
+      <c r="D9" s="56" t="s">
         <v>83</v>
       </c>
       <c r="E9" s="43"/>
@@ -2495,12 +2971,12 @@
       <c r="J9" s="46"/>
     </row>
     <row r="10" spans="1:10" ht="64.5" customHeight="1">
-      <c r="A10" s="79"/>
-      <c r="B10" s="81" t="s">
+      <c r="A10" s="53"/>
+      <c r="B10" s="55" t="s">
         <v>38</v>
       </c>
       <c r="C10" s="44"/>
-      <c r="D10" s="82" t="s">
+      <c r="D10" s="56" t="s">
         <v>43</v>
       </c>
       <c r="E10" s="43"/>
@@ -2511,12 +2987,12 @@
       <c r="J10" s="46"/>
     </row>
     <row r="11" spans="1:10" ht="64.5" customHeight="1">
-      <c r="A11" s="80"/>
-      <c r="B11" s="81" t="s">
+      <c r="A11" s="54"/>
+      <c r="B11" s="55" t="s">
         <v>39</v>
       </c>
       <c r="C11" s="44"/>
-      <c r="D11" s="82" t="s">
+      <c r="D11" s="56" t="s">
         <v>44</v>
       </c>
       <c r="E11" s="43"/>
@@ -2543,18 +3019,18 @@
       <c r="J12" s="46"/>
     </row>
     <row r="13" spans="1:10" ht="26.25" customHeight="1" thickBot="1">
-      <c r="A13" s="73" t="s">
+      <c r="A13" s="47" t="s">
         <v>18</v>
       </c>
-      <c r="B13" s="74"/>
-      <c r="C13" s="75"/>
-      <c r="D13" s="76"/>
-      <c r="E13" s="74"/>
-      <c r="F13" s="74"/>
-      <c r="G13" s="74"/>
-      <c r="H13" s="74"/>
-      <c r="I13" s="74"/>
-      <c r="J13" s="77"/>
+      <c r="B13" s="48"/>
+      <c r="C13" s="49"/>
+      <c r="D13" s="50"/>
+      <c r="E13" s="48"/>
+      <c r="F13" s="48"/>
+      <c r="G13" s="48"/>
+      <c r="H13" s="48"/>
+      <c r="I13" s="48"/>
+      <c r="J13" s="51"/>
     </row>
     <row r="14" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="15" spans="1:10" ht="12.75" customHeight="1"/>
@@ -3545,6 +4021,18 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="A6:C6"/>
+    <mergeCell ref="D6:J6"/>
+    <mergeCell ref="A1:C4"/>
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="F1:G1"/>
+    <mergeCell ref="D2:E4"/>
+    <mergeCell ref="F2:G4"/>
+    <mergeCell ref="H2:H4"/>
+    <mergeCell ref="I2:I4"/>
+    <mergeCell ref="J2:J4"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="D5:J5"/>
     <mergeCell ref="A12:C12"/>
     <mergeCell ref="D12:J12"/>
     <mergeCell ref="A13:C13"/>
@@ -3560,20 +4048,8 @@
     <mergeCell ref="D10:J10"/>
     <mergeCell ref="B11:C11"/>
     <mergeCell ref="D11:J11"/>
-    <mergeCell ref="A6:C6"/>
-    <mergeCell ref="D6:J6"/>
-    <mergeCell ref="A1:C4"/>
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="F1:G1"/>
-    <mergeCell ref="D2:E4"/>
-    <mergeCell ref="F2:G4"/>
-    <mergeCell ref="H2:H4"/>
-    <mergeCell ref="I2:I4"/>
-    <mergeCell ref="J2:J4"/>
-    <mergeCell ref="A5:C5"/>
-    <mergeCell ref="D5:J5"/>
   </mergeCells>
-  <phoneticPr fontId="3"/>
+  <phoneticPr fontId="4"/>
   <pageMargins left="0.70833333333333304" right="0.70833333333333304" top="0.74791666666666701" bottom="0.74791666666666701" header="0" footer="0"/>
   <pageSetup paperSize="9" orientation="landscape"/>
 </worksheet>
@@ -3594,19 +4070,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="101" t="s">
+      <c r="A1" s="93" t="s">
         <v>5</v>
       </c>
-      <c r="B1" s="102"/>
-      <c r="C1" s="103"/>
-      <c r="D1" s="105" t="s">
+      <c r="B1" s="94"/>
+      <c r="C1" s="95"/>
+      <c r="D1" s="97" t="s">
         <v>0</v>
       </c>
-      <c r="E1" s="106"/>
-      <c r="F1" s="105" t="s">
+      <c r="E1" s="98"/>
+      <c r="F1" s="97" t="s">
         <v>1</v>
       </c>
-      <c r="G1" s="106"/>
+      <c r="G1" s="98"/>
       <c r="H1" s="1" t="s">
         <v>2</v>
       </c>
@@ -3618,67 +4094,67 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="98"/>
-      <c r="B2" s="99"/>
-      <c r="C2" s="104"/>
-      <c r="D2" s="107" t="s">
+      <c r="A2" s="90"/>
+      <c r="B2" s="91"/>
+      <c r="C2" s="96"/>
+      <c r="D2" s="99" t="s">
         <v>6</v>
       </c>
-      <c r="E2" s="108"/>
-      <c r="F2" s="107" t="s">
+      <c r="E2" s="100"/>
+      <c r="F2" s="99" t="s">
         <v>7</v>
       </c>
-      <c r="G2" s="108"/>
-      <c r="H2" s="110">
+      <c r="G2" s="100"/>
+      <c r="H2" s="102">
         <v>45806</v>
       </c>
-      <c r="I2" s="112" t="s">
+      <c r="I2" s="104" t="s">
         <v>28</v>
       </c>
-      <c r="J2" s="113"/>
+      <c r="J2" s="105"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="98"/>
-      <c r="B3" s="99"/>
-      <c r="C3" s="104"/>
-      <c r="D3" s="109"/>
-      <c r="E3" s="104"/>
-      <c r="F3" s="109"/>
-      <c r="G3" s="104"/>
-      <c r="H3" s="111"/>
-      <c r="I3" s="111"/>
-      <c r="J3" s="114"/>
+      <c r="A3" s="90"/>
+      <c r="B3" s="91"/>
+      <c r="C3" s="96"/>
+      <c r="D3" s="101"/>
+      <c r="E3" s="96"/>
+      <c r="F3" s="101"/>
+      <c r="G3" s="96"/>
+      <c r="H3" s="103"/>
+      <c r="I3" s="103"/>
+      <c r="J3" s="106"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="98"/>
-      <c r="B4" s="99"/>
-      <c r="C4" s="104"/>
-      <c r="D4" s="109"/>
-      <c r="E4" s="104"/>
-      <c r="F4" s="109"/>
-      <c r="G4" s="104"/>
-      <c r="H4" s="111"/>
-      <c r="I4" s="111"/>
-      <c r="J4" s="114"/>
+      <c r="A4" s="90"/>
+      <c r="B4" s="91"/>
+      <c r="C4" s="96"/>
+      <c r="D4" s="101"/>
+      <c r="E4" s="96"/>
+      <c r="F4" s="101"/>
+      <c r="G4" s="96"/>
+      <c r="H4" s="103"/>
+      <c r="I4" s="103"/>
+      <c r="J4" s="106"/>
     </row>
     <row r="5" spans="1:10" ht="28.5" customHeight="1">
-      <c r="A5" s="115" t="s">
+      <c r="A5" s="107" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="116"/>
-      <c r="C5" s="106"/>
-      <c r="D5" s="117" t="s">
+      <c r="B5" s="108"/>
+      <c r="C5" s="98"/>
+      <c r="D5" s="109" t="s">
         <v>19</v>
       </c>
-      <c r="E5" s="116"/>
-      <c r="F5" s="116"/>
-      <c r="G5" s="116"/>
-      <c r="H5" s="116"/>
-      <c r="I5" s="116"/>
-      <c r="J5" s="118"/>
+      <c r="E5" s="108"/>
+      <c r="F5" s="108"/>
+      <c r="G5" s="108"/>
+      <c r="H5" s="108"/>
+      <c r="I5" s="108"/>
+      <c r="J5" s="110"/>
     </row>
     <row r="6" spans="1:10" ht="21" customHeight="1">
-      <c r="A6" s="93" t="s">
+      <c r="A6" s="83" t="s">
         <v>9</v>
       </c>
       <c r="B6" s="84"/>
@@ -3689,94 +4165,94 @@
       <c r="G6" s="84"/>
       <c r="H6" s="84"/>
       <c r="I6" s="84"/>
-      <c r="J6" s="87"/>
+      <c r="J6" s="85"/>
     </row>
     <row r="7" spans="1:10" ht="21" customHeight="1">
-      <c r="A7" s="95"/>
-      <c r="B7" s="96"/>
-      <c r="C7" s="96"/>
-      <c r="D7" s="96"/>
-      <c r="E7" s="96"/>
-      <c r="F7" s="96"/>
-      <c r="G7" s="96"/>
-      <c r="H7" s="96"/>
-      <c r="I7" s="96"/>
-      <c r="J7" s="97"/>
+      <c r="A7" s="87"/>
+      <c r="B7" s="88"/>
+      <c r="C7" s="88"/>
+      <c r="D7" s="88"/>
+      <c r="E7" s="88"/>
+      <c r="F7" s="88"/>
+      <c r="G7" s="88"/>
+      <c r="H7" s="88"/>
+      <c r="I7" s="88"/>
+      <c r="J7" s="89"/>
     </row>
     <row r="8" spans="1:10" ht="21" customHeight="1">
-      <c r="A8" s="98"/>
-      <c r="B8" s="99"/>
-      <c r="C8" s="99"/>
-      <c r="D8" s="99"/>
-      <c r="E8" s="99"/>
-      <c r="F8" s="99"/>
-      <c r="G8" s="99"/>
-      <c r="H8" s="99"/>
-      <c r="I8" s="99"/>
-      <c r="J8" s="100"/>
+      <c r="A8" s="90"/>
+      <c r="B8" s="91"/>
+      <c r="C8" s="91"/>
+      <c r="D8" s="91"/>
+      <c r="E8" s="91"/>
+      <c r="F8" s="91"/>
+      <c r="G8" s="91"/>
+      <c r="H8" s="91"/>
+      <c r="I8" s="91"/>
+      <c r="J8" s="92"/>
     </row>
     <row r="9" spans="1:10" ht="21" customHeight="1">
-      <c r="A9" s="98"/>
-      <c r="B9" s="99"/>
-      <c r="C9" s="99"/>
-      <c r="D9" s="99"/>
-      <c r="E9" s="99"/>
-      <c r="F9" s="99"/>
-      <c r="G9" s="99"/>
-      <c r="H9" s="99"/>
-      <c r="I9" s="99"/>
-      <c r="J9" s="100"/>
+      <c r="A9" s="90"/>
+      <c r="B9" s="91"/>
+      <c r="C9" s="91"/>
+      <c r="D9" s="91"/>
+      <c r="E9" s="91"/>
+      <c r="F9" s="91"/>
+      <c r="G9" s="91"/>
+      <c r="H9" s="91"/>
+      <c r="I9" s="91"/>
+      <c r="J9" s="92"/>
     </row>
     <row r="10" spans="1:10" ht="21" customHeight="1">
-      <c r="A10" s="98"/>
-      <c r="B10" s="99"/>
-      <c r="C10" s="99"/>
-      <c r="D10" s="99"/>
-      <c r="E10" s="99"/>
-      <c r="F10" s="99"/>
-      <c r="G10" s="99"/>
-      <c r="H10" s="99"/>
-      <c r="I10" s="99"/>
-      <c r="J10" s="100"/>
+      <c r="A10" s="90"/>
+      <c r="B10" s="91"/>
+      <c r="C10" s="91"/>
+      <c r="D10" s="91"/>
+      <c r="E10" s="91"/>
+      <c r="F10" s="91"/>
+      <c r="G10" s="91"/>
+      <c r="H10" s="91"/>
+      <c r="I10" s="91"/>
+      <c r="J10" s="92"/>
     </row>
     <row r="11" spans="1:10" ht="21" customHeight="1">
-      <c r="A11" s="98"/>
-      <c r="B11" s="99"/>
-      <c r="C11" s="99"/>
-      <c r="D11" s="99"/>
-      <c r="E11" s="99"/>
-      <c r="F11" s="99"/>
-      <c r="G11" s="99"/>
-      <c r="H11" s="99"/>
-      <c r="I11" s="99"/>
-      <c r="J11" s="100"/>
+      <c r="A11" s="90"/>
+      <c r="B11" s="91"/>
+      <c r="C11" s="91"/>
+      <c r="D11" s="91"/>
+      <c r="E11" s="91"/>
+      <c r="F11" s="91"/>
+      <c r="G11" s="91"/>
+      <c r="H11" s="91"/>
+      <c r="I11" s="91"/>
+      <c r="J11" s="92"/>
     </row>
     <row r="12" spans="1:10" ht="21" customHeight="1">
-      <c r="A12" s="98"/>
-      <c r="B12" s="99"/>
-      <c r="C12" s="99"/>
-      <c r="D12" s="99"/>
-      <c r="E12" s="99"/>
-      <c r="F12" s="99"/>
-      <c r="G12" s="99"/>
-      <c r="H12" s="99"/>
-      <c r="I12" s="99"/>
-      <c r="J12" s="100"/>
+      <c r="A12" s="90"/>
+      <c r="B12" s="91"/>
+      <c r="C12" s="91"/>
+      <c r="D12" s="91"/>
+      <c r="E12" s="91"/>
+      <c r="F12" s="91"/>
+      <c r="G12" s="91"/>
+      <c r="H12" s="91"/>
+      <c r="I12" s="91"/>
+      <c r="J12" s="92"/>
     </row>
     <row r="13" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A13" s="98"/>
-      <c r="B13" s="99"/>
-      <c r="C13" s="99"/>
-      <c r="D13" s="99"/>
-      <c r="E13" s="99"/>
-      <c r="F13" s="99"/>
-      <c r="G13" s="99"/>
-      <c r="H13" s="99"/>
-      <c r="I13" s="99"/>
-      <c r="J13" s="100"/>
+      <c r="A13" s="90"/>
+      <c r="B13" s="91"/>
+      <c r="C13" s="91"/>
+      <c r="D13" s="91"/>
+      <c r="E13" s="91"/>
+      <c r="F13" s="91"/>
+      <c r="G13" s="91"/>
+      <c r="H13" s="91"/>
+      <c r="I13" s="91"/>
+      <c r="J13" s="92"/>
     </row>
     <row r="14" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A14" s="93" t="s">
+      <c r="A14" s="83" t="s">
         <v>10</v>
       </c>
       <c r="B14" s="84"/>
@@ -3787,21 +4263,21 @@
       <c r="G14" s="84"/>
       <c r="H14" s="84"/>
       <c r="I14" s="84"/>
-      <c r="J14" s="87"/>
+      <c r="J14" s="85"/>
     </row>
     <row r="15" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A15" s="93" t="s">
+      <c r="A15" s="83" t="s">
         <v>11</v>
       </c>
       <c r="B15" s="84"/>
-      <c r="C15" s="85"/>
-      <c r="D15" s="86" t="s">
+      <c r="C15" s="86"/>
+      <c r="D15" s="111" t="s">
         <v>26</v>
       </c>
       <c r="E15" s="84"/>
       <c r="F15" s="84"/>
       <c r="G15" s="84"/>
-      <c r="H15" s="85"/>
+      <c r="H15" s="86"/>
       <c r="I15" s="5" t="s">
         <v>12</v>
       </c>
@@ -3810,11 +4286,11 @@
       </c>
     </row>
     <row r="16" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A16" s="93" t="s">
+      <c r="A16" s="83" t="s">
         <v>13</v>
       </c>
       <c r="B16" s="84"/>
-      <c r="C16" s="85"/>
+      <c r="C16" s="86"/>
       <c r="D16" s="5" t="s">
         <v>14</v>
       </c>
@@ -3827,18 +4303,18 @@
       <c r="G16" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="H16" s="94" t="s">
+      <c r="H16" s="112" t="s">
         <v>18</v>
       </c>
       <c r="I16" s="84"/>
-      <c r="J16" s="87"/>
+      <c r="J16" s="85"/>
     </row>
     <row r="17" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A17" s="83">
+      <c r="A17" s="113">
         <v>1</v>
       </c>
       <c r="B17" s="84"/>
-      <c r="C17" s="85"/>
+      <c r="C17" s="86"/>
       <c r="D17" s="7" t="s">
         <v>21</v>
       </c>
@@ -3851,16 +4327,16 @@
       <c r="G17" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="H17" s="86"/>
+      <c r="H17" s="111"/>
       <c r="I17" s="84"/>
-      <c r="J17" s="87"/>
+      <c r="J17" s="85"/>
     </row>
     <row r="18" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A18" s="83">
+      <c r="A18" s="113">
         <v>2</v>
       </c>
       <c r="B18" s="84"/>
-      <c r="C18" s="85"/>
+      <c r="C18" s="86"/>
       <c r="D18" s="7" t="s">
         <v>22</v>
       </c>
@@ -3871,71 +4347,71 @@
       <c r="G18" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="H18" s="86" t="s">
+      <c r="H18" s="111" t="s">
         <v>27</v>
       </c>
       <c r="I18" s="84"/>
-      <c r="J18" s="87"/>
+      <c r="J18" s="85"/>
     </row>
     <row r="19" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A19" s="83"/>
+      <c r="A19" s="113"/>
       <c r="B19" s="84"/>
-      <c r="C19" s="85"/>
+      <c r="C19" s="86"/>
       <c r="D19" s="7"/>
       <c r="E19" s="7"/>
       <c r="F19" s="8"/>
       <c r="G19" s="8"/>
-      <c r="H19" s="86"/>
+      <c r="H19" s="111"/>
       <c r="I19" s="84"/>
-      <c r="J19" s="87"/>
+      <c r="J19" s="85"/>
     </row>
     <row r="20" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A20" s="83"/>
+      <c r="A20" s="113"/>
       <c r="B20" s="84"/>
-      <c r="C20" s="85"/>
+      <c r="C20" s="86"/>
       <c r="D20" s="7"/>
       <c r="E20" s="7"/>
       <c r="F20" s="8"/>
       <c r="G20" s="8"/>
-      <c r="H20" s="86"/>
+      <c r="H20" s="111"/>
       <c r="I20" s="84"/>
-      <c r="J20" s="87"/>
+      <c r="J20" s="85"/>
     </row>
     <row r="21" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A21" s="83"/>
+      <c r="A21" s="113"/>
       <c r="B21" s="84"/>
-      <c r="C21" s="85"/>
+      <c r="C21" s="86"/>
       <c r="D21" s="7"/>
       <c r="E21" s="7"/>
       <c r="F21" s="8"/>
       <c r="G21" s="8"/>
-      <c r="H21" s="86"/>
+      <c r="H21" s="111"/>
       <c r="I21" s="84"/>
-      <c r="J21" s="87"/>
+      <c r="J21" s="85"/>
     </row>
     <row r="22" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A22" s="83"/>
+      <c r="A22" s="113"/>
       <c r="B22" s="84"/>
-      <c r="C22" s="85"/>
+      <c r="C22" s="86"/>
       <c r="D22" s="7"/>
       <c r="E22" s="7"/>
       <c r="F22" s="8"/>
       <c r="G22" s="8"/>
-      <c r="H22" s="86"/>
+      <c r="H22" s="111"/>
       <c r="I22" s="84"/>
-      <c r="J22" s="87"/>
+      <c r="J22" s="85"/>
     </row>
     <row r="23" spans="1:10" ht="19.5" customHeight="1" thickBot="1">
-      <c r="A23" s="88"/>
-      <c r="B23" s="89"/>
-      <c r="C23" s="90"/>
+      <c r="A23" s="114"/>
+      <c r="B23" s="115"/>
+      <c r="C23" s="116"/>
       <c r="D23" s="9"/>
       <c r="E23" s="9"/>
       <c r="F23" s="10"/>
       <c r="G23" s="10"/>
-      <c r="H23" s="91"/>
-      <c r="I23" s="89"/>
-      <c r="J23" s="92"/>
+      <c r="H23" s="117"/>
+      <c r="I23" s="115"/>
+      <c r="J23" s="118"/>
     </row>
     <row r="24" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="25" spans="1:10" ht="12.75" customHeight="1"/>
@@ -4916,6 +5392,22 @@
     <row r="1000" s="4" customFormat="1" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="31">
+    <mergeCell ref="A22:C22"/>
+    <mergeCell ref="H22:J22"/>
+    <mergeCell ref="A23:C23"/>
+    <mergeCell ref="H23:J23"/>
+    <mergeCell ref="A19:C19"/>
+    <mergeCell ref="H19:J19"/>
+    <mergeCell ref="A20:C20"/>
+    <mergeCell ref="H20:J20"/>
+    <mergeCell ref="A21:C21"/>
+    <mergeCell ref="H21:J21"/>
+    <mergeCell ref="A16:C16"/>
+    <mergeCell ref="H16:J16"/>
+    <mergeCell ref="A18:C18"/>
+    <mergeCell ref="H18:J18"/>
+    <mergeCell ref="A17:C17"/>
+    <mergeCell ref="H17:J17"/>
     <mergeCell ref="A14:J14"/>
     <mergeCell ref="A15:C15"/>
     <mergeCell ref="A7:J13"/>
@@ -4931,24 +5423,8 @@
     <mergeCell ref="D5:J5"/>
     <mergeCell ref="A6:J6"/>
     <mergeCell ref="D15:H15"/>
-    <mergeCell ref="A16:C16"/>
-    <mergeCell ref="H16:J16"/>
-    <mergeCell ref="A18:C18"/>
-    <mergeCell ref="H18:J18"/>
-    <mergeCell ref="A17:C17"/>
-    <mergeCell ref="H17:J17"/>
-    <mergeCell ref="A22:C22"/>
-    <mergeCell ref="H22:J22"/>
-    <mergeCell ref="A23:C23"/>
-    <mergeCell ref="H23:J23"/>
-    <mergeCell ref="A19:C19"/>
-    <mergeCell ref="H19:J19"/>
-    <mergeCell ref="A20:C20"/>
-    <mergeCell ref="H20:J20"/>
-    <mergeCell ref="A21:C21"/>
-    <mergeCell ref="H21:J21"/>
   </mergeCells>
-  <phoneticPr fontId="3"/>
+  <phoneticPr fontId="4"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup paperSize="9" orientation="landscape"/>
   <drawing r:id="rId1"/>
@@ -4967,19 +5443,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="137" t="s">
+      <c r="A1" s="119" t="s">
         <v>86</v>
       </c>
-      <c r="B1" s="48"/>
-      <c r="C1" s="49"/>
-      <c r="D1" s="56" t="s">
+      <c r="B1" s="58"/>
+      <c r="C1" s="59"/>
+      <c r="D1" s="66" t="s">
         <v>0</v>
       </c>
-      <c r="E1" s="57"/>
-      <c r="F1" s="56" t="s">
+      <c r="E1" s="67"/>
+      <c r="F1" s="66" t="s">
         <v>1</v>
       </c>
-      <c r="G1" s="57"/>
+      <c r="G1" s="67"/>
       <c r="H1" s="37" t="s">
         <v>2</v>
       </c>
@@ -4991,48 +5467,48 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="50"/>
-      <c r="B2" s="51"/>
-      <c r="C2" s="52"/>
-      <c r="D2" s="58" t="s">
+      <c r="A2" s="60"/>
+      <c r="B2" s="61"/>
+      <c r="C2" s="62"/>
+      <c r="D2" s="68" t="s">
         <v>6</v>
       </c>
-      <c r="E2" s="59"/>
-      <c r="F2" s="58" t="s">
+      <c r="E2" s="69"/>
+      <c r="F2" s="68" t="s">
         <v>7</v>
       </c>
-      <c r="G2" s="59"/>
-      <c r="H2" s="62">
+      <c r="G2" s="69"/>
+      <c r="H2" s="72">
         <v>45818</v>
       </c>
-      <c r="I2" s="65" t="s">
+      <c r="I2" s="75" t="s">
         <v>28</v>
       </c>
-      <c r="J2" s="66"/>
+      <c r="J2" s="76"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="50"/>
-      <c r="B3" s="51"/>
-      <c r="C3" s="52"/>
-      <c r="D3" s="60"/>
-      <c r="E3" s="52"/>
-      <c r="F3" s="60"/>
-      <c r="G3" s="52"/>
-      <c r="H3" s="63"/>
-      <c r="I3" s="63"/>
-      <c r="J3" s="67"/>
+      <c r="A3" s="60"/>
+      <c r="B3" s="61"/>
+      <c r="C3" s="62"/>
+      <c r="D3" s="70"/>
+      <c r="E3" s="62"/>
+      <c r="F3" s="70"/>
+      <c r="G3" s="62"/>
+      <c r="H3" s="73"/>
+      <c r="I3" s="73"/>
+      <c r="J3" s="77"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="53"/>
-      <c r="B4" s="54"/>
-      <c r="C4" s="55"/>
-      <c r="D4" s="61"/>
-      <c r="E4" s="55"/>
-      <c r="F4" s="61"/>
-      <c r="G4" s="55"/>
-      <c r="H4" s="64"/>
-      <c r="I4" s="64"/>
-      <c r="J4" s="68"/>
+      <c r="A4" s="63"/>
+      <c r="B4" s="64"/>
+      <c r="C4" s="65"/>
+      <c r="D4" s="71"/>
+      <c r="E4" s="65"/>
+      <c r="F4" s="71"/>
+      <c r="G4" s="65"/>
+      <c r="H4" s="74"/>
+      <c r="I4" s="74"/>
+      <c r="J4" s="78"/>
     </row>
     <row r="5" spans="1:10" ht="12.75" customHeight="1">
       <c r="A5" s="24"/>
@@ -6371,7 +6847,7 @@
     <mergeCell ref="D2:E4"/>
     <mergeCell ref="F2:G4"/>
   </mergeCells>
-  <phoneticPr fontId="3"/>
+  <phoneticPr fontId="4"/>
   <pageMargins left="0.70833333333333304" right="0.70833333333333304" top="0.74791666666666701" bottom="0.74791666666666701" header="0" footer="0"/>
   <pageSetup paperSize="9" orientation="landscape"/>
   <drawing r:id="rId1"/>
@@ -6393,141 +6869,141 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="18" customHeight="1">
-      <c r="A1" s="47" t="s">
+      <c r="A1" s="57" t="s">
         <v>67</v>
       </c>
-      <c r="B1" s="48"/>
-      <c r="C1" s="48"/>
-      <c r="D1" s="48"/>
-      <c r="E1" s="48"/>
-      <c r="F1" s="49"/>
-      <c r="G1" s="56" t="s">
+      <c r="B1" s="58"/>
+      <c r="C1" s="58"/>
+      <c r="D1" s="58"/>
+      <c r="E1" s="58"/>
+      <c r="F1" s="59"/>
+      <c r="G1" s="66" t="s">
         <v>0</v>
       </c>
-      <c r="H1" s="70"/>
-      <c r="I1" s="70"/>
-      <c r="J1" s="57"/>
-      <c r="K1" s="56" t="s">
+      <c r="H1" s="80"/>
+      <c r="I1" s="80"/>
+      <c r="J1" s="67"/>
+      <c r="K1" s="66" t="s">
         <v>1</v>
       </c>
-      <c r="L1" s="70"/>
-      <c r="M1" s="70"/>
-      <c r="N1" s="57"/>
-      <c r="O1" s="56" t="s">
+      <c r="L1" s="80"/>
+      <c r="M1" s="80"/>
+      <c r="N1" s="67"/>
+      <c r="O1" s="66" t="s">
         <v>2</v>
       </c>
-      <c r="P1" s="57"/>
-      <c r="Q1" s="56" t="s">
+      <c r="P1" s="67"/>
+      <c r="Q1" s="66" t="s">
         <v>3</v>
       </c>
-      <c r="R1" s="57"/>
-      <c r="S1" s="56" t="s">
+      <c r="R1" s="67"/>
+      <c r="S1" s="66" t="s">
         <v>4</v>
       </c>
-      <c r="T1" s="72"/>
+      <c r="T1" s="82"/>
     </row>
     <row r="2" spans="1:26" ht="18" customHeight="1">
-      <c r="A2" s="50"/>
-      <c r="B2" s="51"/>
-      <c r="C2" s="51"/>
-      <c r="D2" s="51"/>
-      <c r="E2" s="51"/>
-      <c r="F2" s="52"/>
-      <c r="G2" s="58" t="s">
+      <c r="A2" s="60"/>
+      <c r="B2" s="61"/>
+      <c r="C2" s="61"/>
+      <c r="D2" s="61"/>
+      <c r="E2" s="61"/>
+      <c r="F2" s="62"/>
+      <c r="G2" s="68" t="s">
         <v>6</v>
       </c>
-      <c r="H2" s="124"/>
-      <c r="I2" s="124"/>
-      <c r="J2" s="59"/>
-      <c r="K2" s="58" t="s">
+      <c r="H2" s="131"/>
+      <c r="I2" s="131"/>
+      <c r="J2" s="69"/>
+      <c r="K2" s="68" t="s">
         <v>7</v>
       </c>
-      <c r="L2" s="124"/>
-      <c r="M2" s="124"/>
-      <c r="N2" s="59"/>
-      <c r="O2" s="128">
+      <c r="L2" s="131"/>
+      <c r="M2" s="131"/>
+      <c r="N2" s="69"/>
+      <c r="O2" s="132">
         <v>45810</v>
       </c>
-      <c r="P2" s="59"/>
-      <c r="Q2" s="58" t="s">
+      <c r="P2" s="69"/>
+      <c r="Q2" s="68" t="s">
         <v>28</v>
       </c>
-      <c r="R2" s="59"/>
-      <c r="S2" s="58"/>
-      <c r="T2" s="129"/>
+      <c r="R2" s="69"/>
+      <c r="S2" s="68"/>
+      <c r="T2" s="133"/>
     </row>
     <row r="3" spans="1:26" ht="18" customHeight="1">
-      <c r="A3" s="50"/>
-      <c r="B3" s="51"/>
-      <c r="C3" s="51"/>
-      <c r="D3" s="51"/>
-      <c r="E3" s="51"/>
-      <c r="F3" s="52"/>
-      <c r="G3" s="60"/>
-      <c r="H3" s="51"/>
-      <c r="I3" s="51"/>
-      <c r="J3" s="52"/>
-      <c r="K3" s="60"/>
-      <c r="L3" s="51"/>
-      <c r="M3" s="51"/>
-      <c r="N3" s="52"/>
-      <c r="O3" s="60"/>
-      <c r="P3" s="52"/>
-      <c r="Q3" s="60"/>
-      <c r="R3" s="52"/>
-      <c r="S3" s="60"/>
-      <c r="T3" s="130"/>
+      <c r="A3" s="60"/>
+      <c r="B3" s="61"/>
+      <c r="C3" s="61"/>
+      <c r="D3" s="61"/>
+      <c r="E3" s="61"/>
+      <c r="F3" s="62"/>
+      <c r="G3" s="70"/>
+      <c r="H3" s="61"/>
+      <c r="I3" s="61"/>
+      <c r="J3" s="62"/>
+      <c r="K3" s="70"/>
+      <c r="L3" s="61"/>
+      <c r="M3" s="61"/>
+      <c r="N3" s="62"/>
+      <c r="O3" s="70"/>
+      <c r="P3" s="62"/>
+      <c r="Q3" s="70"/>
+      <c r="R3" s="62"/>
+      <c r="S3" s="70"/>
+      <c r="T3" s="134"/>
     </row>
     <row r="4" spans="1:26" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="53"/>
-      <c r="B4" s="54"/>
-      <c r="C4" s="54"/>
-      <c r="D4" s="54"/>
-      <c r="E4" s="54"/>
-      <c r="F4" s="55"/>
-      <c r="G4" s="61"/>
-      <c r="H4" s="54"/>
-      <c r="I4" s="54"/>
-      <c r="J4" s="55"/>
-      <c r="K4" s="61"/>
-      <c r="L4" s="54"/>
-      <c r="M4" s="54"/>
-      <c r="N4" s="55"/>
-      <c r="O4" s="61"/>
-      <c r="P4" s="55"/>
-      <c r="Q4" s="61"/>
-      <c r="R4" s="55"/>
-      <c r="S4" s="61"/>
-      <c r="T4" s="131"/>
+      <c r="A4" s="63"/>
+      <c r="B4" s="64"/>
+      <c r="C4" s="64"/>
+      <c r="D4" s="64"/>
+      <c r="E4" s="64"/>
+      <c r="F4" s="65"/>
+      <c r="G4" s="71"/>
+      <c r="H4" s="64"/>
+      <c r="I4" s="64"/>
+      <c r="J4" s="65"/>
+      <c r="K4" s="71"/>
+      <c r="L4" s="64"/>
+      <c r="M4" s="64"/>
+      <c r="N4" s="65"/>
+      <c r="O4" s="71"/>
+      <c r="P4" s="65"/>
+      <c r="Q4" s="71"/>
+      <c r="R4" s="65"/>
+      <c r="S4" s="71"/>
+      <c r="T4" s="135"/>
     </row>
     <row r="5" spans="1:26" ht="18" customHeight="1">
-      <c r="A5" s="126" t="s">
+      <c r="A5" s="130" t="s">
         <v>66</v>
       </c>
-      <c r="B5" s="70"/>
-      <c r="C5" s="70"/>
-      <c r="D5" s="70"/>
-      <c r="E5" s="70"/>
-      <c r="F5" s="57"/>
-      <c r="G5" s="71" t="s">
+      <c r="B5" s="80"/>
+      <c r="C5" s="80"/>
+      <c r="D5" s="80"/>
+      <c r="E5" s="80"/>
+      <c r="F5" s="67"/>
+      <c r="G5" s="81" t="s">
         <v>65</v>
       </c>
-      <c r="H5" s="70"/>
-      <c r="I5" s="70"/>
-      <c r="J5" s="70"/>
-      <c r="K5" s="70"/>
-      <c r="L5" s="70"/>
-      <c r="M5" s="70"/>
-      <c r="N5" s="70"/>
-      <c r="O5" s="70"/>
-      <c r="P5" s="70"/>
-      <c r="Q5" s="70"/>
-      <c r="R5" s="70"/>
-      <c r="S5" s="70"/>
-      <c r="T5" s="72"/>
+      <c r="H5" s="80"/>
+      <c r="I5" s="80"/>
+      <c r="J5" s="80"/>
+      <c r="K5" s="80"/>
+      <c r="L5" s="80"/>
+      <c r="M5" s="80"/>
+      <c r="N5" s="80"/>
+      <c r="O5" s="80"/>
+      <c r="P5" s="80"/>
+      <c r="Q5" s="80"/>
+      <c r="R5" s="80"/>
+      <c r="S5" s="80"/>
+      <c r="T5" s="82"/>
     </row>
     <row r="6" spans="1:26" ht="18" customHeight="1">
-      <c r="A6" s="127" t="s">
+      <c r="A6" s="128" t="s">
         <v>64</v>
       </c>
       <c r="B6" s="43"/>
@@ -6553,7 +7029,7 @@
       <c r="T6" s="46"/>
     </row>
     <row r="7" spans="1:26" ht="18" customHeight="1">
-      <c r="A7" s="127" t="s">
+      <c r="A7" s="128" t="s">
         <v>63</v>
       </c>
       <c r="B7" s="43"/>
@@ -6775,33 +7251,33 @@
       <c r="T14" s="22"/>
     </row>
     <row r="15" spans="1:26" ht="18.75" customHeight="1">
-      <c r="A15" s="127" t="s">
+      <c r="A15" s="128" t="s">
         <v>57</v>
       </c>
       <c r="B15" s="44"/>
-      <c r="C15" s="134" t="s">
+      <c r="C15" s="129" t="s">
         <v>56</v>
       </c>
       <c r="D15" s="44"/>
-      <c r="E15" s="125" t="s">
+      <c r="E15" s="127" t="s">
         <v>55</v>
       </c>
       <c r="F15" s="44"/>
-      <c r="G15" s="125" t="s">
+      <c r="G15" s="127" t="s">
         <v>54</v>
       </c>
       <c r="H15" s="43"/>
       <c r="I15" s="44"/>
-      <c r="J15" s="125" t="s">
+      <c r="J15" s="127" t="s">
         <v>53</v>
       </c>
       <c r="K15" s="44"/>
-      <c r="L15" s="125" t="s">
+      <c r="L15" s="127" t="s">
         <v>52</v>
       </c>
       <c r="M15" s="43"/>
       <c r="N15" s="44"/>
-      <c r="O15" s="125" t="s">
+      <c r="O15" s="127" t="s">
         <v>51</v>
       </c>
       <c r="P15" s="43"/>
@@ -6817,33 +7293,33 @@
       </c>
     </row>
     <row r="16" spans="1:26" ht="48" customHeight="1">
-      <c r="A16" s="132">
+      <c r="A16" s="120">
         <v>1</v>
       </c>
       <c r="B16" s="44"/>
-      <c r="C16" s="133" t="s">
+      <c r="C16" s="121" t="s">
         <v>47</v>
       </c>
       <c r="D16" s="44"/>
-      <c r="E16" s="133" t="s">
+      <c r="E16" s="121" t="s">
         <v>46</v>
       </c>
       <c r="F16" s="44"/>
-      <c r="G16" s="120" t="s">
+      <c r="G16" s="124" t="s">
         <v>69</v>
       </c>
       <c r="H16" s="43"/>
       <c r="I16" s="44"/>
-      <c r="J16" s="120" t="s">
+      <c r="J16" s="124" t="s">
         <v>68</v>
       </c>
       <c r="K16" s="44"/>
-      <c r="L16" s="119" t="s">
+      <c r="L16" s="125" t="s">
         <v>70</v>
       </c>
       <c r="M16" s="43"/>
       <c r="N16" s="44"/>
-      <c r="O16" s="119" t="s">
+      <c r="O16" s="125" t="s">
         <v>45</v>
       </c>
       <c r="P16" s="43"/>
@@ -6865,33 +7341,33 @@
       <c r="Z16" s="15"/>
     </row>
     <row r="17" spans="1:26" ht="41.25" customHeight="1">
-      <c r="A17" s="132">
+      <c r="A17" s="120">
         <v>2</v>
       </c>
       <c r="B17" s="44"/>
-      <c r="C17" s="133" t="s">
+      <c r="C17" s="121" t="s">
         <v>71</v>
       </c>
       <c r="D17" s="44"/>
-      <c r="E17" s="133" t="s">
+      <c r="E17" s="121" t="s">
         <v>46</v>
       </c>
       <c r="F17" s="44"/>
-      <c r="G17" s="120" t="s">
+      <c r="G17" s="124" t="s">
         <v>72</v>
       </c>
       <c r="H17" s="43"/>
       <c r="I17" s="44"/>
-      <c r="J17" s="120" t="s">
+      <c r="J17" s="124" t="s">
         <v>68</v>
       </c>
       <c r="K17" s="44"/>
-      <c r="L17" s="119" t="s">
+      <c r="L17" s="125" t="s">
         <v>73</v>
       </c>
       <c r="M17" s="43"/>
       <c r="N17" s="44"/>
-      <c r="O17" s="119" t="s">
+      <c r="O17" s="125" t="s">
         <v>74</v>
       </c>
       <c r="P17" s="43"/>
@@ -6913,33 +7389,33 @@
       <c r="Z17" s="15"/>
     </row>
     <row r="18" spans="1:26" ht="57.75" customHeight="1">
-      <c r="A18" s="132">
+      <c r="A18" s="120">
         <v>3</v>
       </c>
       <c r="B18" s="44"/>
-      <c r="C18" s="133" t="s">
+      <c r="C18" s="121" t="s">
         <v>71</v>
       </c>
       <c r="D18" s="44"/>
-      <c r="E18" s="133" t="s">
+      <c r="E18" s="121" t="s">
         <v>75</v>
       </c>
       <c r="F18" s="44"/>
-      <c r="G18" s="120" t="s">
+      <c r="G18" s="124" t="s">
         <v>76</v>
       </c>
       <c r="H18" s="43"/>
       <c r="I18" s="44"/>
-      <c r="J18" s="120" t="s">
+      <c r="J18" s="124" t="s">
         <v>77</v>
       </c>
       <c r="K18" s="44"/>
-      <c r="L18" s="123" t="s">
+      <c r="L18" s="136" t="s">
         <v>81</v>
       </c>
       <c r="M18" s="43"/>
       <c r="N18" s="44"/>
-      <c r="O18" s="119" t="s">
+      <c r="O18" s="125" t="s">
         <v>78</v>
       </c>
       <c r="P18" s="43"/>
@@ -6961,21 +7437,21 @@
       <c r="Z18" s="15"/>
     </row>
     <row r="19" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A19" s="132"/>
+      <c r="A19" s="120"/>
       <c r="B19" s="44"/>
-      <c r="C19" s="133"/>
+      <c r="C19" s="121"/>
       <c r="D19" s="44"/>
-      <c r="E19" s="133"/>
+      <c r="E19" s="121"/>
       <c r="F19" s="44"/>
-      <c r="G19" s="120"/>
+      <c r="G19" s="124"/>
       <c r="H19" s="43"/>
       <c r="I19" s="44"/>
-      <c r="J19" s="120"/>
+      <c r="J19" s="124"/>
       <c r="K19" s="44"/>
-      <c r="L19" s="119"/>
+      <c r="L19" s="125"/>
       <c r="M19" s="43"/>
       <c r="N19" s="44"/>
-      <c r="O19" s="119"/>
+      <c r="O19" s="125"/>
       <c r="P19" s="43"/>
       <c r="Q19" s="44"/>
       <c r="R19" s="19"/>
@@ -6989,21 +7465,21 @@
       <c r="Z19" s="15"/>
     </row>
     <row r="20" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A20" s="132"/>
+      <c r="A20" s="120"/>
       <c r="B20" s="44"/>
-      <c r="C20" s="133"/>
+      <c r="C20" s="121"/>
       <c r="D20" s="44"/>
-      <c r="E20" s="133"/>
+      <c r="E20" s="121"/>
       <c r="F20" s="44"/>
-      <c r="G20" s="120"/>
+      <c r="G20" s="124"/>
       <c r="H20" s="43"/>
       <c r="I20" s="44"/>
-      <c r="J20" s="120"/>
+      <c r="J20" s="124"/>
       <c r="K20" s="44"/>
-      <c r="L20" s="119"/>
+      <c r="L20" s="125"/>
       <c r="M20" s="43"/>
       <c r="N20" s="44"/>
-      <c r="O20" s="119"/>
+      <c r="O20" s="125"/>
       <c r="P20" s="43"/>
       <c r="Q20" s="44"/>
       <c r="R20" s="19"/>
@@ -7017,21 +7493,21 @@
       <c r="Z20" s="15"/>
     </row>
     <row r="21" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A21" s="132"/>
+      <c r="A21" s="120"/>
       <c r="B21" s="44"/>
-      <c r="C21" s="133"/>
+      <c r="C21" s="121"/>
       <c r="D21" s="44"/>
-      <c r="E21" s="133"/>
+      <c r="E21" s="121"/>
       <c r="F21" s="44"/>
-      <c r="G21" s="120"/>
+      <c r="G21" s="124"/>
       <c r="H21" s="43"/>
       <c r="I21" s="44"/>
-      <c r="J21" s="120"/>
+      <c r="J21" s="124"/>
       <c r="K21" s="44"/>
-      <c r="L21" s="119"/>
+      <c r="L21" s="125"/>
       <c r="M21" s="43"/>
       <c r="N21" s="44"/>
-      <c r="O21" s="119"/>
+      <c r="O21" s="125"/>
       <c r="P21" s="43"/>
       <c r="Q21" s="44"/>
       <c r="R21" s="19"/>
@@ -7045,21 +7521,21 @@
       <c r="Z21" s="15"/>
     </row>
     <row r="22" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A22" s="132"/>
+      <c r="A22" s="120"/>
       <c r="B22" s="44"/>
-      <c r="C22" s="133"/>
+      <c r="C22" s="121"/>
       <c r="D22" s="44"/>
-      <c r="E22" s="133"/>
+      <c r="E22" s="121"/>
       <c r="F22" s="44"/>
-      <c r="G22" s="120"/>
+      <c r="G22" s="124"/>
       <c r="H22" s="43"/>
       <c r="I22" s="44"/>
-      <c r="J22" s="120"/>
+      <c r="J22" s="124"/>
       <c r="K22" s="44"/>
-      <c r="L22" s="119"/>
+      <c r="L22" s="125"/>
       <c r="M22" s="43"/>
       <c r="N22" s="44"/>
-      <c r="O22" s="119"/>
+      <c r="O22" s="125"/>
       <c r="P22" s="43"/>
       <c r="Q22" s="44"/>
       <c r="R22" s="19"/>
@@ -7073,21 +7549,21 @@
       <c r="Z22" s="15"/>
     </row>
     <row r="23" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A23" s="132"/>
+      <c r="A23" s="120"/>
       <c r="B23" s="44"/>
-      <c r="C23" s="133"/>
+      <c r="C23" s="121"/>
       <c r="D23" s="44"/>
-      <c r="E23" s="133"/>
+      <c r="E23" s="121"/>
       <c r="F23" s="44"/>
-      <c r="G23" s="120"/>
+      <c r="G23" s="124"/>
       <c r="H23" s="43"/>
       <c r="I23" s="44"/>
-      <c r="J23" s="120"/>
+      <c r="J23" s="124"/>
       <c r="K23" s="44"/>
-      <c r="L23" s="119"/>
+      <c r="L23" s="125"/>
       <c r="M23" s="43"/>
       <c r="N23" s="44"/>
-      <c r="O23" s="119"/>
+      <c r="O23" s="125"/>
       <c r="P23" s="43"/>
       <c r="Q23" s="44"/>
       <c r="R23" s="19"/>
@@ -7101,21 +7577,21 @@
       <c r="Z23" s="15"/>
     </row>
     <row r="24" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A24" s="132"/>
+      <c r="A24" s="120"/>
       <c r="B24" s="44"/>
-      <c r="C24" s="133"/>
+      <c r="C24" s="121"/>
       <c r="D24" s="44"/>
-      <c r="E24" s="133"/>
+      <c r="E24" s="121"/>
       <c r="F24" s="44"/>
-      <c r="G24" s="120"/>
+      <c r="G24" s="124"/>
       <c r="H24" s="43"/>
       <c r="I24" s="44"/>
-      <c r="J24" s="120"/>
+      <c r="J24" s="124"/>
       <c r="K24" s="44"/>
-      <c r="L24" s="119"/>
+      <c r="L24" s="125"/>
       <c r="M24" s="43"/>
       <c r="N24" s="44"/>
-      <c r="O24" s="119"/>
+      <c r="O24" s="125"/>
       <c r="P24" s="43"/>
       <c r="Q24" s="44"/>
       <c r="R24" s="19"/>
@@ -7129,21 +7605,21 @@
       <c r="Z24" s="15"/>
     </row>
     <row r="25" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A25" s="132"/>
+      <c r="A25" s="120"/>
       <c r="B25" s="44"/>
-      <c r="C25" s="133"/>
+      <c r="C25" s="121"/>
       <c r="D25" s="44"/>
-      <c r="E25" s="133"/>
+      <c r="E25" s="121"/>
       <c r="F25" s="44"/>
-      <c r="G25" s="120"/>
+      <c r="G25" s="124"/>
       <c r="H25" s="43"/>
       <c r="I25" s="44"/>
-      <c r="J25" s="120"/>
+      <c r="J25" s="124"/>
       <c r="K25" s="44"/>
-      <c r="L25" s="119"/>
+      <c r="L25" s="125"/>
       <c r="M25" s="43"/>
       <c r="N25" s="44"/>
-      <c r="O25" s="119"/>
+      <c r="O25" s="125"/>
       <c r="P25" s="43"/>
       <c r="Q25" s="44"/>
       <c r="R25" s="19"/>
@@ -7157,21 +7633,21 @@
       <c r="Z25" s="15"/>
     </row>
     <row r="26" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A26" s="132"/>
+      <c r="A26" s="120"/>
       <c r="B26" s="44"/>
-      <c r="C26" s="133"/>
+      <c r="C26" s="121"/>
       <c r="D26" s="44"/>
-      <c r="E26" s="133"/>
+      <c r="E26" s="121"/>
       <c r="F26" s="44"/>
-      <c r="G26" s="120"/>
+      <c r="G26" s="124"/>
       <c r="H26" s="43"/>
       <c r="I26" s="44"/>
-      <c r="J26" s="120"/>
+      <c r="J26" s="124"/>
       <c r="K26" s="44"/>
-      <c r="L26" s="119"/>
+      <c r="L26" s="125"/>
       <c r="M26" s="43"/>
       <c r="N26" s="44"/>
-      <c r="O26" s="119"/>
+      <c r="O26" s="125"/>
       <c r="P26" s="43"/>
       <c r="Q26" s="44"/>
       <c r="R26" s="19"/>
@@ -7185,21 +7661,21 @@
       <c r="Z26" s="15"/>
     </row>
     <row r="27" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A27" s="132"/>
+      <c r="A27" s="120"/>
       <c r="B27" s="44"/>
-      <c r="C27" s="133"/>
+      <c r="C27" s="121"/>
       <c r="D27" s="44"/>
-      <c r="E27" s="133"/>
+      <c r="E27" s="121"/>
       <c r="F27" s="44"/>
-      <c r="G27" s="120"/>
+      <c r="G27" s="124"/>
       <c r="H27" s="43"/>
       <c r="I27" s="44"/>
-      <c r="J27" s="120"/>
+      <c r="J27" s="124"/>
       <c r="K27" s="44"/>
-      <c r="L27" s="119"/>
+      <c r="L27" s="125"/>
       <c r="M27" s="43"/>
       <c r="N27" s="44"/>
-      <c r="O27" s="119"/>
+      <c r="O27" s="125"/>
       <c r="P27" s="43"/>
       <c r="Q27" s="44"/>
       <c r="R27" s="19"/>
@@ -7213,21 +7689,21 @@
       <c r="Z27" s="15"/>
     </row>
     <row r="28" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A28" s="132"/>
+      <c r="A28" s="120"/>
       <c r="B28" s="44"/>
-      <c r="C28" s="133"/>
+      <c r="C28" s="121"/>
       <c r="D28" s="44"/>
-      <c r="E28" s="133"/>
+      <c r="E28" s="121"/>
       <c r="F28" s="44"/>
-      <c r="G28" s="120"/>
+      <c r="G28" s="124"/>
       <c r="H28" s="43"/>
       <c r="I28" s="44"/>
-      <c r="J28" s="120"/>
+      <c r="J28" s="124"/>
       <c r="K28" s="44"/>
-      <c r="L28" s="119"/>
+      <c r="L28" s="125"/>
       <c r="M28" s="43"/>
       <c r="N28" s="44"/>
-      <c r="O28" s="119"/>
+      <c r="O28" s="125"/>
       <c r="P28" s="43"/>
       <c r="Q28" s="44"/>
       <c r="R28" s="19"/>
@@ -7241,21 +7717,21 @@
       <c r="Z28" s="15"/>
     </row>
     <row r="29" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A29" s="132"/>
+      <c r="A29" s="120"/>
       <c r="B29" s="44"/>
-      <c r="C29" s="133"/>
+      <c r="C29" s="121"/>
       <c r="D29" s="44"/>
-      <c r="E29" s="133"/>
+      <c r="E29" s="121"/>
       <c r="F29" s="44"/>
-      <c r="G29" s="120"/>
+      <c r="G29" s="124"/>
       <c r="H29" s="43"/>
       <c r="I29" s="44"/>
-      <c r="J29" s="120"/>
+      <c r="J29" s="124"/>
       <c r="K29" s="44"/>
-      <c r="L29" s="119"/>
+      <c r="L29" s="125"/>
       <c r="M29" s="43"/>
       <c r="N29" s="44"/>
-      <c r="O29" s="119"/>
+      <c r="O29" s="125"/>
       <c r="P29" s="43"/>
       <c r="Q29" s="44"/>
       <c r="R29" s="19"/>
@@ -7269,21 +7745,21 @@
       <c r="Z29" s="15"/>
     </row>
     <row r="30" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A30" s="132"/>
+      <c r="A30" s="120"/>
       <c r="B30" s="44"/>
-      <c r="C30" s="133"/>
+      <c r="C30" s="121"/>
       <c r="D30" s="44"/>
-      <c r="E30" s="133"/>
+      <c r="E30" s="121"/>
       <c r="F30" s="44"/>
-      <c r="G30" s="120"/>
+      <c r="G30" s="124"/>
       <c r="H30" s="43"/>
       <c r="I30" s="44"/>
-      <c r="J30" s="120"/>
+      <c r="J30" s="124"/>
       <c r="K30" s="44"/>
-      <c r="L30" s="119"/>
+      <c r="L30" s="125"/>
       <c r="M30" s="43"/>
       <c r="N30" s="44"/>
-      <c r="O30" s="119"/>
+      <c r="O30" s="125"/>
       <c r="P30" s="43"/>
       <c r="Q30" s="44"/>
       <c r="R30" s="19"/>
@@ -7297,23 +7773,23 @@
       <c r="Z30" s="15"/>
     </row>
     <row r="31" spans="1:26" ht="12.75" customHeight="1" thickBot="1">
-      <c r="A31" s="135"/>
-      <c r="B31" s="75"/>
-      <c r="C31" s="136"/>
-      <c r="D31" s="75"/>
-      <c r="E31" s="136"/>
-      <c r="F31" s="75"/>
-      <c r="G31" s="122"/>
-      <c r="H31" s="74"/>
-      <c r="I31" s="75"/>
-      <c r="J31" s="122"/>
-      <c r="K31" s="75"/>
-      <c r="L31" s="121"/>
-      <c r="M31" s="74"/>
-      <c r="N31" s="75"/>
-      <c r="O31" s="121"/>
-      <c r="P31" s="74"/>
-      <c r="Q31" s="75"/>
+      <c r="A31" s="122"/>
+      <c r="B31" s="49"/>
+      <c r="C31" s="123"/>
+      <c r="D31" s="49"/>
+      <c r="E31" s="123"/>
+      <c r="F31" s="49"/>
+      <c r="G31" s="137"/>
+      <c r="H31" s="48"/>
+      <c r="I31" s="49"/>
+      <c r="J31" s="137"/>
+      <c r="K31" s="49"/>
+      <c r="L31" s="126"/>
+      <c r="M31" s="48"/>
+      <c r="N31" s="49"/>
+      <c r="O31" s="126"/>
+      <c r="P31" s="48"/>
+      <c r="Q31" s="49"/>
       <c r="R31" s="17"/>
       <c r="S31" s="17"/>
       <c r="T31" s="16"/>
@@ -8311,66 +8787,58 @@
     <row r="1000" s="13" customFormat="1" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="136">
-    <mergeCell ref="A23:B23"/>
-    <mergeCell ref="A30:B30"/>
-    <mergeCell ref="C30:D30"/>
-    <mergeCell ref="E30:F30"/>
-    <mergeCell ref="A31:B31"/>
-    <mergeCell ref="C31:D31"/>
-    <mergeCell ref="E31:F31"/>
-    <mergeCell ref="C26:D26"/>
-    <mergeCell ref="E26:F26"/>
-    <mergeCell ref="A24:B24"/>
-    <mergeCell ref="C28:D28"/>
-    <mergeCell ref="E28:F28"/>
-    <mergeCell ref="A29:B29"/>
-    <mergeCell ref="A25:B25"/>
-    <mergeCell ref="C25:D25"/>
-    <mergeCell ref="E25:F25"/>
-    <mergeCell ref="A26:B26"/>
-    <mergeCell ref="C29:D29"/>
-    <mergeCell ref="E29:F29"/>
-    <mergeCell ref="A27:B27"/>
-    <mergeCell ref="C27:D27"/>
-    <mergeCell ref="E27:F27"/>
-    <mergeCell ref="A28:B28"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="E21:F21"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="E22:F22"/>
-    <mergeCell ref="A18:B18"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="E18:F18"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="E19:F19"/>
-    <mergeCell ref="E16:F16"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="E17:F17"/>
-    <mergeCell ref="C23:D23"/>
-    <mergeCell ref="E23:F23"/>
-    <mergeCell ref="C24:D24"/>
-    <mergeCell ref="E24:F24"/>
-    <mergeCell ref="G21:I21"/>
-    <mergeCell ref="J21:K21"/>
-    <mergeCell ref="J16:K16"/>
-    <mergeCell ref="G17:I17"/>
-    <mergeCell ref="J17:K17"/>
-    <mergeCell ref="O27:Q27"/>
-    <mergeCell ref="O28:Q28"/>
-    <mergeCell ref="O29:Q29"/>
-    <mergeCell ref="O30:Q30"/>
-    <mergeCell ref="O31:Q31"/>
-    <mergeCell ref="O19:Q19"/>
-    <mergeCell ref="O21:Q21"/>
-    <mergeCell ref="O22:Q22"/>
-    <mergeCell ref="O23:Q23"/>
-    <mergeCell ref="O24:Q24"/>
-    <mergeCell ref="O20:Q20"/>
-    <mergeCell ref="O25:Q25"/>
-    <mergeCell ref="O26:Q26"/>
+    <mergeCell ref="L26:N26"/>
+    <mergeCell ref="L27:N27"/>
+    <mergeCell ref="L28:N28"/>
+    <mergeCell ref="L29:N29"/>
+    <mergeCell ref="G25:I25"/>
+    <mergeCell ref="J25:K25"/>
+    <mergeCell ref="J26:K26"/>
+    <mergeCell ref="L30:N30"/>
+    <mergeCell ref="L31:N31"/>
+    <mergeCell ref="G30:I30"/>
+    <mergeCell ref="J30:K30"/>
+    <mergeCell ref="G31:I31"/>
+    <mergeCell ref="J31:K31"/>
+    <mergeCell ref="G26:I26"/>
+    <mergeCell ref="G27:I27"/>
+    <mergeCell ref="J27:K27"/>
+    <mergeCell ref="G28:I28"/>
+    <mergeCell ref="J28:K28"/>
+    <mergeCell ref="G29:I29"/>
+    <mergeCell ref="J29:K29"/>
+    <mergeCell ref="L18:N18"/>
+    <mergeCell ref="L19:N19"/>
+    <mergeCell ref="L21:N21"/>
+    <mergeCell ref="L22:N22"/>
+    <mergeCell ref="L23:N23"/>
+    <mergeCell ref="L24:N24"/>
+    <mergeCell ref="L25:N25"/>
+    <mergeCell ref="L20:N20"/>
+    <mergeCell ref="G2:J4"/>
+    <mergeCell ref="L15:N15"/>
+    <mergeCell ref="G22:I22"/>
+    <mergeCell ref="J22:K22"/>
+    <mergeCell ref="G23:I23"/>
+    <mergeCell ref="J23:K23"/>
+    <mergeCell ref="G24:I24"/>
+    <mergeCell ref="J24:K24"/>
+    <mergeCell ref="A5:F5"/>
+    <mergeCell ref="G5:T5"/>
+    <mergeCell ref="A6:F6"/>
+    <mergeCell ref="G6:T6"/>
+    <mergeCell ref="A7:F7"/>
+    <mergeCell ref="G7:T7"/>
+    <mergeCell ref="K2:N4"/>
+    <mergeCell ref="O2:P4"/>
+    <mergeCell ref="Q2:R4"/>
+    <mergeCell ref="S2:T4"/>
+    <mergeCell ref="A1:F4"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="O1:P1"/>
+    <mergeCell ref="Q1:R1"/>
+    <mergeCell ref="S1:T1"/>
     <mergeCell ref="O15:Q15"/>
     <mergeCell ref="L16:N16"/>
     <mergeCell ref="O16:Q16"/>
@@ -8395,64 +8863,513 @@
     <mergeCell ref="J15:K15"/>
     <mergeCell ref="G16:I16"/>
     <mergeCell ref="C16:D16"/>
-    <mergeCell ref="A5:F5"/>
-    <mergeCell ref="G5:T5"/>
-    <mergeCell ref="A6:F6"/>
-    <mergeCell ref="G6:T6"/>
-    <mergeCell ref="A7:F7"/>
-    <mergeCell ref="G7:T7"/>
-    <mergeCell ref="K2:N4"/>
-    <mergeCell ref="O2:P4"/>
-    <mergeCell ref="Q2:R4"/>
-    <mergeCell ref="S2:T4"/>
-    <mergeCell ref="A1:F4"/>
-    <mergeCell ref="G1:J1"/>
-    <mergeCell ref="K1:N1"/>
-    <mergeCell ref="O1:P1"/>
-    <mergeCell ref="Q1:R1"/>
-    <mergeCell ref="S1:T1"/>
-    <mergeCell ref="L18:N18"/>
-    <mergeCell ref="L19:N19"/>
-    <mergeCell ref="L21:N21"/>
-    <mergeCell ref="L22:N22"/>
-    <mergeCell ref="L23:N23"/>
-    <mergeCell ref="L24:N24"/>
-    <mergeCell ref="L25:N25"/>
-    <mergeCell ref="L20:N20"/>
-    <mergeCell ref="G2:J4"/>
-    <mergeCell ref="L15:N15"/>
-    <mergeCell ref="G22:I22"/>
-    <mergeCell ref="J22:K22"/>
-    <mergeCell ref="G23:I23"/>
-    <mergeCell ref="J23:K23"/>
-    <mergeCell ref="G24:I24"/>
-    <mergeCell ref="J24:K24"/>
-    <mergeCell ref="L26:N26"/>
-    <mergeCell ref="L27:N27"/>
-    <mergeCell ref="L28:N28"/>
-    <mergeCell ref="L29:N29"/>
-    <mergeCell ref="G25:I25"/>
-    <mergeCell ref="J25:K25"/>
-    <mergeCell ref="J26:K26"/>
-    <mergeCell ref="L30:N30"/>
-    <mergeCell ref="L31:N31"/>
-    <mergeCell ref="G30:I30"/>
-    <mergeCell ref="J30:K30"/>
-    <mergeCell ref="G31:I31"/>
-    <mergeCell ref="J31:K31"/>
-    <mergeCell ref="G26:I26"/>
-    <mergeCell ref="G27:I27"/>
-    <mergeCell ref="J27:K27"/>
-    <mergeCell ref="G28:I28"/>
-    <mergeCell ref="J28:K28"/>
-    <mergeCell ref="G29:I29"/>
-    <mergeCell ref="J29:K29"/>
+    <mergeCell ref="O27:Q27"/>
+    <mergeCell ref="O28:Q28"/>
+    <mergeCell ref="O29:Q29"/>
+    <mergeCell ref="O30:Q30"/>
+    <mergeCell ref="O31:Q31"/>
+    <mergeCell ref="O19:Q19"/>
+    <mergeCell ref="O21:Q21"/>
+    <mergeCell ref="O22:Q22"/>
+    <mergeCell ref="O23:Q23"/>
+    <mergeCell ref="O24:Q24"/>
+    <mergeCell ref="O20:Q20"/>
+    <mergeCell ref="O25:Q25"/>
+    <mergeCell ref="O26:Q26"/>
+    <mergeCell ref="E16:F16"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="E23:F23"/>
+    <mergeCell ref="C24:D24"/>
+    <mergeCell ref="E24:F24"/>
+    <mergeCell ref="G21:I21"/>
+    <mergeCell ref="J21:K21"/>
+    <mergeCell ref="J16:K16"/>
+    <mergeCell ref="G17:I17"/>
+    <mergeCell ref="J17:K17"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="E21:F21"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="E22:F22"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="E18:F18"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="E19:F19"/>
+    <mergeCell ref="A23:B23"/>
+    <mergeCell ref="A30:B30"/>
+    <mergeCell ref="C30:D30"/>
+    <mergeCell ref="E30:F30"/>
+    <mergeCell ref="A31:B31"/>
+    <mergeCell ref="C31:D31"/>
+    <mergeCell ref="E31:F31"/>
+    <mergeCell ref="C26:D26"/>
+    <mergeCell ref="E26:F26"/>
+    <mergeCell ref="A24:B24"/>
+    <mergeCell ref="C28:D28"/>
+    <mergeCell ref="E28:F28"/>
+    <mergeCell ref="A29:B29"/>
+    <mergeCell ref="A25:B25"/>
+    <mergeCell ref="C25:D25"/>
+    <mergeCell ref="E25:F25"/>
+    <mergeCell ref="A26:B26"/>
+    <mergeCell ref="C29:D29"/>
+    <mergeCell ref="E29:F29"/>
+    <mergeCell ref="A27:B27"/>
+    <mergeCell ref="C27:D27"/>
+    <mergeCell ref="E27:F27"/>
+    <mergeCell ref="A28:B28"/>
   </mergeCells>
-  <phoneticPr fontId="3"/>
+  <phoneticPr fontId="4"/>
   <hyperlinks>
     <hyperlink ref="L18" r:id="rId1" xr:uid="{9277DA13-9E2D-44D7-BE3D-3D83610CC568}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup paperSize="9" orientation="landscape"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C1099CA-27EA-4934-AD05-F88BE657AA80}">
+  <dimension ref="A1:O42"/>
+  <sheetFormatPr defaultRowHeight="18.75"/>
+  <cols>
+    <col min="1" max="16384" width="9" style="148"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:15" ht="19.5" thickBot="1">
+      <c r="A1" s="138" t="s">
+        <v>87</v>
+      </c>
+      <c r="B1" s="139"/>
+      <c r="C1" s="140"/>
+      <c r="D1" s="141" t="s">
+        <v>88</v>
+      </c>
+      <c r="E1" s="142"/>
+      <c r="F1" s="140"/>
+      <c r="G1" s="143" t="s">
+        <v>89</v>
+      </c>
+      <c r="H1" s="142"/>
+      <c r="I1" s="144" t="s">
+        <v>90</v>
+      </c>
+      <c r="J1" s="145"/>
+      <c r="K1" s="144" t="s">
+        <v>91</v>
+      </c>
+      <c r="L1" s="145"/>
+      <c r="M1" s="144" t="s">
+        <v>92</v>
+      </c>
+      <c r="N1" s="146"/>
+      <c r="O1" s="147"/>
+    </row>
+    <row r="2" spans="1:15">
+      <c r="A2" s="149"/>
+      <c r="B2" s="150"/>
+      <c r="C2" s="138" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" s="151"/>
+      <c r="E2" s="139"/>
+      <c r="F2" s="138" t="s">
+        <v>7</v>
+      </c>
+      <c r="G2" s="151"/>
+      <c r="H2" s="139"/>
+      <c r="I2" s="167">
+        <v>45827</v>
+      </c>
+      <c r="J2" s="139"/>
+      <c r="K2" s="138" t="s">
+        <v>28</v>
+      </c>
+      <c r="L2" s="139"/>
+      <c r="M2" s="138"/>
+      <c r="N2" s="139"/>
+      <c r="O2" s="152"/>
+    </row>
+    <row r="3" spans="1:15" ht="19.5" thickBot="1">
+      <c r="A3" s="153"/>
+      <c r="B3" s="154"/>
+      <c r="C3" s="153"/>
+      <c r="D3" s="155"/>
+      <c r="E3" s="154"/>
+      <c r="F3" s="153"/>
+      <c r="G3" s="155"/>
+      <c r="H3" s="154"/>
+      <c r="I3" s="153"/>
+      <c r="J3" s="154"/>
+      <c r="K3" s="153"/>
+      <c r="L3" s="154"/>
+      <c r="M3" s="153"/>
+      <c r="N3" s="154"/>
+      <c r="O3" s="152"/>
+    </row>
+    <row r="4" spans="1:15">
+      <c r="A4" s="138" t="s">
+        <v>93</v>
+      </c>
+      <c r="B4" s="139"/>
+      <c r="C4" s="156" t="s">
+        <v>41</v>
+      </c>
+      <c r="D4" s="157"/>
+      <c r="E4" s="157"/>
+      <c r="F4" s="157"/>
+      <c r="G4" s="157"/>
+      <c r="H4" s="157"/>
+      <c r="I4" s="157"/>
+      <c r="J4" s="157"/>
+      <c r="K4" s="157"/>
+      <c r="L4" s="157"/>
+      <c r="M4" s="157"/>
+      <c r="N4" s="158"/>
+      <c r="O4" s="152"/>
+    </row>
+    <row r="5" spans="1:15" ht="19.5" thickBot="1">
+      <c r="A5" s="153"/>
+      <c r="B5" s="154"/>
+      <c r="C5" s="159"/>
+      <c r="D5" s="160"/>
+      <c r="E5" s="160"/>
+      <c r="F5" s="160"/>
+      <c r="G5" s="160"/>
+      <c r="H5" s="160"/>
+      <c r="I5" s="160"/>
+      <c r="J5" s="160"/>
+      <c r="K5" s="160"/>
+      <c r="L5" s="160"/>
+      <c r="M5" s="160"/>
+      <c r="N5" s="161"/>
+      <c r="O5" s="152"/>
+    </row>
+    <row r="6" spans="1:15" ht="19.5" thickBot="1">
+      <c r="A6" s="144" t="s">
+        <v>94</v>
+      </c>
+      <c r="B6" s="145"/>
+      <c r="C6" s="144" t="s">
+        <v>95</v>
+      </c>
+      <c r="D6" s="146"/>
+      <c r="E6" s="146"/>
+      <c r="F6" s="146"/>
+      <c r="G6" s="146"/>
+      <c r="H6" s="146"/>
+      <c r="I6" s="146"/>
+      <c r="J6" s="146"/>
+      <c r="K6" s="146"/>
+      <c r="L6" s="146"/>
+      <c r="M6" s="146"/>
+      <c r="N6" s="145"/>
+      <c r="O6" s="152"/>
+    </row>
+    <row r="7" spans="1:15">
+      <c r="A7" s="138">
+        <v>1</v>
+      </c>
+      <c r="B7" s="139"/>
+      <c r="C7" s="162"/>
+      <c r="D7" s="162"/>
+      <c r="E7" s="162"/>
+      <c r="F7" s="162"/>
+      <c r="G7" s="162"/>
+      <c r="H7" s="162"/>
+      <c r="I7" s="162"/>
+      <c r="J7" s="162"/>
+      <c r="K7" s="162"/>
+      <c r="L7" s="162"/>
+      <c r="M7" s="162"/>
+      <c r="N7" s="162"/>
+      <c r="O7" s="152"/>
+    </row>
+    <row r="8" spans="1:15">
+      <c r="A8" s="149"/>
+      <c r="B8" s="150"/>
+      <c r="O8" s="152"/>
+    </row>
+    <row r="9" spans="1:15">
+      <c r="A9" s="149"/>
+      <c r="B9" s="150"/>
+      <c r="N9" s="163"/>
+    </row>
+    <row r="10" spans="1:15">
+      <c r="A10" s="149"/>
+      <c r="B10" s="150"/>
+      <c r="O10" s="152"/>
+    </row>
+    <row r="11" spans="1:15">
+      <c r="A11" s="149"/>
+      <c r="B11" s="150"/>
+      <c r="O11" s="152"/>
+    </row>
+    <row r="12" spans="1:15">
+      <c r="A12" s="149"/>
+      <c r="B12" s="150"/>
+      <c r="O12" s="152"/>
+    </row>
+    <row r="13" spans="1:15">
+      <c r="A13" s="149"/>
+      <c r="B13" s="150"/>
+      <c r="O13" s="152"/>
+    </row>
+    <row r="14" spans="1:15">
+      <c r="A14" s="149"/>
+      <c r="B14" s="150"/>
+      <c r="O14" s="152"/>
+    </row>
+    <row r="15" spans="1:15" ht="42" customHeight="1" thickBot="1">
+      <c r="A15" s="153"/>
+      <c r="B15" s="154"/>
+      <c r="C15" s="164"/>
+      <c r="D15" s="164"/>
+      <c r="E15" s="164"/>
+      <c r="F15" s="164"/>
+      <c r="G15" s="164"/>
+      <c r="H15" s="164"/>
+      <c r="I15" s="164"/>
+      <c r="J15" s="164"/>
+      <c r="K15" s="164"/>
+      <c r="L15" s="164"/>
+      <c r="M15" s="164"/>
+      <c r="N15" s="165"/>
+      <c r="O15" s="152"/>
+    </row>
+    <row r="16" spans="1:15">
+      <c r="A16" s="138">
+        <v>2</v>
+      </c>
+      <c r="B16" s="139"/>
+      <c r="C16" s="162"/>
+      <c r="D16" s="162"/>
+      <c r="E16" s="162"/>
+      <c r="F16" s="162"/>
+      <c r="G16" s="162"/>
+      <c r="H16" s="162"/>
+      <c r="I16" s="162"/>
+      <c r="J16" s="162"/>
+      <c r="K16" s="162"/>
+      <c r="L16" s="162"/>
+      <c r="M16" s="162"/>
+      <c r="N16" s="163"/>
+    </row>
+    <row r="17" spans="1:14">
+      <c r="A17" s="149"/>
+      <c r="B17" s="150"/>
+      <c r="N17" s="163"/>
+    </row>
+    <row r="18" spans="1:14">
+      <c r="A18" s="149"/>
+      <c r="B18" s="150"/>
+      <c r="N18" s="163"/>
+    </row>
+    <row r="19" spans="1:14">
+      <c r="A19" s="149"/>
+      <c r="B19" s="150"/>
+      <c r="N19" s="163"/>
+    </row>
+    <row r="20" spans="1:14">
+      <c r="A20" s="149"/>
+      <c r="B20" s="150"/>
+      <c r="N20" s="163"/>
+    </row>
+    <row r="21" spans="1:14">
+      <c r="A21" s="149"/>
+      <c r="B21" s="150"/>
+      <c r="N21" s="163"/>
+    </row>
+    <row r="22" spans="1:14">
+      <c r="A22" s="149"/>
+      <c r="B22" s="150"/>
+      <c r="N22" s="163"/>
+    </row>
+    <row r="23" spans="1:14">
+      <c r="A23" s="149"/>
+      <c r="B23" s="150"/>
+      <c r="N23" s="163"/>
+    </row>
+    <row r="24" spans="1:14" ht="86.25" customHeight="1" thickBot="1">
+      <c r="A24" s="153"/>
+      <c r="B24" s="154"/>
+      <c r="C24" s="164"/>
+      <c r="D24" s="164"/>
+      <c r="E24" s="164"/>
+      <c r="F24" s="164"/>
+      <c r="G24" s="164"/>
+      <c r="H24" s="164"/>
+      <c r="I24" s="164"/>
+      <c r="J24" s="164"/>
+      <c r="K24" s="164"/>
+      <c r="L24" s="164"/>
+      <c r="M24" s="164"/>
+      <c r="N24" s="165"/>
+    </row>
+    <row r="25" spans="1:14">
+      <c r="A25" s="138">
+        <v>3</v>
+      </c>
+      <c r="B25" s="139"/>
+      <c r="C25" s="162"/>
+      <c r="D25" s="162"/>
+      <c r="E25" s="162"/>
+      <c r="F25" s="162"/>
+      <c r="G25" s="162"/>
+      <c r="H25" s="162"/>
+      <c r="I25" s="162"/>
+      <c r="J25" s="162"/>
+      <c r="K25" s="162"/>
+      <c r="L25" s="162"/>
+      <c r="M25" s="162"/>
+      <c r="N25" s="163"/>
+    </row>
+    <row r="26" spans="1:14">
+      <c r="A26" s="149"/>
+      <c r="B26" s="150"/>
+      <c r="N26" s="163"/>
+    </row>
+    <row r="27" spans="1:14">
+      <c r="A27" s="149"/>
+      <c r="B27" s="150"/>
+      <c r="N27" s="163"/>
+    </row>
+    <row r="28" spans="1:14">
+      <c r="A28" s="149"/>
+      <c r="B28" s="150"/>
+      <c r="N28" s="163"/>
+    </row>
+    <row r="29" spans="1:14">
+      <c r="A29" s="149"/>
+      <c r="B29" s="150"/>
+      <c r="N29" s="163"/>
+    </row>
+    <row r="30" spans="1:14">
+      <c r="A30" s="149"/>
+      <c r="B30" s="150"/>
+      <c r="N30" s="163"/>
+    </row>
+    <row r="31" spans="1:14">
+      <c r="A31" s="149"/>
+      <c r="B31" s="150"/>
+      <c r="N31" s="163"/>
+    </row>
+    <row r="32" spans="1:14">
+      <c r="A32" s="149"/>
+      <c r="B32" s="150"/>
+      <c r="N32" s="163"/>
+    </row>
+    <row r="33" spans="1:14" ht="93" customHeight="1" thickBot="1">
+      <c r="A33" s="153"/>
+      <c r="B33" s="154"/>
+      <c r="C33" s="164"/>
+      <c r="D33" s="164"/>
+      <c r="E33" s="164"/>
+      <c r="F33" s="164"/>
+      <c r="G33" s="164"/>
+      <c r="H33" s="164"/>
+      <c r="I33" s="164"/>
+      <c r="J33" s="164"/>
+      <c r="K33" s="164"/>
+      <c r="L33" s="164"/>
+      <c r="N33" s="163"/>
+    </row>
+    <row r="34" spans="1:14">
+      <c r="A34" s="138">
+        <v>4</v>
+      </c>
+      <c r="B34" s="139"/>
+      <c r="C34" s="162"/>
+      <c r="D34" s="162"/>
+      <c r="E34" s="162"/>
+      <c r="F34" s="162"/>
+      <c r="G34" s="162"/>
+      <c r="H34" s="162"/>
+      <c r="I34" s="162"/>
+      <c r="J34" s="162"/>
+      <c r="K34" s="162"/>
+      <c r="L34" s="162"/>
+      <c r="M34" s="162"/>
+      <c r="N34" s="166"/>
+    </row>
+    <row r="35" spans="1:14">
+      <c r="A35" s="149"/>
+      <c r="B35" s="150"/>
+      <c r="N35" s="163"/>
+    </row>
+    <row r="36" spans="1:14">
+      <c r="A36" s="149"/>
+      <c r="B36" s="150"/>
+      <c r="N36" s="163"/>
+    </row>
+    <row r="37" spans="1:14">
+      <c r="A37" s="149"/>
+      <c r="B37" s="150"/>
+      <c r="N37" s="163"/>
+    </row>
+    <row r="38" spans="1:14">
+      <c r="A38" s="149"/>
+      <c r="B38" s="150"/>
+      <c r="N38" s="163"/>
+    </row>
+    <row r="39" spans="1:14">
+      <c r="A39" s="149"/>
+      <c r="B39" s="150"/>
+      <c r="N39" s="163"/>
+    </row>
+    <row r="40" spans="1:14">
+      <c r="A40" s="149"/>
+      <c r="B40" s="150"/>
+      <c r="N40" s="163"/>
+    </row>
+    <row r="41" spans="1:14">
+      <c r="A41" s="149"/>
+      <c r="B41" s="150"/>
+      <c r="N41" s="163"/>
+    </row>
+    <row r="42" spans="1:14" ht="19.5" thickBot="1">
+      <c r="A42" s="153"/>
+      <c r="B42" s="154"/>
+      <c r="C42" s="164"/>
+      <c r="D42" s="164"/>
+      <c r="E42" s="164"/>
+      <c r="F42" s="164"/>
+      <c r="G42" s="164"/>
+      <c r="H42" s="164"/>
+      <c r="I42" s="164"/>
+      <c r="J42" s="164"/>
+      <c r="K42" s="164"/>
+      <c r="L42" s="164"/>
+      <c r="M42" s="164"/>
+      <c r="N42" s="165"/>
+    </row>
+  </sheetData>
+  <mergeCells count="17">
+    <mergeCell ref="A25:B33"/>
+    <mergeCell ref="A34:B42"/>
+    <mergeCell ref="A4:B5"/>
+    <mergeCell ref="C4:N5"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="C6:N6"/>
+    <mergeCell ref="A7:B15"/>
+    <mergeCell ref="A16:B24"/>
+    <mergeCell ref="A1:B3"/>
+    <mergeCell ref="I1:J1"/>
+    <mergeCell ref="K1:L1"/>
+    <mergeCell ref="M1:N1"/>
+    <mergeCell ref="C2:E3"/>
+    <mergeCell ref="F2:H3"/>
+    <mergeCell ref="I2:J3"/>
+    <mergeCell ref="K2:L3"/>
+    <mergeCell ref="M2:N3"/>
+  </mergeCells>
+  <phoneticPr fontId="4"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
 </file>
--- a/Documents/ログアウト機能設計書.xlsx
+++ b/Documents/ログアウト機能設計書.xlsx
@@ -8,18 +8,23 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\S-47\Documents\project\taskUN\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F803266E-78D7-45B7-AE0E-540C28136D45}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73255702-AD06-4BCD-94FC-DBC4417A7FFD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="3" xr2:uid="{72C6CFC4-7293-42D0-8B35-05AE043D8312}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="4" xr2:uid="{72C6CFC4-7293-42D0-8B35-05AE043D8312}"/>
   </bookViews>
   <sheets>
     <sheet name="ユースケース記述" sheetId="3" r:id="rId1"/>
     <sheet name="画面設計書" sheetId="2" r:id="rId2"/>
     <sheet name="画面遷移図" sheetId="5" r:id="rId3"/>
     <sheet name="テスト仕様書兼結果報告書" sheetId="4" r:id="rId4"/>
+    <sheet name="エビデンス" sheetId="6" r:id="rId5"/>
   </sheets>
+  <externalReferences>
+    <externalReference r:id="rId6"/>
+  </externalReferences>
   <definedNames>
     <definedName name="あ">#REF!</definedName>
+    <definedName name="ああ">#REF!</definedName>
     <definedName name="範囲１">#REF!</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -32,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="96">
   <si>
     <t>システム名</t>
   </si>
@@ -53,14 +58,14 @@
   </si>
   <si>
     <t>taskUN</t>
-    <phoneticPr fontId="3"/>
+    <phoneticPr fontId="4"/>
   </si>
   <si>
     <t>56期</t>
     <rPh sb="2" eb="3">
       <t>キ</t>
     </rPh>
-    <phoneticPr fontId="3"/>
+    <phoneticPr fontId="4"/>
   </si>
   <si>
     <t>画面名称</t>
@@ -100,35 +105,35 @@
     <rPh sb="5" eb="7">
       <t>ガメン</t>
     </rPh>
-    <phoneticPr fontId="3"/>
+    <phoneticPr fontId="4"/>
   </si>
   <si>
     <t>POST</t>
-    <phoneticPr fontId="3"/>
+    <phoneticPr fontId="4"/>
   </si>
   <si>
     <t>はいボタン</t>
-    <phoneticPr fontId="3"/>
+    <phoneticPr fontId="4"/>
   </si>
   <si>
     <t>いいえボタン</t>
-    <phoneticPr fontId="3"/>
+    <phoneticPr fontId="4"/>
   </si>
   <si>
     <t>submit</t>
-    <phoneticPr fontId="3"/>
+    <phoneticPr fontId="4"/>
   </si>
   <si>
     <t>はい</t>
-    <phoneticPr fontId="3"/>
+    <phoneticPr fontId="4"/>
   </si>
   <si>
     <t>いいえ</t>
-    <phoneticPr fontId="3"/>
+    <phoneticPr fontId="4"/>
   </si>
   <si>
     <t>logout-servlet</t>
-    <phoneticPr fontId="3"/>
+    <phoneticPr fontId="4"/>
   </si>
   <si>
     <t>いいえボタンが押下された場合メニュー画面に遷移</t>
@@ -144,18 +149,18 @@
     <rPh sb="21" eb="23">
       <t>センイ</t>
     </rPh>
-    <phoneticPr fontId="3"/>
+    <phoneticPr fontId="4"/>
   </si>
   <si>
     <t>山形</t>
     <rPh sb="0" eb="2">
       <t>ヤマガタ</t>
     </rPh>
-    <phoneticPr fontId="3"/>
+    <phoneticPr fontId="4"/>
   </si>
   <si>
     <t>なし</t>
-    <phoneticPr fontId="3"/>
+    <phoneticPr fontId="4"/>
   </si>
   <si>
     <t>ユースケース記述</t>
@@ -171,7 +176,7 @@
   </si>
   <si>
     <t>ユーザー</t>
-    <phoneticPr fontId="3"/>
+    <phoneticPr fontId="4"/>
   </si>
   <si>
     <t>事前条件</t>
@@ -193,14 +198,14 @@
   </si>
   <si>
     <t>ログアウト</t>
-    <phoneticPr fontId="3"/>
+    <phoneticPr fontId="4"/>
   </si>
   <si>
     <t>ログアウト画面からログアウトする</t>
     <rPh sb="5" eb="7">
       <t>ガメン</t>
     </rPh>
-    <phoneticPr fontId="3"/>
+    <phoneticPr fontId="4"/>
   </si>
   <si>
     <t>①ユーザー：ログアウト画面で「いいえ」ボタンを押下する
@@ -217,7 +222,7 @@
     <rPh sb="41" eb="43">
       <t>センイ</t>
     </rPh>
-    <phoneticPr fontId="3"/>
+    <phoneticPr fontId="4"/>
   </si>
   <si>
     <t>①ユーザー：ログインしていない状態で画面を開く
@@ -240,7 +245,7 @@
     <rPh sb="68" eb="70">
       <t>ヒョウジ</t>
     </rPh>
-    <phoneticPr fontId="3"/>
+    <phoneticPr fontId="4"/>
   </si>
   <si>
     <t>ログイン画面へ遷移する</t>
@@ -318,7 +323,7 @@
     <rPh sb="4" eb="6">
       <t>ジョウタイ</t>
     </rPh>
-    <phoneticPr fontId="3"/>
+    <phoneticPr fontId="4"/>
   </si>
   <si>
     <t>ログアウト画面で「はい」ボタンを押下する</t>
@@ -328,15 +333,15 @@
     <rPh sb="16" eb="18">
       <t>オウカ</t>
     </rPh>
-    <phoneticPr fontId="3"/>
+    <phoneticPr fontId="4"/>
   </si>
   <si>
     <t>「はい」ボタンを押下する</t>
-    <phoneticPr fontId="3"/>
+    <phoneticPr fontId="4"/>
   </si>
   <si>
     <t>◎</t>
-    <phoneticPr fontId="3"/>
+    <phoneticPr fontId="4"/>
   </si>
   <si>
     <t>ログアウト画面で「いいえ」ボタンを押下する</t>
@@ -346,22 +351,22 @@
     <rPh sb="17" eb="19">
       <t>オウカ</t>
     </rPh>
-    <phoneticPr fontId="3"/>
+    <phoneticPr fontId="4"/>
   </si>
   <si>
     <t>「いいえ」ボタンを押下する</t>
-    <phoneticPr fontId="3"/>
+    <phoneticPr fontId="4"/>
   </si>
   <si>
     <t>メニュー画面へ遷移する</t>
-    <phoneticPr fontId="3"/>
+    <phoneticPr fontId="4"/>
   </si>
   <si>
     <t>異常系</t>
     <rPh sb="0" eb="3">
       <t>イジョウケイ</t>
     </rPh>
-    <phoneticPr fontId="3"/>
+    <phoneticPr fontId="4"/>
   </si>
   <si>
     <t>ログインされていない状態でログアウト画面の表示させる</t>
@@ -374,14 +379,14 @@
     <rPh sb="21" eb="23">
       <t>ヒョウジ</t>
     </rPh>
-    <phoneticPr fontId="3"/>
+    <phoneticPr fontId="4"/>
   </si>
   <si>
     <t>ログアウト状態であること</t>
     <rPh sb="5" eb="7">
       <t>ジョウタイ</t>
     </rPh>
-    <phoneticPr fontId="3"/>
+    <phoneticPr fontId="4"/>
   </si>
   <si>
     <t>ログインされていませんというメッセージが表示され、その下にログイン画面へ誘導するリンクが表示される</t>
@@ -400,26 +405,26 @@
     <rPh sb="44" eb="46">
       <t>ヒョウジ</t>
     </rPh>
-    <phoneticPr fontId="3"/>
+    <phoneticPr fontId="4"/>
   </si>
   <si>
     <t>ログアウト画面</t>
-    <phoneticPr fontId="3"/>
+    <phoneticPr fontId="4"/>
   </si>
   <si>
     <t>Junitテスト仕様書</t>
     <rPh sb="8" eb="11">
       <t>シヨウショ</t>
     </rPh>
-    <phoneticPr fontId="3"/>
+    <phoneticPr fontId="4"/>
   </si>
   <si>
     <t>http://localhost:8080/taskUN/logout.jsp</t>
-    <phoneticPr fontId="3"/>
+    <phoneticPr fontId="4"/>
   </si>
   <si>
     <t>〇</t>
-    <phoneticPr fontId="3"/>
+    <phoneticPr fontId="4"/>
   </si>
   <si>
     <t>①ユーザー：ログアウト画面で「はい」ボタンを押下する
@@ -446,7 +451,7 @@
     <rPh sb="69" eb="71">
       <t>センイ</t>
     </rPh>
-    <phoneticPr fontId="3"/>
+    <phoneticPr fontId="4"/>
   </si>
   <si>
     <t>ログイン状態でログアウト画面を表示していること</t>
@@ -459,7 +464,7 @@
     <rPh sb="15" eb="17">
       <t>ヒョウジ</t>
     </rPh>
-    <phoneticPr fontId="3"/>
+    <phoneticPr fontId="4"/>
   </si>
   <si>
     <t>セッションが破棄されたのちに、画面が遷移する</t>
@@ -472,57 +477,90 @@
     <rPh sb="18" eb="20">
       <t>センイ</t>
     </rPh>
-    <phoneticPr fontId="3"/>
+    <phoneticPr fontId="4"/>
   </si>
   <si>
     <t>画面遷移図</t>
   </si>
   <si>
-    <t>ログアウト画面でログアウトボタンを押下し、遷移先のログイン画面でブラウザバックした際、エラーとなることを確認する</t>
-    <rPh sb="5" eb="7">
-      <t>ガメン</t>
+    <t>テストエビデンス</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>システム名</t>
+    <rPh sb="4" eb="5">
+      <t>メイ</t>
     </rPh>
-    <rPh sb="17" eb="19">
-      <t>オウカ</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>グループ名</t>
+    <rPh sb="4" eb="5">
+      <t>メイ</t>
     </rPh>
-    <rPh sb="21" eb="23">
-      <t>センイ</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>作成日</t>
+    <rPh sb="0" eb="3">
+      <t>サクセイビ</t>
     </rPh>
-    <rPh sb="23" eb="24">
-      <t>サキ</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>担当</t>
+    <rPh sb="0" eb="2">
+      <t>タントウ</t>
     </rPh>
-    <rPh sb="29" eb="31">
-      <t>ガメン</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>承認印</t>
+    <rPh sb="0" eb="3">
+      <t>ショウニンイン</t>
     </rPh>
-    <rPh sb="41" eb="42">
-      <t>サイ</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>機能名称</t>
+    <rPh sb="0" eb="2">
+      <t>キノウ</t>
     </rPh>
-    <rPh sb="52" eb="54">
-      <t>カクニン</t>
+    <rPh sb="2" eb="4">
+      <t>メイショウ</t>
     </rPh>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t>ログアウト後、ログイン画面でブラウザバックする</t>
-    <rPh sb="5" eb="6">
-      <t>ゴ</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>項番</t>
+    <rPh sb="0" eb="2">
+      <t>コウバン</t>
     </rPh>
-    <rPh sb="11" eb="13">
-      <t>ガメン</t>
-    </rPh>
-    <phoneticPr fontId="3"/>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>エビデンス</t>
+    <phoneticPr fontId="8"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7">
+  <fonts count="9">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="游ゴシック"/>
       <family val="3"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="游ゴシック"/>
+      <family val="2"/>
       <charset val="128"/>
       <scheme val="minor"/>
     </font>
@@ -569,6 +607,13 @@
       <charset val="128"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="6"/>
+      <name val="游ゴシック"/>
+      <family val="2"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -584,7 +629,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="56">
+  <borders count="67">
     <border>
       <left/>
       <right/>
@@ -1235,430 +1280,641 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="3">
+  <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="138">
+  <cellXfs count="168">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="28" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="28" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="29" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="28" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="28" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="33" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="33" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="33" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="33" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="56" fontId="6" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="56" fontId="3" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="20" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="21" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="22" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="26" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="24" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="25" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="56" fontId="3" fillId="0" borderId="12" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="18" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="19" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="19" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="27" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="27" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="20" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="30" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="31" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="32" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="34" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="35" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="56" fontId="3" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="27" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="56" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="57" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="58" xfId="3" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="59" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="60" xfId="3" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="59" xfId="3" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="58" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="60" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="59" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="56" xfId="3" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="3">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="61" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="62" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="63" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="61" xfId="3" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="64" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="65" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="66" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="56" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="63" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="57" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="64" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="66" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="65" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="63" xfId="3" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="62" xfId="3" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="56" fontId="5" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="66" xfId="3" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="65" xfId="3" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="57" xfId="3" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="56" fontId="1" fillId="0" borderId="56" xfId="3" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="56" fontId="2" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="20" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="21" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="22" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="26" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="24" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="25" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="17" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="56" fontId="2" fillId="0" borderId="12" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="18" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="19" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="27" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="27" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="30" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="31" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="32" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="34" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="35" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="56" fontId="2" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="27" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
   </cellXfs>
-  <cellStyles count="3">
+  <cellStyles count="4">
     <cellStyle name="ハイパーリンク" xfId="2" builtinId="8"/>
     <cellStyle name="標準" xfId="0" builtinId="0"/>
     <cellStyle name="標準 2" xfId="1" xr:uid="{A8A8EE7C-E6BE-41B2-83FE-4DDDEF0D5153}"/>
+    <cellStyle name="標準 3" xfId="3" xr:uid="{E06FF395-FDC6-45AE-93E9-080B605A3B0E}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -2071,6 +2327,191 @@
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>504826</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>59702</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>447676</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>436016</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="図 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B68B0D19-DD04-C0FC-49FF-BD730F251394}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3248026" y="1526552"/>
+          <a:ext cx="4057650" cy="2281314"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>466725</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>66188</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>523875</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>744889</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="5" name="図 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EE290B45-3498-2D80-D859-B966938FB30A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3209925" y="4209563"/>
+          <a:ext cx="4171950" cy="2345576"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>219075</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>200026</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>229890</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>1000126</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="7" name="図 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0B4F823D-9820-B621-FB57-ED4A0B5300B5}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2962275" y="7105651"/>
+          <a:ext cx="4811415" cy="2705100"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="ユースケース記述"/>
+      <sheetName val="画面設計書"/>
+      <sheetName val="画面遷移図"/>
+      <sheetName val="詳細クラス図"/>
+      <sheetName val="テスト仕様書兼結果報告書"/>
+      <sheetName val="JUnitテスト仕様書兼報告書"/>
+      <sheetName val="カバレッジレポート"/>
+      <sheetName val="エビデンス"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="1" refreshError="1"/>
+      <sheetData sheetId="2" refreshError="1"/>
+      <sheetData sheetId="3" refreshError="1"/>
+      <sheetData sheetId="4" refreshError="1"/>
+      <sheetData sheetId="5" refreshError="1"/>
+      <sheetData sheetId="6" refreshError="1"/>
+      <sheetData sheetId="7" refreshError="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -3608,7 +4049,7 @@
     <mergeCell ref="B11:C11"/>
     <mergeCell ref="D11:J11"/>
   </mergeCells>
-  <phoneticPr fontId="3"/>
+  <phoneticPr fontId="4"/>
   <pageMargins left="0.70833333333333304" right="0.70833333333333304" top="0.74791666666666701" bottom="0.74791666666666701" header="0" footer="0"/>
   <pageSetup paperSize="9" orientation="landscape"/>
 </worksheet>
@@ -4983,7 +5424,7 @@
     <mergeCell ref="A6:J6"/>
     <mergeCell ref="D15:H15"/>
   </mergeCells>
-  <phoneticPr fontId="3"/>
+  <phoneticPr fontId="4"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup paperSize="9" orientation="landscape"/>
   <drawing r:id="rId1"/>
@@ -6406,7 +6847,7 @@
     <mergeCell ref="D2:E4"/>
     <mergeCell ref="F2:G4"/>
   </mergeCells>
-  <phoneticPr fontId="3"/>
+  <phoneticPr fontId="4"/>
   <pageMargins left="0.70833333333333304" right="0.70833333333333304" top="0.74791666666666701" bottom="0.74791666666666701" header="0" footer="0"/>
   <pageSetup paperSize="9" orientation="landscape"/>
   <drawing r:id="rId1"/>
@@ -6899,7 +7340,7 @@
       <c r="Y16" s="15"/>
       <c r="Z16" s="15"/>
     </row>
-    <row r="17" spans="1:26" ht="51" customHeight="1">
+    <row r="17" spans="1:26" ht="41.25" customHeight="1">
       <c r="A17" s="120">
         <v>2</v>
       </c>
@@ -6995,47 +7436,27 @@
       <c r="Y18" s="15"/>
       <c r="Z18" s="15"/>
     </row>
-    <row r="19" spans="1:26" ht="63.75" customHeight="1">
-      <c r="A19" s="120">
-        <v>4</v>
-      </c>
+    <row r="19" spans="1:26" ht="12.75" customHeight="1">
+      <c r="A19" s="120"/>
       <c r="B19" s="44"/>
-      <c r="C19" s="121" t="s">
-        <v>71</v>
-      </c>
+      <c r="C19" s="121"/>
       <c r="D19" s="44"/>
-      <c r="E19" s="121" t="s">
-        <v>46</v>
-      </c>
+      <c r="E19" s="121"/>
       <c r="F19" s="44"/>
-      <c r="G19" s="124" t="s">
-        <v>87</v>
-      </c>
+      <c r="G19" s="124"/>
       <c r="H19" s="43"/>
       <c r="I19" s="44"/>
-      <c r="J19" s="124" t="s">
-        <v>77</v>
-      </c>
+      <c r="J19" s="124"/>
       <c r="K19" s="44"/>
-      <c r="L19" s="125" t="s">
-        <v>88</v>
-      </c>
+      <c r="L19" s="125"/>
       <c r="M19" s="43"/>
       <c r="N19" s="44"/>
-      <c r="O19" s="125" t="s">
-        <v>78</v>
-      </c>
+      <c r="O19" s="125"/>
       <c r="P19" s="43"/>
       <c r="Q19" s="44"/>
-      <c r="R19" s="36">
-        <v>45826</v>
-      </c>
-      <c r="S19" s="19" t="s">
-        <v>28</v>
-      </c>
-      <c r="T19" s="18" t="s">
-        <v>82</v>
-      </c>
+      <c r="R19" s="19"/>
+      <c r="S19" s="19"/>
+      <c r="T19" s="18"/>
       <c r="U19" s="15"/>
       <c r="V19" s="15"/>
       <c r="W19" s="15"/>
@@ -8503,11 +8924,452 @@
     <mergeCell ref="E27:F27"/>
     <mergeCell ref="A28:B28"/>
   </mergeCells>
-  <phoneticPr fontId="3"/>
+  <phoneticPr fontId="4"/>
   <hyperlinks>
     <hyperlink ref="L18" r:id="rId1" xr:uid="{9277DA13-9E2D-44D7-BE3D-3D83610CC568}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup paperSize="9" orientation="landscape"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C1099CA-27EA-4934-AD05-F88BE657AA80}">
+  <dimension ref="A1:O42"/>
+  <sheetFormatPr defaultRowHeight="18.75"/>
+  <cols>
+    <col min="1" max="16384" width="9" style="148"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:15" ht="19.5" thickBot="1">
+      <c r="A1" s="138" t="s">
+        <v>87</v>
+      </c>
+      <c r="B1" s="139"/>
+      <c r="C1" s="140"/>
+      <c r="D1" s="141" t="s">
+        <v>88</v>
+      </c>
+      <c r="E1" s="142"/>
+      <c r="F1" s="140"/>
+      <c r="G1" s="143" t="s">
+        <v>89</v>
+      </c>
+      <c r="H1" s="142"/>
+      <c r="I1" s="144" t="s">
+        <v>90</v>
+      </c>
+      <c r="J1" s="145"/>
+      <c r="K1" s="144" t="s">
+        <v>91</v>
+      </c>
+      <c r="L1" s="145"/>
+      <c r="M1" s="144" t="s">
+        <v>92</v>
+      </c>
+      <c r="N1" s="146"/>
+      <c r="O1" s="147"/>
+    </row>
+    <row r="2" spans="1:15">
+      <c r="A2" s="149"/>
+      <c r="B2" s="150"/>
+      <c r="C2" s="138" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" s="151"/>
+      <c r="E2" s="139"/>
+      <c r="F2" s="138" t="s">
+        <v>7</v>
+      </c>
+      <c r="G2" s="151"/>
+      <c r="H2" s="139"/>
+      <c r="I2" s="167">
+        <v>45827</v>
+      </c>
+      <c r="J2" s="139"/>
+      <c r="K2" s="138" t="s">
+        <v>28</v>
+      </c>
+      <c r="L2" s="139"/>
+      <c r="M2" s="138"/>
+      <c r="N2" s="139"/>
+      <c r="O2" s="152"/>
+    </row>
+    <row r="3" spans="1:15" ht="19.5" thickBot="1">
+      <c r="A3" s="153"/>
+      <c r="B3" s="154"/>
+      <c r="C3" s="153"/>
+      <c r="D3" s="155"/>
+      <c r="E3" s="154"/>
+      <c r="F3" s="153"/>
+      <c r="G3" s="155"/>
+      <c r="H3" s="154"/>
+      <c r="I3" s="153"/>
+      <c r="J3" s="154"/>
+      <c r="K3" s="153"/>
+      <c r="L3" s="154"/>
+      <c r="M3" s="153"/>
+      <c r="N3" s="154"/>
+      <c r="O3" s="152"/>
+    </row>
+    <row r="4" spans="1:15">
+      <c r="A4" s="138" t="s">
+        <v>93</v>
+      </c>
+      <c r="B4" s="139"/>
+      <c r="C4" s="156" t="s">
+        <v>41</v>
+      </c>
+      <c r="D4" s="157"/>
+      <c r="E4" s="157"/>
+      <c r="F4" s="157"/>
+      <c r="G4" s="157"/>
+      <c r="H4" s="157"/>
+      <c r="I4" s="157"/>
+      <c r="J4" s="157"/>
+      <c r="K4" s="157"/>
+      <c r="L4" s="157"/>
+      <c r="M4" s="157"/>
+      <c r="N4" s="158"/>
+      <c r="O4" s="152"/>
+    </row>
+    <row r="5" spans="1:15" ht="19.5" thickBot="1">
+      <c r="A5" s="153"/>
+      <c r="B5" s="154"/>
+      <c r="C5" s="159"/>
+      <c r="D5" s="160"/>
+      <c r="E5" s="160"/>
+      <c r="F5" s="160"/>
+      <c r="G5" s="160"/>
+      <c r="H5" s="160"/>
+      <c r="I5" s="160"/>
+      <c r="J5" s="160"/>
+      <c r="K5" s="160"/>
+      <c r="L5" s="160"/>
+      <c r="M5" s="160"/>
+      <c r="N5" s="161"/>
+      <c r="O5" s="152"/>
+    </row>
+    <row r="6" spans="1:15" ht="19.5" thickBot="1">
+      <c r="A6" s="144" t="s">
+        <v>94</v>
+      </c>
+      <c r="B6" s="145"/>
+      <c r="C6" s="144" t="s">
+        <v>95</v>
+      </c>
+      <c r="D6" s="146"/>
+      <c r="E6" s="146"/>
+      <c r="F6" s="146"/>
+      <c r="G6" s="146"/>
+      <c r="H6" s="146"/>
+      <c r="I6" s="146"/>
+      <c r="J6" s="146"/>
+      <c r="K6" s="146"/>
+      <c r="L6" s="146"/>
+      <c r="M6" s="146"/>
+      <c r="N6" s="145"/>
+      <c r="O6" s="152"/>
+    </row>
+    <row r="7" spans="1:15">
+      <c r="A7" s="138">
+        <v>1</v>
+      </c>
+      <c r="B7" s="139"/>
+      <c r="C7" s="162"/>
+      <c r="D7" s="162"/>
+      <c r="E7" s="162"/>
+      <c r="F7" s="162"/>
+      <c r="G7" s="162"/>
+      <c r="H7" s="162"/>
+      <c r="I7" s="162"/>
+      <c r="J7" s="162"/>
+      <c r="K7" s="162"/>
+      <c r="L7" s="162"/>
+      <c r="M7" s="162"/>
+      <c r="N7" s="162"/>
+      <c r="O7" s="152"/>
+    </row>
+    <row r="8" spans="1:15">
+      <c r="A8" s="149"/>
+      <c r="B8" s="150"/>
+      <c r="O8" s="152"/>
+    </row>
+    <row r="9" spans="1:15">
+      <c r="A9" s="149"/>
+      <c r="B9" s="150"/>
+      <c r="N9" s="163"/>
+    </row>
+    <row r="10" spans="1:15">
+      <c r="A10" s="149"/>
+      <c r="B10" s="150"/>
+      <c r="O10" s="152"/>
+    </row>
+    <row r="11" spans="1:15">
+      <c r="A11" s="149"/>
+      <c r="B11" s="150"/>
+      <c r="O11" s="152"/>
+    </row>
+    <row r="12" spans="1:15">
+      <c r="A12" s="149"/>
+      <c r="B12" s="150"/>
+      <c r="O12" s="152"/>
+    </row>
+    <row r="13" spans="1:15">
+      <c r="A13" s="149"/>
+      <c r="B13" s="150"/>
+      <c r="O13" s="152"/>
+    </row>
+    <row r="14" spans="1:15">
+      <c r="A14" s="149"/>
+      <c r="B14" s="150"/>
+      <c r="O14" s="152"/>
+    </row>
+    <row r="15" spans="1:15" ht="42" customHeight="1" thickBot="1">
+      <c r="A15" s="153"/>
+      <c r="B15" s="154"/>
+      <c r="C15" s="164"/>
+      <c r="D15" s="164"/>
+      <c r="E15" s="164"/>
+      <c r="F15" s="164"/>
+      <c r="G15" s="164"/>
+      <c r="H15" s="164"/>
+      <c r="I15" s="164"/>
+      <c r="J15" s="164"/>
+      <c r="K15" s="164"/>
+      <c r="L15" s="164"/>
+      <c r="M15" s="164"/>
+      <c r="N15" s="165"/>
+      <c r="O15" s="152"/>
+    </row>
+    <row r="16" spans="1:15">
+      <c r="A16" s="138">
+        <v>2</v>
+      </c>
+      <c r="B16" s="139"/>
+      <c r="C16" s="162"/>
+      <c r="D16" s="162"/>
+      <c r="E16" s="162"/>
+      <c r="F16" s="162"/>
+      <c r="G16" s="162"/>
+      <c r="H16" s="162"/>
+      <c r="I16" s="162"/>
+      <c r="J16" s="162"/>
+      <c r="K16" s="162"/>
+      <c r="L16" s="162"/>
+      <c r="M16" s="162"/>
+      <c r="N16" s="163"/>
+    </row>
+    <row r="17" spans="1:14">
+      <c r="A17" s="149"/>
+      <c r="B17" s="150"/>
+      <c r="N17" s="163"/>
+    </row>
+    <row r="18" spans="1:14">
+      <c r="A18" s="149"/>
+      <c r="B18" s="150"/>
+      <c r="N18" s="163"/>
+    </row>
+    <row r="19" spans="1:14">
+      <c r="A19" s="149"/>
+      <c r="B19" s="150"/>
+      <c r="N19" s="163"/>
+    </row>
+    <row r="20" spans="1:14">
+      <c r="A20" s="149"/>
+      <c r="B20" s="150"/>
+      <c r="N20" s="163"/>
+    </row>
+    <row r="21" spans="1:14">
+      <c r="A21" s="149"/>
+      <c r="B21" s="150"/>
+      <c r="N21" s="163"/>
+    </row>
+    <row r="22" spans="1:14">
+      <c r="A22" s="149"/>
+      <c r="B22" s="150"/>
+      <c r="N22" s="163"/>
+    </row>
+    <row r="23" spans="1:14">
+      <c r="A23" s="149"/>
+      <c r="B23" s="150"/>
+      <c r="N23" s="163"/>
+    </row>
+    <row r="24" spans="1:14" ht="86.25" customHeight="1" thickBot="1">
+      <c r="A24" s="153"/>
+      <c r="B24" s="154"/>
+      <c r="C24" s="164"/>
+      <c r="D24" s="164"/>
+      <c r="E24" s="164"/>
+      <c r="F24" s="164"/>
+      <c r="G24" s="164"/>
+      <c r="H24" s="164"/>
+      <c r="I24" s="164"/>
+      <c r="J24" s="164"/>
+      <c r="K24" s="164"/>
+      <c r="L24" s="164"/>
+      <c r="M24" s="164"/>
+      <c r="N24" s="165"/>
+    </row>
+    <row r="25" spans="1:14">
+      <c r="A25" s="138">
+        <v>3</v>
+      </c>
+      <c r="B25" s="139"/>
+      <c r="C25" s="162"/>
+      <c r="D25" s="162"/>
+      <c r="E25" s="162"/>
+      <c r="F25" s="162"/>
+      <c r="G25" s="162"/>
+      <c r="H25" s="162"/>
+      <c r="I25" s="162"/>
+      <c r="J25" s="162"/>
+      <c r="K25" s="162"/>
+      <c r="L25" s="162"/>
+      <c r="M25" s="162"/>
+      <c r="N25" s="163"/>
+    </row>
+    <row r="26" spans="1:14">
+      <c r="A26" s="149"/>
+      <c r="B26" s="150"/>
+      <c r="N26" s="163"/>
+    </row>
+    <row r="27" spans="1:14">
+      <c r="A27" s="149"/>
+      <c r="B27" s="150"/>
+      <c r="N27" s="163"/>
+    </row>
+    <row r="28" spans="1:14">
+      <c r="A28" s="149"/>
+      <c r="B28" s="150"/>
+      <c r="N28" s="163"/>
+    </row>
+    <row r="29" spans="1:14">
+      <c r="A29" s="149"/>
+      <c r="B29" s="150"/>
+      <c r="N29" s="163"/>
+    </row>
+    <row r="30" spans="1:14">
+      <c r="A30" s="149"/>
+      <c r="B30" s="150"/>
+      <c r="N30" s="163"/>
+    </row>
+    <row r="31" spans="1:14">
+      <c r="A31" s="149"/>
+      <c r="B31" s="150"/>
+      <c r="N31" s="163"/>
+    </row>
+    <row r="32" spans="1:14">
+      <c r="A32" s="149"/>
+      <c r="B32" s="150"/>
+      <c r="N32" s="163"/>
+    </row>
+    <row r="33" spans="1:14" ht="93" customHeight="1" thickBot="1">
+      <c r="A33" s="153"/>
+      <c r="B33" s="154"/>
+      <c r="C33" s="164"/>
+      <c r="D33" s="164"/>
+      <c r="E33" s="164"/>
+      <c r="F33" s="164"/>
+      <c r="G33" s="164"/>
+      <c r="H33" s="164"/>
+      <c r="I33" s="164"/>
+      <c r="J33" s="164"/>
+      <c r="K33" s="164"/>
+      <c r="L33" s="164"/>
+      <c r="N33" s="163"/>
+    </row>
+    <row r="34" spans="1:14">
+      <c r="A34" s="138">
+        <v>4</v>
+      </c>
+      <c r="B34" s="139"/>
+      <c r="C34" s="162"/>
+      <c r="D34" s="162"/>
+      <c r="E34" s="162"/>
+      <c r="F34" s="162"/>
+      <c r="G34" s="162"/>
+      <c r="H34" s="162"/>
+      <c r="I34" s="162"/>
+      <c r="J34" s="162"/>
+      <c r="K34" s="162"/>
+      <c r="L34" s="162"/>
+      <c r="M34" s="162"/>
+      <c r="N34" s="166"/>
+    </row>
+    <row r="35" spans="1:14">
+      <c r="A35" s="149"/>
+      <c r="B35" s="150"/>
+      <c r="N35" s="163"/>
+    </row>
+    <row r="36" spans="1:14">
+      <c r="A36" s="149"/>
+      <c r="B36" s="150"/>
+      <c r="N36" s="163"/>
+    </row>
+    <row r="37" spans="1:14">
+      <c r="A37" s="149"/>
+      <c r="B37" s="150"/>
+      <c r="N37" s="163"/>
+    </row>
+    <row r="38" spans="1:14">
+      <c r="A38" s="149"/>
+      <c r="B38" s="150"/>
+      <c r="N38" s="163"/>
+    </row>
+    <row r="39" spans="1:14">
+      <c r="A39" s="149"/>
+      <c r="B39" s="150"/>
+      <c r="N39" s="163"/>
+    </row>
+    <row r="40" spans="1:14">
+      <c r="A40" s="149"/>
+      <c r="B40" s="150"/>
+      <c r="N40" s="163"/>
+    </row>
+    <row r="41" spans="1:14">
+      <c r="A41" s="149"/>
+      <c r="B41" s="150"/>
+      <c r="N41" s="163"/>
+    </row>
+    <row r="42" spans="1:14" ht="19.5" thickBot="1">
+      <c r="A42" s="153"/>
+      <c r="B42" s="154"/>
+      <c r="C42" s="164"/>
+      <c r="D42" s="164"/>
+      <c r="E42" s="164"/>
+      <c r="F42" s="164"/>
+      <c r="G42" s="164"/>
+      <c r="H42" s="164"/>
+      <c r="I42" s="164"/>
+      <c r="J42" s="164"/>
+      <c r="K42" s="164"/>
+      <c r="L42" s="164"/>
+      <c r="M42" s="164"/>
+      <c r="N42" s="165"/>
+    </row>
+  </sheetData>
+  <mergeCells count="17">
+    <mergeCell ref="A25:B33"/>
+    <mergeCell ref="A34:B42"/>
+    <mergeCell ref="A4:B5"/>
+    <mergeCell ref="C4:N5"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="C6:N6"/>
+    <mergeCell ref="A7:B15"/>
+    <mergeCell ref="A16:B24"/>
+    <mergeCell ref="A1:B3"/>
+    <mergeCell ref="I1:J1"/>
+    <mergeCell ref="K1:L1"/>
+    <mergeCell ref="M1:N1"/>
+    <mergeCell ref="C2:E3"/>
+    <mergeCell ref="F2:H3"/>
+    <mergeCell ref="I2:J3"/>
+    <mergeCell ref="K2:L3"/>
+    <mergeCell ref="M2:N3"/>
+  </mergeCells>
+  <phoneticPr fontId="4"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
 </file>
--- a/Documents/ログアウト機能設計書.xlsx
+++ b/Documents/ログアウト機能設計書.xlsx
@@ -8,20 +8,18 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\S-47\Documents\project\taskUN\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73255702-AD06-4BCD-94FC-DBC4417A7FFD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{677D2FAF-2AFA-42D6-9134-6F6A1834F37E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="4" xr2:uid="{72C6CFC4-7293-42D0-8B35-05AE043D8312}"/>
   </bookViews>
   <sheets>
-    <sheet name="ユースケース記述" sheetId="3" r:id="rId1"/>
-    <sheet name="画面設計書" sheetId="2" r:id="rId2"/>
-    <sheet name="画面遷移図" sheetId="5" r:id="rId3"/>
-    <sheet name="テスト仕様書兼結果報告書" sheetId="4" r:id="rId4"/>
-    <sheet name="エビデンス" sheetId="6" r:id="rId5"/>
+    <sheet name="表紙" sheetId="7" r:id="rId1"/>
+    <sheet name="ユースケース記述" sheetId="3" r:id="rId2"/>
+    <sheet name="画面設計書" sheetId="2" r:id="rId3"/>
+    <sheet name="画面遷移図" sheetId="5" r:id="rId4"/>
+    <sheet name="テスト仕様書兼結果報告書" sheetId="4" r:id="rId5"/>
+    <sheet name="エビデンス" sheetId="6" r:id="rId6"/>
   </sheets>
-  <externalReferences>
-    <externalReference r:id="rId6"/>
-  </externalReferences>
   <definedNames>
     <definedName name="あ">#REF!</definedName>
     <definedName name="ああ">#REF!</definedName>
@@ -37,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="101">
   <si>
     <t>システム名</t>
   </si>
@@ -542,12 +540,35 @@
     <t>エビデンス</t>
     <phoneticPr fontId="8"/>
   </si>
+  <si>
+    <t>プロジェクト型演習　成果ドキュメント</t>
+  </si>
+  <si>
+    <t>初版</t>
+  </si>
+  <si>
+    <t>YYYY/MM/DD</t>
+  </si>
+  <si>
+    <t>山形みづき</t>
+    <rPh sb="0" eb="2">
+      <t>ヤマガタ</t>
+    </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>ログアウト機能</t>
+    <rPh sb="5" eb="7">
+      <t>キノウ</t>
+    </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9">
+  <fonts count="13">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -614,6 +635,36 @@
       <charset val="128"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="26"/>
+      <color theme="1"/>
+      <name val="MS PGothic"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="28"/>
+      <color theme="1"/>
+      <name val="MS PGothic"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <sz val="20"/>
+      <color theme="1"/>
+      <name val="MS PGothic"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="MS PGothic"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -629,7 +680,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="67">
+  <borders count="73">
     <border>
       <left/>
       <right/>
@@ -1170,21 +1221,6 @@
       </right>
       <top/>
       <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="medium">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="medium">
         <color rgb="FF000000"/>
       </bottom>
       <diagonal/>
@@ -1397,6 +1433,95 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="double">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -1406,7 +1531,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="168">
+  <cellXfs count="179">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1453,12 +1578,6 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -1486,18 +1605,21 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1510,16 +1632,13 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="56" fontId="6" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1531,21 +1650,159 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="57" xfId="3" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="58" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="59" xfId="3" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="58" xfId="3" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="55" xfId="3" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="60" xfId="3" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="62" xfId="3" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="61" xfId="3" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="65" xfId="3" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="64" xfId="3" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="56" xfId="3" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="66" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="66" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="66" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="3" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="56" fontId="3" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1576,95 +1833,41 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="20" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="21" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="26" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="27" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="22" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="30" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="31" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="32" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="56" fontId="3" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="34" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="35" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="20" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="21" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="22" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="26" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="27" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1738,176 +1941,131 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="27" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="27" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="20" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="30" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="31" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="32" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="34" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="35" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="56" fontId="3" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="55" xfId="3" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="56" fontId="3" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="27" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="56" xfId="3" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="60" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="61" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="63" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="64" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="55" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="62" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="56" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="63" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="65" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="64" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="57" xfId="3" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="58" xfId="3" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="59" xfId="3" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="60" xfId="3" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="59" xfId="3" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="58" xfId="3" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="60" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="59" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="56" xfId="3" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="3">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="61" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="62" xfId="3" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="63" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="61" xfId="3" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="64" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="65" xfId="3" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="66" xfId="3" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="56" fontId="1" fillId="0" borderId="55" xfId="3" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="56" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="63" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="57" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="64" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="66" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="65" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="63" xfId="3" applyBorder="1">
+    <xf numFmtId="56" fontId="6" fillId="0" borderId="68" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="68" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="69" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="70" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="67" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="62" xfId="3" applyBorder="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="71" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="66" xfId="3" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="65" xfId="3" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="57" xfId="3" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="56" fontId="1" fillId="0" borderId="56" xfId="3" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="72" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="70" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="70" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="70" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -2484,36 +2642,6 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="ユースケース記述"/>
-      <sheetName val="画面設計書"/>
-      <sheetName val="画面遷移図"/>
-      <sheetName val="詳細クラス図"/>
-      <sheetName val="テスト仕様書兼結果報告書"/>
-      <sheetName val="JUnitテスト仕様書兼報告書"/>
-      <sheetName val="カバレッジレポート"/>
-      <sheetName val="エビデンス"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1"/>
-      <sheetData sheetId="1" refreshError="1"/>
-      <sheetData sheetId="2" refreshError="1"/>
-      <sheetData sheetId="3" refreshError="1"/>
-      <sheetData sheetId="4" refreshError="1"/>
-      <sheetData sheetId="5" refreshError="1"/>
-      <sheetData sheetId="6" refreshError="1"/>
-      <sheetData sheetId="7" refreshError="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office テーマ">
   <a:themeElements>
@@ -2810,6 +2938,1177 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3484637A-4303-4D67-A1A6-4E759A3C610D}">
+  <dimension ref="C1:P1000"/>
+  <sheetFormatPr defaultColWidth="12.625" defaultRowHeight="15" customHeight="1"/>
+  <cols>
+    <col min="1" max="16" width="6.75" style="13" customWidth="1"/>
+    <col min="17" max="26" width="7.625" style="13" customWidth="1"/>
+    <col min="27" max="16384" width="12.625" style="13"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="3:16" ht="30" customHeight="1" thickBot="1"/>
+    <row r="2" spans="3:16" ht="30" customHeight="1" thickTop="1">
+      <c r="C2" s="59" t="s">
+        <v>96</v>
+      </c>
+      <c r="D2" s="60"/>
+      <c r="E2" s="60"/>
+      <c r="F2" s="60"/>
+      <c r="G2" s="60"/>
+      <c r="H2" s="60"/>
+      <c r="I2" s="60"/>
+      <c r="J2" s="60"/>
+      <c r="K2" s="60"/>
+      <c r="L2" s="60"/>
+      <c r="M2" s="60"/>
+      <c r="N2" s="60"/>
+      <c r="O2" s="60"/>
+      <c r="P2" s="52"/>
+    </row>
+    <row r="3" spans="3:16" ht="30" customHeight="1">
+      <c r="C3" s="58"/>
+      <c r="D3" s="58"/>
+      <c r="E3" s="58"/>
+      <c r="F3" s="58"/>
+      <c r="G3" s="58"/>
+      <c r="H3" s="58"/>
+      <c r="I3" s="58"/>
+      <c r="J3" s="58"/>
+      <c r="K3" s="58"/>
+      <c r="L3" s="58"/>
+      <c r="M3" s="58"/>
+      <c r="N3" s="58"/>
+      <c r="O3" s="58"/>
+      <c r="P3" s="52"/>
+    </row>
+    <row r="4" spans="3:16" ht="30" customHeight="1">
+      <c r="C4" s="58"/>
+      <c r="D4" s="58"/>
+      <c r="E4" s="58"/>
+      <c r="F4" s="58"/>
+      <c r="G4" s="58"/>
+      <c r="H4" s="58"/>
+      <c r="I4" s="58"/>
+      <c r="J4" s="58"/>
+      <c r="K4" s="58"/>
+      <c r="L4" s="58"/>
+      <c r="M4" s="58"/>
+      <c r="N4" s="58"/>
+      <c r="O4" s="58"/>
+      <c r="P4" s="52"/>
+    </row>
+    <row r="5" spans="3:16" ht="30" customHeight="1">
+      <c r="C5" s="58"/>
+      <c r="D5" s="58"/>
+      <c r="E5" s="58"/>
+      <c r="F5" s="58"/>
+      <c r="G5" s="58"/>
+      <c r="H5" s="58"/>
+      <c r="I5" s="58"/>
+      <c r="J5" s="58"/>
+      <c r="K5" s="58"/>
+      <c r="L5" s="58"/>
+      <c r="M5" s="58"/>
+      <c r="N5" s="58"/>
+      <c r="O5" s="58"/>
+      <c r="P5" s="52"/>
+    </row>
+    <row r="6" spans="3:16" ht="30" customHeight="1" thickBot="1">
+      <c r="C6" s="58"/>
+      <c r="D6" s="58"/>
+      <c r="E6" s="58"/>
+      <c r="F6" s="58"/>
+      <c r="G6" s="58"/>
+      <c r="H6" s="58"/>
+      <c r="I6" s="58"/>
+      <c r="J6" s="58"/>
+      <c r="K6" s="58"/>
+      <c r="L6" s="58"/>
+      <c r="M6" s="58"/>
+      <c r="N6" s="58"/>
+      <c r="O6" s="58"/>
+      <c r="P6" s="52"/>
+    </row>
+    <row r="7" spans="3:16" ht="30" customHeight="1" thickTop="1">
+      <c r="C7" s="53"/>
+      <c r="D7" s="53"/>
+      <c r="E7" s="53"/>
+      <c r="F7" s="53"/>
+      <c r="G7" s="53"/>
+      <c r="H7" s="53"/>
+      <c r="I7" s="53"/>
+      <c r="J7" s="53"/>
+      <c r="K7" s="53"/>
+      <c r="L7" s="53"/>
+      <c r="M7" s="53"/>
+      <c r="N7" s="53"/>
+      <c r="O7" s="53"/>
+      <c r="P7" s="52"/>
+    </row>
+    <row r="8" spans="3:16" ht="30" customHeight="1">
+      <c r="E8" s="61" t="s">
+        <v>100</v>
+      </c>
+      <c r="F8" s="58"/>
+      <c r="G8" s="58"/>
+      <c r="H8" s="58"/>
+      <c r="I8" s="58"/>
+      <c r="J8" s="58"/>
+      <c r="K8" s="58"/>
+      <c r="L8" s="58"/>
+      <c r="M8" s="58"/>
+    </row>
+    <row r="9" spans="3:16" ht="30" customHeight="1"/>
+    <row r="10" spans="3:16" ht="30" customHeight="1"/>
+    <row r="11" spans="3:16" ht="30" customHeight="1"/>
+    <row r="12" spans="3:16" ht="30" customHeight="1"/>
+    <row r="13" spans="3:16" ht="15.75" customHeight="1">
+      <c r="G13" s="54" t="s">
+        <v>97</v>
+      </c>
+      <c r="H13" s="55"/>
+      <c r="I13" s="54" t="s">
+        <v>98</v>
+      </c>
+      <c r="J13" s="56"/>
+      <c r="K13" s="55"/>
+    </row>
+    <row r="14" spans="3:16" ht="15.75" customHeight="1">
+      <c r="G14" s="54" t="s">
+        <v>99</v>
+      </c>
+      <c r="H14" s="55"/>
+      <c r="I14" s="62">
+        <v>45828</v>
+      </c>
+      <c r="J14" s="56"/>
+      <c r="K14" s="55"/>
+    </row>
+    <row r="15" spans="3:16" ht="15.75" customHeight="1">
+      <c r="G15" s="54"/>
+      <c r="H15" s="55"/>
+      <c r="I15" s="54"/>
+      <c r="J15" s="56"/>
+      <c r="K15" s="55"/>
+    </row>
+    <row r="16" spans="3:16" ht="15.75" customHeight="1">
+      <c r="G16" s="14"/>
+      <c r="H16" s="14"/>
+      <c r="I16" s="14"/>
+      <c r="J16" s="14"/>
+    </row>
+    <row r="17" spans="7:11" ht="30" customHeight="1">
+      <c r="G17" s="57" t="s">
+        <v>7</v>
+      </c>
+      <c r="H17" s="58"/>
+      <c r="I17" s="58"/>
+      <c r="J17" s="58"/>
+      <c r="K17" s="58"/>
+    </row>
+    <row r="18" spans="7:11" ht="14.25" customHeight="1"/>
+    <row r="19" spans="7:11" ht="24.75" customHeight="1"/>
+    <row r="20" spans="7:11" ht="24.75" customHeight="1"/>
+    <row r="21" spans="7:11" ht="24.75" customHeight="1"/>
+    <row r="22" spans="7:11" ht="12.75" customHeight="1"/>
+    <row r="23" spans="7:11" ht="12.75" customHeight="1"/>
+    <row r="24" spans="7:11" ht="12.75" customHeight="1"/>
+    <row r="25" spans="7:11" ht="12.75" customHeight="1"/>
+    <row r="26" spans="7:11" ht="12.75" customHeight="1"/>
+    <row r="27" spans="7:11" ht="12.75" customHeight="1"/>
+    <row r="28" spans="7:11" ht="12.75" customHeight="1"/>
+    <row r="29" spans="7:11" ht="12.75" customHeight="1"/>
+    <row r="30" spans="7:11" ht="12.75" customHeight="1"/>
+    <row r="31" spans="7:11" ht="12.75" customHeight="1"/>
+    <row r="32" spans="7:11" ht="12.75" customHeight="1"/>
+    <row r="33" ht="12.75" customHeight="1"/>
+    <row r="34" ht="12.75" customHeight="1"/>
+    <row r="35" ht="12.75" customHeight="1"/>
+    <row r="36" ht="12.75" customHeight="1"/>
+    <row r="37" ht="12.75" customHeight="1"/>
+    <row r="38" ht="12.75" customHeight="1"/>
+    <row r="39" ht="12.75" customHeight="1"/>
+    <row r="40" ht="12.75" customHeight="1"/>
+    <row r="41" ht="12.75" customHeight="1"/>
+    <row r="42" ht="12.75" customHeight="1"/>
+    <row r="43" ht="12.75" customHeight="1"/>
+    <row r="44" ht="12.75" customHeight="1"/>
+    <row r="45" ht="12.75" customHeight="1"/>
+    <row r="46" ht="12.75" customHeight="1"/>
+    <row r="47" ht="12.75" customHeight="1"/>
+    <row r="48" ht="12.75" customHeight="1"/>
+    <row r="49" ht="12.75" customHeight="1"/>
+    <row r="50" ht="12.75" customHeight="1"/>
+    <row r="51" ht="12.75" customHeight="1"/>
+    <row r="52" ht="12.75" customHeight="1"/>
+    <row r="53" ht="12.75" customHeight="1"/>
+    <row r="54" ht="12.75" customHeight="1"/>
+    <row r="55" ht="12.75" customHeight="1"/>
+    <row r="56" ht="12.75" customHeight="1"/>
+    <row r="57" ht="12.75" customHeight="1"/>
+    <row r="58" ht="12.75" customHeight="1"/>
+    <row r="59" ht="12.75" customHeight="1"/>
+    <row r="60" ht="12.75" customHeight="1"/>
+    <row r="61" ht="12.75" customHeight="1"/>
+    <row r="62" ht="12.75" customHeight="1"/>
+    <row r="63" ht="12.75" customHeight="1"/>
+    <row r="64" ht="12.75" customHeight="1"/>
+    <row r="65" ht="12.75" customHeight="1"/>
+    <row r="66" ht="12.75" customHeight="1"/>
+    <row r="67" ht="12.75" customHeight="1"/>
+    <row r="68" ht="12.75" customHeight="1"/>
+    <row r="69" ht="12.75" customHeight="1"/>
+    <row r="70" ht="12.75" customHeight="1"/>
+    <row r="71" ht="12.75" customHeight="1"/>
+    <row r="72" ht="12.75" customHeight="1"/>
+    <row r="73" ht="12.75" customHeight="1"/>
+    <row r="74" ht="12.75" customHeight="1"/>
+    <row r="75" ht="12.75" customHeight="1"/>
+    <row r="76" ht="12.75" customHeight="1"/>
+    <row r="77" ht="12.75" customHeight="1"/>
+    <row r="78" ht="12.75" customHeight="1"/>
+    <row r="79" ht="12.75" customHeight="1"/>
+    <row r="80" ht="12.75" customHeight="1"/>
+    <row r="81" ht="12.75" customHeight="1"/>
+    <row r="82" ht="12.75" customHeight="1"/>
+    <row r="83" ht="12.75" customHeight="1"/>
+    <row r="84" ht="12.75" customHeight="1"/>
+    <row r="85" ht="12.75" customHeight="1"/>
+    <row r="86" ht="12.75" customHeight="1"/>
+    <row r="87" ht="12.75" customHeight="1"/>
+    <row r="88" ht="12.75" customHeight="1"/>
+    <row r="89" ht="12.75" customHeight="1"/>
+    <row r="90" ht="12.75" customHeight="1"/>
+    <row r="91" ht="12.75" customHeight="1"/>
+    <row r="92" ht="12.75" customHeight="1"/>
+    <row r="93" ht="12.75" customHeight="1"/>
+    <row r="94" ht="12.75" customHeight="1"/>
+    <row r="95" ht="12.75" customHeight="1"/>
+    <row r="96" ht="12.75" customHeight="1"/>
+    <row r="97" ht="12.75" customHeight="1"/>
+    <row r="98" ht="12.75" customHeight="1"/>
+    <row r="99" ht="12.75" customHeight="1"/>
+    <row r="100" ht="12.75" customHeight="1"/>
+    <row r="101" ht="12.75" customHeight="1"/>
+    <row r="102" ht="12.75" customHeight="1"/>
+    <row r="103" ht="12.75" customHeight="1"/>
+    <row r="104" ht="12.75" customHeight="1"/>
+    <row r="105" ht="12.75" customHeight="1"/>
+    <row r="106" ht="12.75" customHeight="1"/>
+    <row r="107" ht="12.75" customHeight="1"/>
+    <row r="108" ht="12.75" customHeight="1"/>
+    <row r="109" ht="12.75" customHeight="1"/>
+    <row r="110" ht="12.75" customHeight="1"/>
+    <row r="111" ht="12.75" customHeight="1"/>
+    <row r="112" ht="12.75" customHeight="1"/>
+    <row r="113" ht="12.75" customHeight="1"/>
+    <row r="114" ht="12.75" customHeight="1"/>
+    <row r="115" ht="12.75" customHeight="1"/>
+    <row r="116" ht="12.75" customHeight="1"/>
+    <row r="117" ht="12.75" customHeight="1"/>
+    <row r="118" ht="12.75" customHeight="1"/>
+    <row r="119" ht="12.75" customHeight="1"/>
+    <row r="120" ht="12.75" customHeight="1"/>
+    <row r="121" ht="12.75" customHeight="1"/>
+    <row r="122" ht="12.75" customHeight="1"/>
+    <row r="123" ht="12.75" customHeight="1"/>
+    <row r="124" ht="12.75" customHeight="1"/>
+    <row r="125" ht="12.75" customHeight="1"/>
+    <row r="126" ht="12.75" customHeight="1"/>
+    <row r="127" ht="12.75" customHeight="1"/>
+    <row r="128" ht="12.75" customHeight="1"/>
+    <row r="129" ht="12.75" customHeight="1"/>
+    <row r="130" ht="12.75" customHeight="1"/>
+    <row r="131" ht="12.75" customHeight="1"/>
+    <row r="132" ht="12.75" customHeight="1"/>
+    <row r="133" ht="12.75" customHeight="1"/>
+    <row r="134" ht="12.75" customHeight="1"/>
+    <row r="135" ht="12.75" customHeight="1"/>
+    <row r="136" ht="12.75" customHeight="1"/>
+    <row r="137" ht="12.75" customHeight="1"/>
+    <row r="138" ht="12.75" customHeight="1"/>
+    <row r="139" ht="12.75" customHeight="1"/>
+    <row r="140" ht="12.75" customHeight="1"/>
+    <row r="141" ht="12.75" customHeight="1"/>
+    <row r="142" ht="12.75" customHeight="1"/>
+    <row r="143" ht="12.75" customHeight="1"/>
+    <row r="144" ht="12.75" customHeight="1"/>
+    <row r="145" ht="12.75" customHeight="1"/>
+    <row r="146" ht="12.75" customHeight="1"/>
+    <row r="147" ht="12.75" customHeight="1"/>
+    <row r="148" ht="12.75" customHeight="1"/>
+    <row r="149" ht="12.75" customHeight="1"/>
+    <row r="150" ht="12.75" customHeight="1"/>
+    <row r="151" ht="12.75" customHeight="1"/>
+    <row r="152" ht="12.75" customHeight="1"/>
+    <row r="153" ht="12.75" customHeight="1"/>
+    <row r="154" ht="12.75" customHeight="1"/>
+    <row r="155" ht="12.75" customHeight="1"/>
+    <row r="156" ht="12.75" customHeight="1"/>
+    <row r="157" ht="12.75" customHeight="1"/>
+    <row r="158" ht="12.75" customHeight="1"/>
+    <row r="159" ht="12.75" customHeight="1"/>
+    <row r="160" ht="12.75" customHeight="1"/>
+    <row r="161" ht="12.75" customHeight="1"/>
+    <row r="162" ht="12.75" customHeight="1"/>
+    <row r="163" ht="12.75" customHeight="1"/>
+    <row r="164" ht="12.75" customHeight="1"/>
+    <row r="165" ht="12.75" customHeight="1"/>
+    <row r="166" ht="12.75" customHeight="1"/>
+    <row r="167" ht="12.75" customHeight="1"/>
+    <row r="168" ht="12.75" customHeight="1"/>
+    <row r="169" ht="12.75" customHeight="1"/>
+    <row r="170" ht="12.75" customHeight="1"/>
+    <row r="171" ht="12.75" customHeight="1"/>
+    <row r="172" ht="12.75" customHeight="1"/>
+    <row r="173" ht="12.75" customHeight="1"/>
+    <row r="174" ht="12.75" customHeight="1"/>
+    <row r="175" ht="12.75" customHeight="1"/>
+    <row r="176" ht="12.75" customHeight="1"/>
+    <row r="177" ht="12.75" customHeight="1"/>
+    <row r="178" ht="12.75" customHeight="1"/>
+    <row r="179" ht="12.75" customHeight="1"/>
+    <row r="180" ht="12.75" customHeight="1"/>
+    <row r="181" ht="12.75" customHeight="1"/>
+    <row r="182" ht="12.75" customHeight="1"/>
+    <row r="183" ht="12.75" customHeight="1"/>
+    <row r="184" ht="12.75" customHeight="1"/>
+    <row r="185" ht="12.75" customHeight="1"/>
+    <row r="186" ht="12.75" customHeight="1"/>
+    <row r="187" ht="12.75" customHeight="1"/>
+    <row r="188" ht="12.75" customHeight="1"/>
+    <row r="189" ht="12.75" customHeight="1"/>
+    <row r="190" ht="12.75" customHeight="1"/>
+    <row r="191" ht="12.75" customHeight="1"/>
+    <row r="192" ht="12.75" customHeight="1"/>
+    <row r="193" ht="12.75" customHeight="1"/>
+    <row r="194" ht="12.75" customHeight="1"/>
+    <row r="195" ht="12.75" customHeight="1"/>
+    <row r="196" ht="12.75" customHeight="1"/>
+    <row r="197" ht="12.75" customHeight="1"/>
+    <row r="198" ht="12.75" customHeight="1"/>
+    <row r="199" ht="12.75" customHeight="1"/>
+    <row r="200" ht="12.75" customHeight="1"/>
+    <row r="201" ht="12.75" customHeight="1"/>
+    <row r="202" ht="12.75" customHeight="1"/>
+    <row r="203" ht="12.75" customHeight="1"/>
+    <row r="204" ht="12.75" customHeight="1"/>
+    <row r="205" ht="12.75" customHeight="1"/>
+    <row r="206" ht="12.75" customHeight="1"/>
+    <row r="207" ht="12.75" customHeight="1"/>
+    <row r="208" ht="12.75" customHeight="1"/>
+    <row r="209" ht="12.75" customHeight="1"/>
+    <row r="210" ht="12.75" customHeight="1"/>
+    <row r="211" ht="12.75" customHeight="1"/>
+    <row r="212" ht="12.75" customHeight="1"/>
+    <row r="213" ht="12.75" customHeight="1"/>
+    <row r="214" ht="12.75" customHeight="1"/>
+    <row r="215" ht="12.75" customHeight="1"/>
+    <row r="216" ht="12.75" customHeight="1"/>
+    <row r="217" ht="12.75" customHeight="1"/>
+    <row r="218" ht="12.75" customHeight="1"/>
+    <row r="219" ht="12.75" customHeight="1"/>
+    <row r="220" ht="12.75" customHeight="1"/>
+    <row r="221" ht="12.75" customHeight="1"/>
+    <row r="222" ht="12.75" customHeight="1"/>
+    <row r="223" ht="12.75" customHeight="1"/>
+    <row r="224" ht="12.75" customHeight="1"/>
+    <row r="225" ht="12.75" customHeight="1"/>
+    <row r="226" ht="12.75" customHeight="1"/>
+    <row r="227" ht="12.75" customHeight="1"/>
+    <row r="228" ht="12.75" customHeight="1"/>
+    <row r="229" ht="12.75" customHeight="1"/>
+    <row r="230" ht="12.75" customHeight="1"/>
+    <row r="231" ht="12.75" customHeight="1"/>
+    <row r="232" ht="12.75" customHeight="1"/>
+    <row r="233" ht="12.75" customHeight="1"/>
+    <row r="234" ht="12.75" customHeight="1"/>
+    <row r="235" ht="12.75" customHeight="1"/>
+    <row r="236" ht="12.75" customHeight="1"/>
+    <row r="237" ht="12.75" customHeight="1"/>
+    <row r="238" ht="12.75" customHeight="1"/>
+    <row r="239" ht="12.75" customHeight="1"/>
+    <row r="240" ht="12.75" customHeight="1"/>
+    <row r="241" ht="12.75" customHeight="1"/>
+    <row r="242" ht="12.75" customHeight="1"/>
+    <row r="243" ht="12.75" customHeight="1"/>
+    <row r="244" ht="12.75" customHeight="1"/>
+    <row r="245" ht="12.75" customHeight="1"/>
+    <row r="246" ht="12.75" customHeight="1"/>
+    <row r="247" ht="12.75" customHeight="1"/>
+    <row r="248" ht="12.75" customHeight="1"/>
+    <row r="249" ht="12.75" customHeight="1"/>
+    <row r="250" ht="12.75" customHeight="1"/>
+    <row r="251" ht="12.75" customHeight="1"/>
+    <row r="252" ht="12.75" customHeight="1"/>
+    <row r="253" ht="12.75" customHeight="1"/>
+    <row r="254" ht="12.75" customHeight="1"/>
+    <row r="255" ht="12.75" customHeight="1"/>
+    <row r="256" ht="12.75" customHeight="1"/>
+    <row r="257" ht="12.75" customHeight="1"/>
+    <row r="258" ht="12.75" customHeight="1"/>
+    <row r="259" ht="12.75" customHeight="1"/>
+    <row r="260" ht="12.75" customHeight="1"/>
+    <row r="261" ht="12.75" customHeight="1"/>
+    <row r="262" ht="12.75" customHeight="1"/>
+    <row r="263" ht="12.75" customHeight="1"/>
+    <row r="264" ht="12.75" customHeight="1"/>
+    <row r="265" ht="12.75" customHeight="1"/>
+    <row r="266" ht="12.75" customHeight="1"/>
+    <row r="267" ht="12.75" customHeight="1"/>
+    <row r="268" ht="12.75" customHeight="1"/>
+    <row r="269" ht="12.75" customHeight="1"/>
+    <row r="270" ht="12.75" customHeight="1"/>
+    <row r="271" ht="12.75" customHeight="1"/>
+    <row r="272" ht="12.75" customHeight="1"/>
+    <row r="273" ht="12.75" customHeight="1"/>
+    <row r="274" ht="12.75" customHeight="1"/>
+    <row r="275" ht="12.75" customHeight="1"/>
+    <row r="276" ht="12.75" customHeight="1"/>
+    <row r="277" ht="12.75" customHeight="1"/>
+    <row r="278" ht="12.75" customHeight="1"/>
+    <row r="279" ht="12.75" customHeight="1"/>
+    <row r="280" ht="12.75" customHeight="1"/>
+    <row r="281" ht="12.75" customHeight="1"/>
+    <row r="282" ht="12.75" customHeight="1"/>
+    <row r="283" ht="12.75" customHeight="1"/>
+    <row r="284" ht="12.75" customHeight="1"/>
+    <row r="285" ht="12.75" customHeight="1"/>
+    <row r="286" ht="12.75" customHeight="1"/>
+    <row r="287" ht="12.75" customHeight="1"/>
+    <row r="288" ht="12.75" customHeight="1"/>
+    <row r="289" ht="12.75" customHeight="1"/>
+    <row r="290" ht="12.75" customHeight="1"/>
+    <row r="291" ht="12.75" customHeight="1"/>
+    <row r="292" ht="12.75" customHeight="1"/>
+    <row r="293" ht="12.75" customHeight="1"/>
+    <row r="294" ht="12.75" customHeight="1"/>
+    <row r="295" ht="12.75" customHeight="1"/>
+    <row r="296" ht="12.75" customHeight="1"/>
+    <row r="297" ht="12.75" customHeight="1"/>
+    <row r="298" ht="12.75" customHeight="1"/>
+    <row r="299" ht="12.75" customHeight="1"/>
+    <row r="300" ht="12.75" customHeight="1"/>
+    <row r="301" ht="12.75" customHeight="1"/>
+    <row r="302" ht="12.75" customHeight="1"/>
+    <row r="303" ht="12.75" customHeight="1"/>
+    <row r="304" ht="12.75" customHeight="1"/>
+    <row r="305" ht="12.75" customHeight="1"/>
+    <row r="306" ht="12.75" customHeight="1"/>
+    <row r="307" ht="12.75" customHeight="1"/>
+    <row r="308" ht="12.75" customHeight="1"/>
+    <row r="309" ht="12.75" customHeight="1"/>
+    <row r="310" ht="12.75" customHeight="1"/>
+    <row r="311" ht="12.75" customHeight="1"/>
+    <row r="312" ht="12.75" customHeight="1"/>
+    <row r="313" ht="12.75" customHeight="1"/>
+    <row r="314" ht="12.75" customHeight="1"/>
+    <row r="315" ht="12.75" customHeight="1"/>
+    <row r="316" ht="12.75" customHeight="1"/>
+    <row r="317" ht="12.75" customHeight="1"/>
+    <row r="318" ht="12.75" customHeight="1"/>
+    <row r="319" ht="12.75" customHeight="1"/>
+    <row r="320" ht="12.75" customHeight="1"/>
+    <row r="321" ht="12.75" customHeight="1"/>
+    <row r="322" ht="12.75" customHeight="1"/>
+    <row r="323" ht="12.75" customHeight="1"/>
+    <row r="324" ht="12.75" customHeight="1"/>
+    <row r="325" ht="12.75" customHeight="1"/>
+    <row r="326" ht="12.75" customHeight="1"/>
+    <row r="327" ht="12.75" customHeight="1"/>
+    <row r="328" ht="12.75" customHeight="1"/>
+    <row r="329" ht="12.75" customHeight="1"/>
+    <row r="330" ht="12.75" customHeight="1"/>
+    <row r="331" ht="12.75" customHeight="1"/>
+    <row r="332" ht="12.75" customHeight="1"/>
+    <row r="333" ht="12.75" customHeight="1"/>
+    <row r="334" ht="12.75" customHeight="1"/>
+    <row r="335" ht="12.75" customHeight="1"/>
+    <row r="336" ht="12.75" customHeight="1"/>
+    <row r="337" ht="12.75" customHeight="1"/>
+    <row r="338" ht="12.75" customHeight="1"/>
+    <row r="339" ht="12.75" customHeight="1"/>
+    <row r="340" ht="12.75" customHeight="1"/>
+    <row r="341" ht="12.75" customHeight="1"/>
+    <row r="342" ht="12.75" customHeight="1"/>
+    <row r="343" ht="12.75" customHeight="1"/>
+    <row r="344" ht="12.75" customHeight="1"/>
+    <row r="345" ht="12.75" customHeight="1"/>
+    <row r="346" ht="12.75" customHeight="1"/>
+    <row r="347" ht="12.75" customHeight="1"/>
+    <row r="348" ht="12.75" customHeight="1"/>
+    <row r="349" ht="12.75" customHeight="1"/>
+    <row r="350" ht="12.75" customHeight="1"/>
+    <row r="351" ht="12.75" customHeight="1"/>
+    <row r="352" ht="12.75" customHeight="1"/>
+    <row r="353" ht="12.75" customHeight="1"/>
+    <row r="354" ht="12.75" customHeight="1"/>
+    <row r="355" ht="12.75" customHeight="1"/>
+    <row r="356" ht="12.75" customHeight="1"/>
+    <row r="357" ht="12.75" customHeight="1"/>
+    <row r="358" ht="12.75" customHeight="1"/>
+    <row r="359" ht="12.75" customHeight="1"/>
+    <row r="360" ht="12.75" customHeight="1"/>
+    <row r="361" ht="12.75" customHeight="1"/>
+    <row r="362" ht="12.75" customHeight="1"/>
+    <row r="363" ht="12.75" customHeight="1"/>
+    <row r="364" ht="12.75" customHeight="1"/>
+    <row r="365" ht="12.75" customHeight="1"/>
+    <row r="366" ht="12.75" customHeight="1"/>
+    <row r="367" ht="12.75" customHeight="1"/>
+    <row r="368" ht="12.75" customHeight="1"/>
+    <row r="369" ht="12.75" customHeight="1"/>
+    <row r="370" ht="12.75" customHeight="1"/>
+    <row r="371" ht="12.75" customHeight="1"/>
+    <row r="372" ht="12.75" customHeight="1"/>
+    <row r="373" ht="12.75" customHeight="1"/>
+    <row r="374" ht="12.75" customHeight="1"/>
+    <row r="375" ht="12.75" customHeight="1"/>
+    <row r="376" ht="12.75" customHeight="1"/>
+    <row r="377" ht="12.75" customHeight="1"/>
+    <row r="378" ht="12.75" customHeight="1"/>
+    <row r="379" ht="12.75" customHeight="1"/>
+    <row r="380" ht="12.75" customHeight="1"/>
+    <row r="381" ht="12.75" customHeight="1"/>
+    <row r="382" ht="12.75" customHeight="1"/>
+    <row r="383" ht="12.75" customHeight="1"/>
+    <row r="384" ht="12.75" customHeight="1"/>
+    <row r="385" ht="12.75" customHeight="1"/>
+    <row r="386" ht="12.75" customHeight="1"/>
+    <row r="387" ht="12.75" customHeight="1"/>
+    <row r="388" ht="12.75" customHeight="1"/>
+    <row r="389" ht="12.75" customHeight="1"/>
+    <row r="390" ht="12.75" customHeight="1"/>
+    <row r="391" ht="12.75" customHeight="1"/>
+    <row r="392" ht="12.75" customHeight="1"/>
+    <row r="393" ht="12.75" customHeight="1"/>
+    <row r="394" ht="12.75" customHeight="1"/>
+    <row r="395" ht="12.75" customHeight="1"/>
+    <row r="396" ht="12.75" customHeight="1"/>
+    <row r="397" ht="12.75" customHeight="1"/>
+    <row r="398" ht="12.75" customHeight="1"/>
+    <row r="399" ht="12.75" customHeight="1"/>
+    <row r="400" ht="12.75" customHeight="1"/>
+    <row r="401" ht="12.75" customHeight="1"/>
+    <row r="402" ht="12.75" customHeight="1"/>
+    <row r="403" ht="12.75" customHeight="1"/>
+    <row r="404" ht="12.75" customHeight="1"/>
+    <row r="405" ht="12.75" customHeight="1"/>
+    <row r="406" ht="12.75" customHeight="1"/>
+    <row r="407" ht="12.75" customHeight="1"/>
+    <row r="408" ht="12.75" customHeight="1"/>
+    <row r="409" ht="12.75" customHeight="1"/>
+    <row r="410" ht="12.75" customHeight="1"/>
+    <row r="411" ht="12.75" customHeight="1"/>
+    <row r="412" ht="12.75" customHeight="1"/>
+    <row r="413" ht="12.75" customHeight="1"/>
+    <row r="414" ht="12.75" customHeight="1"/>
+    <row r="415" ht="12.75" customHeight="1"/>
+    <row r="416" ht="12.75" customHeight="1"/>
+    <row r="417" ht="12.75" customHeight="1"/>
+    <row r="418" ht="12.75" customHeight="1"/>
+    <row r="419" ht="12.75" customHeight="1"/>
+    <row r="420" ht="12.75" customHeight="1"/>
+    <row r="421" ht="12.75" customHeight="1"/>
+    <row r="422" ht="12.75" customHeight="1"/>
+    <row r="423" ht="12.75" customHeight="1"/>
+    <row r="424" ht="12.75" customHeight="1"/>
+    <row r="425" ht="12.75" customHeight="1"/>
+    <row r="426" ht="12.75" customHeight="1"/>
+    <row r="427" ht="12.75" customHeight="1"/>
+    <row r="428" ht="12.75" customHeight="1"/>
+    <row r="429" ht="12.75" customHeight="1"/>
+    <row r="430" ht="12.75" customHeight="1"/>
+    <row r="431" ht="12.75" customHeight="1"/>
+    <row r="432" ht="12.75" customHeight="1"/>
+    <row r="433" ht="12.75" customHeight="1"/>
+    <row r="434" ht="12.75" customHeight="1"/>
+    <row r="435" ht="12.75" customHeight="1"/>
+    <row r="436" ht="12.75" customHeight="1"/>
+    <row r="437" ht="12.75" customHeight="1"/>
+    <row r="438" ht="12.75" customHeight="1"/>
+    <row r="439" ht="12.75" customHeight="1"/>
+    <row r="440" ht="12.75" customHeight="1"/>
+    <row r="441" ht="12.75" customHeight="1"/>
+    <row r="442" ht="12.75" customHeight="1"/>
+    <row r="443" ht="12.75" customHeight="1"/>
+    <row r="444" ht="12.75" customHeight="1"/>
+    <row r="445" ht="12.75" customHeight="1"/>
+    <row r="446" ht="12.75" customHeight="1"/>
+    <row r="447" ht="12.75" customHeight="1"/>
+    <row r="448" ht="12.75" customHeight="1"/>
+    <row r="449" ht="12.75" customHeight="1"/>
+    <row r="450" ht="12.75" customHeight="1"/>
+    <row r="451" ht="12.75" customHeight="1"/>
+    <row r="452" ht="12.75" customHeight="1"/>
+    <row r="453" ht="12.75" customHeight="1"/>
+    <row r="454" ht="12.75" customHeight="1"/>
+    <row r="455" ht="12.75" customHeight="1"/>
+    <row r="456" ht="12.75" customHeight="1"/>
+    <row r="457" ht="12.75" customHeight="1"/>
+    <row r="458" ht="12.75" customHeight="1"/>
+    <row r="459" ht="12.75" customHeight="1"/>
+    <row r="460" ht="12.75" customHeight="1"/>
+    <row r="461" ht="12.75" customHeight="1"/>
+    <row r="462" ht="12.75" customHeight="1"/>
+    <row r="463" ht="12.75" customHeight="1"/>
+    <row r="464" ht="12.75" customHeight="1"/>
+    <row r="465" ht="12.75" customHeight="1"/>
+    <row r="466" ht="12.75" customHeight="1"/>
+    <row r="467" ht="12.75" customHeight="1"/>
+    <row r="468" ht="12.75" customHeight="1"/>
+    <row r="469" ht="12.75" customHeight="1"/>
+    <row r="470" ht="12.75" customHeight="1"/>
+    <row r="471" ht="12.75" customHeight="1"/>
+    <row r="472" ht="12.75" customHeight="1"/>
+    <row r="473" ht="12.75" customHeight="1"/>
+    <row r="474" ht="12.75" customHeight="1"/>
+    <row r="475" ht="12.75" customHeight="1"/>
+    <row r="476" ht="12.75" customHeight="1"/>
+    <row r="477" ht="12.75" customHeight="1"/>
+    <row r="478" ht="12.75" customHeight="1"/>
+    <row r="479" ht="12.75" customHeight="1"/>
+    <row r="480" ht="12.75" customHeight="1"/>
+    <row r="481" ht="12.75" customHeight="1"/>
+    <row r="482" ht="12.75" customHeight="1"/>
+    <row r="483" ht="12.75" customHeight="1"/>
+    <row r="484" ht="12.75" customHeight="1"/>
+    <row r="485" ht="12.75" customHeight="1"/>
+    <row r="486" ht="12.75" customHeight="1"/>
+    <row r="487" ht="12.75" customHeight="1"/>
+    <row r="488" ht="12.75" customHeight="1"/>
+    <row r="489" ht="12.75" customHeight="1"/>
+    <row r="490" ht="12.75" customHeight="1"/>
+    <row r="491" ht="12.75" customHeight="1"/>
+    <row r="492" ht="12.75" customHeight="1"/>
+    <row r="493" ht="12.75" customHeight="1"/>
+    <row r="494" ht="12.75" customHeight="1"/>
+    <row r="495" ht="12.75" customHeight="1"/>
+    <row r="496" ht="12.75" customHeight="1"/>
+    <row r="497" ht="12.75" customHeight="1"/>
+    <row r="498" ht="12.75" customHeight="1"/>
+    <row r="499" ht="12.75" customHeight="1"/>
+    <row r="500" ht="12.75" customHeight="1"/>
+    <row r="501" ht="12.75" customHeight="1"/>
+    <row r="502" ht="12.75" customHeight="1"/>
+    <row r="503" ht="12.75" customHeight="1"/>
+    <row r="504" ht="12.75" customHeight="1"/>
+    <row r="505" ht="12.75" customHeight="1"/>
+    <row r="506" ht="12.75" customHeight="1"/>
+    <row r="507" ht="12.75" customHeight="1"/>
+    <row r="508" ht="12.75" customHeight="1"/>
+    <row r="509" ht="12.75" customHeight="1"/>
+    <row r="510" ht="12.75" customHeight="1"/>
+    <row r="511" ht="12.75" customHeight="1"/>
+    <row r="512" ht="12.75" customHeight="1"/>
+    <row r="513" ht="12.75" customHeight="1"/>
+    <row r="514" ht="12.75" customHeight="1"/>
+    <row r="515" ht="12.75" customHeight="1"/>
+    <row r="516" ht="12.75" customHeight="1"/>
+    <row r="517" ht="12.75" customHeight="1"/>
+    <row r="518" ht="12.75" customHeight="1"/>
+    <row r="519" ht="12.75" customHeight="1"/>
+    <row r="520" ht="12.75" customHeight="1"/>
+    <row r="521" ht="12.75" customHeight="1"/>
+    <row r="522" ht="12.75" customHeight="1"/>
+    <row r="523" ht="12.75" customHeight="1"/>
+    <row r="524" ht="12.75" customHeight="1"/>
+    <row r="525" ht="12.75" customHeight="1"/>
+    <row r="526" ht="12.75" customHeight="1"/>
+    <row r="527" ht="12.75" customHeight="1"/>
+    <row r="528" ht="12.75" customHeight="1"/>
+    <row r="529" ht="12.75" customHeight="1"/>
+    <row r="530" ht="12.75" customHeight="1"/>
+    <row r="531" ht="12.75" customHeight="1"/>
+    <row r="532" ht="12.75" customHeight="1"/>
+    <row r="533" ht="12.75" customHeight="1"/>
+    <row r="534" ht="12.75" customHeight="1"/>
+    <row r="535" ht="12.75" customHeight="1"/>
+    <row r="536" ht="12.75" customHeight="1"/>
+    <row r="537" ht="12.75" customHeight="1"/>
+    <row r="538" ht="12.75" customHeight="1"/>
+    <row r="539" ht="12.75" customHeight="1"/>
+    <row r="540" ht="12.75" customHeight="1"/>
+    <row r="541" ht="12.75" customHeight="1"/>
+    <row r="542" ht="12.75" customHeight="1"/>
+    <row r="543" ht="12.75" customHeight="1"/>
+    <row r="544" ht="12.75" customHeight="1"/>
+    <row r="545" ht="12.75" customHeight="1"/>
+    <row r="546" ht="12.75" customHeight="1"/>
+    <row r="547" ht="12.75" customHeight="1"/>
+    <row r="548" ht="12.75" customHeight="1"/>
+    <row r="549" ht="12.75" customHeight="1"/>
+    <row r="550" ht="12.75" customHeight="1"/>
+    <row r="551" ht="12.75" customHeight="1"/>
+    <row r="552" ht="12.75" customHeight="1"/>
+    <row r="553" ht="12.75" customHeight="1"/>
+    <row r="554" ht="12.75" customHeight="1"/>
+    <row r="555" ht="12.75" customHeight="1"/>
+    <row r="556" ht="12.75" customHeight="1"/>
+    <row r="557" ht="12.75" customHeight="1"/>
+    <row r="558" ht="12.75" customHeight="1"/>
+    <row r="559" ht="12.75" customHeight="1"/>
+    <row r="560" ht="12.75" customHeight="1"/>
+    <row r="561" ht="12.75" customHeight="1"/>
+    <row r="562" ht="12.75" customHeight="1"/>
+    <row r="563" ht="12.75" customHeight="1"/>
+    <row r="564" ht="12.75" customHeight="1"/>
+    <row r="565" ht="12.75" customHeight="1"/>
+    <row r="566" ht="12.75" customHeight="1"/>
+    <row r="567" ht="12.75" customHeight="1"/>
+    <row r="568" ht="12.75" customHeight="1"/>
+    <row r="569" ht="12.75" customHeight="1"/>
+    <row r="570" ht="12.75" customHeight="1"/>
+    <row r="571" ht="12.75" customHeight="1"/>
+    <row r="572" ht="12.75" customHeight="1"/>
+    <row r="573" ht="12.75" customHeight="1"/>
+    <row r="574" ht="12.75" customHeight="1"/>
+    <row r="575" ht="12.75" customHeight="1"/>
+    <row r="576" ht="12.75" customHeight="1"/>
+    <row r="577" ht="12.75" customHeight="1"/>
+    <row r="578" ht="12.75" customHeight="1"/>
+    <row r="579" ht="12.75" customHeight="1"/>
+    <row r="580" ht="12.75" customHeight="1"/>
+    <row r="581" ht="12.75" customHeight="1"/>
+    <row r="582" ht="12.75" customHeight="1"/>
+    <row r="583" ht="12.75" customHeight="1"/>
+    <row r="584" ht="12.75" customHeight="1"/>
+    <row r="585" ht="12.75" customHeight="1"/>
+    <row r="586" ht="12.75" customHeight="1"/>
+    <row r="587" ht="12.75" customHeight="1"/>
+    <row r="588" ht="12.75" customHeight="1"/>
+    <row r="589" ht="12.75" customHeight="1"/>
+    <row r="590" ht="12.75" customHeight="1"/>
+    <row r="591" ht="12.75" customHeight="1"/>
+    <row r="592" ht="12.75" customHeight="1"/>
+    <row r="593" ht="12.75" customHeight="1"/>
+    <row r="594" ht="12.75" customHeight="1"/>
+    <row r="595" ht="12.75" customHeight="1"/>
+    <row r="596" ht="12.75" customHeight="1"/>
+    <row r="597" ht="12.75" customHeight="1"/>
+    <row r="598" ht="12.75" customHeight="1"/>
+    <row r="599" ht="12.75" customHeight="1"/>
+    <row r="600" ht="12.75" customHeight="1"/>
+    <row r="601" ht="12.75" customHeight="1"/>
+    <row r="602" ht="12.75" customHeight="1"/>
+    <row r="603" ht="12.75" customHeight="1"/>
+    <row r="604" ht="12.75" customHeight="1"/>
+    <row r="605" ht="12.75" customHeight="1"/>
+    <row r="606" ht="12.75" customHeight="1"/>
+    <row r="607" ht="12.75" customHeight="1"/>
+    <row r="608" ht="12.75" customHeight="1"/>
+    <row r="609" ht="12.75" customHeight="1"/>
+    <row r="610" ht="12.75" customHeight="1"/>
+    <row r="611" ht="12.75" customHeight="1"/>
+    <row r="612" ht="12.75" customHeight="1"/>
+    <row r="613" ht="12.75" customHeight="1"/>
+    <row r="614" ht="12.75" customHeight="1"/>
+    <row r="615" ht="12.75" customHeight="1"/>
+    <row r="616" ht="12.75" customHeight="1"/>
+    <row r="617" ht="12.75" customHeight="1"/>
+    <row r="618" ht="12.75" customHeight="1"/>
+    <row r="619" ht="12.75" customHeight="1"/>
+    <row r="620" ht="12.75" customHeight="1"/>
+    <row r="621" ht="12.75" customHeight="1"/>
+    <row r="622" ht="12.75" customHeight="1"/>
+    <row r="623" ht="12.75" customHeight="1"/>
+    <row r="624" ht="12.75" customHeight="1"/>
+    <row r="625" ht="12.75" customHeight="1"/>
+    <row r="626" ht="12.75" customHeight="1"/>
+    <row r="627" ht="12.75" customHeight="1"/>
+    <row r="628" ht="12.75" customHeight="1"/>
+    <row r="629" ht="12.75" customHeight="1"/>
+    <row r="630" ht="12.75" customHeight="1"/>
+    <row r="631" ht="12.75" customHeight="1"/>
+    <row r="632" ht="12.75" customHeight="1"/>
+    <row r="633" ht="12.75" customHeight="1"/>
+    <row r="634" ht="12.75" customHeight="1"/>
+    <row r="635" ht="12.75" customHeight="1"/>
+    <row r="636" ht="12.75" customHeight="1"/>
+    <row r="637" ht="12.75" customHeight="1"/>
+    <row r="638" ht="12.75" customHeight="1"/>
+    <row r="639" ht="12.75" customHeight="1"/>
+    <row r="640" ht="12.75" customHeight="1"/>
+    <row r="641" ht="12.75" customHeight="1"/>
+    <row r="642" ht="12.75" customHeight="1"/>
+    <row r="643" ht="12.75" customHeight="1"/>
+    <row r="644" ht="12.75" customHeight="1"/>
+    <row r="645" ht="12.75" customHeight="1"/>
+    <row r="646" ht="12.75" customHeight="1"/>
+    <row r="647" ht="12.75" customHeight="1"/>
+    <row r="648" ht="12.75" customHeight="1"/>
+    <row r="649" ht="12.75" customHeight="1"/>
+    <row r="650" ht="12.75" customHeight="1"/>
+    <row r="651" ht="12.75" customHeight="1"/>
+    <row r="652" ht="12.75" customHeight="1"/>
+    <row r="653" ht="12.75" customHeight="1"/>
+    <row r="654" ht="12.75" customHeight="1"/>
+    <row r="655" ht="12.75" customHeight="1"/>
+    <row r="656" ht="12.75" customHeight="1"/>
+    <row r="657" ht="12.75" customHeight="1"/>
+    <row r="658" ht="12.75" customHeight="1"/>
+    <row r="659" ht="12.75" customHeight="1"/>
+    <row r="660" ht="12.75" customHeight="1"/>
+    <row r="661" ht="12.75" customHeight="1"/>
+    <row r="662" ht="12.75" customHeight="1"/>
+    <row r="663" ht="12.75" customHeight="1"/>
+    <row r="664" ht="12.75" customHeight="1"/>
+    <row r="665" ht="12.75" customHeight="1"/>
+    <row r="666" ht="12.75" customHeight="1"/>
+    <row r="667" ht="12.75" customHeight="1"/>
+    <row r="668" ht="12.75" customHeight="1"/>
+    <row r="669" ht="12.75" customHeight="1"/>
+    <row r="670" ht="12.75" customHeight="1"/>
+    <row r="671" ht="12.75" customHeight="1"/>
+    <row r="672" ht="12.75" customHeight="1"/>
+    <row r="673" ht="12.75" customHeight="1"/>
+    <row r="674" ht="12.75" customHeight="1"/>
+    <row r="675" ht="12.75" customHeight="1"/>
+    <row r="676" ht="12.75" customHeight="1"/>
+    <row r="677" ht="12.75" customHeight="1"/>
+    <row r="678" ht="12.75" customHeight="1"/>
+    <row r="679" ht="12.75" customHeight="1"/>
+    <row r="680" ht="12.75" customHeight="1"/>
+    <row r="681" ht="12.75" customHeight="1"/>
+    <row r="682" ht="12.75" customHeight="1"/>
+    <row r="683" ht="12.75" customHeight="1"/>
+    <row r="684" ht="12.75" customHeight="1"/>
+    <row r="685" ht="12.75" customHeight="1"/>
+    <row r="686" ht="12.75" customHeight="1"/>
+    <row r="687" ht="12.75" customHeight="1"/>
+    <row r="688" ht="12.75" customHeight="1"/>
+    <row r="689" ht="12.75" customHeight="1"/>
+    <row r="690" ht="12.75" customHeight="1"/>
+    <row r="691" ht="12.75" customHeight="1"/>
+    <row r="692" ht="12.75" customHeight="1"/>
+    <row r="693" ht="12.75" customHeight="1"/>
+    <row r="694" ht="12.75" customHeight="1"/>
+    <row r="695" ht="12.75" customHeight="1"/>
+    <row r="696" ht="12.75" customHeight="1"/>
+    <row r="697" ht="12.75" customHeight="1"/>
+    <row r="698" ht="12.75" customHeight="1"/>
+    <row r="699" ht="12.75" customHeight="1"/>
+    <row r="700" ht="12.75" customHeight="1"/>
+    <row r="701" ht="12.75" customHeight="1"/>
+    <row r="702" ht="12.75" customHeight="1"/>
+    <row r="703" ht="12.75" customHeight="1"/>
+    <row r="704" ht="12.75" customHeight="1"/>
+    <row r="705" ht="12.75" customHeight="1"/>
+    <row r="706" ht="12.75" customHeight="1"/>
+    <row r="707" ht="12.75" customHeight="1"/>
+    <row r="708" ht="12.75" customHeight="1"/>
+    <row r="709" ht="12.75" customHeight="1"/>
+    <row r="710" ht="12.75" customHeight="1"/>
+    <row r="711" ht="12.75" customHeight="1"/>
+    <row r="712" ht="12.75" customHeight="1"/>
+    <row r="713" ht="12.75" customHeight="1"/>
+    <row r="714" ht="12.75" customHeight="1"/>
+    <row r="715" ht="12.75" customHeight="1"/>
+    <row r="716" ht="12.75" customHeight="1"/>
+    <row r="717" ht="12.75" customHeight="1"/>
+    <row r="718" ht="12.75" customHeight="1"/>
+    <row r="719" ht="12.75" customHeight="1"/>
+    <row r="720" ht="12.75" customHeight="1"/>
+    <row r="721" ht="12.75" customHeight="1"/>
+    <row r="722" ht="12.75" customHeight="1"/>
+    <row r="723" ht="12.75" customHeight="1"/>
+    <row r="724" ht="12.75" customHeight="1"/>
+    <row r="725" ht="12.75" customHeight="1"/>
+    <row r="726" ht="12.75" customHeight="1"/>
+    <row r="727" ht="12.75" customHeight="1"/>
+    <row r="728" ht="12.75" customHeight="1"/>
+    <row r="729" ht="12.75" customHeight="1"/>
+    <row r="730" ht="12.75" customHeight="1"/>
+    <row r="731" ht="12.75" customHeight="1"/>
+    <row r="732" ht="12.75" customHeight="1"/>
+    <row r="733" ht="12.75" customHeight="1"/>
+    <row r="734" ht="12.75" customHeight="1"/>
+    <row r="735" ht="12.75" customHeight="1"/>
+    <row r="736" ht="12.75" customHeight="1"/>
+    <row r="737" ht="12.75" customHeight="1"/>
+    <row r="738" ht="12.75" customHeight="1"/>
+    <row r="739" ht="12.75" customHeight="1"/>
+    <row r="740" ht="12.75" customHeight="1"/>
+    <row r="741" ht="12.75" customHeight="1"/>
+    <row r="742" ht="12.75" customHeight="1"/>
+    <row r="743" ht="12.75" customHeight="1"/>
+    <row r="744" ht="12.75" customHeight="1"/>
+    <row r="745" ht="12.75" customHeight="1"/>
+    <row r="746" ht="12.75" customHeight="1"/>
+    <row r="747" ht="12.75" customHeight="1"/>
+    <row r="748" ht="12.75" customHeight="1"/>
+    <row r="749" ht="12.75" customHeight="1"/>
+    <row r="750" ht="12.75" customHeight="1"/>
+    <row r="751" ht="12.75" customHeight="1"/>
+    <row r="752" ht="12.75" customHeight="1"/>
+    <row r="753" ht="12.75" customHeight="1"/>
+    <row r="754" ht="12.75" customHeight="1"/>
+    <row r="755" ht="12.75" customHeight="1"/>
+    <row r="756" ht="12.75" customHeight="1"/>
+    <row r="757" ht="12.75" customHeight="1"/>
+    <row r="758" ht="12.75" customHeight="1"/>
+    <row r="759" ht="12.75" customHeight="1"/>
+    <row r="760" ht="12.75" customHeight="1"/>
+    <row r="761" ht="12.75" customHeight="1"/>
+    <row r="762" ht="12.75" customHeight="1"/>
+    <row r="763" ht="12.75" customHeight="1"/>
+    <row r="764" ht="12.75" customHeight="1"/>
+    <row r="765" ht="12.75" customHeight="1"/>
+    <row r="766" ht="12.75" customHeight="1"/>
+    <row r="767" ht="12.75" customHeight="1"/>
+    <row r="768" ht="12.75" customHeight="1"/>
+    <row r="769" ht="12.75" customHeight="1"/>
+    <row r="770" ht="12.75" customHeight="1"/>
+    <row r="771" ht="12.75" customHeight="1"/>
+    <row r="772" ht="12.75" customHeight="1"/>
+    <row r="773" ht="12.75" customHeight="1"/>
+    <row r="774" ht="12.75" customHeight="1"/>
+    <row r="775" ht="12.75" customHeight="1"/>
+    <row r="776" ht="12.75" customHeight="1"/>
+    <row r="777" ht="12.75" customHeight="1"/>
+    <row r="778" ht="12.75" customHeight="1"/>
+    <row r="779" ht="12.75" customHeight="1"/>
+    <row r="780" ht="12.75" customHeight="1"/>
+    <row r="781" ht="12.75" customHeight="1"/>
+    <row r="782" ht="12.75" customHeight="1"/>
+    <row r="783" ht="12.75" customHeight="1"/>
+    <row r="784" ht="12.75" customHeight="1"/>
+    <row r="785" ht="12.75" customHeight="1"/>
+    <row r="786" ht="12.75" customHeight="1"/>
+    <row r="787" ht="12.75" customHeight="1"/>
+    <row r="788" ht="12.75" customHeight="1"/>
+    <row r="789" ht="12.75" customHeight="1"/>
+    <row r="790" ht="12.75" customHeight="1"/>
+    <row r="791" ht="12.75" customHeight="1"/>
+    <row r="792" ht="12.75" customHeight="1"/>
+    <row r="793" ht="12.75" customHeight="1"/>
+    <row r="794" ht="12.75" customHeight="1"/>
+    <row r="795" ht="12.75" customHeight="1"/>
+    <row r="796" ht="12.75" customHeight="1"/>
+    <row r="797" ht="12.75" customHeight="1"/>
+    <row r="798" ht="12.75" customHeight="1"/>
+    <row r="799" ht="12.75" customHeight="1"/>
+    <row r="800" ht="12.75" customHeight="1"/>
+    <row r="801" ht="12.75" customHeight="1"/>
+    <row r="802" ht="12.75" customHeight="1"/>
+    <row r="803" ht="12.75" customHeight="1"/>
+    <row r="804" ht="12.75" customHeight="1"/>
+    <row r="805" ht="12.75" customHeight="1"/>
+    <row r="806" ht="12.75" customHeight="1"/>
+    <row r="807" ht="12.75" customHeight="1"/>
+    <row r="808" ht="12.75" customHeight="1"/>
+    <row r="809" ht="12.75" customHeight="1"/>
+    <row r="810" ht="12.75" customHeight="1"/>
+    <row r="811" ht="12.75" customHeight="1"/>
+    <row r="812" ht="12.75" customHeight="1"/>
+    <row r="813" ht="12.75" customHeight="1"/>
+    <row r="814" ht="12.75" customHeight="1"/>
+    <row r="815" ht="12.75" customHeight="1"/>
+    <row r="816" ht="12.75" customHeight="1"/>
+    <row r="817" ht="12.75" customHeight="1"/>
+    <row r="818" ht="12.75" customHeight="1"/>
+    <row r="819" ht="12.75" customHeight="1"/>
+    <row r="820" ht="12.75" customHeight="1"/>
+    <row r="821" ht="12.75" customHeight="1"/>
+    <row r="822" ht="12.75" customHeight="1"/>
+    <row r="823" ht="12.75" customHeight="1"/>
+    <row r="824" ht="12.75" customHeight="1"/>
+    <row r="825" ht="12.75" customHeight="1"/>
+    <row r="826" ht="12.75" customHeight="1"/>
+    <row r="827" ht="12.75" customHeight="1"/>
+    <row r="828" ht="12.75" customHeight="1"/>
+    <row r="829" ht="12.75" customHeight="1"/>
+    <row r="830" ht="12.75" customHeight="1"/>
+    <row r="831" ht="12.75" customHeight="1"/>
+    <row r="832" ht="12.75" customHeight="1"/>
+    <row r="833" ht="12.75" customHeight="1"/>
+    <row r="834" ht="12.75" customHeight="1"/>
+    <row r="835" ht="12.75" customHeight="1"/>
+    <row r="836" ht="12.75" customHeight="1"/>
+    <row r="837" ht="12.75" customHeight="1"/>
+    <row r="838" ht="12.75" customHeight="1"/>
+    <row r="839" ht="12.75" customHeight="1"/>
+    <row r="840" ht="12.75" customHeight="1"/>
+    <row r="841" ht="12.75" customHeight="1"/>
+    <row r="842" ht="12.75" customHeight="1"/>
+    <row r="843" ht="12.75" customHeight="1"/>
+    <row r="844" ht="12.75" customHeight="1"/>
+    <row r="845" ht="12.75" customHeight="1"/>
+    <row r="846" ht="12.75" customHeight="1"/>
+    <row r="847" ht="12.75" customHeight="1"/>
+    <row r="848" ht="12.75" customHeight="1"/>
+    <row r="849" ht="12.75" customHeight="1"/>
+    <row r="850" ht="12.75" customHeight="1"/>
+    <row r="851" ht="12.75" customHeight="1"/>
+    <row r="852" ht="12.75" customHeight="1"/>
+    <row r="853" ht="12.75" customHeight="1"/>
+    <row r="854" ht="12.75" customHeight="1"/>
+    <row r="855" ht="12.75" customHeight="1"/>
+    <row r="856" ht="12.75" customHeight="1"/>
+    <row r="857" ht="12.75" customHeight="1"/>
+    <row r="858" ht="12.75" customHeight="1"/>
+    <row r="859" ht="12.75" customHeight="1"/>
+    <row r="860" ht="12.75" customHeight="1"/>
+    <row r="861" ht="12.75" customHeight="1"/>
+    <row r="862" ht="12.75" customHeight="1"/>
+    <row r="863" ht="12.75" customHeight="1"/>
+    <row r="864" ht="12.75" customHeight="1"/>
+    <row r="865" ht="12.75" customHeight="1"/>
+    <row r="866" ht="12.75" customHeight="1"/>
+    <row r="867" ht="12.75" customHeight="1"/>
+    <row r="868" ht="12.75" customHeight="1"/>
+    <row r="869" ht="12.75" customHeight="1"/>
+    <row r="870" ht="12.75" customHeight="1"/>
+    <row r="871" ht="12.75" customHeight="1"/>
+    <row r="872" ht="12.75" customHeight="1"/>
+    <row r="873" ht="12.75" customHeight="1"/>
+    <row r="874" ht="12.75" customHeight="1"/>
+    <row r="875" ht="12.75" customHeight="1"/>
+    <row r="876" ht="12.75" customHeight="1"/>
+    <row r="877" ht="12.75" customHeight="1"/>
+    <row r="878" ht="12.75" customHeight="1"/>
+    <row r="879" ht="12.75" customHeight="1"/>
+    <row r="880" ht="12.75" customHeight="1"/>
+    <row r="881" ht="12.75" customHeight="1"/>
+    <row r="882" ht="12.75" customHeight="1"/>
+    <row r="883" ht="12.75" customHeight="1"/>
+    <row r="884" ht="12.75" customHeight="1"/>
+    <row r="885" ht="12.75" customHeight="1"/>
+    <row r="886" ht="12.75" customHeight="1"/>
+    <row r="887" ht="12.75" customHeight="1"/>
+    <row r="888" ht="12.75" customHeight="1"/>
+    <row r="889" ht="12.75" customHeight="1"/>
+    <row r="890" ht="12.75" customHeight="1"/>
+    <row r="891" ht="12.75" customHeight="1"/>
+    <row r="892" ht="12.75" customHeight="1"/>
+    <row r="893" ht="12.75" customHeight="1"/>
+    <row r="894" ht="12.75" customHeight="1"/>
+    <row r="895" ht="12.75" customHeight="1"/>
+    <row r="896" ht="12.75" customHeight="1"/>
+    <row r="897" ht="12.75" customHeight="1"/>
+    <row r="898" ht="12.75" customHeight="1"/>
+    <row r="899" ht="12.75" customHeight="1"/>
+    <row r="900" ht="12.75" customHeight="1"/>
+    <row r="901" ht="12.75" customHeight="1"/>
+    <row r="902" ht="12.75" customHeight="1"/>
+    <row r="903" ht="12.75" customHeight="1"/>
+    <row r="904" ht="12.75" customHeight="1"/>
+    <row r="905" ht="12.75" customHeight="1"/>
+    <row r="906" ht="12.75" customHeight="1"/>
+    <row r="907" ht="12.75" customHeight="1"/>
+    <row r="908" ht="12.75" customHeight="1"/>
+    <row r="909" ht="12.75" customHeight="1"/>
+    <row r="910" ht="12.75" customHeight="1"/>
+    <row r="911" ht="12.75" customHeight="1"/>
+    <row r="912" ht="12.75" customHeight="1"/>
+    <row r="913" ht="12.75" customHeight="1"/>
+    <row r="914" ht="12.75" customHeight="1"/>
+    <row r="915" ht="12.75" customHeight="1"/>
+    <row r="916" ht="12.75" customHeight="1"/>
+    <row r="917" ht="12.75" customHeight="1"/>
+    <row r="918" ht="12.75" customHeight="1"/>
+    <row r="919" ht="12.75" customHeight="1"/>
+    <row r="920" ht="12.75" customHeight="1"/>
+    <row r="921" ht="12.75" customHeight="1"/>
+    <row r="922" ht="12.75" customHeight="1"/>
+    <row r="923" ht="12.75" customHeight="1"/>
+    <row r="924" ht="12.75" customHeight="1"/>
+    <row r="925" ht="12.75" customHeight="1"/>
+    <row r="926" ht="12.75" customHeight="1"/>
+    <row r="927" ht="12.75" customHeight="1"/>
+    <row r="928" ht="12.75" customHeight="1"/>
+    <row r="929" ht="12.75" customHeight="1"/>
+    <row r="930" ht="12.75" customHeight="1"/>
+    <row r="931" ht="12.75" customHeight="1"/>
+    <row r="932" ht="12.75" customHeight="1"/>
+    <row r="933" ht="12.75" customHeight="1"/>
+    <row r="934" ht="12.75" customHeight="1"/>
+    <row r="935" ht="12.75" customHeight="1"/>
+    <row r="936" ht="12.75" customHeight="1"/>
+    <row r="937" ht="12.75" customHeight="1"/>
+    <row r="938" ht="12.75" customHeight="1"/>
+    <row r="939" ht="12.75" customHeight="1"/>
+    <row r="940" ht="12.75" customHeight="1"/>
+    <row r="941" ht="12.75" customHeight="1"/>
+    <row r="942" ht="12.75" customHeight="1"/>
+    <row r="943" ht="12.75" customHeight="1"/>
+    <row r="944" ht="12.75" customHeight="1"/>
+    <row r="945" ht="12.75" customHeight="1"/>
+    <row r="946" ht="12.75" customHeight="1"/>
+    <row r="947" ht="12.75" customHeight="1"/>
+    <row r="948" ht="12.75" customHeight="1"/>
+    <row r="949" ht="12.75" customHeight="1"/>
+    <row r="950" ht="12.75" customHeight="1"/>
+    <row r="951" ht="12.75" customHeight="1"/>
+    <row r="952" ht="12.75" customHeight="1"/>
+    <row r="953" ht="12.75" customHeight="1"/>
+    <row r="954" ht="12.75" customHeight="1"/>
+    <row r="955" ht="12.75" customHeight="1"/>
+    <row r="956" ht="12.75" customHeight="1"/>
+    <row r="957" ht="12.75" customHeight="1"/>
+    <row r="958" ht="12.75" customHeight="1"/>
+    <row r="959" ht="12.75" customHeight="1"/>
+    <row r="960" ht="12.75" customHeight="1"/>
+    <row r="961" ht="12.75" customHeight="1"/>
+    <row r="962" ht="12.75" customHeight="1"/>
+    <row r="963" ht="12.75" customHeight="1"/>
+    <row r="964" ht="12.75" customHeight="1"/>
+    <row r="965" ht="12.75" customHeight="1"/>
+    <row r="966" ht="12.75" customHeight="1"/>
+    <row r="967" ht="12.75" customHeight="1"/>
+    <row r="968" ht="12.75" customHeight="1"/>
+    <row r="969" ht="12.75" customHeight="1"/>
+    <row r="970" ht="12.75" customHeight="1"/>
+    <row r="971" ht="12.75" customHeight="1"/>
+    <row r="972" ht="12.75" customHeight="1"/>
+    <row r="973" ht="12.75" customHeight="1"/>
+    <row r="974" ht="12.75" customHeight="1"/>
+    <row r="975" ht="12.75" customHeight="1"/>
+    <row r="976" ht="12.75" customHeight="1"/>
+    <row r="977" ht="12.75" customHeight="1"/>
+    <row r="978" ht="12.75" customHeight="1"/>
+    <row r="979" ht="12.75" customHeight="1"/>
+    <row r="980" ht="12.75" customHeight="1"/>
+    <row r="981" ht="12.75" customHeight="1"/>
+    <row r="982" ht="12.75" customHeight="1"/>
+    <row r="983" ht="12.75" customHeight="1"/>
+    <row r="984" ht="12.75" customHeight="1"/>
+    <row r="985" ht="12.75" customHeight="1"/>
+    <row r="986" ht="12.75" customHeight="1"/>
+    <row r="987" ht="12.75" customHeight="1"/>
+    <row r="988" ht="12.75" customHeight="1"/>
+    <row r="989" ht="12.75" customHeight="1"/>
+    <row r="990" ht="12.75" customHeight="1"/>
+    <row r="991" ht="12.75" customHeight="1"/>
+    <row r="992" ht="12.75" customHeight="1"/>
+    <row r="993" ht="12.75" customHeight="1"/>
+    <row r="994" ht="12.75" customHeight="1"/>
+    <row r="995" ht="12.75" customHeight="1"/>
+    <row r="996" ht="12.75" customHeight="1"/>
+    <row r="997" ht="12.75" customHeight="1"/>
+    <row r="998" ht="12.75" customHeight="1"/>
+    <row r="999" ht="12.75" customHeight="1"/>
+    <row r="1000" ht="12.75" customHeight="1"/>
+  </sheetData>
+  <mergeCells count="9">
+    <mergeCell ref="G15:H15"/>
+    <mergeCell ref="I15:K15"/>
+    <mergeCell ref="G17:K17"/>
+    <mergeCell ref="C2:O6"/>
+    <mergeCell ref="E8:M8"/>
+    <mergeCell ref="G13:H13"/>
+    <mergeCell ref="I13:K13"/>
+    <mergeCell ref="G14:H14"/>
+    <mergeCell ref="I14:K14"/>
+  </mergeCells>
+  <phoneticPr fontId="4"/>
+  <pageMargins left="0.70833333333333304" right="0.70833333333333304" top="0.74791666666666701" bottom="0.74791666666666701" header="0" footer="0"/>
+  <pageSetup paperSize="9" orientation="landscape"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{48C6F589-ABD7-4CAC-9D7A-DCB601C13749}">
   <dimension ref="A1:J1000"/>
   <sheetFormatPr defaultColWidth="12.625" defaultRowHeight="15" customHeight="1"/>
@@ -2821,19 +4120,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="57" t="s">
+      <c r="A1" s="66" t="s">
         <v>30</v>
       </c>
-      <c r="B1" s="58"/>
-      <c r="C1" s="59"/>
-      <c r="D1" s="66" t="s">
+      <c r="B1" s="67"/>
+      <c r="C1" s="68"/>
+      <c r="D1" s="74" t="s">
         <v>0</v>
       </c>
-      <c r="E1" s="67"/>
-      <c r="F1" s="66" t="s">
+      <c r="E1" s="75"/>
+      <c r="F1" s="74" t="s">
         <v>1</v>
       </c>
-      <c r="G1" s="67"/>
+      <c r="G1" s="75"/>
       <c r="H1" s="11" t="s">
         <v>2</v>
       </c>
@@ -2845,192 +4144,192 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="60"/>
-      <c r="B2" s="61"/>
-      <c r="C2" s="62"/>
-      <c r="D2" s="68" t="s">
+      <c r="A2" s="69"/>
+      <c r="B2" s="58"/>
+      <c r="C2" s="70"/>
+      <c r="D2" s="76" t="s">
         <v>6</v>
       </c>
-      <c r="E2" s="69"/>
-      <c r="F2" s="68" t="s">
+      <c r="E2" s="77"/>
+      <c r="F2" s="76" t="s">
         <v>7</v>
       </c>
-      <c r="G2" s="69"/>
-      <c r="H2" s="72">
+      <c r="G2" s="77"/>
+      <c r="H2" s="80">
         <v>45806</v>
       </c>
-      <c r="I2" s="75" t="s">
+      <c r="I2" s="83" t="s">
         <v>28</v>
       </c>
-      <c r="J2" s="76"/>
+      <c r="J2" s="84"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="60"/>
-      <c r="B3" s="61"/>
-      <c r="C3" s="62"/>
-      <c r="D3" s="70"/>
-      <c r="E3" s="62"/>
-      <c r="F3" s="70"/>
-      <c r="G3" s="62"/>
-      <c r="H3" s="73"/>
-      <c r="I3" s="73"/>
-      <c r="J3" s="77"/>
+      <c r="A3" s="69"/>
+      <c r="B3" s="58"/>
+      <c r="C3" s="70"/>
+      <c r="D3" s="78"/>
+      <c r="E3" s="70"/>
+      <c r="F3" s="78"/>
+      <c r="G3" s="70"/>
+      <c r="H3" s="81"/>
+      <c r="I3" s="81"/>
+      <c r="J3" s="85"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="63"/>
-      <c r="B4" s="64"/>
-      <c r="C4" s="65"/>
-      <c r="D4" s="71"/>
-      <c r="E4" s="65"/>
-      <c r="F4" s="71"/>
-      <c r="G4" s="65"/>
-      <c r="H4" s="74"/>
-      <c r="I4" s="74"/>
-      <c r="J4" s="78"/>
+      <c r="A4" s="71"/>
+      <c r="B4" s="72"/>
+      <c r="C4" s="73"/>
+      <c r="D4" s="79"/>
+      <c r="E4" s="73"/>
+      <c r="F4" s="79"/>
+      <c r="G4" s="73"/>
+      <c r="H4" s="82"/>
+      <c r="I4" s="82"/>
+      <c r="J4" s="86"/>
     </row>
     <row r="5" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A5" s="79" t="s">
+      <c r="A5" s="87" t="s">
         <v>31</v>
       </c>
-      <c r="B5" s="80"/>
-      <c r="C5" s="67"/>
-      <c r="D5" s="81" t="s">
+      <c r="B5" s="88"/>
+      <c r="C5" s="75"/>
+      <c r="D5" s="89" t="s">
         <v>41</v>
       </c>
-      <c r="E5" s="80"/>
-      <c r="F5" s="80"/>
-      <c r="G5" s="80"/>
-      <c r="H5" s="80"/>
-      <c r="I5" s="80"/>
-      <c r="J5" s="82"/>
+      <c r="E5" s="88"/>
+      <c r="F5" s="88"/>
+      <c r="G5" s="88"/>
+      <c r="H5" s="88"/>
+      <c r="I5" s="88"/>
+      <c r="J5" s="90"/>
     </row>
     <row r="6" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A6" s="42" t="s">
+      <c r="A6" s="63" t="s">
         <v>32</v>
       </c>
-      <c r="B6" s="43"/>
-      <c r="C6" s="44"/>
-      <c r="D6" s="45" t="s">
+      <c r="B6" s="56"/>
+      <c r="C6" s="55"/>
+      <c r="D6" s="64" t="s">
         <v>42</v>
       </c>
-      <c r="E6" s="43"/>
-      <c r="F6" s="43"/>
-      <c r="G6" s="43"/>
-      <c r="H6" s="43"/>
-      <c r="I6" s="43"/>
-      <c r="J6" s="46"/>
+      <c r="E6" s="56"/>
+      <c r="F6" s="56"/>
+      <c r="G6" s="56"/>
+      <c r="H6" s="56"/>
+      <c r="I6" s="56"/>
+      <c r="J6" s="65"/>
     </row>
     <row r="7" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A7" s="42" t="s">
+      <c r="A7" s="63" t="s">
         <v>33</v>
       </c>
-      <c r="B7" s="43"/>
-      <c r="C7" s="44"/>
-      <c r="D7" s="45" t="s">
+      <c r="B7" s="56"/>
+      <c r="C7" s="55"/>
+      <c r="D7" s="64" t="s">
         <v>34</v>
       </c>
-      <c r="E7" s="43"/>
-      <c r="F7" s="43"/>
-      <c r="G7" s="43"/>
-      <c r="H7" s="43"/>
-      <c r="I7" s="43"/>
-      <c r="J7" s="46"/>
+      <c r="E7" s="56"/>
+      <c r="F7" s="56"/>
+      <c r="G7" s="56"/>
+      <c r="H7" s="56"/>
+      <c r="I7" s="56"/>
+      <c r="J7" s="65"/>
     </row>
     <row r="8" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A8" s="42" t="s">
+      <c r="A8" s="63" t="s">
         <v>35</v>
       </c>
-      <c r="B8" s="43"/>
-      <c r="C8" s="44"/>
-      <c r="D8" s="45" t="s">
+      <c r="B8" s="56"/>
+      <c r="C8" s="55"/>
+      <c r="D8" s="64" t="s">
         <v>84</v>
       </c>
-      <c r="E8" s="43"/>
-      <c r="F8" s="43"/>
-      <c r="G8" s="43"/>
-      <c r="H8" s="43"/>
-      <c r="I8" s="43"/>
-      <c r="J8" s="46"/>
+      <c r="E8" s="56"/>
+      <c r="F8" s="56"/>
+      <c r="G8" s="56"/>
+      <c r="H8" s="56"/>
+      <c r="I8" s="56"/>
+      <c r="J8" s="65"/>
     </row>
     <row r="9" spans="1:10" ht="64.5" customHeight="1">
-      <c r="A9" s="52" t="s">
+      <c r="A9" s="96" t="s">
         <v>36</v>
       </c>
-      <c r="B9" s="55" t="s">
+      <c r="B9" s="99" t="s">
         <v>37</v>
       </c>
-      <c r="C9" s="44"/>
-      <c r="D9" s="56" t="s">
+      <c r="C9" s="55"/>
+      <c r="D9" s="100" t="s">
         <v>83</v>
       </c>
-      <c r="E9" s="43"/>
-      <c r="F9" s="43"/>
-      <c r="G9" s="43"/>
-      <c r="H9" s="43"/>
-      <c r="I9" s="43"/>
-      <c r="J9" s="46"/>
+      <c r="E9" s="56"/>
+      <c r="F9" s="56"/>
+      <c r="G9" s="56"/>
+      <c r="H9" s="56"/>
+      <c r="I9" s="56"/>
+      <c r="J9" s="65"/>
     </row>
     <row r="10" spans="1:10" ht="64.5" customHeight="1">
-      <c r="A10" s="53"/>
-      <c r="B10" s="55" t="s">
+      <c r="A10" s="97"/>
+      <c r="B10" s="99" t="s">
         <v>38</v>
       </c>
-      <c r="C10" s="44"/>
-      <c r="D10" s="56" t="s">
+      <c r="C10" s="55"/>
+      <c r="D10" s="100" t="s">
         <v>43</v>
       </c>
-      <c r="E10" s="43"/>
-      <c r="F10" s="43"/>
-      <c r="G10" s="43"/>
-      <c r="H10" s="43"/>
-      <c r="I10" s="43"/>
-      <c r="J10" s="46"/>
+      <c r="E10" s="56"/>
+      <c r="F10" s="56"/>
+      <c r="G10" s="56"/>
+      <c r="H10" s="56"/>
+      <c r="I10" s="56"/>
+      <c r="J10" s="65"/>
     </row>
     <row r="11" spans="1:10" ht="64.5" customHeight="1">
-      <c r="A11" s="54"/>
-      <c r="B11" s="55" t="s">
+      <c r="A11" s="98"/>
+      <c r="B11" s="99" t="s">
         <v>39</v>
       </c>
-      <c r="C11" s="44"/>
-      <c r="D11" s="56" t="s">
+      <c r="C11" s="55"/>
+      <c r="D11" s="100" t="s">
         <v>44</v>
       </c>
-      <c r="E11" s="43"/>
-      <c r="F11" s="43"/>
-      <c r="G11" s="43"/>
-      <c r="H11" s="43"/>
-      <c r="I11" s="43"/>
-      <c r="J11" s="46"/>
+      <c r="E11" s="56"/>
+      <c r="F11" s="56"/>
+      <c r="G11" s="56"/>
+      <c r="H11" s="56"/>
+      <c r="I11" s="56"/>
+      <c r="J11" s="65"/>
     </row>
     <row r="12" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A12" s="42" t="s">
+      <c r="A12" s="63" t="s">
         <v>40</v>
       </c>
-      <c r="B12" s="43"/>
-      <c r="C12" s="44"/>
-      <c r="D12" s="45" t="s">
+      <c r="B12" s="56"/>
+      <c r="C12" s="55"/>
+      <c r="D12" s="64" t="s">
         <v>85</v>
       </c>
-      <c r="E12" s="43"/>
-      <c r="F12" s="43"/>
-      <c r="G12" s="43"/>
-      <c r="H12" s="43"/>
-      <c r="I12" s="43"/>
-      <c r="J12" s="46"/>
+      <c r="E12" s="56"/>
+      <c r="F12" s="56"/>
+      <c r="G12" s="56"/>
+      <c r="H12" s="56"/>
+      <c r="I12" s="56"/>
+      <c r="J12" s="65"/>
     </row>
     <row r="13" spans="1:10" ht="26.25" customHeight="1" thickBot="1">
-      <c r="A13" s="47" t="s">
+      <c r="A13" s="91" t="s">
         <v>18</v>
       </c>
-      <c r="B13" s="48"/>
-      <c r="C13" s="49"/>
-      <c r="D13" s="50"/>
-      <c r="E13" s="48"/>
-      <c r="F13" s="48"/>
-      <c r="G13" s="48"/>
-      <c r="H13" s="48"/>
-      <c r="I13" s="48"/>
-      <c r="J13" s="51"/>
+      <c r="B13" s="92"/>
+      <c r="C13" s="93"/>
+      <c r="D13" s="94"/>
+      <c r="E13" s="92"/>
+      <c r="F13" s="92"/>
+      <c r="G13" s="92"/>
+      <c r="H13" s="92"/>
+      <c r="I13" s="92"/>
+      <c r="J13" s="95"/>
     </row>
     <row r="14" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="15" spans="1:10" ht="12.75" customHeight="1"/>
@@ -4021,18 +5320,6 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="A6:C6"/>
-    <mergeCell ref="D6:J6"/>
-    <mergeCell ref="A1:C4"/>
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="F1:G1"/>
-    <mergeCell ref="D2:E4"/>
-    <mergeCell ref="F2:G4"/>
-    <mergeCell ref="H2:H4"/>
-    <mergeCell ref="I2:I4"/>
-    <mergeCell ref="J2:J4"/>
-    <mergeCell ref="A5:C5"/>
-    <mergeCell ref="D5:J5"/>
     <mergeCell ref="A12:C12"/>
     <mergeCell ref="D12:J12"/>
     <mergeCell ref="A13:C13"/>
@@ -4048,6 +5335,18 @@
     <mergeCell ref="D10:J10"/>
     <mergeCell ref="B11:C11"/>
     <mergeCell ref="D11:J11"/>
+    <mergeCell ref="A6:C6"/>
+    <mergeCell ref="D6:J6"/>
+    <mergeCell ref="A1:C4"/>
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="F1:G1"/>
+    <mergeCell ref="D2:E4"/>
+    <mergeCell ref="F2:G4"/>
+    <mergeCell ref="H2:H4"/>
+    <mergeCell ref="I2:I4"/>
+    <mergeCell ref="J2:J4"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="D5:J5"/>
   </mergeCells>
   <phoneticPr fontId="4"/>
   <pageMargins left="0.70833333333333304" right="0.70833333333333304" top="0.74791666666666701" bottom="0.74791666666666701" header="0" footer="0"/>
@@ -4055,7 +5354,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{35A30B2F-9CA5-49B1-A5AF-C51D258A3AC8}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
@@ -4070,19 +5369,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="93" t="s">
+      <c r="A1" s="119" t="s">
         <v>5</v>
       </c>
-      <c r="B1" s="94"/>
-      <c r="C1" s="95"/>
-      <c r="D1" s="97" t="s">
+      <c r="B1" s="120"/>
+      <c r="C1" s="121"/>
+      <c r="D1" s="123" t="s">
         <v>0</v>
       </c>
-      <c r="E1" s="98"/>
-      <c r="F1" s="97" t="s">
+      <c r="E1" s="124"/>
+      <c r="F1" s="123" t="s">
         <v>1</v>
       </c>
-      <c r="G1" s="98"/>
+      <c r="G1" s="124"/>
       <c r="H1" s="1" t="s">
         <v>2</v>
       </c>
@@ -4094,190 +5393,190 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="90"/>
-      <c r="B2" s="91"/>
-      <c r="C2" s="96"/>
-      <c r="D2" s="99" t="s">
+      <c r="A2" s="116"/>
+      <c r="B2" s="117"/>
+      <c r="C2" s="122"/>
+      <c r="D2" s="125" t="s">
         <v>6</v>
       </c>
-      <c r="E2" s="100"/>
-      <c r="F2" s="99" t="s">
+      <c r="E2" s="126"/>
+      <c r="F2" s="125" t="s">
         <v>7</v>
       </c>
-      <c r="G2" s="100"/>
-      <c r="H2" s="102">
+      <c r="G2" s="126"/>
+      <c r="H2" s="128">
         <v>45806</v>
       </c>
-      <c r="I2" s="104" t="s">
+      <c r="I2" s="130" t="s">
         <v>28</v>
       </c>
-      <c r="J2" s="105"/>
+      <c r="J2" s="131"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="90"/>
-      <c r="B3" s="91"/>
-      <c r="C3" s="96"/>
-      <c r="D3" s="101"/>
-      <c r="E3" s="96"/>
-      <c r="F3" s="101"/>
-      <c r="G3" s="96"/>
-      <c r="H3" s="103"/>
-      <c r="I3" s="103"/>
-      <c r="J3" s="106"/>
+      <c r="A3" s="116"/>
+      <c r="B3" s="117"/>
+      <c r="C3" s="122"/>
+      <c r="D3" s="127"/>
+      <c r="E3" s="122"/>
+      <c r="F3" s="127"/>
+      <c r="G3" s="122"/>
+      <c r="H3" s="129"/>
+      <c r="I3" s="129"/>
+      <c r="J3" s="132"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="90"/>
-      <c r="B4" s="91"/>
-      <c r="C4" s="96"/>
-      <c r="D4" s="101"/>
-      <c r="E4" s="96"/>
-      <c r="F4" s="101"/>
-      <c r="G4" s="96"/>
-      <c r="H4" s="103"/>
-      <c r="I4" s="103"/>
-      <c r="J4" s="106"/>
+      <c r="A4" s="116"/>
+      <c r="B4" s="117"/>
+      <c r="C4" s="122"/>
+      <c r="D4" s="127"/>
+      <c r="E4" s="122"/>
+      <c r="F4" s="127"/>
+      <c r="G4" s="122"/>
+      <c r="H4" s="129"/>
+      <c r="I4" s="129"/>
+      <c r="J4" s="132"/>
     </row>
     <row r="5" spans="1:10" ht="28.5" customHeight="1">
-      <c r="A5" s="107" t="s">
+      <c r="A5" s="133" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="108"/>
-      <c r="C5" s="98"/>
-      <c r="D5" s="109" t="s">
+      <c r="B5" s="134"/>
+      <c r="C5" s="124"/>
+      <c r="D5" s="135" t="s">
         <v>19</v>
       </c>
-      <c r="E5" s="108"/>
-      <c r="F5" s="108"/>
-      <c r="G5" s="108"/>
-      <c r="H5" s="108"/>
-      <c r="I5" s="108"/>
-      <c r="J5" s="110"/>
+      <c r="E5" s="134"/>
+      <c r="F5" s="134"/>
+      <c r="G5" s="134"/>
+      <c r="H5" s="134"/>
+      <c r="I5" s="134"/>
+      <c r="J5" s="136"/>
     </row>
     <row r="6" spans="1:10" ht="21" customHeight="1">
-      <c r="A6" s="83" t="s">
+      <c r="A6" s="111" t="s">
         <v>9</v>
       </c>
-      <c r="B6" s="84"/>
-      <c r="C6" s="84"/>
-      <c r="D6" s="84"/>
-      <c r="E6" s="84"/>
-      <c r="F6" s="84"/>
-      <c r="G6" s="84"/>
-      <c r="H6" s="84"/>
-      <c r="I6" s="84"/>
-      <c r="J6" s="85"/>
+      <c r="B6" s="102"/>
+      <c r="C6" s="102"/>
+      <c r="D6" s="102"/>
+      <c r="E6" s="102"/>
+      <c r="F6" s="102"/>
+      <c r="G6" s="102"/>
+      <c r="H6" s="102"/>
+      <c r="I6" s="102"/>
+      <c r="J6" s="105"/>
     </row>
     <row r="7" spans="1:10" ht="21" customHeight="1">
-      <c r="A7" s="87"/>
-      <c r="B7" s="88"/>
-      <c r="C7" s="88"/>
-      <c r="D7" s="88"/>
-      <c r="E7" s="88"/>
-      <c r="F7" s="88"/>
-      <c r="G7" s="88"/>
-      <c r="H7" s="88"/>
-      <c r="I7" s="88"/>
-      <c r="J7" s="89"/>
+      <c r="A7" s="113"/>
+      <c r="B7" s="114"/>
+      <c r="C7" s="114"/>
+      <c r="D7" s="114"/>
+      <c r="E7" s="114"/>
+      <c r="F7" s="114"/>
+      <c r="G7" s="114"/>
+      <c r="H7" s="114"/>
+      <c r="I7" s="114"/>
+      <c r="J7" s="115"/>
     </row>
     <row r="8" spans="1:10" ht="21" customHeight="1">
-      <c r="A8" s="90"/>
-      <c r="B8" s="91"/>
-      <c r="C8" s="91"/>
-      <c r="D8" s="91"/>
-      <c r="E8" s="91"/>
-      <c r="F8" s="91"/>
-      <c r="G8" s="91"/>
-      <c r="H8" s="91"/>
-      <c r="I8" s="91"/>
-      <c r="J8" s="92"/>
+      <c r="A8" s="116"/>
+      <c r="B8" s="117"/>
+      <c r="C8" s="117"/>
+      <c r="D8" s="117"/>
+      <c r="E8" s="117"/>
+      <c r="F8" s="117"/>
+      <c r="G8" s="117"/>
+      <c r="H8" s="117"/>
+      <c r="I8" s="117"/>
+      <c r="J8" s="118"/>
     </row>
     <row r="9" spans="1:10" ht="21" customHeight="1">
-      <c r="A9" s="90"/>
-      <c r="B9" s="91"/>
-      <c r="C9" s="91"/>
-      <c r="D9" s="91"/>
-      <c r="E9" s="91"/>
-      <c r="F9" s="91"/>
-      <c r="G9" s="91"/>
-      <c r="H9" s="91"/>
-      <c r="I9" s="91"/>
-      <c r="J9" s="92"/>
+      <c r="A9" s="116"/>
+      <c r="B9" s="117"/>
+      <c r="C9" s="117"/>
+      <c r="D9" s="117"/>
+      <c r="E9" s="117"/>
+      <c r="F9" s="117"/>
+      <c r="G9" s="117"/>
+      <c r="H9" s="117"/>
+      <c r="I9" s="117"/>
+      <c r="J9" s="118"/>
     </row>
     <row r="10" spans="1:10" ht="21" customHeight="1">
-      <c r="A10" s="90"/>
-      <c r="B10" s="91"/>
-      <c r="C10" s="91"/>
-      <c r="D10" s="91"/>
-      <c r="E10" s="91"/>
-      <c r="F10" s="91"/>
-      <c r="G10" s="91"/>
-      <c r="H10" s="91"/>
-      <c r="I10" s="91"/>
-      <c r="J10" s="92"/>
+      <c r="A10" s="116"/>
+      <c r="B10" s="117"/>
+      <c r="C10" s="117"/>
+      <c r="D10" s="117"/>
+      <c r="E10" s="117"/>
+      <c r="F10" s="117"/>
+      <c r="G10" s="117"/>
+      <c r="H10" s="117"/>
+      <c r="I10" s="117"/>
+      <c r="J10" s="118"/>
     </row>
     <row r="11" spans="1:10" ht="21" customHeight="1">
-      <c r="A11" s="90"/>
-      <c r="B11" s="91"/>
-      <c r="C11" s="91"/>
-      <c r="D11" s="91"/>
-      <c r="E11" s="91"/>
-      <c r="F11" s="91"/>
-      <c r="G11" s="91"/>
-      <c r="H11" s="91"/>
-      <c r="I11" s="91"/>
-      <c r="J11" s="92"/>
+      <c r="A11" s="116"/>
+      <c r="B11" s="117"/>
+      <c r="C11" s="117"/>
+      <c r="D11" s="117"/>
+      <c r="E11" s="117"/>
+      <c r="F11" s="117"/>
+      <c r="G11" s="117"/>
+      <c r="H11" s="117"/>
+      <c r="I11" s="117"/>
+      <c r="J11" s="118"/>
     </row>
     <row r="12" spans="1:10" ht="21" customHeight="1">
-      <c r="A12" s="90"/>
-      <c r="B12" s="91"/>
-      <c r="C12" s="91"/>
-      <c r="D12" s="91"/>
-      <c r="E12" s="91"/>
-      <c r="F12" s="91"/>
-      <c r="G12" s="91"/>
-      <c r="H12" s="91"/>
-      <c r="I12" s="91"/>
-      <c r="J12" s="92"/>
+      <c r="A12" s="116"/>
+      <c r="B12" s="117"/>
+      <c r="C12" s="117"/>
+      <c r="D12" s="117"/>
+      <c r="E12" s="117"/>
+      <c r="F12" s="117"/>
+      <c r="G12" s="117"/>
+      <c r="H12" s="117"/>
+      <c r="I12" s="117"/>
+      <c r="J12" s="118"/>
     </row>
     <row r="13" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A13" s="90"/>
-      <c r="B13" s="91"/>
-      <c r="C13" s="91"/>
-      <c r="D13" s="91"/>
-      <c r="E13" s="91"/>
-      <c r="F13" s="91"/>
-      <c r="G13" s="91"/>
-      <c r="H13" s="91"/>
-      <c r="I13" s="91"/>
-      <c r="J13" s="92"/>
+      <c r="A13" s="116"/>
+      <c r="B13" s="117"/>
+      <c r="C13" s="117"/>
+      <c r="D13" s="117"/>
+      <c r="E13" s="117"/>
+      <c r="F13" s="117"/>
+      <c r="G13" s="117"/>
+      <c r="H13" s="117"/>
+      <c r="I13" s="117"/>
+      <c r="J13" s="118"/>
     </row>
     <row r="14" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A14" s="83" t="s">
+      <c r="A14" s="111" t="s">
         <v>10</v>
       </c>
-      <c r="B14" s="84"/>
-      <c r="C14" s="84"/>
-      <c r="D14" s="84"/>
-      <c r="E14" s="84"/>
-      <c r="F14" s="84"/>
-      <c r="G14" s="84"/>
-      <c r="H14" s="84"/>
-      <c r="I14" s="84"/>
-      <c r="J14" s="85"/>
+      <c r="B14" s="102"/>
+      <c r="C14" s="102"/>
+      <c r="D14" s="102"/>
+      <c r="E14" s="102"/>
+      <c r="F14" s="102"/>
+      <c r="G14" s="102"/>
+      <c r="H14" s="102"/>
+      <c r="I14" s="102"/>
+      <c r="J14" s="105"/>
     </row>
     <row r="15" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A15" s="83" t="s">
+      <c r="A15" s="111" t="s">
         <v>11</v>
       </c>
-      <c r="B15" s="84"/>
-      <c r="C15" s="86"/>
-      <c r="D15" s="111" t="s">
+      <c r="B15" s="102"/>
+      <c r="C15" s="103"/>
+      <c r="D15" s="104" t="s">
         <v>26</v>
       </c>
-      <c r="E15" s="84"/>
-      <c r="F15" s="84"/>
-      <c r="G15" s="84"/>
-      <c r="H15" s="86"/>
+      <c r="E15" s="102"/>
+      <c r="F15" s="102"/>
+      <c r="G15" s="102"/>
+      <c r="H15" s="103"/>
       <c r="I15" s="5" t="s">
         <v>12</v>
       </c>
@@ -4286,11 +5585,11 @@
       </c>
     </row>
     <row r="16" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A16" s="83" t="s">
+      <c r="A16" s="111" t="s">
         <v>13</v>
       </c>
-      <c r="B16" s="84"/>
-      <c r="C16" s="86"/>
+      <c r="B16" s="102"/>
+      <c r="C16" s="103"/>
       <c r="D16" s="5" t="s">
         <v>14</v>
       </c>
@@ -4306,15 +5605,15 @@
       <c r="H16" s="112" t="s">
         <v>18</v>
       </c>
-      <c r="I16" s="84"/>
-      <c r="J16" s="85"/>
+      <c r="I16" s="102"/>
+      <c r="J16" s="105"/>
     </row>
     <row r="17" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A17" s="113">
+      <c r="A17" s="101">
         <v>1</v>
       </c>
-      <c r="B17" s="84"/>
-      <c r="C17" s="86"/>
+      <c r="B17" s="102"/>
+      <c r="C17" s="103"/>
       <c r="D17" s="7" t="s">
         <v>21</v>
       </c>
@@ -4327,16 +5626,16 @@
       <c r="G17" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="H17" s="111"/>
-      <c r="I17" s="84"/>
-      <c r="J17" s="85"/>
+      <c r="H17" s="104"/>
+      <c r="I17" s="102"/>
+      <c r="J17" s="105"/>
     </row>
     <row r="18" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A18" s="113">
+      <c r="A18" s="101">
         <v>2</v>
       </c>
-      <c r="B18" s="84"/>
-      <c r="C18" s="86"/>
+      <c r="B18" s="102"/>
+      <c r="C18" s="103"/>
       <c r="D18" s="7" t="s">
         <v>22</v>
       </c>
@@ -4347,71 +5646,71 @@
       <c r="G18" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="H18" s="111" t="s">
+      <c r="H18" s="104" t="s">
         <v>27</v>
       </c>
-      <c r="I18" s="84"/>
-      <c r="J18" s="85"/>
+      <c r="I18" s="102"/>
+      <c r="J18" s="105"/>
     </row>
     <row r="19" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A19" s="113"/>
-      <c r="B19" s="84"/>
-      <c r="C19" s="86"/>
+      <c r="A19" s="101"/>
+      <c r="B19" s="102"/>
+      <c r="C19" s="103"/>
       <c r="D19" s="7"/>
       <c r="E19" s="7"/>
       <c r="F19" s="8"/>
       <c r="G19" s="8"/>
-      <c r="H19" s="111"/>
-      <c r="I19" s="84"/>
-      <c r="J19" s="85"/>
+      <c r="H19" s="104"/>
+      <c r="I19" s="102"/>
+      <c r="J19" s="105"/>
     </row>
     <row r="20" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A20" s="113"/>
-      <c r="B20" s="84"/>
-      <c r="C20" s="86"/>
+      <c r="A20" s="101"/>
+      <c r="B20" s="102"/>
+      <c r="C20" s="103"/>
       <c r="D20" s="7"/>
       <c r="E20" s="7"/>
       <c r="F20" s="8"/>
       <c r="G20" s="8"/>
-      <c r="H20" s="111"/>
-      <c r="I20" s="84"/>
-      <c r="J20" s="85"/>
+      <c r="H20" s="104"/>
+      <c r="I20" s="102"/>
+      <c r="J20" s="105"/>
     </row>
     <row r="21" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A21" s="113"/>
-      <c r="B21" s="84"/>
-      <c r="C21" s="86"/>
+      <c r="A21" s="101"/>
+      <c r="B21" s="102"/>
+      <c r="C21" s="103"/>
       <c r="D21" s="7"/>
       <c r="E21" s="7"/>
       <c r="F21" s="8"/>
       <c r="G21" s="8"/>
-      <c r="H21" s="111"/>
-      <c r="I21" s="84"/>
-      <c r="J21" s="85"/>
+      <c r="H21" s="104"/>
+      <c r="I21" s="102"/>
+      <c r="J21" s="105"/>
     </row>
     <row r="22" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A22" s="113"/>
-      <c r="B22" s="84"/>
-      <c r="C22" s="86"/>
+      <c r="A22" s="101"/>
+      <c r="B22" s="102"/>
+      <c r="C22" s="103"/>
       <c r="D22" s="7"/>
       <c r="E22" s="7"/>
       <c r="F22" s="8"/>
       <c r="G22" s="8"/>
-      <c r="H22" s="111"/>
-      <c r="I22" s="84"/>
-      <c r="J22" s="85"/>
+      <c r="H22" s="104"/>
+      <c r="I22" s="102"/>
+      <c r="J22" s="105"/>
     </row>
     <row r="23" spans="1:10" ht="19.5" customHeight="1" thickBot="1">
-      <c r="A23" s="114"/>
-      <c r="B23" s="115"/>
-      <c r="C23" s="116"/>
+      <c r="A23" s="106"/>
+      <c r="B23" s="107"/>
+      <c r="C23" s="108"/>
       <c r="D23" s="9"/>
       <c r="E23" s="9"/>
       <c r="F23" s="10"/>
       <c r="G23" s="10"/>
-      <c r="H23" s="117"/>
-      <c r="I23" s="115"/>
-      <c r="J23" s="118"/>
+      <c r="H23" s="109"/>
+      <c r="I23" s="107"/>
+      <c r="J23" s="110"/>
     </row>
     <row r="24" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="25" spans="1:10" ht="12.75" customHeight="1"/>
@@ -5392,22 +6691,6 @@
     <row r="1000" s="4" customFormat="1" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="31">
-    <mergeCell ref="A22:C22"/>
-    <mergeCell ref="H22:J22"/>
-    <mergeCell ref="A23:C23"/>
-    <mergeCell ref="H23:J23"/>
-    <mergeCell ref="A19:C19"/>
-    <mergeCell ref="H19:J19"/>
-    <mergeCell ref="A20:C20"/>
-    <mergeCell ref="H20:J20"/>
-    <mergeCell ref="A21:C21"/>
-    <mergeCell ref="H21:J21"/>
-    <mergeCell ref="A16:C16"/>
-    <mergeCell ref="H16:J16"/>
-    <mergeCell ref="A18:C18"/>
-    <mergeCell ref="H18:J18"/>
-    <mergeCell ref="A17:C17"/>
-    <mergeCell ref="H17:J17"/>
     <mergeCell ref="A14:J14"/>
     <mergeCell ref="A15:C15"/>
     <mergeCell ref="A7:J13"/>
@@ -5423,6 +6706,22 @@
     <mergeCell ref="D5:J5"/>
     <mergeCell ref="A6:J6"/>
     <mergeCell ref="D15:H15"/>
+    <mergeCell ref="A16:C16"/>
+    <mergeCell ref="H16:J16"/>
+    <mergeCell ref="A18:C18"/>
+    <mergeCell ref="H18:J18"/>
+    <mergeCell ref="A17:C17"/>
+    <mergeCell ref="H17:J17"/>
+    <mergeCell ref="A22:C22"/>
+    <mergeCell ref="H22:J22"/>
+    <mergeCell ref="A23:C23"/>
+    <mergeCell ref="H23:J23"/>
+    <mergeCell ref="A19:C19"/>
+    <mergeCell ref="H19:J19"/>
+    <mergeCell ref="A20:C20"/>
+    <mergeCell ref="H20:J20"/>
+    <mergeCell ref="A21:C21"/>
+    <mergeCell ref="H21:J21"/>
   </mergeCells>
   <phoneticPr fontId="4"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
@@ -5431,7 +6730,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F3EE704D-4986-4CB2-806F-AC50916B16CA}">
   <dimension ref="A1:J1000"/>
   <sheetFormatPr defaultColWidth="12.625" defaultRowHeight="15" customHeight="1"/>
@@ -5443,432 +6742,432 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="119" t="s">
+      <c r="A1" s="137" t="s">
         <v>86</v>
       </c>
-      <c r="B1" s="58"/>
-      <c r="C1" s="59"/>
-      <c r="D1" s="66" t="s">
+      <c r="B1" s="67"/>
+      <c r="C1" s="68"/>
+      <c r="D1" s="74" t="s">
         <v>0</v>
       </c>
-      <c r="E1" s="67"/>
-      <c r="F1" s="66" t="s">
+      <c r="E1" s="75"/>
+      <c r="F1" s="74" t="s">
         <v>1</v>
       </c>
-      <c r="G1" s="67"/>
-      <c r="H1" s="37" t="s">
+      <c r="G1" s="75"/>
+      <c r="H1" s="35" t="s">
         <v>2</v>
       </c>
       <c r="I1" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="J1" s="41" t="s">
+      <c r="J1" s="39" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="60"/>
-      <c r="B2" s="61"/>
-      <c r="C2" s="62"/>
-      <c r="D2" s="68" t="s">
+      <c r="A2" s="69"/>
+      <c r="B2" s="58"/>
+      <c r="C2" s="70"/>
+      <c r="D2" s="76" t="s">
         <v>6</v>
       </c>
-      <c r="E2" s="69"/>
-      <c r="F2" s="68" t="s">
+      <c r="E2" s="77"/>
+      <c r="F2" s="76" t="s">
         <v>7</v>
       </c>
-      <c r="G2" s="69"/>
-      <c r="H2" s="72">
+      <c r="G2" s="77"/>
+      <c r="H2" s="80">
         <v>45818</v>
       </c>
-      <c r="I2" s="75" t="s">
+      <c r="I2" s="83" t="s">
         <v>28</v>
       </c>
-      <c r="J2" s="76"/>
+      <c r="J2" s="84"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="60"/>
-      <c r="B3" s="61"/>
-      <c r="C3" s="62"/>
-      <c r="D3" s="70"/>
-      <c r="E3" s="62"/>
-      <c r="F3" s="70"/>
-      <c r="G3" s="62"/>
-      <c r="H3" s="73"/>
-      <c r="I3" s="73"/>
-      <c r="J3" s="77"/>
+      <c r="A3" s="69"/>
+      <c r="B3" s="58"/>
+      <c r="C3" s="70"/>
+      <c r="D3" s="78"/>
+      <c r="E3" s="70"/>
+      <c r="F3" s="78"/>
+      <c r="G3" s="70"/>
+      <c r="H3" s="81"/>
+      <c r="I3" s="81"/>
+      <c r="J3" s="85"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="63"/>
-      <c r="B4" s="64"/>
-      <c r="C4" s="65"/>
-      <c r="D4" s="71"/>
-      <c r="E4" s="65"/>
-      <c r="F4" s="71"/>
-      <c r="G4" s="65"/>
-      <c r="H4" s="74"/>
-      <c r="I4" s="74"/>
-      <c r="J4" s="78"/>
+      <c r="A4" s="71"/>
+      <c r="B4" s="72"/>
+      <c r="C4" s="73"/>
+      <c r="D4" s="79"/>
+      <c r="E4" s="73"/>
+      <c r="F4" s="79"/>
+      <c r="G4" s="73"/>
+      <c r="H4" s="82"/>
+      <c r="I4" s="82"/>
+      <c r="J4" s="86"/>
     </row>
     <row r="5" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A5" s="24"/>
-      <c r="B5" s="23"/>
-      <c r="C5" s="23"/>
-      <c r="D5" s="23"/>
-      <c r="E5" s="23"/>
-      <c r="F5" s="23"/>
-      <c r="G5" s="23"/>
-      <c r="H5" s="23"/>
-      <c r="I5" s="23"/>
-      <c r="J5" s="22"/>
+      <c r="A5" s="22"/>
+      <c r="B5" s="21"/>
+      <c r="C5" s="21"/>
+      <c r="D5" s="21"/>
+      <c r="E5" s="21"/>
+      <c r="F5" s="21"/>
+      <c r="G5" s="21"/>
+      <c r="H5" s="21"/>
+      <c r="I5" s="21"/>
+      <c r="J5" s="20"/>
     </row>
     <row r="6" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A6" s="24"/>
-      <c r="B6" s="23"/>
-      <c r="C6" s="23"/>
-      <c r="D6" s="23"/>
-      <c r="E6" s="23"/>
-      <c r="F6" s="23"/>
-      <c r="G6" s="23"/>
-      <c r="H6" s="23"/>
-      <c r="I6" s="23"/>
-      <c r="J6" s="22"/>
+      <c r="A6" s="22"/>
+      <c r="B6" s="21"/>
+      <c r="C6" s="21"/>
+      <c r="D6" s="21"/>
+      <c r="E6" s="21"/>
+      <c r="F6" s="21"/>
+      <c r="G6" s="21"/>
+      <c r="H6" s="21"/>
+      <c r="I6" s="21"/>
+      <c r="J6" s="20"/>
     </row>
     <row r="7" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A7" s="24"/>
-      <c r="B7" s="23"/>
-      <c r="C7" s="23"/>
-      <c r="D7" s="23"/>
-      <c r="E7" s="23"/>
-      <c r="F7" s="23"/>
-      <c r="G7" s="23"/>
-      <c r="H7" s="23"/>
-      <c r="I7" s="23"/>
-      <c r="J7" s="22"/>
+      <c r="A7" s="22"/>
+      <c r="B7" s="21"/>
+      <c r="C7" s="21"/>
+      <c r="D7" s="21"/>
+      <c r="E7" s="21"/>
+      <c r="F7" s="21"/>
+      <c r="G7" s="21"/>
+      <c r="H7" s="21"/>
+      <c r="I7" s="21"/>
+      <c r="J7" s="20"/>
     </row>
     <row r="8" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A8" s="24"/>
-      <c r="B8" s="23"/>
-      <c r="C8" s="23"/>
-      <c r="D8" s="23"/>
-      <c r="E8" s="23"/>
-      <c r="F8" s="23"/>
-      <c r="G8" s="23"/>
-      <c r="H8" s="23"/>
-      <c r="I8" s="23"/>
-      <c r="J8" s="22"/>
+      <c r="A8" s="22"/>
+      <c r="B8" s="21"/>
+      <c r="C8" s="21"/>
+      <c r="D8" s="21"/>
+      <c r="E8" s="21"/>
+      <c r="F8" s="21"/>
+      <c r="G8" s="21"/>
+      <c r="H8" s="21"/>
+      <c r="I8" s="21"/>
+      <c r="J8" s="20"/>
     </row>
     <row r="9" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A9" s="24"/>
-      <c r="B9" s="23"/>
-      <c r="C9" s="23"/>
-      <c r="D9" s="23"/>
-      <c r="E9" s="23"/>
-      <c r="F9" s="23"/>
-      <c r="G9" s="23"/>
-      <c r="H9" s="23"/>
-      <c r="I9" s="23"/>
-      <c r="J9" s="22"/>
+      <c r="A9" s="22"/>
+      <c r="B9" s="21"/>
+      <c r="C9" s="21"/>
+      <c r="D9" s="21"/>
+      <c r="E9" s="21"/>
+      <c r="F9" s="21"/>
+      <c r="G9" s="21"/>
+      <c r="H9" s="21"/>
+      <c r="I9" s="21"/>
+      <c r="J9" s="20"/>
     </row>
     <row r="10" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A10" s="24"/>
-      <c r="B10" s="23"/>
-      <c r="C10" s="23"/>
-      <c r="D10" s="23"/>
-      <c r="E10" s="23"/>
-      <c r="F10" s="23"/>
-      <c r="G10" s="23"/>
-      <c r="H10" s="23"/>
-      <c r="I10" s="23"/>
-      <c r="J10" s="22"/>
+      <c r="A10" s="22"/>
+      <c r="B10" s="21"/>
+      <c r="C10" s="21"/>
+      <c r="D10" s="21"/>
+      <c r="E10" s="21"/>
+      <c r="F10" s="21"/>
+      <c r="G10" s="21"/>
+      <c r="H10" s="21"/>
+      <c r="I10" s="21"/>
+      <c r="J10" s="20"/>
     </row>
     <row r="11" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A11" s="24"/>
-      <c r="B11" s="23"/>
-      <c r="C11" s="23"/>
-      <c r="D11" s="23"/>
-      <c r="E11" s="23"/>
-      <c r="F11" s="23"/>
-      <c r="G11" s="23"/>
-      <c r="H11" s="23"/>
-      <c r="I11" s="23"/>
-      <c r="J11" s="22"/>
+      <c r="A11" s="22"/>
+      <c r="B11" s="21"/>
+      <c r="C11" s="21"/>
+      <c r="D11" s="21"/>
+      <c r="E11" s="21"/>
+      <c r="F11" s="21"/>
+      <c r="G11" s="21"/>
+      <c r="H11" s="21"/>
+      <c r="I11" s="21"/>
+      <c r="J11" s="20"/>
     </row>
     <row r="12" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A12" s="24"/>
-      <c r="B12" s="23"/>
-      <c r="C12" s="23"/>
-      <c r="D12" s="23"/>
-      <c r="E12" s="23"/>
-      <c r="F12" s="23"/>
-      <c r="G12" s="23"/>
-      <c r="H12" s="23"/>
-      <c r="I12" s="23"/>
-      <c r="J12" s="22"/>
+      <c r="A12" s="22"/>
+      <c r="B12" s="21"/>
+      <c r="C12" s="21"/>
+      <c r="D12" s="21"/>
+      <c r="E12" s="21"/>
+      <c r="F12" s="21"/>
+      <c r="G12" s="21"/>
+      <c r="H12" s="21"/>
+      <c r="I12" s="21"/>
+      <c r="J12" s="20"/>
     </row>
     <row r="13" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A13" s="24"/>
-      <c r="B13" s="23"/>
-      <c r="C13" s="23"/>
-      <c r="D13" s="23"/>
-      <c r="E13" s="23"/>
-      <c r="F13" s="23"/>
-      <c r="G13" s="23"/>
-      <c r="H13" s="23"/>
-      <c r="I13" s="23"/>
-      <c r="J13" s="22"/>
+      <c r="A13" s="22"/>
+      <c r="B13" s="21"/>
+      <c r="C13" s="21"/>
+      <c r="D13" s="21"/>
+      <c r="E13" s="21"/>
+      <c r="F13" s="21"/>
+      <c r="G13" s="21"/>
+      <c r="H13" s="21"/>
+      <c r="I13" s="21"/>
+      <c r="J13" s="20"/>
     </row>
     <row r="14" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A14" s="24"/>
-      <c r="B14" s="23"/>
-      <c r="C14" s="23"/>
-      <c r="D14" s="23"/>
-      <c r="E14" s="23"/>
-      <c r="F14" s="23"/>
-      <c r="G14" s="23"/>
-      <c r="H14" s="23"/>
-      <c r="I14" s="23"/>
-      <c r="J14" s="22"/>
+      <c r="A14" s="22"/>
+      <c r="B14" s="21"/>
+      <c r="C14" s="21"/>
+      <c r="D14" s="21"/>
+      <c r="E14" s="21"/>
+      <c r="F14" s="21"/>
+      <c r="G14" s="21"/>
+      <c r="H14" s="21"/>
+      <c r="I14" s="21"/>
+      <c r="J14" s="20"/>
     </row>
     <row r="15" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A15" s="24"/>
-      <c r="B15" s="23"/>
-      <c r="C15" s="23"/>
-      <c r="D15" s="23"/>
-      <c r="E15" s="23"/>
-      <c r="F15" s="23"/>
-      <c r="G15" s="23"/>
-      <c r="H15" s="23"/>
-      <c r="I15" s="23"/>
-      <c r="J15" s="22"/>
+      <c r="A15" s="22"/>
+      <c r="B15" s="21"/>
+      <c r="C15" s="21"/>
+      <c r="D15" s="21"/>
+      <c r="E15" s="21"/>
+      <c r="F15" s="21"/>
+      <c r="G15" s="21"/>
+      <c r="H15" s="21"/>
+      <c r="I15" s="21"/>
+      <c r="J15" s="20"/>
     </row>
     <row r="16" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A16" s="24"/>
-      <c r="B16" s="23"/>
-      <c r="C16" s="23"/>
-      <c r="D16" s="23"/>
-      <c r="E16" s="23"/>
-      <c r="F16" s="23"/>
-      <c r="G16" s="23"/>
-      <c r="H16" s="23"/>
-      <c r="I16" s="23"/>
-      <c r="J16" s="22"/>
+      <c r="A16" s="22"/>
+      <c r="B16" s="21"/>
+      <c r="C16" s="21"/>
+      <c r="D16" s="21"/>
+      <c r="E16" s="21"/>
+      <c r="F16" s="21"/>
+      <c r="G16" s="21"/>
+      <c r="H16" s="21"/>
+      <c r="I16" s="21"/>
+      <c r="J16" s="20"/>
     </row>
     <row r="17" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A17" s="24"/>
-      <c r="B17" s="23"/>
-      <c r="C17" s="23"/>
-      <c r="D17" s="23"/>
-      <c r="E17" s="23"/>
-      <c r="F17" s="23"/>
-      <c r="G17" s="23"/>
-      <c r="H17" s="23"/>
-      <c r="I17" s="23"/>
-      <c r="J17" s="22"/>
+      <c r="A17" s="22"/>
+      <c r="B17" s="21"/>
+      <c r="C17" s="21"/>
+      <c r="D17" s="21"/>
+      <c r="E17" s="21"/>
+      <c r="F17" s="21"/>
+      <c r="G17" s="21"/>
+      <c r="H17" s="21"/>
+      <c r="I17" s="21"/>
+      <c r="J17" s="20"/>
     </row>
     <row r="18" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A18" s="24"/>
-      <c r="B18" s="23"/>
-      <c r="C18" s="23"/>
-      <c r="D18" s="23"/>
-      <c r="E18" s="23"/>
-      <c r="F18" s="23"/>
-      <c r="G18" s="23"/>
-      <c r="H18" s="23"/>
-      <c r="I18" s="23"/>
-      <c r="J18" s="22"/>
+      <c r="A18" s="22"/>
+      <c r="B18" s="21"/>
+      <c r="C18" s="21"/>
+      <c r="D18" s="21"/>
+      <c r="E18" s="21"/>
+      <c r="F18" s="21"/>
+      <c r="G18" s="21"/>
+      <c r="H18" s="21"/>
+      <c r="I18" s="21"/>
+      <c r="J18" s="20"/>
     </row>
     <row r="19" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A19" s="24"/>
-      <c r="B19" s="23"/>
-      <c r="C19" s="23"/>
-      <c r="D19" s="23"/>
-      <c r="E19" s="23"/>
-      <c r="F19" s="23"/>
-      <c r="G19" s="23"/>
-      <c r="H19" s="23"/>
-      <c r="I19" s="23"/>
-      <c r="J19" s="22"/>
+      <c r="A19" s="22"/>
+      <c r="B19" s="21"/>
+      <c r="C19" s="21"/>
+      <c r="D19" s="21"/>
+      <c r="E19" s="21"/>
+      <c r="F19" s="21"/>
+      <c r="G19" s="21"/>
+      <c r="H19" s="21"/>
+      <c r="I19" s="21"/>
+      <c r="J19" s="20"/>
     </row>
     <row r="20" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A20" s="24"/>
-      <c r="B20" s="23"/>
-      <c r="C20" s="23"/>
-      <c r="D20" s="23"/>
-      <c r="E20" s="23"/>
-      <c r="F20" s="23"/>
-      <c r="G20" s="23"/>
-      <c r="H20" s="23"/>
-      <c r="I20" s="23"/>
-      <c r="J20" s="22"/>
+      <c r="A20" s="22"/>
+      <c r="B20" s="21"/>
+      <c r="C20" s="21"/>
+      <c r="D20" s="21"/>
+      <c r="E20" s="21"/>
+      <c r="F20" s="21"/>
+      <c r="G20" s="21"/>
+      <c r="H20" s="21"/>
+      <c r="I20" s="21"/>
+      <c r="J20" s="20"/>
     </row>
     <row r="21" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A21" s="24"/>
-      <c r="B21" s="23"/>
-      <c r="C21" s="23"/>
-      <c r="D21" s="23"/>
-      <c r="E21" s="23"/>
-      <c r="F21" s="23"/>
-      <c r="G21" s="23"/>
-      <c r="H21" s="23"/>
-      <c r="I21" s="23"/>
-      <c r="J21" s="22"/>
+      <c r="A21" s="22"/>
+      <c r="B21" s="21"/>
+      <c r="C21" s="21"/>
+      <c r="D21" s="21"/>
+      <c r="E21" s="21"/>
+      <c r="F21" s="21"/>
+      <c r="G21" s="21"/>
+      <c r="H21" s="21"/>
+      <c r="I21" s="21"/>
+      <c r="J21" s="20"/>
     </row>
     <row r="22" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A22" s="24"/>
-      <c r="B22" s="23"/>
-      <c r="C22" s="23"/>
-      <c r="D22" s="23"/>
-      <c r="E22" s="23"/>
-      <c r="F22" s="23"/>
-      <c r="G22" s="23"/>
-      <c r="H22" s="23"/>
-      <c r="I22" s="23"/>
-      <c r="J22" s="22"/>
+      <c r="A22" s="22"/>
+      <c r="B22" s="21"/>
+      <c r="C22" s="21"/>
+      <c r="D22" s="21"/>
+      <c r="E22" s="21"/>
+      <c r="F22" s="21"/>
+      <c r="G22" s="21"/>
+      <c r="H22" s="21"/>
+      <c r="I22" s="21"/>
+      <c r="J22" s="20"/>
     </row>
     <row r="23" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A23" s="24"/>
-      <c r="B23" s="23"/>
-      <c r="C23" s="23"/>
-      <c r="D23" s="23"/>
-      <c r="E23" s="23"/>
-      <c r="F23" s="23"/>
-      <c r="G23" s="23"/>
-      <c r="H23" s="23"/>
-      <c r="I23" s="23"/>
-      <c r="J23" s="22"/>
+      <c r="A23" s="22"/>
+      <c r="B23" s="21"/>
+      <c r="C23" s="21"/>
+      <c r="D23" s="21"/>
+      <c r="E23" s="21"/>
+      <c r="F23" s="21"/>
+      <c r="G23" s="21"/>
+      <c r="H23" s="21"/>
+      <c r="I23" s="21"/>
+      <c r="J23" s="20"/>
     </row>
     <row r="24" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A24" s="24"/>
-      <c r="B24" s="23"/>
-      <c r="C24" s="23"/>
-      <c r="D24" s="23"/>
-      <c r="E24" s="23"/>
-      <c r="F24" s="23"/>
-      <c r="G24" s="23"/>
-      <c r="H24" s="23"/>
-      <c r="I24" s="23"/>
-      <c r="J24" s="22"/>
+      <c r="A24" s="22"/>
+      <c r="B24" s="21"/>
+      <c r="C24" s="21"/>
+      <c r="D24" s="21"/>
+      <c r="E24" s="21"/>
+      <c r="F24" s="21"/>
+      <c r="G24" s="21"/>
+      <c r="H24" s="21"/>
+      <c r="I24" s="21"/>
+      <c r="J24" s="20"/>
     </row>
     <row r="25" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A25" s="24"/>
-      <c r="B25" s="23"/>
-      <c r="C25" s="23"/>
-      <c r="D25" s="23"/>
-      <c r="E25" s="23"/>
-      <c r="F25" s="23"/>
-      <c r="G25" s="23"/>
-      <c r="H25" s="23"/>
-      <c r="I25" s="23"/>
-      <c r="J25" s="22"/>
+      <c r="A25" s="22"/>
+      <c r="B25" s="21"/>
+      <c r="C25" s="21"/>
+      <c r="D25" s="21"/>
+      <c r="E25" s="21"/>
+      <c r="F25" s="21"/>
+      <c r="G25" s="21"/>
+      <c r="H25" s="21"/>
+      <c r="I25" s="21"/>
+      <c r="J25" s="20"/>
     </row>
     <row r="26" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A26" s="24"/>
-      <c r="B26" s="23"/>
-      <c r="C26" s="23"/>
-      <c r="D26" s="23"/>
-      <c r="E26" s="23"/>
-      <c r="F26" s="23"/>
-      <c r="G26" s="23"/>
-      <c r="H26" s="23"/>
-      <c r="I26" s="23"/>
-      <c r="J26" s="22"/>
+      <c r="A26" s="22"/>
+      <c r="B26" s="21"/>
+      <c r="C26" s="21"/>
+      <c r="D26" s="21"/>
+      <c r="E26" s="21"/>
+      <c r="F26" s="21"/>
+      <c r="G26" s="21"/>
+      <c r="H26" s="21"/>
+      <c r="I26" s="21"/>
+      <c r="J26" s="20"/>
     </row>
     <row r="27" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A27" s="24"/>
-      <c r="B27" s="23"/>
-      <c r="C27" s="23"/>
-      <c r="D27" s="23"/>
-      <c r="E27" s="23"/>
-      <c r="F27" s="23"/>
-      <c r="G27" s="23"/>
-      <c r="H27" s="23"/>
-      <c r="I27" s="23"/>
-      <c r="J27" s="22"/>
+      <c r="A27" s="22"/>
+      <c r="B27" s="21"/>
+      <c r="C27" s="21"/>
+      <c r="D27" s="21"/>
+      <c r="E27" s="21"/>
+      <c r="F27" s="21"/>
+      <c r="G27" s="21"/>
+      <c r="H27" s="21"/>
+      <c r="I27" s="21"/>
+      <c r="J27" s="20"/>
     </row>
     <row r="28" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A28" s="24"/>
-      <c r="B28" s="23"/>
-      <c r="C28" s="23"/>
-      <c r="D28" s="23"/>
-      <c r="E28" s="23"/>
-      <c r="F28" s="23"/>
-      <c r="G28" s="23"/>
-      <c r="H28" s="23"/>
-      <c r="I28" s="23"/>
-      <c r="J28" s="22"/>
+      <c r="A28" s="22"/>
+      <c r="B28" s="21"/>
+      <c r="C28" s="21"/>
+      <c r="D28" s="21"/>
+      <c r="E28" s="21"/>
+      <c r="F28" s="21"/>
+      <c r="G28" s="21"/>
+      <c r="H28" s="21"/>
+      <c r="I28" s="21"/>
+      <c r="J28" s="20"/>
     </row>
     <row r="29" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A29" s="24"/>
-      <c r="B29" s="23"/>
-      <c r="C29" s="23"/>
-      <c r="D29" s="23"/>
-      <c r="E29" s="23"/>
-      <c r="F29" s="23"/>
-      <c r="G29" s="23"/>
-      <c r="H29" s="23"/>
-      <c r="I29" s="23"/>
-      <c r="J29" s="22"/>
+      <c r="A29" s="22"/>
+      <c r="B29" s="21"/>
+      <c r="C29" s="21"/>
+      <c r="D29" s="21"/>
+      <c r="E29" s="21"/>
+      <c r="F29" s="21"/>
+      <c r="G29" s="21"/>
+      <c r="H29" s="21"/>
+      <c r="I29" s="21"/>
+      <c r="J29" s="20"/>
     </row>
     <row r="30" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A30" s="24"/>
-      <c r="B30" s="23"/>
-      <c r="C30" s="23"/>
-      <c r="D30" s="23"/>
-      <c r="E30" s="23"/>
-      <c r="F30" s="23"/>
-      <c r="G30" s="23"/>
-      <c r="H30" s="23"/>
-      <c r="I30" s="23"/>
-      <c r="J30" s="22"/>
+      <c r="A30" s="22"/>
+      <c r="B30" s="21"/>
+      <c r="C30" s="21"/>
+      <c r="D30" s="21"/>
+      <c r="E30" s="21"/>
+      <c r="F30" s="21"/>
+      <c r="G30" s="21"/>
+      <c r="H30" s="21"/>
+      <c r="I30" s="21"/>
+      <c r="J30" s="20"/>
     </row>
     <row r="31" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A31" s="24"/>
-      <c r="B31" s="23"/>
-      <c r="C31" s="23"/>
-      <c r="D31" s="23"/>
-      <c r="E31" s="23"/>
-      <c r="F31" s="23"/>
-      <c r="G31" s="23"/>
-      <c r="H31" s="23"/>
-      <c r="I31" s="23"/>
-      <c r="J31" s="22"/>
+      <c r="A31" s="22"/>
+      <c r="B31" s="21"/>
+      <c r="C31" s="21"/>
+      <c r="D31" s="21"/>
+      <c r="E31" s="21"/>
+      <c r="F31" s="21"/>
+      <c r="G31" s="21"/>
+      <c r="H31" s="21"/>
+      <c r="I31" s="21"/>
+      <c r="J31" s="20"/>
     </row>
     <row r="32" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A32" s="24"/>
-      <c r="B32" s="23"/>
-      <c r="C32" s="23"/>
-      <c r="D32" s="23"/>
-      <c r="E32" s="23"/>
-      <c r="F32" s="23"/>
-      <c r="G32" s="23"/>
-      <c r="H32" s="23"/>
-      <c r="I32" s="23"/>
-      <c r="J32" s="22"/>
+      <c r="A32" s="22"/>
+      <c r="B32" s="21"/>
+      <c r="C32" s="21"/>
+      <c r="D32" s="21"/>
+      <c r="E32" s="21"/>
+      <c r="F32" s="21"/>
+      <c r="G32" s="21"/>
+      <c r="H32" s="21"/>
+      <c r="I32" s="21"/>
+      <c r="J32" s="20"/>
     </row>
     <row r="33" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A33" s="24"/>
-      <c r="B33" s="23"/>
-      <c r="C33" s="23"/>
-      <c r="D33" s="23"/>
-      <c r="E33" s="23"/>
-      <c r="F33" s="23"/>
-      <c r="G33" s="23"/>
-      <c r="H33" s="23"/>
-      <c r="I33" s="23"/>
-      <c r="J33" s="22"/>
+      <c r="A33" s="22"/>
+      <c r="B33" s="21"/>
+      <c r="C33" s="21"/>
+      <c r="D33" s="21"/>
+      <c r="E33" s="21"/>
+      <c r="F33" s="21"/>
+      <c r="G33" s="21"/>
+      <c r="H33" s="21"/>
+      <c r="I33" s="21"/>
+      <c r="J33" s="20"/>
     </row>
     <row r="34" spans="1:10" ht="12.75" customHeight="1" thickBot="1">
-      <c r="A34" s="40"/>
-      <c r="B34" s="39"/>
-      <c r="C34" s="39"/>
-      <c r="D34" s="39"/>
-      <c r="E34" s="39"/>
-      <c r="F34" s="39"/>
-      <c r="G34" s="39"/>
-      <c r="H34" s="39"/>
-      <c r="I34" s="39"/>
-      <c r="J34" s="38"/>
+      <c r="A34" s="38"/>
+      <c r="B34" s="37"/>
+      <c r="C34" s="37"/>
+      <c r="D34" s="37"/>
+      <c r="E34" s="37"/>
+      <c r="F34" s="37"/>
+      <c r="G34" s="37"/>
+      <c r="H34" s="37"/>
+      <c r="I34" s="37"/>
+      <c r="J34" s="36"/>
     </row>
     <row r="35" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="36" spans="1:10" ht="12.75" customHeight="1"/>
@@ -6854,7 +8153,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4B2F631B-71E1-442C-9AE2-53D543A90339}">
   <dimension ref="A1:Z1000"/>
   <sheetFormatPr defaultColWidth="12.625" defaultRowHeight="15" customHeight="1"/>
@@ -6869,468 +8168,468 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="18" customHeight="1">
-      <c r="A1" s="57" t="s">
+      <c r="A1" s="66" t="s">
         <v>67</v>
       </c>
-      <c r="B1" s="58"/>
-      <c r="C1" s="58"/>
-      <c r="D1" s="58"/>
-      <c r="E1" s="58"/>
-      <c r="F1" s="59"/>
-      <c r="G1" s="66" t="s">
+      <c r="B1" s="67"/>
+      <c r="C1" s="67"/>
+      <c r="D1" s="67"/>
+      <c r="E1" s="67"/>
+      <c r="F1" s="68"/>
+      <c r="G1" s="74" t="s">
         <v>0</v>
       </c>
-      <c r="H1" s="80"/>
-      <c r="I1" s="80"/>
-      <c r="J1" s="67"/>
-      <c r="K1" s="66" t="s">
+      <c r="H1" s="88"/>
+      <c r="I1" s="88"/>
+      <c r="J1" s="75"/>
+      <c r="K1" s="74" t="s">
         <v>1</v>
       </c>
-      <c r="L1" s="80"/>
-      <c r="M1" s="80"/>
-      <c r="N1" s="67"/>
-      <c r="O1" s="66" t="s">
+      <c r="L1" s="88"/>
+      <c r="M1" s="88"/>
+      <c r="N1" s="75"/>
+      <c r="O1" s="74" t="s">
         <v>2</v>
       </c>
-      <c r="P1" s="67"/>
-      <c r="Q1" s="66" t="s">
+      <c r="P1" s="75"/>
+      <c r="Q1" s="74" t="s">
         <v>3</v>
       </c>
-      <c r="R1" s="67"/>
-      <c r="S1" s="66" t="s">
+      <c r="R1" s="75"/>
+      <c r="S1" s="74" t="s">
         <v>4</v>
       </c>
-      <c r="T1" s="82"/>
+      <c r="T1" s="90"/>
     </row>
     <row r="2" spans="1:26" ht="18" customHeight="1">
-      <c r="A2" s="60"/>
-      <c r="B2" s="61"/>
-      <c r="C2" s="61"/>
-      <c r="D2" s="61"/>
-      <c r="E2" s="61"/>
-      <c r="F2" s="62"/>
-      <c r="G2" s="68" t="s">
+      <c r="A2" s="69"/>
+      <c r="B2" s="58"/>
+      <c r="C2" s="58"/>
+      <c r="D2" s="58"/>
+      <c r="E2" s="58"/>
+      <c r="F2" s="70"/>
+      <c r="G2" s="76" t="s">
         <v>6</v>
       </c>
-      <c r="H2" s="131"/>
-      <c r="I2" s="131"/>
-      <c r="J2" s="69"/>
-      <c r="K2" s="68" t="s">
+      <c r="H2" s="140"/>
+      <c r="I2" s="140"/>
+      <c r="J2" s="77"/>
+      <c r="K2" s="76" t="s">
         <v>7</v>
       </c>
-      <c r="L2" s="131"/>
-      <c r="M2" s="131"/>
-      <c r="N2" s="69"/>
-      <c r="O2" s="132">
+      <c r="L2" s="140"/>
+      <c r="M2" s="140"/>
+      <c r="N2" s="77"/>
+      <c r="O2" s="144">
         <v>45810</v>
       </c>
-      <c r="P2" s="69"/>
-      <c r="Q2" s="68" t="s">
+      <c r="P2" s="77"/>
+      <c r="Q2" s="76" t="s">
         <v>28</v>
       </c>
-      <c r="R2" s="69"/>
-      <c r="S2" s="68"/>
-      <c r="T2" s="133"/>
+      <c r="R2" s="77"/>
+      <c r="S2" s="76"/>
+      <c r="T2" s="145"/>
     </row>
     <row r="3" spans="1:26" ht="18" customHeight="1">
-      <c r="A3" s="60"/>
-      <c r="B3" s="61"/>
-      <c r="C3" s="61"/>
-      <c r="D3" s="61"/>
-      <c r="E3" s="61"/>
-      <c r="F3" s="62"/>
-      <c r="G3" s="70"/>
-      <c r="H3" s="61"/>
-      <c r="I3" s="61"/>
-      <c r="J3" s="62"/>
-      <c r="K3" s="70"/>
-      <c r="L3" s="61"/>
-      <c r="M3" s="61"/>
-      <c r="N3" s="62"/>
-      <c r="O3" s="70"/>
-      <c r="P3" s="62"/>
-      <c r="Q3" s="70"/>
-      <c r="R3" s="62"/>
-      <c r="S3" s="70"/>
-      <c r="T3" s="134"/>
+      <c r="A3" s="69"/>
+      <c r="B3" s="58"/>
+      <c r="C3" s="58"/>
+      <c r="D3" s="58"/>
+      <c r="E3" s="58"/>
+      <c r="F3" s="70"/>
+      <c r="G3" s="78"/>
+      <c r="H3" s="58"/>
+      <c r="I3" s="58"/>
+      <c r="J3" s="70"/>
+      <c r="K3" s="78"/>
+      <c r="L3" s="58"/>
+      <c r="M3" s="58"/>
+      <c r="N3" s="70"/>
+      <c r="O3" s="78"/>
+      <c r="P3" s="70"/>
+      <c r="Q3" s="78"/>
+      <c r="R3" s="70"/>
+      <c r="S3" s="78"/>
+      <c r="T3" s="146"/>
     </row>
     <row r="4" spans="1:26" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="63"/>
-      <c r="B4" s="64"/>
-      <c r="C4" s="64"/>
-      <c r="D4" s="64"/>
-      <c r="E4" s="64"/>
-      <c r="F4" s="65"/>
-      <c r="G4" s="71"/>
-      <c r="H4" s="64"/>
-      <c r="I4" s="64"/>
-      <c r="J4" s="65"/>
-      <c r="K4" s="71"/>
-      <c r="L4" s="64"/>
-      <c r="M4" s="64"/>
-      <c r="N4" s="65"/>
-      <c r="O4" s="71"/>
-      <c r="P4" s="65"/>
-      <c r="Q4" s="71"/>
-      <c r="R4" s="65"/>
-      <c r="S4" s="71"/>
-      <c r="T4" s="135"/>
+      <c r="A4" s="71"/>
+      <c r="B4" s="72"/>
+      <c r="C4" s="72"/>
+      <c r="D4" s="72"/>
+      <c r="E4" s="72"/>
+      <c r="F4" s="73"/>
+      <c r="G4" s="79"/>
+      <c r="H4" s="72"/>
+      <c r="I4" s="72"/>
+      <c r="J4" s="73"/>
+      <c r="K4" s="79"/>
+      <c r="L4" s="72"/>
+      <c r="M4" s="72"/>
+      <c r="N4" s="73"/>
+      <c r="O4" s="79"/>
+      <c r="P4" s="73"/>
+      <c r="Q4" s="79"/>
+      <c r="R4" s="73"/>
+      <c r="S4" s="79"/>
+      <c r="T4" s="147"/>
     </row>
     <row r="5" spans="1:26" ht="18" customHeight="1">
-      <c r="A5" s="130" t="s">
+      <c r="A5" s="142" t="s">
         <v>66</v>
       </c>
-      <c r="B5" s="80"/>
-      <c r="C5" s="80"/>
-      <c r="D5" s="80"/>
-      <c r="E5" s="80"/>
-      <c r="F5" s="67"/>
-      <c r="G5" s="81" t="s">
+      <c r="B5" s="88"/>
+      <c r="C5" s="88"/>
+      <c r="D5" s="88"/>
+      <c r="E5" s="88"/>
+      <c r="F5" s="75"/>
+      <c r="G5" s="89" t="s">
         <v>65</v>
       </c>
-      <c r="H5" s="80"/>
-      <c r="I5" s="80"/>
-      <c r="J5" s="80"/>
-      <c r="K5" s="80"/>
-      <c r="L5" s="80"/>
-      <c r="M5" s="80"/>
-      <c r="N5" s="80"/>
-      <c r="O5" s="80"/>
-      <c r="P5" s="80"/>
-      <c r="Q5" s="80"/>
-      <c r="R5" s="80"/>
-      <c r="S5" s="80"/>
-      <c r="T5" s="82"/>
+      <c r="H5" s="88"/>
+      <c r="I5" s="88"/>
+      <c r="J5" s="88"/>
+      <c r="K5" s="88"/>
+      <c r="L5" s="88"/>
+      <c r="M5" s="88"/>
+      <c r="N5" s="88"/>
+      <c r="O5" s="88"/>
+      <c r="P5" s="88"/>
+      <c r="Q5" s="88"/>
+      <c r="R5" s="88"/>
+      <c r="S5" s="88"/>
+      <c r="T5" s="90"/>
     </row>
     <row r="6" spans="1:26" ht="18" customHeight="1">
-      <c r="A6" s="128" t="s">
+      <c r="A6" s="143" t="s">
         <v>64</v>
       </c>
-      <c r="B6" s="43"/>
-      <c r="C6" s="43"/>
-      <c r="D6" s="43"/>
-      <c r="E6" s="43"/>
-      <c r="F6" s="44"/>
-      <c r="G6" s="45" t="s">
+      <c r="B6" s="56"/>
+      <c r="C6" s="56"/>
+      <c r="D6" s="56"/>
+      <c r="E6" s="56"/>
+      <c r="F6" s="55"/>
+      <c r="G6" s="64" t="s">
         <v>80</v>
       </c>
-      <c r="H6" s="43"/>
-      <c r="I6" s="43"/>
-      <c r="J6" s="43"/>
-      <c r="K6" s="43"/>
-      <c r="L6" s="43"/>
-      <c r="M6" s="43"/>
-      <c r="N6" s="43"/>
-      <c r="O6" s="43"/>
-      <c r="P6" s="43"/>
-      <c r="Q6" s="43"/>
-      <c r="R6" s="43"/>
-      <c r="S6" s="43"/>
-      <c r="T6" s="46"/>
+      <c r="H6" s="56"/>
+      <c r="I6" s="56"/>
+      <c r="J6" s="56"/>
+      <c r="K6" s="56"/>
+      <c r="L6" s="56"/>
+      <c r="M6" s="56"/>
+      <c r="N6" s="56"/>
+      <c r="O6" s="56"/>
+      <c r="P6" s="56"/>
+      <c r="Q6" s="56"/>
+      <c r="R6" s="56"/>
+      <c r="S6" s="56"/>
+      <c r="T6" s="65"/>
     </row>
     <row r="7" spans="1:26" ht="18" customHeight="1">
-      <c r="A7" s="128" t="s">
+      <c r="A7" s="143" t="s">
         <v>63</v>
       </c>
-      <c r="B7" s="43"/>
-      <c r="C7" s="43"/>
-      <c r="D7" s="43"/>
-      <c r="E7" s="43"/>
-      <c r="F7" s="44"/>
-      <c r="G7" s="45" t="s">
+      <c r="B7" s="56"/>
+      <c r="C7" s="56"/>
+      <c r="D7" s="56"/>
+      <c r="E7" s="56"/>
+      <c r="F7" s="55"/>
+      <c r="G7" s="64" t="s">
         <v>79</v>
       </c>
-      <c r="H7" s="43"/>
-      <c r="I7" s="43"/>
-      <c r="J7" s="43"/>
-      <c r="K7" s="43"/>
-      <c r="L7" s="43"/>
-      <c r="M7" s="43"/>
-      <c r="N7" s="43"/>
-      <c r="O7" s="43"/>
-      <c r="P7" s="43"/>
-      <c r="Q7" s="43"/>
-      <c r="R7" s="43"/>
-      <c r="S7" s="43"/>
-      <c r="T7" s="46"/>
+      <c r="H7" s="56"/>
+      <c r="I7" s="56"/>
+      <c r="J7" s="56"/>
+      <c r="K7" s="56"/>
+      <c r="L7" s="56"/>
+      <c r="M7" s="56"/>
+      <c r="N7" s="56"/>
+      <c r="O7" s="56"/>
+      <c r="P7" s="56"/>
+      <c r="Q7" s="56"/>
+      <c r="R7" s="56"/>
+      <c r="S7" s="56"/>
+      <c r="T7" s="65"/>
     </row>
     <row r="8" spans="1:26" ht="7.5" customHeight="1">
-      <c r="A8" s="24"/>
-      <c r="B8" s="23"/>
-      <c r="C8" s="23"/>
-      <c r="D8" s="23"/>
-      <c r="E8" s="23"/>
-      <c r="F8" s="23"/>
-      <c r="G8" s="23"/>
-      <c r="H8" s="23"/>
-      <c r="I8" s="23"/>
-      <c r="J8" s="23"/>
-      <c r="K8" s="23"/>
-      <c r="L8" s="23"/>
-      <c r="M8" s="23"/>
-      <c r="N8" s="23"/>
-      <c r="O8" s="23"/>
-      <c r="P8" s="23"/>
-      <c r="Q8" s="23"/>
-      <c r="R8" s="23"/>
-      <c r="S8" s="23"/>
-      <c r="T8" s="22"/>
+      <c r="A8" s="22"/>
+      <c r="B8" s="21"/>
+      <c r="C8" s="21"/>
+      <c r="D8" s="21"/>
+      <c r="E8" s="21"/>
+      <c r="F8" s="21"/>
+      <c r="G8" s="21"/>
+      <c r="H8" s="21"/>
+      <c r="I8" s="21"/>
+      <c r="J8" s="21"/>
+      <c r="K8" s="21"/>
+      <c r="L8" s="21"/>
+      <c r="M8" s="21"/>
+      <c r="N8" s="21"/>
+      <c r="O8" s="21"/>
+      <c r="P8" s="21"/>
+      <c r="Q8" s="21"/>
+      <c r="R8" s="21"/>
+      <c r="S8" s="21"/>
+      <c r="T8" s="20"/>
     </row>
     <row r="9" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A9" s="30"/>
-      <c r="B9" s="25"/>
-      <c r="C9" s="35" t="s">
+      <c r="A9" s="28"/>
+      <c r="B9" s="23"/>
+      <c r="C9" s="33" t="s">
         <v>56</v>
       </c>
-      <c r="D9" s="34"/>
-      <c r="E9" s="34" t="s">
+      <c r="D9" s="32"/>
+      <c r="E9" s="32" t="s">
         <v>62</v>
       </c>
-      <c r="F9" s="34"/>
-      <c r="G9" s="33"/>
-      <c r="H9" s="34"/>
-      <c r="I9" s="34"/>
-      <c r="J9" s="34"/>
-      <c r="K9" s="33"/>
-      <c r="L9" s="25"/>
-      <c r="M9" s="25"/>
-      <c r="N9" s="25"/>
-      <c r="O9" s="25"/>
-      <c r="P9" s="25"/>
-      <c r="Q9" s="25"/>
-      <c r="R9" s="25"/>
-      <c r="S9" s="25"/>
-      <c r="T9" s="26"/>
-      <c r="U9" s="25"/>
-      <c r="V9" s="25"/>
-      <c r="W9" s="25"/>
-      <c r="X9" s="25"/>
-      <c r="Y9" s="25"/>
-      <c r="Z9" s="25"/>
+      <c r="F9" s="32"/>
+      <c r="G9" s="31"/>
+      <c r="H9" s="32"/>
+      <c r="I9" s="32"/>
+      <c r="J9" s="32"/>
+      <c r="K9" s="31"/>
+      <c r="L9" s="23"/>
+      <c r="M9" s="23"/>
+      <c r="N9" s="23"/>
+      <c r="O9" s="23"/>
+      <c r="P9" s="23"/>
+      <c r="Q9" s="23"/>
+      <c r="R9" s="23"/>
+      <c r="S9" s="23"/>
+      <c r="T9" s="24"/>
+      <c r="U9" s="23"/>
+      <c r="V9" s="23"/>
+      <c r="W9" s="23"/>
+      <c r="X9" s="23"/>
+      <c r="Y9" s="23"/>
+      <c r="Z9" s="23"/>
     </row>
     <row r="10" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A10" s="30"/>
-      <c r="B10" s="25"/>
-      <c r="C10" s="32"/>
-      <c r="D10" s="25"/>
-      <c r="E10" s="25" t="s">
+      <c r="A10" s="28"/>
+      <c r="B10" s="23"/>
+      <c r="C10" s="30"/>
+      <c r="D10" s="23"/>
+      <c r="E10" s="23" t="s">
         <v>61</v>
       </c>
-      <c r="F10" s="25"/>
-      <c r="G10" s="31"/>
-      <c r="H10" s="25"/>
-      <c r="I10" s="25"/>
-      <c r="J10" s="25"/>
-      <c r="K10" s="31"/>
-      <c r="L10" s="25"/>
-      <c r="M10" s="25"/>
-      <c r="N10" s="25"/>
-      <c r="O10" s="25"/>
-      <c r="P10" s="25"/>
-      <c r="Q10" s="25"/>
-      <c r="R10" s="25"/>
-      <c r="S10" s="25"/>
-      <c r="T10" s="26"/>
-      <c r="U10" s="25"/>
-      <c r="V10" s="25"/>
-      <c r="W10" s="25"/>
-      <c r="X10" s="25"/>
-      <c r="Y10" s="25"/>
-      <c r="Z10" s="25"/>
+      <c r="F10" s="23"/>
+      <c r="G10" s="29"/>
+      <c r="H10" s="23"/>
+      <c r="I10" s="23"/>
+      <c r="J10" s="23"/>
+      <c r="K10" s="29"/>
+      <c r="L10" s="23"/>
+      <c r="M10" s="23"/>
+      <c r="N10" s="23"/>
+      <c r="O10" s="23"/>
+      <c r="P10" s="23"/>
+      <c r="Q10" s="23"/>
+      <c r="R10" s="23"/>
+      <c r="S10" s="23"/>
+      <c r="T10" s="24"/>
+      <c r="U10" s="23"/>
+      <c r="V10" s="23"/>
+      <c r="W10" s="23"/>
+      <c r="X10" s="23"/>
+      <c r="Y10" s="23"/>
+      <c r="Z10" s="23"/>
     </row>
     <row r="11" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A11" s="30"/>
-      <c r="B11" s="25"/>
-      <c r="C11" s="32"/>
-      <c r="D11" s="25"/>
-      <c r="E11" s="25" t="s">
+      <c r="A11" s="28"/>
+      <c r="B11" s="23"/>
+      <c r="C11" s="30"/>
+      <c r="D11" s="23"/>
+      <c r="E11" s="23" t="s">
         <v>60</v>
       </c>
-      <c r="F11" s="25"/>
-      <c r="G11" s="31"/>
-      <c r="H11" s="25"/>
-      <c r="I11" s="25"/>
-      <c r="J11" s="25"/>
-      <c r="K11" s="31"/>
-      <c r="L11" s="25"/>
-      <c r="M11" s="25"/>
-      <c r="N11" s="25"/>
-      <c r="O11" s="25"/>
-      <c r="P11" s="25"/>
-      <c r="Q11" s="25"/>
-      <c r="R11" s="25"/>
-      <c r="S11" s="25"/>
-      <c r="T11" s="26"/>
-      <c r="U11" s="25"/>
-      <c r="V11" s="25"/>
-      <c r="W11" s="25"/>
-      <c r="X11" s="25"/>
-      <c r="Y11" s="25"/>
-      <c r="Z11" s="25"/>
+      <c r="F11" s="23"/>
+      <c r="G11" s="29"/>
+      <c r="H11" s="23"/>
+      <c r="I11" s="23"/>
+      <c r="J11" s="23"/>
+      <c r="K11" s="29"/>
+      <c r="L11" s="23"/>
+      <c r="M11" s="23"/>
+      <c r="N11" s="23"/>
+      <c r="O11" s="23"/>
+      <c r="P11" s="23"/>
+      <c r="Q11" s="23"/>
+      <c r="R11" s="23"/>
+      <c r="S11" s="23"/>
+      <c r="T11" s="24"/>
+      <c r="U11" s="23"/>
+      <c r="V11" s="23"/>
+      <c r="W11" s="23"/>
+      <c r="X11" s="23"/>
+      <c r="Y11" s="23"/>
+      <c r="Z11" s="23"/>
     </row>
     <row r="12" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A12" s="30"/>
-      <c r="B12" s="25"/>
-      <c r="C12" s="32"/>
-      <c r="D12" s="25"/>
-      <c r="E12" s="25" t="s">
+      <c r="A12" s="28"/>
+      <c r="B12" s="23"/>
+      <c r="C12" s="30"/>
+      <c r="D12" s="23"/>
+      <c r="E12" s="23" t="s">
         <v>59</v>
       </c>
-      <c r="F12" s="25"/>
-      <c r="G12" s="31"/>
-      <c r="H12" s="25"/>
-      <c r="I12" s="25"/>
-      <c r="J12" s="25"/>
-      <c r="K12" s="31"/>
-      <c r="L12" s="25"/>
-      <c r="M12" s="25"/>
-      <c r="N12" s="25"/>
-      <c r="O12" s="25"/>
-      <c r="P12" s="25"/>
-      <c r="Q12" s="25"/>
-      <c r="R12" s="25"/>
-      <c r="S12" s="25"/>
-      <c r="T12" s="26"/>
-      <c r="U12" s="25"/>
-      <c r="V12" s="25"/>
-      <c r="W12" s="25"/>
-      <c r="X12" s="25"/>
-      <c r="Y12" s="25"/>
-      <c r="Z12" s="25"/>
+      <c r="F12" s="23"/>
+      <c r="G12" s="29"/>
+      <c r="H12" s="23"/>
+      <c r="I12" s="23"/>
+      <c r="J12" s="23"/>
+      <c r="K12" s="29"/>
+      <c r="L12" s="23"/>
+      <c r="M12" s="23"/>
+      <c r="N12" s="23"/>
+      <c r="O12" s="23"/>
+      <c r="P12" s="23"/>
+      <c r="Q12" s="23"/>
+      <c r="R12" s="23"/>
+      <c r="S12" s="23"/>
+      <c r="T12" s="24"/>
+      <c r="U12" s="23"/>
+      <c r="V12" s="23"/>
+      <c r="W12" s="23"/>
+      <c r="X12" s="23"/>
+      <c r="Y12" s="23"/>
+      <c r="Z12" s="23"/>
     </row>
     <row r="13" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A13" s="30"/>
-      <c r="B13" s="25"/>
-      <c r="C13" s="29"/>
-      <c r="D13" s="28"/>
-      <c r="E13" s="28" t="s">
+      <c r="A13" s="28"/>
+      <c r="B13" s="23"/>
+      <c r="C13" s="27"/>
+      <c r="D13" s="26"/>
+      <c r="E13" s="26" t="s">
         <v>58</v>
       </c>
-      <c r="F13" s="28"/>
-      <c r="G13" s="27"/>
-      <c r="H13" s="28"/>
-      <c r="I13" s="28"/>
-      <c r="J13" s="28"/>
-      <c r="K13" s="27"/>
-      <c r="L13" s="25"/>
-      <c r="M13" s="25"/>
-      <c r="N13" s="25"/>
-      <c r="O13" s="25"/>
-      <c r="P13" s="25"/>
-      <c r="Q13" s="25"/>
-      <c r="R13" s="25"/>
-      <c r="S13" s="25"/>
-      <c r="T13" s="26"/>
-      <c r="U13" s="25"/>
-      <c r="V13" s="25"/>
-      <c r="W13" s="25"/>
-      <c r="X13" s="25"/>
-      <c r="Y13" s="25"/>
-      <c r="Z13" s="25"/>
+      <c r="F13" s="26"/>
+      <c r="G13" s="25"/>
+      <c r="H13" s="26"/>
+      <c r="I13" s="26"/>
+      <c r="J13" s="26"/>
+      <c r="K13" s="25"/>
+      <c r="L13" s="23"/>
+      <c r="M13" s="23"/>
+      <c r="N13" s="23"/>
+      <c r="O13" s="23"/>
+      <c r="P13" s="23"/>
+      <c r="Q13" s="23"/>
+      <c r="R13" s="23"/>
+      <c r="S13" s="23"/>
+      <c r="T13" s="24"/>
+      <c r="U13" s="23"/>
+      <c r="V13" s="23"/>
+      <c r="W13" s="23"/>
+      <c r="X13" s="23"/>
+      <c r="Y13" s="23"/>
+      <c r="Z13" s="23"/>
     </row>
     <row r="14" spans="1:26" ht="8.25" customHeight="1">
-      <c r="A14" s="24"/>
-      <c r="B14" s="23"/>
-      <c r="C14" s="23"/>
-      <c r="D14" s="23"/>
-      <c r="E14" s="23"/>
-      <c r="F14" s="23"/>
-      <c r="G14" s="23"/>
-      <c r="H14" s="23"/>
-      <c r="I14" s="23"/>
-      <c r="J14" s="23"/>
-      <c r="K14" s="23"/>
-      <c r="L14" s="23"/>
-      <c r="M14" s="23"/>
-      <c r="N14" s="23"/>
-      <c r="O14" s="23"/>
-      <c r="P14" s="23"/>
-      <c r="Q14" s="23"/>
-      <c r="R14" s="23"/>
-      <c r="S14" s="23"/>
-      <c r="T14" s="22"/>
+      <c r="A14" s="22"/>
+      <c r="B14" s="21"/>
+      <c r="C14" s="21"/>
+      <c r="D14" s="21"/>
+      <c r="E14" s="21"/>
+      <c r="F14" s="21"/>
+      <c r="G14" s="21"/>
+      <c r="H14" s="21"/>
+      <c r="I14" s="21"/>
+      <c r="J14" s="21"/>
+      <c r="K14" s="21"/>
+      <c r="L14" s="21"/>
+      <c r="M14" s="21"/>
+      <c r="N14" s="21"/>
+      <c r="O14" s="21"/>
+      <c r="P14" s="21"/>
+      <c r="Q14" s="21"/>
+      <c r="R14" s="21"/>
+      <c r="S14" s="21"/>
+      <c r="T14" s="20"/>
     </row>
     <row r="15" spans="1:26" ht="18.75" customHeight="1">
-      <c r="A15" s="128" t="s">
+      <c r="A15" s="143" t="s">
         <v>57</v>
       </c>
-      <c r="B15" s="44"/>
-      <c r="C15" s="129" t="s">
+      <c r="B15" s="55"/>
+      <c r="C15" s="150" t="s">
         <v>56</v>
       </c>
-      <c r="D15" s="44"/>
-      <c r="E15" s="127" t="s">
+      <c r="D15" s="55"/>
+      <c r="E15" s="141" t="s">
         <v>55</v>
       </c>
-      <c r="F15" s="44"/>
-      <c r="G15" s="127" t="s">
+      <c r="F15" s="55"/>
+      <c r="G15" s="141" t="s">
         <v>54</v>
       </c>
-      <c r="H15" s="43"/>
-      <c r="I15" s="44"/>
-      <c r="J15" s="127" t="s">
+      <c r="H15" s="56"/>
+      <c r="I15" s="55"/>
+      <c r="J15" s="141" t="s">
         <v>53</v>
       </c>
-      <c r="K15" s="44"/>
-      <c r="L15" s="127" t="s">
+      <c r="K15" s="55"/>
+      <c r="L15" s="141" t="s">
         <v>52</v>
       </c>
-      <c r="M15" s="43"/>
-      <c r="N15" s="44"/>
-      <c r="O15" s="127" t="s">
+      <c r="M15" s="56"/>
+      <c r="N15" s="55"/>
+      <c r="O15" s="141" t="s">
         <v>51</v>
       </c>
-      <c r="P15" s="43"/>
-      <c r="Q15" s="44"/>
-      <c r="R15" s="21" t="s">
+      <c r="P15" s="56"/>
+      <c r="Q15" s="55"/>
+      <c r="R15" s="19" t="s">
         <v>50</v>
       </c>
-      <c r="S15" s="21" t="s">
+      <c r="S15" s="19" t="s">
         <v>49</v>
       </c>
-      <c r="T15" s="20" t="s">
+      <c r="T15" s="18" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="16" spans="1:26" ht="48" customHeight="1">
-      <c r="A16" s="120">
+      <c r="A16" s="148">
         <v>1</v>
       </c>
-      <c r="B16" s="44"/>
-      <c r="C16" s="121" t="s">
+      <c r="B16" s="55"/>
+      <c r="C16" s="149" t="s">
         <v>47</v>
       </c>
-      <c r="D16" s="44"/>
-      <c r="E16" s="121" t="s">
+      <c r="D16" s="55"/>
+      <c r="E16" s="149" t="s">
         <v>46</v>
       </c>
-      <c r="F16" s="44"/>
-      <c r="G16" s="124" t="s">
+      <c r="F16" s="55"/>
+      <c r="G16" s="139" t="s">
         <v>69</v>
       </c>
-      <c r="H16" s="43"/>
-      <c r="I16" s="44"/>
-      <c r="J16" s="124" t="s">
+      <c r="H16" s="56"/>
+      <c r="I16" s="55"/>
+      <c r="J16" s="139" t="s">
         <v>68</v>
       </c>
-      <c r="K16" s="44"/>
-      <c r="L16" s="125" t="s">
+      <c r="K16" s="55"/>
+      <c r="L16" s="138" t="s">
         <v>70</v>
       </c>
-      <c r="M16" s="43"/>
-      <c r="N16" s="44"/>
-      <c r="O16" s="125" t="s">
+      <c r="M16" s="56"/>
+      <c r="N16" s="55"/>
+      <c r="O16" s="138" t="s">
         <v>45</v>
       </c>
-      <c r="P16" s="43"/>
-      <c r="Q16" s="44"/>
-      <c r="R16" s="36">
+      <c r="P16" s="56"/>
+      <c r="Q16" s="55"/>
+      <c r="R16" s="34">
         <v>45810</v>
       </c>
-      <c r="S16" s="19" t="s">
+      <c r="S16" s="17" t="s">
         <v>28</v>
       </c>
-      <c r="T16" s="18" t="s">
+      <c r="T16" s="16" t="s">
         <v>82</v>
       </c>
       <c r="U16" s="15"/>
@@ -7341,44 +8640,44 @@
       <c r="Z16" s="15"/>
     </row>
     <row r="17" spans="1:26" ht="41.25" customHeight="1">
-      <c r="A17" s="120">
+      <c r="A17" s="148">
         <v>2</v>
       </c>
-      <c r="B17" s="44"/>
-      <c r="C17" s="121" t="s">
+      <c r="B17" s="55"/>
+      <c r="C17" s="149" t="s">
         <v>71</v>
       </c>
-      <c r="D17" s="44"/>
-      <c r="E17" s="121" t="s">
+      <c r="D17" s="55"/>
+      <c r="E17" s="149" t="s">
         <v>46</v>
       </c>
-      <c r="F17" s="44"/>
-      <c r="G17" s="124" t="s">
+      <c r="F17" s="55"/>
+      <c r="G17" s="139" t="s">
         <v>72</v>
       </c>
-      <c r="H17" s="43"/>
-      <c r="I17" s="44"/>
-      <c r="J17" s="124" t="s">
+      <c r="H17" s="56"/>
+      <c r="I17" s="55"/>
+      <c r="J17" s="139" t="s">
         <v>68</v>
       </c>
-      <c r="K17" s="44"/>
-      <c r="L17" s="125" t="s">
+      <c r="K17" s="55"/>
+      <c r="L17" s="138" t="s">
         <v>73</v>
       </c>
-      <c r="M17" s="43"/>
-      <c r="N17" s="44"/>
-      <c r="O17" s="125" t="s">
+      <c r="M17" s="56"/>
+      <c r="N17" s="55"/>
+      <c r="O17" s="138" t="s">
         <v>74</v>
       </c>
-      <c r="P17" s="43"/>
-      <c r="Q17" s="44"/>
-      <c r="R17" s="36">
+      <c r="P17" s="56"/>
+      <c r="Q17" s="55"/>
+      <c r="R17" s="34">
         <v>45810</v>
       </c>
-      <c r="S17" s="19" t="s">
+      <c r="S17" s="17" t="s">
         <v>28</v>
       </c>
-      <c r="T17" s="18" t="s">
+      <c r="T17" s="16" t="s">
         <v>82</v>
       </c>
       <c r="U17" s="15"/>
@@ -7388,45 +8687,45 @@
       <c r="Y17" s="15"/>
       <c r="Z17" s="15"/>
     </row>
-    <row r="18" spans="1:26" ht="57.75" customHeight="1">
-      <c r="A18" s="120">
+    <row r="18" spans="1:26" ht="57.75" customHeight="1" thickBot="1">
+      <c r="A18" s="175">
         <v>3</v>
       </c>
-      <c r="B18" s="44"/>
-      <c r="C18" s="121" t="s">
+      <c r="B18" s="174"/>
+      <c r="C18" s="176" t="s">
         <v>71</v>
       </c>
-      <c r="D18" s="44"/>
-      <c r="E18" s="121" t="s">
+      <c r="D18" s="174"/>
+      <c r="E18" s="176" t="s">
         <v>75</v>
       </c>
-      <c r="F18" s="44"/>
-      <c r="G18" s="124" t="s">
+      <c r="F18" s="174"/>
+      <c r="G18" s="177" t="s">
         <v>76</v>
       </c>
-      <c r="H18" s="43"/>
-      <c r="I18" s="44"/>
-      <c r="J18" s="124" t="s">
+      <c r="H18" s="173"/>
+      <c r="I18" s="174"/>
+      <c r="J18" s="177" t="s">
         <v>77</v>
       </c>
-      <c r="K18" s="44"/>
-      <c r="L18" s="136" t="s">
+      <c r="K18" s="174"/>
+      <c r="L18" s="178" t="s">
         <v>81</v>
       </c>
-      <c r="M18" s="43"/>
-      <c r="N18" s="44"/>
-      <c r="O18" s="125" t="s">
+      <c r="M18" s="173"/>
+      <c r="N18" s="174"/>
+      <c r="O18" s="172" t="s">
         <v>78</v>
       </c>
-      <c r="P18" s="43"/>
-      <c r="Q18" s="44"/>
-      <c r="R18" s="36">
+      <c r="P18" s="173"/>
+      <c r="Q18" s="174"/>
+      <c r="R18" s="169">
         <v>45810</v>
       </c>
-      <c r="S18" s="19" t="s">
+      <c r="S18" s="170" t="s">
         <v>28</v>
       </c>
-      <c r="T18" s="18" t="s">
+      <c r="T18" s="171" t="s">
         <v>82</v>
       </c>
       <c r="U18" s="15"/>
@@ -7437,368 +8736,108 @@
       <c r="Z18" s="15"/>
     </row>
     <row r="19" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A19" s="120"/>
-      <c r="B19" s="44"/>
-      <c r="C19" s="121"/>
-      <c r="D19" s="44"/>
-      <c r="E19" s="121"/>
-      <c r="F19" s="44"/>
-      <c r="G19" s="124"/>
-      <c r="H19" s="43"/>
-      <c r="I19" s="44"/>
-      <c r="J19" s="124"/>
-      <c r="K19" s="44"/>
-      <c r="L19" s="125"/>
-      <c r="M19" s="43"/>
-      <c r="N19" s="44"/>
-      <c r="O19" s="125"/>
-      <c r="P19" s="43"/>
-      <c r="Q19" s="44"/>
-      <c r="R19" s="19"/>
-      <c r="S19" s="19"/>
-      <c r="T19" s="18"/>
-      <c r="U19" s="15"/>
-      <c r="V19" s="15"/>
-      <c r="W19" s="15"/>
-      <c r="X19" s="15"/>
-      <c r="Y19" s="15"/>
-      <c r="Z19" s="15"/>
+      <c r="A19" s="15"/>
+      <c r="B19" s="15"/>
+      <c r="C19" s="15"/>
+      <c r="D19" s="15"/>
+      <c r="E19" s="15"/>
+      <c r="F19" s="15"/>
     </row>
     <row r="20" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A20" s="120"/>
-      <c r="B20" s="44"/>
-      <c r="C20" s="121"/>
-      <c r="D20" s="44"/>
-      <c r="E20" s="121"/>
-      <c r="F20" s="44"/>
-      <c r="G20" s="124"/>
-      <c r="H20" s="43"/>
-      <c r="I20" s="44"/>
-      <c r="J20" s="124"/>
-      <c r="K20" s="44"/>
-      <c r="L20" s="125"/>
-      <c r="M20" s="43"/>
-      <c r="N20" s="44"/>
-      <c r="O20" s="125"/>
-      <c r="P20" s="43"/>
-      <c r="Q20" s="44"/>
-      <c r="R20" s="19"/>
-      <c r="S20" s="19"/>
-      <c r="T20" s="18"/>
-      <c r="U20" s="15"/>
-      <c r="V20" s="15"/>
-      <c r="W20" s="15"/>
-      <c r="X20" s="15"/>
-      <c r="Y20" s="15"/>
-      <c r="Z20" s="15"/>
+      <c r="A20" s="15"/>
+      <c r="B20" s="15"/>
+      <c r="C20" s="15"/>
+      <c r="D20" s="15"/>
+      <c r="E20" s="15"/>
+      <c r="F20" s="15"/>
     </row>
     <row r="21" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A21" s="120"/>
-      <c r="B21" s="44"/>
-      <c r="C21" s="121"/>
-      <c r="D21" s="44"/>
-      <c r="E21" s="121"/>
-      <c r="F21" s="44"/>
-      <c r="G21" s="124"/>
-      <c r="H21" s="43"/>
-      <c r="I21" s="44"/>
-      <c r="J21" s="124"/>
-      <c r="K21" s="44"/>
-      <c r="L21" s="125"/>
-      <c r="M21" s="43"/>
-      <c r="N21" s="44"/>
-      <c r="O21" s="125"/>
-      <c r="P21" s="43"/>
-      <c r="Q21" s="44"/>
-      <c r="R21" s="19"/>
-      <c r="S21" s="19"/>
-      <c r="T21" s="18"/>
-      <c r="U21" s="15"/>
-      <c r="V21" s="15"/>
-      <c r="W21" s="15"/>
-      <c r="X21" s="15"/>
-      <c r="Y21" s="15"/>
-      <c r="Z21" s="15"/>
+      <c r="A21" s="15"/>
+      <c r="B21" s="15"/>
+      <c r="C21" s="15"/>
+      <c r="D21" s="15"/>
+      <c r="E21" s="15"/>
+      <c r="F21" s="15"/>
     </row>
     <row r="22" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A22" s="120"/>
-      <c r="B22" s="44"/>
-      <c r="C22" s="121"/>
-      <c r="D22" s="44"/>
-      <c r="E22" s="121"/>
-      <c r="F22" s="44"/>
-      <c r="G22" s="124"/>
-      <c r="H22" s="43"/>
-      <c r="I22" s="44"/>
-      <c r="J22" s="124"/>
-      <c r="K22" s="44"/>
-      <c r="L22" s="125"/>
-      <c r="M22" s="43"/>
-      <c r="N22" s="44"/>
-      <c r="O22" s="125"/>
-      <c r="P22" s="43"/>
-      <c r="Q22" s="44"/>
-      <c r="R22" s="19"/>
-      <c r="S22" s="19"/>
-      <c r="T22" s="18"/>
-      <c r="U22" s="15"/>
-      <c r="V22" s="15"/>
-      <c r="W22" s="15"/>
-      <c r="X22" s="15"/>
-      <c r="Y22" s="15"/>
-      <c r="Z22" s="15"/>
+      <c r="A22" s="15"/>
+      <c r="B22" s="15"/>
+      <c r="C22" s="15"/>
+      <c r="D22" s="15"/>
+      <c r="E22" s="15"/>
+      <c r="F22" s="15"/>
     </row>
     <row r="23" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A23" s="120"/>
-      <c r="B23" s="44"/>
-      <c r="C23" s="121"/>
-      <c r="D23" s="44"/>
-      <c r="E23" s="121"/>
-      <c r="F23" s="44"/>
-      <c r="G23" s="124"/>
-      <c r="H23" s="43"/>
-      <c r="I23" s="44"/>
-      <c r="J23" s="124"/>
-      <c r="K23" s="44"/>
-      <c r="L23" s="125"/>
-      <c r="M23" s="43"/>
-      <c r="N23" s="44"/>
-      <c r="O23" s="125"/>
-      <c r="P23" s="43"/>
-      <c r="Q23" s="44"/>
-      <c r="R23" s="19"/>
-      <c r="S23" s="19"/>
-      <c r="T23" s="18"/>
-      <c r="U23" s="15"/>
-      <c r="V23" s="15"/>
-      <c r="W23" s="15"/>
-      <c r="X23" s="15"/>
-      <c r="Y23" s="15"/>
-      <c r="Z23" s="15"/>
+      <c r="A23" s="15"/>
+      <c r="B23" s="15"/>
+      <c r="C23" s="15"/>
+      <c r="D23" s="15"/>
+      <c r="E23" s="15"/>
+      <c r="F23" s="15"/>
     </row>
     <row r="24" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A24" s="120"/>
-      <c r="B24" s="44"/>
-      <c r="C24" s="121"/>
-      <c r="D24" s="44"/>
-      <c r="E24" s="121"/>
-      <c r="F24" s="44"/>
-      <c r="G24" s="124"/>
-      <c r="H24" s="43"/>
-      <c r="I24" s="44"/>
-      <c r="J24" s="124"/>
-      <c r="K24" s="44"/>
-      <c r="L24" s="125"/>
-      <c r="M24" s="43"/>
-      <c r="N24" s="44"/>
-      <c r="O24" s="125"/>
-      <c r="P24" s="43"/>
-      <c r="Q24" s="44"/>
-      <c r="R24" s="19"/>
-      <c r="S24" s="19"/>
-      <c r="T24" s="18"/>
-      <c r="U24" s="15"/>
-      <c r="V24" s="15"/>
-      <c r="W24" s="15"/>
-      <c r="X24" s="15"/>
-      <c r="Y24" s="15"/>
-      <c r="Z24" s="15"/>
+      <c r="A24" s="15"/>
+      <c r="B24" s="15"/>
+      <c r="C24" s="15"/>
+      <c r="D24" s="15"/>
+      <c r="E24" s="15"/>
+      <c r="F24" s="15"/>
     </row>
     <row r="25" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A25" s="120"/>
-      <c r="B25" s="44"/>
-      <c r="C25" s="121"/>
-      <c r="D25" s="44"/>
-      <c r="E25" s="121"/>
-      <c r="F25" s="44"/>
-      <c r="G25" s="124"/>
-      <c r="H25" s="43"/>
-      <c r="I25" s="44"/>
-      <c r="J25" s="124"/>
-      <c r="K25" s="44"/>
-      <c r="L25" s="125"/>
-      <c r="M25" s="43"/>
-      <c r="N25" s="44"/>
-      <c r="O25" s="125"/>
-      <c r="P25" s="43"/>
-      <c r="Q25" s="44"/>
-      <c r="R25" s="19"/>
-      <c r="S25" s="19"/>
-      <c r="T25" s="18"/>
-      <c r="U25" s="15"/>
-      <c r="V25" s="15"/>
-      <c r="W25" s="15"/>
-      <c r="X25" s="15"/>
-      <c r="Y25" s="15"/>
-      <c r="Z25" s="15"/>
+      <c r="A25" s="15"/>
+      <c r="B25" s="15"/>
+      <c r="C25" s="15"/>
+      <c r="D25" s="15"/>
+      <c r="E25" s="15"/>
+      <c r="F25" s="15"/>
     </row>
     <row r="26" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A26" s="120"/>
-      <c r="B26" s="44"/>
-      <c r="C26" s="121"/>
-      <c r="D26" s="44"/>
-      <c r="E26" s="121"/>
-      <c r="F26" s="44"/>
-      <c r="G26" s="124"/>
-      <c r="H26" s="43"/>
-      <c r="I26" s="44"/>
-      <c r="J26" s="124"/>
-      <c r="K26" s="44"/>
-      <c r="L26" s="125"/>
-      <c r="M26" s="43"/>
-      <c r="N26" s="44"/>
-      <c r="O26" s="125"/>
-      <c r="P26" s="43"/>
-      <c r="Q26" s="44"/>
-      <c r="R26" s="19"/>
-      <c r="S26" s="19"/>
-      <c r="T26" s="18"/>
-      <c r="U26" s="15"/>
-      <c r="V26" s="15"/>
-      <c r="W26" s="15"/>
-      <c r="X26" s="15"/>
-      <c r="Y26" s="15"/>
-      <c r="Z26" s="15"/>
+      <c r="A26" s="15"/>
+      <c r="B26" s="15"/>
+      <c r="C26" s="15"/>
+      <c r="D26" s="15"/>
+      <c r="E26" s="15"/>
+      <c r="F26" s="15"/>
     </row>
     <row r="27" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A27" s="120"/>
-      <c r="B27" s="44"/>
-      <c r="C27" s="121"/>
-      <c r="D27" s="44"/>
-      <c r="E27" s="121"/>
-      <c r="F27" s="44"/>
-      <c r="G27" s="124"/>
-      <c r="H27" s="43"/>
-      <c r="I27" s="44"/>
-      <c r="J27" s="124"/>
-      <c r="K27" s="44"/>
-      <c r="L27" s="125"/>
-      <c r="M27" s="43"/>
-      <c r="N27" s="44"/>
-      <c r="O27" s="125"/>
-      <c r="P27" s="43"/>
-      <c r="Q27" s="44"/>
-      <c r="R27" s="19"/>
-      <c r="S27" s="19"/>
-      <c r="T27" s="18"/>
-      <c r="U27" s="15"/>
-      <c r="V27" s="15"/>
-      <c r="W27" s="15"/>
-      <c r="X27" s="15"/>
-      <c r="Y27" s="15"/>
-      <c r="Z27" s="15"/>
+      <c r="A27" s="15"/>
+      <c r="B27" s="15"/>
+      <c r="C27" s="15"/>
+      <c r="D27" s="15"/>
+      <c r="E27" s="15"/>
+      <c r="F27" s="15"/>
     </row>
     <row r="28" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A28" s="120"/>
-      <c r="B28" s="44"/>
-      <c r="C28" s="121"/>
-      <c r="D28" s="44"/>
-      <c r="E28" s="121"/>
-      <c r="F28" s="44"/>
-      <c r="G28" s="124"/>
-      <c r="H28" s="43"/>
-      <c r="I28" s="44"/>
-      <c r="J28" s="124"/>
-      <c r="K28" s="44"/>
-      <c r="L28" s="125"/>
-      <c r="M28" s="43"/>
-      <c r="N28" s="44"/>
-      <c r="O28" s="125"/>
-      <c r="P28" s="43"/>
-      <c r="Q28" s="44"/>
-      <c r="R28" s="19"/>
-      <c r="S28" s="19"/>
-      <c r="T28" s="18"/>
-      <c r="U28" s="15"/>
-      <c r="V28" s="15"/>
-      <c r="W28" s="15"/>
-      <c r="X28" s="15"/>
-      <c r="Y28" s="15"/>
-      <c r="Z28" s="15"/>
+      <c r="A28" s="15"/>
+      <c r="B28" s="15"/>
+      <c r="C28" s="15"/>
+      <c r="D28" s="15"/>
+      <c r="E28" s="15"/>
+      <c r="F28" s="15"/>
     </row>
     <row r="29" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A29" s="120"/>
-      <c r="B29" s="44"/>
-      <c r="C29" s="121"/>
-      <c r="D29" s="44"/>
-      <c r="E29" s="121"/>
-      <c r="F29" s="44"/>
-      <c r="G29" s="124"/>
-      <c r="H29" s="43"/>
-      <c r="I29" s="44"/>
-      <c r="J29" s="124"/>
-      <c r="K29" s="44"/>
-      <c r="L29" s="125"/>
-      <c r="M29" s="43"/>
-      <c r="N29" s="44"/>
-      <c r="O29" s="125"/>
-      <c r="P29" s="43"/>
-      <c r="Q29" s="44"/>
-      <c r="R29" s="19"/>
-      <c r="S29" s="19"/>
-      <c r="T29" s="18"/>
-      <c r="U29" s="15"/>
-      <c r="V29" s="15"/>
-      <c r="W29" s="15"/>
-      <c r="X29" s="15"/>
-      <c r="Y29" s="15"/>
-      <c r="Z29" s="15"/>
+      <c r="A29" s="15"/>
+      <c r="B29" s="15"/>
+      <c r="C29" s="15"/>
+      <c r="D29" s="15"/>
+      <c r="E29" s="15"/>
+      <c r="F29" s="15"/>
     </row>
     <row r="30" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A30" s="120"/>
-      <c r="B30" s="44"/>
-      <c r="C30" s="121"/>
-      <c r="D30" s="44"/>
-      <c r="E30" s="121"/>
-      <c r="F30" s="44"/>
-      <c r="G30" s="124"/>
-      <c r="H30" s="43"/>
-      <c r="I30" s="44"/>
-      <c r="J30" s="124"/>
-      <c r="K30" s="44"/>
-      <c r="L30" s="125"/>
-      <c r="M30" s="43"/>
-      <c r="N30" s="44"/>
-      <c r="O30" s="125"/>
-      <c r="P30" s="43"/>
-      <c r="Q30" s="44"/>
-      <c r="R30" s="19"/>
-      <c r="S30" s="19"/>
-      <c r="T30" s="18"/>
-      <c r="U30" s="15"/>
-      <c r="V30" s="15"/>
-      <c r="W30" s="15"/>
-      <c r="X30" s="15"/>
-      <c r="Y30" s="15"/>
-      <c r="Z30" s="15"/>
-    </row>
-    <row r="31" spans="1:26" ht="12.75" customHeight="1" thickBot="1">
-      <c r="A31" s="122"/>
-      <c r="B31" s="49"/>
-      <c r="C31" s="123"/>
-      <c r="D31" s="49"/>
-      <c r="E31" s="123"/>
-      <c r="F31" s="49"/>
-      <c r="G31" s="137"/>
-      <c r="H31" s="48"/>
-      <c r="I31" s="49"/>
-      <c r="J31" s="137"/>
-      <c r="K31" s="49"/>
-      <c r="L31" s="126"/>
-      <c r="M31" s="48"/>
-      <c r="N31" s="49"/>
-      <c r="O31" s="126"/>
-      <c r="P31" s="48"/>
-      <c r="Q31" s="49"/>
-      <c r="R31" s="17"/>
-      <c r="S31" s="17"/>
-      <c r="T31" s="16"/>
-      <c r="U31" s="15"/>
-      <c r="V31" s="15"/>
-      <c r="W31" s="15"/>
-      <c r="X31" s="15"/>
-      <c r="Y31" s="15"/>
-      <c r="Z31" s="15"/>
+      <c r="A30" s="15"/>
+      <c r="B30" s="15"/>
+      <c r="C30" s="15"/>
+      <c r="D30" s="15"/>
+      <c r="E30" s="15"/>
+      <c r="F30" s="15"/>
+    </row>
+    <row r="31" spans="1:26" ht="12.75" customHeight="1">
+      <c r="A31" s="15"/>
+      <c r="B31" s="15"/>
+      <c r="C31" s="15"/>
+      <c r="D31" s="15"/>
+      <c r="E31" s="15"/>
+      <c r="F31" s="15"/>
     </row>
     <row r="32" spans="1:26" ht="12.75" customHeight="1">
       <c r="D32" s="14"/>
@@ -8786,43 +9825,33 @@
     <row r="999" s="13" customFormat="1" ht="12.75" customHeight="1"/>
     <row r="1000" s="13" customFormat="1" ht="12.75" customHeight="1"/>
   </sheetData>
-  <mergeCells count="136">
-    <mergeCell ref="L26:N26"/>
-    <mergeCell ref="L27:N27"/>
-    <mergeCell ref="L28:N28"/>
-    <mergeCell ref="L29:N29"/>
-    <mergeCell ref="G25:I25"/>
-    <mergeCell ref="J25:K25"/>
-    <mergeCell ref="J26:K26"/>
-    <mergeCell ref="L30:N30"/>
-    <mergeCell ref="L31:N31"/>
-    <mergeCell ref="G30:I30"/>
-    <mergeCell ref="J30:K30"/>
-    <mergeCell ref="G31:I31"/>
-    <mergeCell ref="J31:K31"/>
-    <mergeCell ref="G26:I26"/>
-    <mergeCell ref="G27:I27"/>
-    <mergeCell ref="J27:K27"/>
-    <mergeCell ref="G28:I28"/>
-    <mergeCell ref="J28:K28"/>
-    <mergeCell ref="G29:I29"/>
-    <mergeCell ref="J29:K29"/>
-    <mergeCell ref="L18:N18"/>
-    <mergeCell ref="L19:N19"/>
-    <mergeCell ref="L21:N21"/>
-    <mergeCell ref="L22:N22"/>
-    <mergeCell ref="L23:N23"/>
-    <mergeCell ref="L24:N24"/>
-    <mergeCell ref="L25:N25"/>
-    <mergeCell ref="L20:N20"/>
-    <mergeCell ref="G2:J4"/>
-    <mergeCell ref="L15:N15"/>
-    <mergeCell ref="G22:I22"/>
-    <mergeCell ref="J22:K22"/>
-    <mergeCell ref="G23:I23"/>
-    <mergeCell ref="J23:K23"/>
-    <mergeCell ref="G24:I24"/>
-    <mergeCell ref="J24:K24"/>
+  <mergeCells count="45">
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="E18:F18"/>
+    <mergeCell ref="E16:F16"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="J16:K16"/>
+    <mergeCell ref="G17:I17"/>
+    <mergeCell ref="J17:K17"/>
+    <mergeCell ref="O15:Q15"/>
+    <mergeCell ref="L16:N16"/>
+    <mergeCell ref="O16:Q16"/>
+    <mergeCell ref="L17:N17"/>
+    <mergeCell ref="O17:Q17"/>
+    <mergeCell ref="O18:Q18"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="E15:F15"/>
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="J18:K18"/>
+    <mergeCell ref="G18:I18"/>
+    <mergeCell ref="G15:I15"/>
+    <mergeCell ref="J15:K15"/>
+    <mergeCell ref="G16:I16"/>
+    <mergeCell ref="C16:D16"/>
     <mergeCell ref="A5:F5"/>
     <mergeCell ref="G5:T5"/>
     <mergeCell ref="A6:F6"/>
@@ -8839,90 +9868,9 @@
     <mergeCell ref="O1:P1"/>
     <mergeCell ref="Q1:R1"/>
     <mergeCell ref="S1:T1"/>
-    <mergeCell ref="O15:Q15"/>
-    <mergeCell ref="L16:N16"/>
-    <mergeCell ref="O16:Q16"/>
-    <mergeCell ref="L17:N17"/>
-    <mergeCell ref="O17:Q17"/>
-    <mergeCell ref="O18:Q18"/>
-    <mergeCell ref="A15:B15"/>
-    <mergeCell ref="A20:B20"/>
-    <mergeCell ref="C20:D20"/>
-    <mergeCell ref="E20:F20"/>
-    <mergeCell ref="G20:I20"/>
-    <mergeCell ref="J20:K20"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="E15:F15"/>
-    <mergeCell ref="A16:B16"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="J18:K18"/>
-    <mergeCell ref="G18:I18"/>
-    <mergeCell ref="G19:I19"/>
-    <mergeCell ref="J19:K19"/>
-    <mergeCell ref="G15:I15"/>
-    <mergeCell ref="J15:K15"/>
-    <mergeCell ref="G16:I16"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="O27:Q27"/>
-    <mergeCell ref="O28:Q28"/>
-    <mergeCell ref="O29:Q29"/>
-    <mergeCell ref="O30:Q30"/>
-    <mergeCell ref="O31:Q31"/>
-    <mergeCell ref="O19:Q19"/>
-    <mergeCell ref="O21:Q21"/>
-    <mergeCell ref="O22:Q22"/>
-    <mergeCell ref="O23:Q23"/>
-    <mergeCell ref="O24:Q24"/>
-    <mergeCell ref="O20:Q20"/>
-    <mergeCell ref="O25:Q25"/>
-    <mergeCell ref="O26:Q26"/>
-    <mergeCell ref="E16:F16"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="E17:F17"/>
-    <mergeCell ref="C23:D23"/>
-    <mergeCell ref="E23:F23"/>
-    <mergeCell ref="C24:D24"/>
-    <mergeCell ref="E24:F24"/>
-    <mergeCell ref="G21:I21"/>
-    <mergeCell ref="J21:K21"/>
-    <mergeCell ref="J16:K16"/>
-    <mergeCell ref="G17:I17"/>
-    <mergeCell ref="J17:K17"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="E21:F21"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="E22:F22"/>
-    <mergeCell ref="A18:B18"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="E18:F18"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="E19:F19"/>
-    <mergeCell ref="A23:B23"/>
-    <mergeCell ref="A30:B30"/>
-    <mergeCell ref="C30:D30"/>
-    <mergeCell ref="E30:F30"/>
-    <mergeCell ref="A31:B31"/>
-    <mergeCell ref="C31:D31"/>
-    <mergeCell ref="E31:F31"/>
-    <mergeCell ref="C26:D26"/>
-    <mergeCell ref="E26:F26"/>
-    <mergeCell ref="A24:B24"/>
-    <mergeCell ref="C28:D28"/>
-    <mergeCell ref="E28:F28"/>
-    <mergeCell ref="A29:B29"/>
-    <mergeCell ref="A25:B25"/>
-    <mergeCell ref="C25:D25"/>
-    <mergeCell ref="E25:F25"/>
-    <mergeCell ref="A26:B26"/>
-    <mergeCell ref="C29:D29"/>
-    <mergeCell ref="E29:F29"/>
-    <mergeCell ref="A27:B27"/>
-    <mergeCell ref="C27:D27"/>
-    <mergeCell ref="E27:F27"/>
-    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="L18:N18"/>
+    <mergeCell ref="G2:J4"/>
+    <mergeCell ref="L15:N15"/>
   </mergeCells>
   <phoneticPr fontId="4"/>
   <hyperlinks>
@@ -8933,431 +9881,423 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C1099CA-27EA-4934-AD05-F88BE657AA80}">
   <dimension ref="A1:O42"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
-    <col min="1" max="16384" width="9" style="148"/>
+    <col min="1" max="16384" width="9" style="45"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="19.5" thickBot="1">
-      <c r="A1" s="138" t="s">
+      <c r="A1" s="151" t="s">
         <v>87</v>
       </c>
-      <c r="B1" s="139"/>
-      <c r="C1" s="140"/>
-      <c r="D1" s="141" t="s">
+      <c r="B1" s="152"/>
+      <c r="C1" s="40"/>
+      <c r="D1" s="41" t="s">
         <v>88</v>
       </c>
-      <c r="E1" s="142"/>
-      <c r="F1" s="140"/>
-      <c r="G1" s="143" t="s">
+      <c r="E1" s="42"/>
+      <c r="F1" s="40"/>
+      <c r="G1" s="43" t="s">
         <v>89</v>
       </c>
-      <c r="H1" s="142"/>
-      <c r="I1" s="144" t="s">
+      <c r="H1" s="42"/>
+      <c r="I1" s="163" t="s">
         <v>90</v>
       </c>
-      <c r="J1" s="145"/>
-      <c r="K1" s="144" t="s">
+      <c r="J1" s="164"/>
+      <c r="K1" s="163" t="s">
         <v>91</v>
       </c>
-      <c r="L1" s="145"/>
-      <c r="M1" s="144" t="s">
+      <c r="L1" s="164"/>
+      <c r="M1" s="163" t="s">
         <v>92</v>
       </c>
-      <c r="N1" s="146"/>
-      <c r="O1" s="147"/>
+      <c r="N1" s="165"/>
+      <c r="O1" s="44"/>
     </row>
     <row r="2" spans="1:15">
-      <c r="A2" s="149"/>
-      <c r="B2" s="150"/>
-      <c r="C2" s="138" t="s">
+      <c r="A2" s="153"/>
+      <c r="B2" s="154"/>
+      <c r="C2" s="151" t="s">
         <v>6</v>
       </c>
-      <c r="D2" s="151"/>
-      <c r="E2" s="139"/>
-      <c r="F2" s="138" t="s">
+      <c r="D2" s="166"/>
+      <c r="E2" s="152"/>
+      <c r="F2" s="151" t="s">
         <v>7</v>
       </c>
-      <c r="G2" s="151"/>
-      <c r="H2" s="139"/>
-      <c r="I2" s="167">
+      <c r="G2" s="166"/>
+      <c r="H2" s="152"/>
+      <c r="I2" s="168">
         <v>45827</v>
       </c>
-      <c r="J2" s="139"/>
-      <c r="K2" s="138" t="s">
+      <c r="J2" s="152"/>
+      <c r="K2" s="151" t="s">
         <v>28</v>
       </c>
-      <c r="L2" s="139"/>
-      <c r="M2" s="138"/>
-      <c r="N2" s="139"/>
-      <c r="O2" s="152"/>
+      <c r="L2" s="152"/>
+      <c r="M2" s="151"/>
+      <c r="N2" s="152"/>
+      <c r="O2" s="46"/>
     </row>
     <row r="3" spans="1:15" ht="19.5" thickBot="1">
-      <c r="A3" s="153"/>
-      <c r="B3" s="154"/>
-      <c r="C3" s="153"/>
-      <c r="D3" s="155"/>
-      <c r="E3" s="154"/>
-      <c r="F3" s="153"/>
-      <c r="G3" s="155"/>
-      <c r="H3" s="154"/>
-      <c r="I3" s="153"/>
-      <c r="J3" s="154"/>
-      <c r="K3" s="153"/>
-      <c r="L3" s="154"/>
-      <c r="M3" s="153"/>
-      <c r="N3" s="154"/>
-      <c r="O3" s="152"/>
+      <c r="A3" s="155"/>
+      <c r="B3" s="156"/>
+      <c r="C3" s="155"/>
+      <c r="D3" s="167"/>
+      <c r="E3" s="156"/>
+      <c r="F3" s="155"/>
+      <c r="G3" s="167"/>
+      <c r="H3" s="156"/>
+      <c r="I3" s="155"/>
+      <c r="J3" s="156"/>
+      <c r="K3" s="155"/>
+      <c r="L3" s="156"/>
+      <c r="M3" s="155"/>
+      <c r="N3" s="156"/>
+      <c r="O3" s="46"/>
     </row>
     <row r="4" spans="1:15">
-      <c r="A4" s="138" t="s">
+      <c r="A4" s="151" t="s">
         <v>93</v>
       </c>
-      <c r="B4" s="139"/>
-      <c r="C4" s="156" t="s">
+      <c r="B4" s="152"/>
+      <c r="C4" s="157" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="157"/>
-      <c r="E4" s="157"/>
-      <c r="F4" s="157"/>
-      <c r="G4" s="157"/>
-      <c r="H4" s="157"/>
-      <c r="I4" s="157"/>
-      <c r="J4" s="157"/>
-      <c r="K4" s="157"/>
-      <c r="L4" s="157"/>
-      <c r="M4" s="157"/>
-      <c r="N4" s="158"/>
-      <c r="O4" s="152"/>
+      <c r="D4" s="158"/>
+      <c r="E4" s="158"/>
+      <c r="F4" s="158"/>
+      <c r="G4" s="158"/>
+      <c r="H4" s="158"/>
+      <c r="I4" s="158"/>
+      <c r="J4" s="158"/>
+      <c r="K4" s="158"/>
+      <c r="L4" s="158"/>
+      <c r="M4" s="158"/>
+      <c r="N4" s="159"/>
+      <c r="O4" s="46"/>
     </row>
     <row r="5" spans="1:15" ht="19.5" thickBot="1">
-      <c r="A5" s="153"/>
-      <c r="B5" s="154"/>
-      <c r="C5" s="159"/>
-      <c r="D5" s="160"/>
-      <c r="E5" s="160"/>
-      <c r="F5" s="160"/>
-      <c r="G5" s="160"/>
-      <c r="H5" s="160"/>
-      <c r="I5" s="160"/>
-      <c r="J5" s="160"/>
-      <c r="K5" s="160"/>
-      <c r="L5" s="160"/>
-      <c r="M5" s="160"/>
-      <c r="N5" s="161"/>
-      <c r="O5" s="152"/>
+      <c r="A5" s="155"/>
+      <c r="B5" s="156"/>
+      <c r="C5" s="160"/>
+      <c r="D5" s="161"/>
+      <c r="E5" s="161"/>
+      <c r="F5" s="161"/>
+      <c r="G5" s="161"/>
+      <c r="H5" s="161"/>
+      <c r="I5" s="161"/>
+      <c r="J5" s="161"/>
+      <c r="K5" s="161"/>
+      <c r="L5" s="161"/>
+      <c r="M5" s="161"/>
+      <c r="N5" s="162"/>
+      <c r="O5" s="46"/>
     </row>
     <row r="6" spans="1:15" ht="19.5" thickBot="1">
-      <c r="A6" s="144" t="s">
+      <c r="A6" s="163" t="s">
         <v>94</v>
       </c>
-      <c r="B6" s="145"/>
-      <c r="C6" s="144" t="s">
+      <c r="B6" s="164"/>
+      <c r="C6" s="163" t="s">
         <v>95</v>
       </c>
-      <c r="D6" s="146"/>
-      <c r="E6" s="146"/>
-      <c r="F6" s="146"/>
-      <c r="G6" s="146"/>
-      <c r="H6" s="146"/>
-      <c r="I6" s="146"/>
-      <c r="J6" s="146"/>
-      <c r="K6" s="146"/>
-      <c r="L6" s="146"/>
-      <c r="M6" s="146"/>
-      <c r="N6" s="145"/>
-      <c r="O6" s="152"/>
+      <c r="D6" s="165"/>
+      <c r="E6" s="165"/>
+      <c r="F6" s="165"/>
+      <c r="G6" s="165"/>
+      <c r="H6" s="165"/>
+      <c r="I6" s="165"/>
+      <c r="J6" s="165"/>
+      <c r="K6" s="165"/>
+      <c r="L6" s="165"/>
+      <c r="M6" s="165"/>
+      <c r="N6" s="164"/>
+      <c r="O6" s="46"/>
     </row>
     <row r="7" spans="1:15">
-      <c r="A7" s="138">
+      <c r="A7" s="151">
         <v>1</v>
       </c>
-      <c r="B7" s="139"/>
-      <c r="C7" s="162"/>
-      <c r="D7" s="162"/>
-      <c r="E7" s="162"/>
-      <c r="F7" s="162"/>
-      <c r="G7" s="162"/>
-      <c r="H7" s="162"/>
-      <c r="I7" s="162"/>
-      <c r="J7" s="162"/>
-      <c r="K7" s="162"/>
-      <c r="L7" s="162"/>
-      <c r="M7" s="162"/>
-      <c r="N7" s="162"/>
-      <c r="O7" s="152"/>
+      <c r="B7" s="152"/>
+      <c r="C7" s="47"/>
+      <c r="D7" s="47"/>
+      <c r="E7" s="47"/>
+      <c r="F7" s="47"/>
+      <c r="G7" s="47"/>
+      <c r="H7" s="47"/>
+      <c r="I7" s="47"/>
+      <c r="J7" s="47"/>
+      <c r="K7" s="47"/>
+      <c r="L7" s="47"/>
+      <c r="M7" s="47"/>
+      <c r="N7" s="47"/>
+      <c r="O7" s="46"/>
     </row>
     <row r="8" spans="1:15">
-      <c r="A8" s="149"/>
-      <c r="B8" s="150"/>
-      <c r="O8" s="152"/>
+      <c r="A8" s="153"/>
+      <c r="B8" s="154"/>
+      <c r="O8" s="46"/>
     </row>
     <row r="9" spans="1:15">
-      <c r="A9" s="149"/>
-      <c r="B9" s="150"/>
-      <c r="N9" s="163"/>
+      <c r="A9" s="153"/>
+      <c r="B9" s="154"/>
+      <c r="N9" s="48"/>
     </row>
     <row r="10" spans="1:15">
-      <c r="A10" s="149"/>
-      <c r="B10" s="150"/>
-      <c r="O10" s="152"/>
+      <c r="A10" s="153"/>
+      <c r="B10" s="154"/>
+      <c r="O10" s="46"/>
     </row>
     <row r="11" spans="1:15">
-      <c r="A11" s="149"/>
-      <c r="B11" s="150"/>
-      <c r="O11" s="152"/>
+      <c r="A11" s="153"/>
+      <c r="B11" s="154"/>
+      <c r="O11" s="46"/>
     </row>
     <row r="12" spans="1:15">
-      <c r="A12" s="149"/>
-      <c r="B12" s="150"/>
-      <c r="O12" s="152"/>
+      <c r="A12" s="153"/>
+      <c r="B12" s="154"/>
+      <c r="O12" s="46"/>
     </row>
     <row r="13" spans="1:15">
-      <c r="A13" s="149"/>
-      <c r="B13" s="150"/>
-      <c r="O13" s="152"/>
+      <c r="A13" s="153"/>
+      <c r="B13" s="154"/>
+      <c r="O13" s="46"/>
     </row>
     <row r="14" spans="1:15">
-      <c r="A14" s="149"/>
-      <c r="B14" s="150"/>
-      <c r="O14" s="152"/>
+      <c r="A14" s="153"/>
+      <c r="B14" s="154"/>
+      <c r="O14" s="46"/>
     </row>
     <row r="15" spans="1:15" ht="42" customHeight="1" thickBot="1">
-      <c r="A15" s="153"/>
-      <c r="B15" s="154"/>
-      <c r="C15" s="164"/>
-      <c r="D15" s="164"/>
-      <c r="E15" s="164"/>
-      <c r="F15" s="164"/>
-      <c r="G15" s="164"/>
-      <c r="H15" s="164"/>
-      <c r="I15" s="164"/>
-      <c r="J15" s="164"/>
-      <c r="K15" s="164"/>
-      <c r="L15" s="164"/>
-      <c r="M15" s="164"/>
-      <c r="N15" s="165"/>
-      <c r="O15" s="152"/>
+      <c r="A15" s="155"/>
+      <c r="B15" s="156"/>
+      <c r="C15" s="49"/>
+      <c r="D15" s="49"/>
+      <c r="E15" s="49"/>
+      <c r="F15" s="49"/>
+      <c r="G15" s="49"/>
+      <c r="H15" s="49"/>
+      <c r="I15" s="49"/>
+      <c r="J15" s="49"/>
+      <c r="K15" s="49"/>
+      <c r="L15" s="49"/>
+      <c r="M15" s="49"/>
+      <c r="N15" s="50"/>
+      <c r="O15" s="46"/>
     </row>
     <row r="16" spans="1:15">
-      <c r="A16" s="138">
+      <c r="A16" s="151">
         <v>2</v>
       </c>
-      <c r="B16" s="139"/>
-      <c r="C16" s="162"/>
-      <c r="D16" s="162"/>
-      <c r="E16" s="162"/>
-      <c r="F16" s="162"/>
-      <c r="G16" s="162"/>
-      <c r="H16" s="162"/>
-      <c r="I16" s="162"/>
-      <c r="J16" s="162"/>
-      <c r="K16" s="162"/>
-      <c r="L16" s="162"/>
-      <c r="M16" s="162"/>
-      <c r="N16" s="163"/>
+      <c r="B16" s="152"/>
+      <c r="C16" s="47"/>
+      <c r="D16" s="47"/>
+      <c r="E16" s="47"/>
+      <c r="F16" s="47"/>
+      <c r="G16" s="47"/>
+      <c r="H16" s="47"/>
+      <c r="I16" s="47"/>
+      <c r="J16" s="47"/>
+      <c r="K16" s="47"/>
+      <c r="L16" s="47"/>
+      <c r="M16" s="47"/>
+      <c r="N16" s="48"/>
     </row>
     <row r="17" spans="1:14">
-      <c r="A17" s="149"/>
-      <c r="B17" s="150"/>
-      <c r="N17" s="163"/>
+      <c r="A17" s="153"/>
+      <c r="B17" s="154"/>
+      <c r="N17" s="48"/>
     </row>
     <row r="18" spans="1:14">
-      <c r="A18" s="149"/>
-      <c r="B18" s="150"/>
-      <c r="N18" s="163"/>
+      <c r="A18" s="153"/>
+      <c r="B18" s="154"/>
+      <c r="N18" s="48"/>
     </row>
     <row r="19" spans="1:14">
-      <c r="A19" s="149"/>
-      <c r="B19" s="150"/>
-      <c r="N19" s="163"/>
+      <c r="A19" s="153"/>
+      <c r="B19" s="154"/>
+      <c r="N19" s="48"/>
     </row>
     <row r="20" spans="1:14">
-      <c r="A20" s="149"/>
-      <c r="B20" s="150"/>
-      <c r="N20" s="163"/>
+      <c r="A20" s="153"/>
+      <c r="B20" s="154"/>
+      <c r="N20" s="48"/>
     </row>
     <row r="21" spans="1:14">
-      <c r="A21" s="149"/>
-      <c r="B21" s="150"/>
-      <c r="N21" s="163"/>
+      <c r="A21" s="153"/>
+      <c r="B21" s="154"/>
+      <c r="N21" s="48"/>
     </row>
     <row r="22" spans="1:14">
-      <c r="A22" s="149"/>
-      <c r="B22" s="150"/>
-      <c r="N22" s="163"/>
+      <c r="A22" s="153"/>
+      <c r="B22" s="154"/>
+      <c r="N22" s="48"/>
     </row>
     <row r="23" spans="1:14">
-      <c r="A23" s="149"/>
-      <c r="B23" s="150"/>
-      <c r="N23" s="163"/>
+      <c r="A23" s="153"/>
+      <c r="B23" s="154"/>
+      <c r="N23" s="48"/>
     </row>
     <row r="24" spans="1:14" ht="86.25" customHeight="1" thickBot="1">
-      <c r="A24" s="153"/>
-      <c r="B24" s="154"/>
-      <c r="C24" s="164"/>
-      <c r="D24" s="164"/>
-      <c r="E24" s="164"/>
-      <c r="F24" s="164"/>
-      <c r="G24" s="164"/>
-      <c r="H24" s="164"/>
-      <c r="I24" s="164"/>
-      <c r="J24" s="164"/>
-      <c r="K24" s="164"/>
-      <c r="L24" s="164"/>
-      <c r="M24" s="164"/>
-      <c r="N24" s="165"/>
+      <c r="A24" s="155"/>
+      <c r="B24" s="156"/>
+      <c r="C24" s="49"/>
+      <c r="D24" s="49"/>
+      <c r="E24" s="49"/>
+      <c r="F24" s="49"/>
+      <c r="G24" s="49"/>
+      <c r="H24" s="49"/>
+      <c r="I24" s="49"/>
+      <c r="J24" s="49"/>
+      <c r="K24" s="49"/>
+      <c r="L24" s="49"/>
+      <c r="M24" s="49"/>
+      <c r="N24" s="50"/>
     </row>
     <row r="25" spans="1:14">
-      <c r="A25" s="138">
+      <c r="A25" s="151">
         <v>3</v>
       </c>
-      <c r="B25" s="139"/>
-      <c r="C25" s="162"/>
-      <c r="D25" s="162"/>
-      <c r="E25" s="162"/>
-      <c r="F25" s="162"/>
-      <c r="G25" s="162"/>
-      <c r="H25" s="162"/>
-      <c r="I25" s="162"/>
-      <c r="J25" s="162"/>
-      <c r="K25" s="162"/>
-      <c r="L25" s="162"/>
-      <c r="M25" s="162"/>
-      <c r="N25" s="163"/>
+      <c r="B25" s="152"/>
+      <c r="C25" s="47"/>
+      <c r="D25" s="47"/>
+      <c r="E25" s="47"/>
+      <c r="F25" s="47"/>
+      <c r="G25" s="47"/>
+      <c r="H25" s="47"/>
+      <c r="I25" s="47"/>
+      <c r="J25" s="47"/>
+      <c r="K25" s="47"/>
+      <c r="L25" s="47"/>
+      <c r="M25" s="47"/>
+      <c r="N25" s="48"/>
     </row>
     <row r="26" spans="1:14">
-      <c r="A26" s="149"/>
-      <c r="B26" s="150"/>
-      <c r="N26" s="163"/>
+      <c r="A26" s="153"/>
+      <c r="B26" s="154"/>
+      <c r="N26" s="48"/>
     </row>
     <row r="27" spans="1:14">
-      <c r="A27" s="149"/>
-      <c r="B27" s="150"/>
-      <c r="N27" s="163"/>
+      <c r="A27" s="153"/>
+      <c r="B27" s="154"/>
+      <c r="N27" s="48"/>
     </row>
     <row r="28" spans="1:14">
-      <c r="A28" s="149"/>
-      <c r="B28" s="150"/>
-      <c r="N28" s="163"/>
+      <c r="A28" s="153"/>
+      <c r="B28" s="154"/>
+      <c r="N28" s="48"/>
     </row>
     <row r="29" spans="1:14">
-      <c r="A29" s="149"/>
-      <c r="B29" s="150"/>
-      <c r="N29" s="163"/>
+      <c r="A29" s="153"/>
+      <c r="B29" s="154"/>
+      <c r="N29" s="48"/>
     </row>
     <row r="30" spans="1:14">
-      <c r="A30" s="149"/>
-      <c r="B30" s="150"/>
-      <c r="N30" s="163"/>
+      <c r="A30" s="153"/>
+      <c r="B30" s="154"/>
+      <c r="N30" s="48"/>
     </row>
     <row r="31" spans="1:14">
-      <c r="A31" s="149"/>
-      <c r="B31" s="150"/>
-      <c r="N31" s="163"/>
+      <c r="A31" s="153"/>
+      <c r="B31" s="154"/>
+      <c r="N31" s="48"/>
     </row>
     <row r="32" spans="1:14">
-      <c r="A32" s="149"/>
-      <c r="B32" s="150"/>
-      <c r="N32" s="163"/>
+      <c r="A32" s="153"/>
+      <c r="B32" s="154"/>
+      <c r="N32" s="48"/>
     </row>
     <row r="33" spans="1:14" ht="93" customHeight="1" thickBot="1">
-      <c r="A33" s="153"/>
-      <c r="B33" s="154"/>
-      <c r="C33" s="164"/>
-      <c r="D33" s="164"/>
-      <c r="E33" s="164"/>
-      <c r="F33" s="164"/>
-      <c r="G33" s="164"/>
-      <c r="H33" s="164"/>
-      <c r="I33" s="164"/>
-      <c r="J33" s="164"/>
-      <c r="K33" s="164"/>
-      <c r="L33" s="164"/>
-      <c r="N33" s="163"/>
+      <c r="A33" s="155"/>
+      <c r="B33" s="156"/>
+      <c r="C33" s="49"/>
+      <c r="D33" s="49"/>
+      <c r="E33" s="49"/>
+      <c r="F33" s="49"/>
+      <c r="G33" s="49"/>
+      <c r="H33" s="49"/>
+      <c r="I33" s="49"/>
+      <c r="J33" s="49"/>
+      <c r="K33" s="49"/>
+      <c r="L33" s="49"/>
+      <c r="N33" s="48"/>
     </row>
     <row r="34" spans="1:14">
-      <c r="A34" s="138">
+      <c r="A34" s="151">
         <v>4</v>
       </c>
-      <c r="B34" s="139"/>
-      <c r="C34" s="162"/>
-      <c r="D34" s="162"/>
-      <c r="E34" s="162"/>
-      <c r="F34" s="162"/>
-      <c r="G34" s="162"/>
-      <c r="H34" s="162"/>
-      <c r="I34" s="162"/>
-      <c r="J34" s="162"/>
-      <c r="K34" s="162"/>
-      <c r="L34" s="162"/>
-      <c r="M34" s="162"/>
-      <c r="N34" s="166"/>
+      <c r="B34" s="152"/>
+      <c r="C34" s="47"/>
+      <c r="D34" s="47"/>
+      <c r="E34" s="47"/>
+      <c r="F34" s="47"/>
+      <c r="G34" s="47"/>
+      <c r="H34" s="47"/>
+      <c r="I34" s="47"/>
+      <c r="J34" s="47"/>
+      <c r="K34" s="47"/>
+      <c r="L34" s="47"/>
+      <c r="M34" s="47"/>
+      <c r="N34" s="51"/>
     </row>
     <row r="35" spans="1:14">
-      <c r="A35" s="149"/>
-      <c r="B35" s="150"/>
-      <c r="N35" s="163"/>
+      <c r="A35" s="153"/>
+      <c r="B35" s="154"/>
+      <c r="N35" s="48"/>
     </row>
     <row r="36" spans="1:14">
-      <c r="A36" s="149"/>
-      <c r="B36" s="150"/>
-      <c r="N36" s="163"/>
+      <c r="A36" s="153"/>
+      <c r="B36" s="154"/>
+      <c r="N36" s="48"/>
     </row>
     <row r="37" spans="1:14">
-      <c r="A37" s="149"/>
-      <c r="B37" s="150"/>
-      <c r="N37" s="163"/>
+      <c r="A37" s="153"/>
+      <c r="B37" s="154"/>
+      <c r="N37" s="48"/>
     </row>
     <row r="38" spans="1:14">
-      <c r="A38" s="149"/>
-      <c r="B38" s="150"/>
-      <c r="N38" s="163"/>
+      <c r="A38" s="153"/>
+      <c r="B38" s="154"/>
+      <c r="N38" s="48"/>
     </row>
     <row r="39" spans="1:14">
-      <c r="A39" s="149"/>
-      <c r="B39" s="150"/>
-      <c r="N39" s="163"/>
+      <c r="A39" s="153"/>
+      <c r="B39" s="154"/>
+      <c r="N39" s="48"/>
     </row>
     <row r="40" spans="1:14">
-      <c r="A40" s="149"/>
-      <c r="B40" s="150"/>
-      <c r="N40" s="163"/>
+      <c r="A40" s="153"/>
+      <c r="B40" s="154"/>
+      <c r="N40" s="48"/>
     </row>
     <row r="41" spans="1:14">
-      <c r="A41" s="149"/>
-      <c r="B41" s="150"/>
-      <c r="N41" s="163"/>
+      <c r="A41" s="153"/>
+      <c r="B41" s="154"/>
+      <c r="N41" s="48"/>
     </row>
     <row r="42" spans="1:14" ht="19.5" thickBot="1">
-      <c r="A42" s="153"/>
-      <c r="B42" s="154"/>
-      <c r="C42" s="164"/>
-      <c r="D42" s="164"/>
-      <c r="E42" s="164"/>
-      <c r="F42" s="164"/>
-      <c r="G42" s="164"/>
-      <c r="H42" s="164"/>
-      <c r="I42" s="164"/>
-      <c r="J42" s="164"/>
-      <c r="K42" s="164"/>
-      <c r="L42" s="164"/>
-      <c r="M42" s="164"/>
-      <c r="N42" s="165"/>
+      <c r="A42" s="155"/>
+      <c r="B42" s="156"/>
+      <c r="C42" s="49"/>
+      <c r="D42" s="49"/>
+      <c r="E42" s="49"/>
+      <c r="F42" s="49"/>
+      <c r="G42" s="49"/>
+      <c r="H42" s="49"/>
+      <c r="I42" s="49"/>
+      <c r="J42" s="49"/>
+      <c r="K42" s="49"/>
+      <c r="L42" s="49"/>
+      <c r="M42" s="49"/>
+      <c r="N42" s="50"/>
     </row>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="A25:B33"/>
-    <mergeCell ref="A34:B42"/>
-    <mergeCell ref="A4:B5"/>
-    <mergeCell ref="C4:N5"/>
-    <mergeCell ref="A6:B6"/>
-    <mergeCell ref="C6:N6"/>
-    <mergeCell ref="A7:B15"/>
-    <mergeCell ref="A16:B24"/>
     <mergeCell ref="A1:B3"/>
     <mergeCell ref="I1:J1"/>
     <mergeCell ref="K1:L1"/>
@@ -9367,6 +10307,14 @@
     <mergeCell ref="I2:J3"/>
     <mergeCell ref="K2:L3"/>
     <mergeCell ref="M2:N3"/>
+    <mergeCell ref="A25:B33"/>
+    <mergeCell ref="A34:B42"/>
+    <mergeCell ref="A4:B5"/>
+    <mergeCell ref="C4:N5"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="C6:N6"/>
+    <mergeCell ref="A7:B15"/>
+    <mergeCell ref="A16:B24"/>
   </mergeCells>
   <phoneticPr fontId="4"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
